--- a/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Company_HTX586.xlsx
+++ b/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Company_HTX586.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_COMPANY" sheetId="1" r:id="R5f3329c4fa794a7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="2" r:id="R8dd6d77de8a244a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_COMPANY" sheetId="1" r:id="R3963a5b682ed413a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="2" r:id="R7523141b2e4541a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48,7 +48,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -83,6 +83,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -267,7 +272,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="146">
+  <x:cellXfs count="151">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -614,6 +619,17 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -625,7 +641,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -636,7 +652,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -647,7 +663,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -658,7 +674,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -669,7 +685,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFC7CE"/>
         </x:patternFill>
       </x:fill>
@@ -680,7 +696,7 @@
         <x:color rgb="FF9C5700"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4B084"/>
         </x:patternFill>
       </x:fill>
@@ -690,7 +706,7 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -765,9 +781,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -886,6 +902,7 @@
     <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="42" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
@@ -934,6 +951,9 @@
       <x:c r="O1" s="15" t="str">
         <x:v>IsActive</x:v>
       </x:c>
+      <x:c r="P1" s="150" t="str">
+        <x:v>ComplaintContact</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="43" t="str">
@@ -981,6 +1001,9 @@
       <x:c r="O2" s="43" t="str">
         <x:v>TRUE</x:v>
       </x:c>
+      <x:c r="P2" s="32" t="str">
+        <x:v>Sở GTVT Cần Thơ: 0939.984.333 - 0907.877.758</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="34"/>
@@ -998,6 +1021,7 @@
       <x:c r="M3" s="46"/>
       <x:c r="N3" s="46"/>
       <x:c r="O3" s="34"/>
+      <x:c r="P3" s="32"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="34"/>
@@ -1015,6 +1039,7 @@
       <x:c r="M4" s="46"/>
       <x:c r="N4" s="46"/>
       <x:c r="O4" s="34"/>
+      <x:c r="P4" s="32"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="34"/>
@@ -1032,6 +1057,7 @@
       <x:c r="M5" s="46"/>
       <x:c r="N5" s="46"/>
       <x:c r="O5" s="34"/>
+      <x:c r="P5" s="32"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="34"/>
@@ -1049,6 +1075,7 @@
       <x:c r="M6" s="46"/>
       <x:c r="N6" s="46"/>
       <x:c r="O6" s="34"/>
+      <x:c r="P6" s="32"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="34"/>
@@ -1066,6 +1093,7 @@
       <x:c r="M7" s="46"/>
       <x:c r="N7" s="46"/>
       <x:c r="O7" s="34"/>
+      <x:c r="P7" s="32"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="34"/>
@@ -1083,6 +1111,7 @@
       <x:c r="M8" s="46"/>
       <x:c r="N8" s="46"/>
       <x:c r="O8" s="34"/>
+      <x:c r="P8" s="32"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="34"/>
@@ -1100,6 +1129,7 @@
       <x:c r="M9" s="46"/>
       <x:c r="N9" s="46"/>
       <x:c r="O9" s="34"/>
+      <x:c r="P9" s="32"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="34"/>
@@ -1117,6 +1147,7 @@
       <x:c r="M10" s="46"/>
       <x:c r="N10" s="46"/>
       <x:c r="O10" s="34"/>
+      <x:c r="P10" s="32"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="34"/>
@@ -1134,6 +1165,7 @@
       <x:c r="M11" s="46"/>
       <x:c r="N11" s="46"/>
       <x:c r="O11" s="34"/>
+      <x:c r="P11" s="32"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="34"/>
@@ -1151,6 +1183,7 @@
       <x:c r="M12" s="46"/>
       <x:c r="N12" s="46"/>
       <x:c r="O12" s="34"/>
+      <x:c r="P12" s="32"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="34"/>
@@ -1168,6 +1201,7 @@
       <x:c r="M13" s="46"/>
       <x:c r="N13" s="46"/>
       <x:c r="O13" s="34"/>
+      <x:c r="P13" s="32"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="34"/>
@@ -1185,6 +1219,7 @@
       <x:c r="M14" s="46"/>
       <x:c r="N14" s="46"/>
       <x:c r="O14" s="34"/>
+      <x:c r="P14" s="32"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="34"/>
@@ -1202,6 +1237,7 @@
       <x:c r="M15" s="46"/>
       <x:c r="N15" s="46"/>
       <x:c r="O15" s="34"/>
+      <x:c r="P15" s="32"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="34"/>
@@ -1219,6 +1255,7 @@
       <x:c r="M16" s="46"/>
       <x:c r="N16" s="46"/>
       <x:c r="O16" s="34"/>
+      <x:c r="P16" s="32"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="34"/>
@@ -1236,6 +1273,7 @@
       <x:c r="M17" s="46"/>
       <x:c r="N17" s="46"/>
       <x:c r="O17" s="34"/>
+      <x:c r="P17" s="32"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="34"/>
@@ -1253,6 +1291,7 @@
       <x:c r="M18" s="46"/>
       <x:c r="N18" s="46"/>
       <x:c r="O18" s="34"/>
+      <x:c r="P18" s="32"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="34"/>
@@ -1270,6 +1309,7 @@
       <x:c r="M19" s="46"/>
       <x:c r="N19" s="46"/>
       <x:c r="O19" s="34"/>
+      <x:c r="P19" s="32"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="34"/>
@@ -1287,6 +1327,7 @@
       <x:c r="M20" s="46"/>
       <x:c r="N20" s="46"/>
       <x:c r="O20" s="34"/>
+      <x:c r="P20" s="32"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="34"/>
@@ -1304,6 +1345,7 @@
       <x:c r="M21" s="46"/>
       <x:c r="N21" s="46"/>
       <x:c r="O21" s="34"/>
+      <x:c r="P21" s="32"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="34"/>
@@ -1321,6 +1363,7 @@
       <x:c r="M22" s="46"/>
       <x:c r="N22" s="46"/>
       <x:c r="O22" s="34"/>
+      <x:c r="P22" s="32"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="34"/>
@@ -1338,6 +1381,7 @@
       <x:c r="M23" s="46"/>
       <x:c r="N23" s="46"/>
       <x:c r="O23" s="34"/>
+      <x:c r="P23" s="32"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="34"/>
@@ -1355,6 +1399,7 @@
       <x:c r="M24" s="46"/>
       <x:c r="N24" s="46"/>
       <x:c r="O24" s="34"/>
+      <x:c r="P24" s="32"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="34"/>
@@ -1372,6 +1417,7 @@
       <x:c r="M25" s="46"/>
       <x:c r="N25" s="46"/>
       <x:c r="O25" s="34"/>
+      <x:c r="P25" s="32"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="34"/>
@@ -1389,6 +1435,7 @@
       <x:c r="M26" s="46"/>
       <x:c r="N26" s="46"/>
       <x:c r="O26" s="34"/>
+      <x:c r="P26" s="32"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="34"/>
@@ -1406,6 +1453,7 @@
       <x:c r="M27" s="46"/>
       <x:c r="N27" s="46"/>
       <x:c r="O27" s="34"/>
+      <x:c r="P27" s="32"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="34"/>
@@ -1423,6 +1471,7 @@
       <x:c r="M28" s="46"/>
       <x:c r="N28" s="46"/>
       <x:c r="O28" s="34"/>
+      <x:c r="P28" s="32"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="34"/>
@@ -1440,6 +1489,7 @@
       <x:c r="M29" s="46"/>
       <x:c r="N29" s="46"/>
       <x:c r="O29" s="34"/>
+      <x:c r="P29" s="32"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="34"/>
@@ -1457,6 +1507,7 @@
       <x:c r="M30" s="46"/>
       <x:c r="N30" s="46"/>
       <x:c r="O30" s="34"/>
+      <x:c r="P30" s="32"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="34"/>
@@ -1474,6 +1525,7 @@
       <x:c r="M31" s="46"/>
       <x:c r="N31" s="46"/>
       <x:c r="O31" s="34"/>
+      <x:c r="P31" s="32"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="34"/>
@@ -1491,6 +1543,7 @@
       <x:c r="M32" s="46"/>
       <x:c r="N32" s="46"/>
       <x:c r="O32" s="34"/>
+      <x:c r="P32" s="32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="34"/>
@@ -1508,6 +1561,7 @@
       <x:c r="M33" s="46"/>
       <x:c r="N33" s="46"/>
       <x:c r="O33" s="34"/>
+      <x:c r="P33" s="32"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="34"/>
@@ -1525,6 +1579,7 @@
       <x:c r="M34" s="46"/>
       <x:c r="N34" s="46"/>
       <x:c r="O34" s="34"/>
+      <x:c r="P34" s="32"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="34"/>
@@ -1542,6 +1597,7 @@
       <x:c r="M35" s="46"/>
       <x:c r="N35" s="46"/>
       <x:c r="O35" s="34"/>
+      <x:c r="P35" s="32"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="34"/>
@@ -1559,6 +1615,7 @@
       <x:c r="M36" s="46"/>
       <x:c r="N36" s="46"/>
       <x:c r="O36" s="34"/>
+      <x:c r="P36" s="32"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="34"/>
@@ -1576,6 +1633,7 @@
       <x:c r="M37" s="46"/>
       <x:c r="N37" s="46"/>
       <x:c r="O37" s="34"/>
+      <x:c r="P37" s="32"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="34"/>
@@ -1593,6 +1651,7 @@
       <x:c r="M38" s="46"/>
       <x:c r="N38" s="46"/>
       <x:c r="O38" s="34"/>
+      <x:c r="P38" s="32"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="34"/>
@@ -1610,6 +1669,7 @@
       <x:c r="M39" s="46"/>
       <x:c r="N39" s="46"/>
       <x:c r="O39" s="34"/>
+      <x:c r="P39" s="32"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="34"/>
@@ -1627,6 +1687,7 @@
       <x:c r="M40" s="46"/>
       <x:c r="N40" s="46"/>
       <x:c r="O40" s="34"/>
+      <x:c r="P40" s="32"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="34"/>
@@ -1644,6 +1705,7 @@
       <x:c r="M41" s="46"/>
       <x:c r="N41" s="46"/>
       <x:c r="O41" s="34"/>
+      <x:c r="P41" s="32"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="34"/>
@@ -1661,6 +1723,7 @@
       <x:c r="M42" s="46"/>
       <x:c r="N42" s="46"/>
       <x:c r="O42" s="34"/>
+      <x:c r="P42" s="32"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="34"/>
@@ -1678,6 +1741,7 @@
       <x:c r="M43" s="46"/>
       <x:c r="N43" s="46"/>
       <x:c r="O43" s="34"/>
+      <x:c r="P43" s="32"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="34"/>
@@ -1695,6 +1759,7 @@
       <x:c r="M44" s="46"/>
       <x:c r="N44" s="46"/>
       <x:c r="O44" s="34"/>
+      <x:c r="P44" s="32"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="34"/>
@@ -1712,6 +1777,7 @@
       <x:c r="M45" s="46"/>
       <x:c r="N45" s="46"/>
       <x:c r="O45" s="34"/>
+      <x:c r="P45" s="32"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="34"/>
@@ -1729,6 +1795,7 @@
       <x:c r="M46" s="46"/>
       <x:c r="N46" s="46"/>
       <x:c r="O46" s="34"/>
+      <x:c r="P46" s="32"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="34"/>
@@ -1746,6 +1813,7 @@
       <x:c r="M47" s="46"/>
       <x:c r="N47" s="46"/>
       <x:c r="O47" s="34"/>
+      <x:c r="P47" s="32"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="34"/>
@@ -1763,6 +1831,7 @@
       <x:c r="M48" s="46"/>
       <x:c r="N48" s="46"/>
       <x:c r="O48" s="34"/>
+      <x:c r="P48" s="32"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="34"/>
@@ -1780,6 +1849,7 @@
       <x:c r="M49" s="46"/>
       <x:c r="N49" s="46"/>
       <x:c r="O49" s="34"/>
+      <x:c r="P49" s="32"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="34"/>
@@ -1797,6 +1867,7 @@
       <x:c r="M50" s="46"/>
       <x:c r="N50" s="46"/>
       <x:c r="O50" s="34"/>
+      <x:c r="P50" s="32"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="34"/>
@@ -1814,6 +1885,7 @@
       <x:c r="M51" s="46"/>
       <x:c r="N51" s="46"/>
       <x:c r="O51" s="34"/>
+      <x:c r="P51" s="32"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="34"/>
@@ -1831,6 +1903,7 @@
       <x:c r="M52" s="46"/>
       <x:c r="N52" s="46"/>
       <x:c r="O52" s="34"/>
+      <x:c r="P52" s="32"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="34"/>
@@ -1848,6 +1921,7 @@
       <x:c r="M53" s="46"/>
       <x:c r="N53" s="46"/>
       <x:c r="O53" s="34"/>
+      <x:c r="P53" s="32"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="34"/>
@@ -1865,6 +1939,7 @@
       <x:c r="M54" s="46"/>
       <x:c r="N54" s="46"/>
       <x:c r="O54" s="34"/>
+      <x:c r="P54" s="32"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="34"/>
@@ -1882,6 +1957,7 @@
       <x:c r="M55" s="46"/>
       <x:c r="N55" s="46"/>
       <x:c r="O55" s="34"/>
+      <x:c r="P55" s="32"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="34"/>
@@ -1899,6 +1975,7 @@
       <x:c r="M56" s="46"/>
       <x:c r="N56" s="46"/>
       <x:c r="O56" s="34"/>
+      <x:c r="P56" s="32"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="34"/>
@@ -1916,6 +1993,7 @@
       <x:c r="M57" s="46"/>
       <x:c r="N57" s="46"/>
       <x:c r="O57" s="34"/>
+      <x:c r="P57" s="32"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="34"/>
@@ -1933,6 +2011,7 @@
       <x:c r="M58" s="46"/>
       <x:c r="N58" s="46"/>
       <x:c r="O58" s="34"/>
+      <x:c r="P58" s="32"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="34"/>
@@ -1950,6 +2029,7 @@
       <x:c r="M59" s="46"/>
       <x:c r="N59" s="46"/>
       <x:c r="O59" s="34"/>
+      <x:c r="P59" s="32"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="34"/>
@@ -1967,6 +2047,7 @@
       <x:c r="M60" s="46"/>
       <x:c r="N60" s="46"/>
       <x:c r="O60" s="34"/>
+      <x:c r="P60" s="32"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="34"/>
@@ -1984,6 +2065,7 @@
       <x:c r="M61" s="46"/>
       <x:c r="N61" s="46"/>
       <x:c r="O61" s="34"/>
+      <x:c r="P61" s="32"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="34"/>
@@ -2001,6 +2083,7 @@
       <x:c r="M62" s="46"/>
       <x:c r="N62" s="46"/>
       <x:c r="O62" s="34"/>
+      <x:c r="P62" s="32"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="34"/>
@@ -2018,6 +2101,7 @@
       <x:c r="M63" s="46"/>
       <x:c r="N63" s="46"/>
       <x:c r="O63" s="34"/>
+      <x:c r="P63" s="32"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="34"/>
@@ -2035,6 +2119,7 @@
       <x:c r="M64" s="46"/>
       <x:c r="N64" s="46"/>
       <x:c r="O64" s="34"/>
+      <x:c r="P64" s="32"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="34"/>
@@ -2052,6 +2137,7 @@
       <x:c r="M65" s="46"/>
       <x:c r="N65" s="46"/>
       <x:c r="O65" s="34"/>
+      <x:c r="P65" s="32"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="34"/>
@@ -2069,6 +2155,7 @@
       <x:c r="M66" s="46"/>
       <x:c r="N66" s="46"/>
       <x:c r="O66" s="34"/>
+      <x:c r="P66" s="32"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="34"/>
@@ -2086,6 +2173,7 @@
       <x:c r="M67" s="46"/>
       <x:c r="N67" s="46"/>
       <x:c r="O67" s="34"/>
+      <x:c r="P67" s="32"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="34"/>
@@ -2103,6 +2191,7 @@
       <x:c r="M68" s="46"/>
       <x:c r="N68" s="46"/>
       <x:c r="O68" s="34"/>
+      <x:c r="P68" s="32"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="34"/>
@@ -2120,6 +2209,7 @@
       <x:c r="M69" s="46"/>
       <x:c r="N69" s="46"/>
       <x:c r="O69" s="34"/>
+      <x:c r="P69" s="32"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="34"/>
@@ -2137,6 +2227,7 @@
       <x:c r="M70" s="46"/>
       <x:c r="N70" s="46"/>
       <x:c r="O70" s="34"/>
+      <x:c r="P70" s="32"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="34"/>
@@ -2154,6 +2245,7 @@
       <x:c r="M71" s="46"/>
       <x:c r="N71" s="46"/>
       <x:c r="O71" s="34"/>
+      <x:c r="P71" s="32"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="34"/>
@@ -2171,6 +2263,7 @@
       <x:c r="M72" s="46"/>
       <x:c r="N72" s="46"/>
       <x:c r="O72" s="34"/>
+      <x:c r="P72" s="32"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="34"/>
@@ -2188,6 +2281,7 @@
       <x:c r="M73" s="46"/>
       <x:c r="N73" s="46"/>
       <x:c r="O73" s="34"/>
+      <x:c r="P73" s="32"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="34"/>
@@ -2205,6 +2299,7 @@
       <x:c r="M74" s="46"/>
       <x:c r="N74" s="46"/>
       <x:c r="O74" s="34"/>
+      <x:c r="P74" s="32"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="34"/>
@@ -2222,6 +2317,7 @@
       <x:c r="M75" s="46"/>
       <x:c r="N75" s="46"/>
       <x:c r="O75" s="34"/>
+      <x:c r="P75" s="32"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="34"/>
@@ -2239,6 +2335,7 @@
       <x:c r="M76" s="46"/>
       <x:c r="N76" s="46"/>
       <x:c r="O76" s="34"/>
+      <x:c r="P76" s="32"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="34"/>
@@ -2256,6 +2353,7 @@
       <x:c r="M77" s="46"/>
       <x:c r="N77" s="46"/>
       <x:c r="O77" s="34"/>
+      <x:c r="P77" s="32"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="34"/>
@@ -2273,6 +2371,7 @@
       <x:c r="M78" s="46"/>
       <x:c r="N78" s="46"/>
       <x:c r="O78" s="34"/>
+      <x:c r="P78" s="32"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="34"/>
@@ -2290,6 +2389,7 @@
       <x:c r="M79" s="46"/>
       <x:c r="N79" s="46"/>
       <x:c r="O79" s="34"/>
+      <x:c r="P79" s="32"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="34"/>
@@ -2307,6 +2407,7 @@
       <x:c r="M80" s="46"/>
       <x:c r="N80" s="46"/>
       <x:c r="O80" s="34"/>
+      <x:c r="P80" s="32"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="34"/>
@@ -2324,6 +2425,7 @@
       <x:c r="M81" s="46"/>
       <x:c r="N81" s="46"/>
       <x:c r="O81" s="34"/>
+      <x:c r="P81" s="32"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="34"/>
@@ -2341,6 +2443,7 @@
       <x:c r="M82" s="46"/>
       <x:c r="N82" s="46"/>
       <x:c r="O82" s="34"/>
+      <x:c r="P82" s="32"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="34"/>
@@ -2358,6 +2461,7 @@
       <x:c r="M83" s="46"/>
       <x:c r="N83" s="46"/>
       <x:c r="O83" s="34"/>
+      <x:c r="P83" s="32"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="34"/>
@@ -2375,6 +2479,7 @@
       <x:c r="M84" s="46"/>
       <x:c r="N84" s="46"/>
       <x:c r="O84" s="34"/>
+      <x:c r="P84" s="32"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="34"/>
@@ -2392,6 +2497,7 @@
       <x:c r="M85" s="46"/>
       <x:c r="N85" s="46"/>
       <x:c r="O85" s="34"/>
+      <x:c r="P85" s="32"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="34"/>
@@ -2409,6 +2515,7 @@
       <x:c r="M86" s="46"/>
       <x:c r="N86" s="46"/>
       <x:c r="O86" s="34"/>
+      <x:c r="P86" s="32"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="34"/>
@@ -2426,6 +2533,7 @@
       <x:c r="M87" s="46"/>
       <x:c r="N87" s="46"/>
       <x:c r="O87" s="34"/>
+      <x:c r="P87" s="32"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="34"/>
@@ -2443,6 +2551,7 @@
       <x:c r="M88" s="46"/>
       <x:c r="N88" s="46"/>
       <x:c r="O88" s="34"/>
+      <x:c r="P88" s="32"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="34"/>
@@ -2460,6 +2569,7 @@
       <x:c r="M89" s="46"/>
       <x:c r="N89" s="46"/>
       <x:c r="O89" s="34"/>
+      <x:c r="P89" s="32"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="34"/>
@@ -2477,6 +2587,7 @@
       <x:c r="M90" s="46"/>
       <x:c r="N90" s="46"/>
       <x:c r="O90" s="34"/>
+      <x:c r="P90" s="32"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="34"/>
@@ -2494,6 +2605,7 @@
       <x:c r="M91" s="46"/>
       <x:c r="N91" s="46"/>
       <x:c r="O91" s="34"/>
+      <x:c r="P91" s="32"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="34"/>
@@ -2511,6 +2623,7 @@
       <x:c r="M92" s="46"/>
       <x:c r="N92" s="46"/>
       <x:c r="O92" s="34"/>
+      <x:c r="P92" s="32"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="34"/>
@@ -2528,6 +2641,7 @@
       <x:c r="M93" s="46"/>
       <x:c r="N93" s="46"/>
       <x:c r="O93" s="34"/>
+      <x:c r="P93" s="32"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="34"/>
@@ -2545,6 +2659,7 @@
       <x:c r="M94" s="46"/>
       <x:c r="N94" s="46"/>
       <x:c r="O94" s="34"/>
+      <x:c r="P94" s="32"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="34"/>
@@ -2562,6 +2677,7 @@
       <x:c r="M95" s="46"/>
       <x:c r="N95" s="46"/>
       <x:c r="O95" s="34"/>
+      <x:c r="P95" s="32"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="34"/>
@@ -2579,6 +2695,7 @@
       <x:c r="M96" s="46"/>
       <x:c r="N96" s="46"/>
       <x:c r="O96" s="34"/>
+      <x:c r="P96" s="32"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="34"/>
@@ -2596,6 +2713,7 @@
       <x:c r="M97" s="46"/>
       <x:c r="N97" s="46"/>
       <x:c r="O97" s="34"/>
+      <x:c r="P97" s="32"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="34"/>
@@ -2613,6 +2731,7 @@
       <x:c r="M98" s="46"/>
       <x:c r="N98" s="46"/>
       <x:c r="O98" s="34"/>
+      <x:c r="P98" s="32"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="34"/>
@@ -2630,6 +2749,7 @@
       <x:c r="M99" s="46"/>
       <x:c r="N99" s="46"/>
       <x:c r="O99" s="34"/>
+      <x:c r="P99" s="32"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="34"/>
@@ -2647,6 +2767,7 @@
       <x:c r="M100" s="46"/>
       <x:c r="N100" s="46"/>
       <x:c r="O100" s="34"/>
+      <x:c r="P100" s="32"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="34"/>
@@ -2664,6 +2785,7 @@
       <x:c r="M101" s="46"/>
       <x:c r="N101" s="46"/>
       <x:c r="O101" s="34"/>
+      <x:c r="P101" s="32"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="34"/>
@@ -2681,6 +2803,7 @@
       <x:c r="M102" s="46"/>
       <x:c r="N102" s="46"/>
       <x:c r="O102" s="34"/>
+      <x:c r="P102" s="32"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="34"/>
@@ -2698,6 +2821,7 @@
       <x:c r="M103" s="46"/>
       <x:c r="N103" s="46"/>
       <x:c r="O103" s="34"/>
+      <x:c r="P103" s="32"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="34"/>
@@ -2715,6 +2839,7 @@
       <x:c r="M104" s="46"/>
       <x:c r="N104" s="46"/>
       <x:c r="O104" s="34"/>
+      <x:c r="P104" s="32"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="34"/>
@@ -2732,6 +2857,7 @@
       <x:c r="M105" s="46"/>
       <x:c r="N105" s="46"/>
       <x:c r="O105" s="34"/>
+      <x:c r="P105" s="32"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="34"/>
@@ -2749,6 +2875,7 @@
       <x:c r="M106" s="46"/>
       <x:c r="N106" s="46"/>
       <x:c r="O106" s="34"/>
+      <x:c r="P106" s="32"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="34"/>
@@ -2766,6 +2893,7 @@
       <x:c r="M107" s="46"/>
       <x:c r="N107" s="46"/>
       <x:c r="O107" s="34"/>
+      <x:c r="P107" s="32"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="34"/>
@@ -2783,6 +2911,7 @@
       <x:c r="M108" s="46"/>
       <x:c r="N108" s="46"/>
       <x:c r="O108" s="34"/>
+      <x:c r="P108" s="32"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="34"/>
@@ -2800,6 +2929,7 @@
       <x:c r="M109" s="46"/>
       <x:c r="N109" s="46"/>
       <x:c r="O109" s="34"/>
+      <x:c r="P109" s="32"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="34"/>
@@ -2817,6 +2947,7 @@
       <x:c r="M110" s="46"/>
       <x:c r="N110" s="46"/>
       <x:c r="O110" s="34"/>
+      <x:c r="P110" s="32"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="34"/>
@@ -2834,6 +2965,7 @@
       <x:c r="M111" s="46"/>
       <x:c r="N111" s="46"/>
       <x:c r="O111" s="34"/>
+      <x:c r="P111" s="32"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="34"/>
@@ -2851,6 +2983,7 @@
       <x:c r="M112" s="46"/>
       <x:c r="N112" s="46"/>
       <x:c r="O112" s="34"/>
+      <x:c r="P112" s="32"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="34"/>
@@ -2868,6 +3001,7 @@
       <x:c r="M113" s="46"/>
       <x:c r="N113" s="46"/>
       <x:c r="O113" s="34"/>
+      <x:c r="P113" s="32"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="34"/>
@@ -2885,6 +3019,7 @@
       <x:c r="M114" s="46"/>
       <x:c r="N114" s="46"/>
       <x:c r="O114" s="34"/>
+      <x:c r="P114" s="32"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="34"/>
@@ -2902,6 +3037,7 @@
       <x:c r="M115" s="46"/>
       <x:c r="N115" s="46"/>
       <x:c r="O115" s="34"/>
+      <x:c r="P115" s="32"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="34"/>
@@ -2919,6 +3055,7 @@
       <x:c r="M116" s="46"/>
       <x:c r="N116" s="46"/>
       <x:c r="O116" s="34"/>
+      <x:c r="P116" s="32"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="34"/>
@@ -2936,6 +3073,7 @@
       <x:c r="M117" s="46"/>
       <x:c r="N117" s="46"/>
       <x:c r="O117" s="34"/>
+      <x:c r="P117" s="32"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="34"/>
@@ -2953,6 +3091,7 @@
       <x:c r="M118" s="46"/>
       <x:c r="N118" s="46"/>
       <x:c r="O118" s="34"/>
+      <x:c r="P118" s="32"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="34"/>
@@ -2970,6 +3109,7 @@
       <x:c r="M119" s="46"/>
       <x:c r="N119" s="46"/>
       <x:c r="O119" s="34"/>
+      <x:c r="P119" s="32"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="34"/>
@@ -2987,6 +3127,7 @@
       <x:c r="M120" s="46"/>
       <x:c r="N120" s="46"/>
       <x:c r="O120" s="34"/>
+      <x:c r="P120" s="32"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="34"/>
@@ -3004,6 +3145,7 @@
       <x:c r="M121" s="46"/>
       <x:c r="N121" s="46"/>
       <x:c r="O121" s="34"/>
+      <x:c r="P121" s="32"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="34"/>
@@ -3021,6 +3163,7 @@
       <x:c r="M122" s="46"/>
       <x:c r="N122" s="46"/>
       <x:c r="O122" s="34"/>
+      <x:c r="P122" s="32"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="34"/>
@@ -3038,6 +3181,7 @@
       <x:c r="M123" s="46"/>
       <x:c r="N123" s="46"/>
       <x:c r="O123" s="34"/>
+      <x:c r="P123" s="32"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="34"/>
@@ -3055,6 +3199,7 @@
       <x:c r="M124" s="46"/>
       <x:c r="N124" s="46"/>
       <x:c r="O124" s="34"/>
+      <x:c r="P124" s="32"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="34"/>
@@ -3072,6 +3217,7 @@
       <x:c r="M125" s="46"/>
       <x:c r="N125" s="46"/>
       <x:c r="O125" s="34"/>
+      <x:c r="P125" s="32"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="34"/>
@@ -3089,6 +3235,7 @@
       <x:c r="M126" s="46"/>
       <x:c r="N126" s="46"/>
       <x:c r="O126" s="34"/>
+      <x:c r="P126" s="32"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="34"/>
@@ -3106,6 +3253,7 @@
       <x:c r="M127" s="46"/>
       <x:c r="N127" s="46"/>
       <x:c r="O127" s="34"/>
+      <x:c r="P127" s="32"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="34"/>
@@ -3123,6 +3271,7 @@
       <x:c r="M128" s="46"/>
       <x:c r="N128" s="46"/>
       <x:c r="O128" s="34"/>
+      <x:c r="P128" s="32"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="34"/>
@@ -3140,6 +3289,7 @@
       <x:c r="M129" s="46"/>
       <x:c r="N129" s="46"/>
       <x:c r="O129" s="34"/>
+      <x:c r="P129" s="32"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="34"/>
@@ -3157,6 +3307,7 @@
       <x:c r="M130" s="46"/>
       <x:c r="N130" s="46"/>
       <x:c r="O130" s="34"/>
+      <x:c r="P130" s="32"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="34"/>
@@ -3174,6 +3325,7 @@
       <x:c r="M131" s="46"/>
       <x:c r="N131" s="46"/>
       <x:c r="O131" s="34"/>
+      <x:c r="P131" s="32"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="34"/>
@@ -3191,6 +3343,7 @@
       <x:c r="M132" s="46"/>
       <x:c r="N132" s="46"/>
       <x:c r="O132" s="34"/>
+      <x:c r="P132" s="32"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="34"/>
@@ -3208,6 +3361,7 @@
       <x:c r="M133" s="46"/>
       <x:c r="N133" s="46"/>
       <x:c r="O133" s="34"/>
+      <x:c r="P133" s="32"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="34"/>
@@ -3225,6 +3379,7 @@
       <x:c r="M134" s="46"/>
       <x:c r="N134" s="46"/>
       <x:c r="O134" s="34"/>
+      <x:c r="P134" s="32"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="34"/>
@@ -3242,6 +3397,7 @@
       <x:c r="M135" s="46"/>
       <x:c r="N135" s="46"/>
       <x:c r="O135" s="34"/>
+      <x:c r="P135" s="32"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="34"/>
@@ -3259,6 +3415,7 @@
       <x:c r="M136" s="46"/>
       <x:c r="N136" s="46"/>
       <x:c r="O136" s="34"/>
+      <x:c r="P136" s="32"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="34"/>
@@ -3276,6 +3433,7 @@
       <x:c r="M137" s="46"/>
       <x:c r="N137" s="46"/>
       <x:c r="O137" s="34"/>
+      <x:c r="P137" s="32"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="34"/>
@@ -3293,6 +3451,7 @@
       <x:c r="M138" s="46"/>
       <x:c r="N138" s="46"/>
       <x:c r="O138" s="34"/>
+      <x:c r="P138" s="32"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="34"/>
@@ -3310,6 +3469,7 @@
       <x:c r="M139" s="46"/>
       <x:c r="N139" s="46"/>
       <x:c r="O139" s="34"/>
+      <x:c r="P139" s="32"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="34"/>
@@ -3327,6 +3487,7 @@
       <x:c r="M140" s="46"/>
       <x:c r="N140" s="46"/>
       <x:c r="O140" s="34"/>
+      <x:c r="P140" s="32"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="34"/>
@@ -3344,6 +3505,7 @@
       <x:c r="M141" s="46"/>
       <x:c r="N141" s="46"/>
       <x:c r="O141" s="34"/>
+      <x:c r="P141" s="32"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="34"/>
@@ -3361,6 +3523,7 @@
       <x:c r="M142" s="46"/>
       <x:c r="N142" s="46"/>
       <x:c r="O142" s="34"/>
+      <x:c r="P142" s="32"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="34"/>
@@ -3378,6 +3541,7 @@
       <x:c r="M143" s="46"/>
       <x:c r="N143" s="46"/>
       <x:c r="O143" s="34"/>
+      <x:c r="P143" s="32"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="34"/>
@@ -3395,6 +3559,7 @@
       <x:c r="M144" s="46"/>
       <x:c r="N144" s="46"/>
       <x:c r="O144" s="34"/>
+      <x:c r="P144" s="32"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="34"/>
@@ -3412,6 +3577,7 @@
       <x:c r="M145" s="46"/>
       <x:c r="N145" s="46"/>
       <x:c r="O145" s="34"/>
+      <x:c r="P145" s="32"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="34"/>
@@ -3429,6 +3595,7 @@
       <x:c r="M146" s="46"/>
       <x:c r="N146" s="46"/>
       <x:c r="O146" s="34"/>
+      <x:c r="P146" s="32"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="34"/>
@@ -3446,6 +3613,7 @@
       <x:c r="M147" s="46"/>
       <x:c r="N147" s="46"/>
       <x:c r="O147" s="34"/>
+      <x:c r="P147" s="32"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="34"/>
@@ -3463,6 +3631,7 @@
       <x:c r="M148" s="46"/>
       <x:c r="N148" s="46"/>
       <x:c r="O148" s="34"/>
+      <x:c r="P148" s="32"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="34"/>
@@ -3480,6 +3649,7 @@
       <x:c r="M149" s="46"/>
       <x:c r="N149" s="46"/>
       <x:c r="O149" s="34"/>
+      <x:c r="P149" s="32"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="34"/>
@@ -3497,6 +3667,7 @@
       <x:c r="M150" s="46"/>
       <x:c r="N150" s="46"/>
       <x:c r="O150" s="34"/>
+      <x:c r="P150" s="32"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="34"/>
@@ -3514,6 +3685,7 @@
       <x:c r="M151" s="46"/>
       <x:c r="N151" s="46"/>
       <x:c r="O151" s="34"/>
+      <x:c r="P151" s="32"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="34"/>
@@ -3531,6 +3703,7 @@
       <x:c r="M152" s="46"/>
       <x:c r="N152" s="46"/>
       <x:c r="O152" s="34"/>
+      <x:c r="P152" s="32"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="34"/>
@@ -3548,6 +3721,7 @@
       <x:c r="M153" s="46"/>
       <x:c r="N153" s="46"/>
       <x:c r="O153" s="34"/>
+      <x:c r="P153" s="32"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="34"/>
@@ -3565,6 +3739,7 @@
       <x:c r="M154" s="46"/>
       <x:c r="N154" s="46"/>
       <x:c r="O154" s="34"/>
+      <x:c r="P154" s="32"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="34"/>
@@ -3582,6 +3757,7 @@
       <x:c r="M155" s="46"/>
       <x:c r="N155" s="46"/>
       <x:c r="O155" s="34"/>
+      <x:c r="P155" s="32"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="34"/>
@@ -3599,6 +3775,7 @@
       <x:c r="M156" s="46"/>
       <x:c r="N156" s="46"/>
       <x:c r="O156" s="34"/>
+      <x:c r="P156" s="32"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="34"/>
@@ -3616,6 +3793,7 @@
       <x:c r="M157" s="46"/>
       <x:c r="N157" s="46"/>
       <x:c r="O157" s="34"/>
+      <x:c r="P157" s="32"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="34"/>
@@ -3633,6 +3811,7 @@
       <x:c r="M158" s="46"/>
       <x:c r="N158" s="46"/>
       <x:c r="O158" s="34"/>
+      <x:c r="P158" s="32"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="34"/>
@@ -3650,6 +3829,7 @@
       <x:c r="M159" s="46"/>
       <x:c r="N159" s="46"/>
       <x:c r="O159" s="34"/>
+      <x:c r="P159" s="32"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="34"/>
@@ -3667,6 +3847,7 @@
       <x:c r="M160" s="46"/>
       <x:c r="N160" s="46"/>
       <x:c r="O160" s="34"/>
+      <x:c r="P160" s="32"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="34"/>
@@ -3684,6 +3865,7 @@
       <x:c r="M161" s="46"/>
       <x:c r="N161" s="46"/>
       <x:c r="O161" s="34"/>
+      <x:c r="P161" s="32"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="34"/>
@@ -3701,6 +3883,7 @@
       <x:c r="M162" s="46"/>
       <x:c r="N162" s="46"/>
       <x:c r="O162" s="34"/>
+      <x:c r="P162" s="32"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="34"/>
@@ -3718,6 +3901,7 @@
       <x:c r="M163" s="46"/>
       <x:c r="N163" s="46"/>
       <x:c r="O163" s="34"/>
+      <x:c r="P163" s="32"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="34"/>
@@ -3735,6 +3919,7 @@
       <x:c r="M164" s="46"/>
       <x:c r="N164" s="46"/>
       <x:c r="O164" s="34"/>
+      <x:c r="P164" s="32"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="34"/>
@@ -3752,6 +3937,7 @@
       <x:c r="M165" s="46"/>
       <x:c r="N165" s="46"/>
       <x:c r="O165" s="34"/>
+      <x:c r="P165" s="32"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="34"/>
@@ -3769,6 +3955,7 @@
       <x:c r="M166" s="46"/>
       <x:c r="N166" s="46"/>
       <x:c r="O166" s="34"/>
+      <x:c r="P166" s="32"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="34"/>
@@ -3786,6 +3973,7 @@
       <x:c r="M167" s="46"/>
       <x:c r="N167" s="46"/>
       <x:c r="O167" s="34"/>
+      <x:c r="P167" s="32"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="34"/>
@@ -3803,6 +3991,7 @@
       <x:c r="M168" s="46"/>
       <x:c r="N168" s="46"/>
       <x:c r="O168" s="34"/>
+      <x:c r="P168" s="32"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="34"/>
@@ -3820,6 +4009,7 @@
       <x:c r="M169" s="46"/>
       <x:c r="N169" s="46"/>
       <x:c r="O169" s="34"/>
+      <x:c r="P169" s="32"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="34"/>
@@ -3837,6 +4027,7 @@
       <x:c r="M170" s="46"/>
       <x:c r="N170" s="46"/>
       <x:c r="O170" s="34"/>
+      <x:c r="P170" s="32"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="34"/>
@@ -3854,6 +4045,7 @@
       <x:c r="M171" s="46"/>
       <x:c r="N171" s="46"/>
       <x:c r="O171" s="34"/>
+      <x:c r="P171" s="32"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="34"/>
@@ -3871,6 +4063,7 @@
       <x:c r="M172" s="46"/>
       <x:c r="N172" s="46"/>
       <x:c r="O172" s="34"/>
+      <x:c r="P172" s="32"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="34"/>
@@ -3888,6 +4081,7 @@
       <x:c r="M173" s="46"/>
       <x:c r="N173" s="46"/>
       <x:c r="O173" s="34"/>
+      <x:c r="P173" s="32"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="34"/>
@@ -3905,6 +4099,7 @@
       <x:c r="M174" s="46"/>
       <x:c r="N174" s="46"/>
       <x:c r="O174" s="34"/>
+      <x:c r="P174" s="32"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="34"/>
@@ -3922,6 +4117,7 @@
       <x:c r="M175" s="46"/>
       <x:c r="N175" s="46"/>
       <x:c r="O175" s="34"/>
+      <x:c r="P175" s="32"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="34"/>
@@ -3939,6 +4135,7 @@
       <x:c r="M176" s="46"/>
       <x:c r="N176" s="46"/>
       <x:c r="O176" s="34"/>
+      <x:c r="P176" s="32"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="34"/>
@@ -3956,6 +4153,7 @@
       <x:c r="M177" s="46"/>
       <x:c r="N177" s="46"/>
       <x:c r="O177" s="34"/>
+      <x:c r="P177" s="32"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="34"/>
@@ -3973,6 +4171,7 @@
       <x:c r="M178" s="46"/>
       <x:c r="N178" s="46"/>
       <x:c r="O178" s="34"/>
+      <x:c r="P178" s="32"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="34"/>
@@ -3990,6 +4189,7 @@
       <x:c r="M179" s="46"/>
       <x:c r="N179" s="46"/>
       <x:c r="O179" s="34"/>
+      <x:c r="P179" s="32"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="34"/>
@@ -4007,6 +4207,7 @@
       <x:c r="M180" s="46"/>
       <x:c r="N180" s="46"/>
       <x:c r="O180" s="34"/>
+      <x:c r="P180" s="32"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="34"/>
@@ -4024,6 +4225,7 @@
       <x:c r="M181" s="46"/>
       <x:c r="N181" s="46"/>
       <x:c r="O181" s="34"/>
+      <x:c r="P181" s="32"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="34"/>
@@ -4041,6 +4243,7 @@
       <x:c r="M182" s="46"/>
       <x:c r="N182" s="46"/>
       <x:c r="O182" s="34"/>
+      <x:c r="P182" s="32"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="34"/>
@@ -4058,6 +4261,7 @@
       <x:c r="M183" s="46"/>
       <x:c r="N183" s="46"/>
       <x:c r="O183" s="34"/>
+      <x:c r="P183" s="32"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="34"/>
@@ -4075,6 +4279,7 @@
       <x:c r="M184" s="46"/>
       <x:c r="N184" s="46"/>
       <x:c r="O184" s="34"/>
+      <x:c r="P184" s="32"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="34"/>
@@ -4092,6 +4297,7 @@
       <x:c r="M185" s="46"/>
       <x:c r="N185" s="46"/>
       <x:c r="O185" s="34"/>
+      <x:c r="P185" s="32"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="34"/>
@@ -4109,6 +4315,7 @@
       <x:c r="M186" s="46"/>
       <x:c r="N186" s="46"/>
       <x:c r="O186" s="34"/>
+      <x:c r="P186" s="32"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="34"/>
@@ -4126,6 +4333,7 @@
       <x:c r="M187" s="46"/>
       <x:c r="N187" s="46"/>
       <x:c r="O187" s="34"/>
+      <x:c r="P187" s="32"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="34"/>
@@ -4143,6 +4351,7 @@
       <x:c r="M188" s="46"/>
       <x:c r="N188" s="46"/>
       <x:c r="O188" s="34"/>
+      <x:c r="P188" s="32"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="34"/>
@@ -4160,6 +4369,7 @@
       <x:c r="M189" s="46"/>
       <x:c r="N189" s="46"/>
       <x:c r="O189" s="34"/>
+      <x:c r="P189" s="32"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="34"/>
@@ -4177,6 +4387,7 @@
       <x:c r="M190" s="46"/>
       <x:c r="N190" s="46"/>
       <x:c r="O190" s="34"/>
+      <x:c r="P190" s="32"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="34"/>
@@ -4194,6 +4405,7 @@
       <x:c r="M191" s="46"/>
       <x:c r="N191" s="46"/>
       <x:c r="O191" s="34"/>
+      <x:c r="P191" s="32"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="34"/>
@@ -4211,6 +4423,7 @@
       <x:c r="M192" s="46"/>
       <x:c r="N192" s="46"/>
       <x:c r="O192" s="34"/>
+      <x:c r="P192" s="32"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="34"/>
@@ -4228,6 +4441,7 @@
       <x:c r="M193" s="46"/>
       <x:c r="N193" s="46"/>
       <x:c r="O193" s="34"/>
+      <x:c r="P193" s="32"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="34"/>
@@ -4245,6 +4459,7 @@
       <x:c r="M194" s="46"/>
       <x:c r="N194" s="46"/>
       <x:c r="O194" s="34"/>
+      <x:c r="P194" s="32"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="34"/>
@@ -4262,6 +4477,7 @@
       <x:c r="M195" s="46"/>
       <x:c r="N195" s="46"/>
       <x:c r="O195" s="34"/>
+      <x:c r="P195" s="32"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="34"/>
@@ -4279,6 +4495,7 @@
       <x:c r="M196" s="46"/>
       <x:c r="N196" s="46"/>
       <x:c r="O196" s="34"/>
+      <x:c r="P196" s="32"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="34"/>
@@ -4296,6 +4513,7 @@
       <x:c r="M197" s="46"/>
       <x:c r="N197" s="46"/>
       <x:c r="O197" s="34"/>
+      <x:c r="P197" s="32"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="34"/>
@@ -4313,6 +4531,7 @@
       <x:c r="M198" s="46"/>
       <x:c r="N198" s="46"/>
       <x:c r="O198" s="34"/>
+      <x:c r="P198" s="32"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="34"/>
@@ -4330,6 +4549,7 @@
       <x:c r="M199" s="46"/>
       <x:c r="N199" s="46"/>
       <x:c r="O199" s="34"/>
+      <x:c r="P199" s="32"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="34"/>
@@ -4347,6 +4567,7 @@
       <x:c r="M200" s="46"/>
       <x:c r="N200" s="46"/>
       <x:c r="O200" s="34"/>
+      <x:c r="P200" s="32"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="34"/>
@@ -4364,6 +4585,7 @@
       <x:c r="M201" s="46"/>
       <x:c r="N201" s="46"/>
       <x:c r="O201" s="34"/>
+      <x:c r="P201" s="32"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="34"/>
@@ -4381,6 +4603,7 @@
       <x:c r="M202" s="46"/>
       <x:c r="N202" s="46"/>
       <x:c r="O202" s="34"/>
+      <x:c r="P202" s="32"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="34"/>
@@ -4398,6 +4621,7 @@
       <x:c r="M203" s="46"/>
       <x:c r="N203" s="46"/>
       <x:c r="O203" s="34"/>
+      <x:c r="P203" s="32"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="34"/>
@@ -4415,6 +4639,7 @@
       <x:c r="M204" s="46"/>
       <x:c r="N204" s="46"/>
       <x:c r="O204" s="34"/>
+      <x:c r="P204" s="32"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="34"/>
@@ -4432,6 +4657,7 @@
       <x:c r="M205" s="46"/>
       <x:c r="N205" s="46"/>
       <x:c r="O205" s="34"/>
+      <x:c r="P205" s="32"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="34"/>
@@ -4449,6 +4675,7 @@
       <x:c r="M206" s="46"/>
       <x:c r="N206" s="46"/>
       <x:c r="O206" s="34"/>
+      <x:c r="P206" s="32"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="34"/>
@@ -4466,6 +4693,7 @@
       <x:c r="M207" s="46"/>
       <x:c r="N207" s="46"/>
       <x:c r="O207" s="34"/>
+      <x:c r="P207" s="32"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="34"/>
@@ -4483,6 +4711,7 @@
       <x:c r="M208" s="46"/>
       <x:c r="N208" s="46"/>
       <x:c r="O208" s="34"/>
+      <x:c r="P208" s="32"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="34"/>
@@ -4500,6 +4729,7 @@
       <x:c r="M209" s="46"/>
       <x:c r="N209" s="46"/>
       <x:c r="O209" s="34"/>
+      <x:c r="P209" s="32"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="34"/>
@@ -4517,6 +4747,7 @@
       <x:c r="M210" s="46"/>
       <x:c r="N210" s="46"/>
       <x:c r="O210" s="34"/>
+      <x:c r="P210" s="32"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="34"/>
@@ -4534,6 +4765,7 @@
       <x:c r="M211" s="46"/>
       <x:c r="N211" s="46"/>
       <x:c r="O211" s="34"/>
+      <x:c r="P211" s="32"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="34"/>
@@ -4551,6 +4783,7 @@
       <x:c r="M212" s="46"/>
       <x:c r="N212" s="46"/>
       <x:c r="O212" s="34"/>
+      <x:c r="P212" s="32"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="34"/>
@@ -4568,6 +4801,7 @@
       <x:c r="M213" s="46"/>
       <x:c r="N213" s="46"/>
       <x:c r="O213" s="34"/>
+      <x:c r="P213" s="32"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="34"/>
@@ -4585,6 +4819,7 @@
       <x:c r="M214" s="46"/>
       <x:c r="N214" s="46"/>
       <x:c r="O214" s="34"/>
+      <x:c r="P214" s="32"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="34"/>
@@ -4602,6 +4837,7 @@
       <x:c r="M215" s="46"/>
       <x:c r="N215" s="46"/>
       <x:c r="O215" s="34"/>
+      <x:c r="P215" s="32"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="34"/>
@@ -4619,6 +4855,7 @@
       <x:c r="M216" s="46"/>
       <x:c r="N216" s="46"/>
       <x:c r="O216" s="34"/>
+      <x:c r="P216" s="32"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="34"/>
@@ -4636,6 +4873,7 @@
       <x:c r="M217" s="46"/>
       <x:c r="N217" s="46"/>
       <x:c r="O217" s="34"/>
+      <x:c r="P217" s="32"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="34"/>
@@ -4653,6 +4891,7 @@
       <x:c r="M218" s="46"/>
       <x:c r="N218" s="46"/>
       <x:c r="O218" s="34"/>
+      <x:c r="P218" s="32"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="34"/>
@@ -4670,6 +4909,7 @@
       <x:c r="M219" s="46"/>
       <x:c r="N219" s="46"/>
       <x:c r="O219" s="34"/>
+      <x:c r="P219" s="32"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="34"/>
@@ -4687,6 +4927,7 @@
       <x:c r="M220" s="46"/>
       <x:c r="N220" s="46"/>
       <x:c r="O220" s="34"/>
+      <x:c r="P220" s="32"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="34"/>
@@ -4704,6 +4945,7 @@
       <x:c r="M221" s="46"/>
       <x:c r="N221" s="46"/>
       <x:c r="O221" s="34"/>
+      <x:c r="P221" s="32"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="34"/>
@@ -4721,6 +4963,7 @@
       <x:c r="M222" s="46"/>
       <x:c r="N222" s="46"/>
       <x:c r="O222" s="34"/>
+      <x:c r="P222" s="32"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="34"/>
@@ -4738,6 +4981,7 @@
       <x:c r="M223" s="46"/>
       <x:c r="N223" s="46"/>
       <x:c r="O223" s="34"/>
+      <x:c r="P223" s="32"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="34"/>
@@ -4755,6 +4999,7 @@
       <x:c r="M224" s="46"/>
       <x:c r="N224" s="46"/>
       <x:c r="O224" s="34"/>
+      <x:c r="P224" s="32"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="34"/>
@@ -4772,6 +5017,7 @@
       <x:c r="M225" s="46"/>
       <x:c r="N225" s="46"/>
       <x:c r="O225" s="34"/>
+      <x:c r="P225" s="32"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="34"/>
@@ -4789,6 +5035,7 @@
       <x:c r="M226" s="46"/>
       <x:c r="N226" s="46"/>
       <x:c r="O226" s="34"/>
+      <x:c r="P226" s="32"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="34"/>
@@ -4806,6 +5053,7 @@
       <x:c r="M227" s="46"/>
       <x:c r="N227" s="46"/>
       <x:c r="O227" s="34"/>
+      <x:c r="P227" s="32"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="34"/>
@@ -4823,6 +5071,7 @@
       <x:c r="M228" s="46"/>
       <x:c r="N228" s="46"/>
       <x:c r="O228" s="34"/>
+      <x:c r="P228" s="32"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="34"/>
@@ -4840,6 +5089,7 @@
       <x:c r="M229" s="46"/>
       <x:c r="N229" s="46"/>
       <x:c r="O229" s="34"/>
+      <x:c r="P229" s="32"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="34"/>
@@ -4857,6 +5107,7 @@
       <x:c r="M230" s="46"/>
       <x:c r="N230" s="46"/>
       <x:c r="O230" s="34"/>
+      <x:c r="P230" s="32"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="34"/>
@@ -4874,6 +5125,7 @@
       <x:c r="M231" s="46"/>
       <x:c r="N231" s="46"/>
       <x:c r="O231" s="34"/>
+      <x:c r="P231" s="32"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="34"/>
@@ -4891,6 +5143,7 @@
       <x:c r="M232" s="46"/>
       <x:c r="N232" s="46"/>
       <x:c r="O232" s="34"/>
+      <x:c r="P232" s="32"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="34"/>
@@ -4908,6 +5161,7 @@
       <x:c r="M233" s="46"/>
       <x:c r="N233" s="46"/>
       <x:c r="O233" s="34"/>
+      <x:c r="P233" s="32"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="34"/>
@@ -4925,6 +5179,7 @@
       <x:c r="M234" s="46"/>
       <x:c r="N234" s="46"/>
       <x:c r="O234" s="34"/>
+      <x:c r="P234" s="32"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="34"/>
@@ -4942,6 +5197,7 @@
       <x:c r="M235" s="46"/>
       <x:c r="N235" s="46"/>
       <x:c r="O235" s="34"/>
+      <x:c r="P235" s="32"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="34"/>
@@ -4959,6 +5215,7 @@
       <x:c r="M236" s="46"/>
       <x:c r="N236" s="46"/>
       <x:c r="O236" s="34"/>
+      <x:c r="P236" s="32"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="34"/>
@@ -4976,6 +5233,7 @@
       <x:c r="M237" s="46"/>
       <x:c r="N237" s="46"/>
       <x:c r="O237" s="34"/>
+      <x:c r="P237" s="32"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="34"/>
@@ -4993,6 +5251,7 @@
       <x:c r="M238" s="46"/>
       <x:c r="N238" s="46"/>
       <x:c r="O238" s="34"/>
+      <x:c r="P238" s="32"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="34"/>
@@ -5010,6 +5269,7 @@
       <x:c r="M239" s="46"/>
       <x:c r="N239" s="46"/>
       <x:c r="O239" s="34"/>
+      <x:c r="P239" s="32"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="34"/>
@@ -5027,6 +5287,7 @@
       <x:c r="M240" s="46"/>
       <x:c r="N240" s="46"/>
       <x:c r="O240" s="34"/>
+      <x:c r="P240" s="32"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="34"/>
@@ -5044,6 +5305,7 @@
       <x:c r="M241" s="46"/>
       <x:c r="N241" s="46"/>
       <x:c r="O241" s="34"/>
+      <x:c r="P241" s="32"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="34"/>
@@ -5061,6 +5323,7 @@
       <x:c r="M242" s="46"/>
       <x:c r="N242" s="46"/>
       <x:c r="O242" s="34"/>
+      <x:c r="P242" s="32"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="34"/>
@@ -5078,6 +5341,7 @@
       <x:c r="M243" s="46"/>
       <x:c r="N243" s="46"/>
       <x:c r="O243" s="34"/>
+      <x:c r="P243" s="32"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="34"/>
@@ -5095,6 +5359,7 @@
       <x:c r="M244" s="46"/>
       <x:c r="N244" s="46"/>
       <x:c r="O244" s="34"/>
+      <x:c r="P244" s="32"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="34"/>
@@ -5112,6 +5377,7 @@
       <x:c r="M245" s="46"/>
       <x:c r="N245" s="46"/>
       <x:c r="O245" s="34"/>
+      <x:c r="P245" s="32"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="34"/>
@@ -5129,6 +5395,7 @@
       <x:c r="M246" s="46"/>
       <x:c r="N246" s="46"/>
       <x:c r="O246" s="34"/>
+      <x:c r="P246" s="32"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="34"/>
@@ -5146,6 +5413,7 @@
       <x:c r="M247" s="46"/>
       <x:c r="N247" s="46"/>
       <x:c r="O247" s="34"/>
+      <x:c r="P247" s="32"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="34"/>
@@ -5163,6 +5431,7 @@
       <x:c r="M248" s="46"/>
       <x:c r="N248" s="46"/>
       <x:c r="O248" s="34"/>
+      <x:c r="P248" s="32"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="34"/>
@@ -5180,6 +5449,7 @@
       <x:c r="M249" s="46"/>
       <x:c r="N249" s="46"/>
       <x:c r="O249" s="34"/>
+      <x:c r="P249" s="32"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="34"/>
@@ -5197,6 +5467,7 @@
       <x:c r="M250" s="46"/>
       <x:c r="N250" s="46"/>
       <x:c r="O250" s="34"/>
+      <x:c r="P250" s="32"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="34"/>
@@ -5214,6 +5485,7 @@
       <x:c r="M251" s="46"/>
       <x:c r="N251" s="46"/>
       <x:c r="O251" s="34"/>
+      <x:c r="P251" s="32"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="34"/>
@@ -5231,6 +5503,7 @@
       <x:c r="M252" s="46"/>
       <x:c r="N252" s="46"/>
       <x:c r="O252" s="34"/>
+      <x:c r="P252" s="32"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="34"/>
@@ -5248,6 +5521,7 @@
       <x:c r="M253" s="46"/>
       <x:c r="N253" s="46"/>
       <x:c r="O253" s="34"/>
+      <x:c r="P253" s="32"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="34"/>
@@ -5265,6 +5539,7 @@
       <x:c r="M254" s="46"/>
       <x:c r="N254" s="46"/>
       <x:c r="O254" s="34"/>
+      <x:c r="P254" s="32"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="34"/>
@@ -5282,6 +5557,7 @@
       <x:c r="M255" s="46"/>
       <x:c r="N255" s="46"/>
       <x:c r="O255" s="34"/>
+      <x:c r="P255" s="32"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="34"/>
@@ -5299,6 +5575,7 @@
       <x:c r="M256" s="46"/>
       <x:c r="N256" s="46"/>
       <x:c r="O256" s="34"/>
+      <x:c r="P256" s="32"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="34"/>
@@ -5316,6 +5593,7 @@
       <x:c r="M257" s="46"/>
       <x:c r="N257" s="46"/>
       <x:c r="O257" s="34"/>
+      <x:c r="P257" s="32"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="34"/>
@@ -5333,6 +5611,7 @@
       <x:c r="M258" s="46"/>
       <x:c r="N258" s="46"/>
       <x:c r="O258" s="34"/>
+      <x:c r="P258" s="32"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="34"/>
@@ -5350,6 +5629,7 @@
       <x:c r="M259" s="46"/>
       <x:c r="N259" s="46"/>
       <x:c r="O259" s="34"/>
+      <x:c r="P259" s="32"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="34"/>
@@ -5367,6 +5647,7 @@
       <x:c r="M260" s="46"/>
       <x:c r="N260" s="46"/>
       <x:c r="O260" s="34"/>
+      <x:c r="P260" s="32"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="34"/>
@@ -5384,6 +5665,7 @@
       <x:c r="M261" s="46"/>
       <x:c r="N261" s="46"/>
       <x:c r="O261" s="34"/>
+      <x:c r="P261" s="32"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="34"/>
@@ -5401,6 +5683,7 @@
       <x:c r="M262" s="46"/>
       <x:c r="N262" s="46"/>
       <x:c r="O262" s="34"/>
+      <x:c r="P262" s="32"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="34"/>
@@ -5418,6 +5701,7 @@
       <x:c r="M263" s="46"/>
       <x:c r="N263" s="46"/>
       <x:c r="O263" s="34"/>
+      <x:c r="P263" s="32"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="34"/>
@@ -5435,6 +5719,7 @@
       <x:c r="M264" s="46"/>
       <x:c r="N264" s="46"/>
       <x:c r="O264" s="34"/>
+      <x:c r="P264" s="32"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="34"/>
@@ -5452,6 +5737,7 @@
       <x:c r="M265" s="46"/>
       <x:c r="N265" s="46"/>
       <x:c r="O265" s="34"/>
+      <x:c r="P265" s="32"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="34"/>
@@ -5469,6 +5755,7 @@
       <x:c r="M266" s="46"/>
       <x:c r="N266" s="46"/>
       <x:c r="O266" s="34"/>
+      <x:c r="P266" s="32"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="34"/>
@@ -5486,6 +5773,7 @@
       <x:c r="M267" s="46"/>
       <x:c r="N267" s="46"/>
       <x:c r="O267" s="34"/>
+      <x:c r="P267" s="32"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="34"/>
@@ -5503,6 +5791,7 @@
       <x:c r="M268" s="46"/>
       <x:c r="N268" s="46"/>
       <x:c r="O268" s="34"/>
+      <x:c r="P268" s="32"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="34"/>
@@ -5520,6 +5809,7 @@
       <x:c r="M269" s="46"/>
       <x:c r="N269" s="46"/>
       <x:c r="O269" s="34"/>
+      <x:c r="P269" s="32"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="34"/>
@@ -5537,6 +5827,7 @@
       <x:c r="M270" s="46"/>
       <x:c r="N270" s="46"/>
       <x:c r="O270" s="34"/>
+      <x:c r="P270" s="32"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="34"/>
@@ -5554,6 +5845,7 @@
       <x:c r="M271" s="46"/>
       <x:c r="N271" s="46"/>
       <x:c r="O271" s="34"/>
+      <x:c r="P271" s="32"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="34"/>
@@ -5571,6 +5863,7 @@
       <x:c r="M272" s="46"/>
       <x:c r="N272" s="46"/>
       <x:c r="O272" s="34"/>
+      <x:c r="P272" s="32"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="34"/>
@@ -5588,6 +5881,7 @@
       <x:c r="M273" s="46"/>
       <x:c r="N273" s="46"/>
       <x:c r="O273" s="34"/>
+      <x:c r="P273" s="32"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="34"/>
@@ -5605,6 +5899,7 @@
       <x:c r="M274" s="46"/>
       <x:c r="N274" s="46"/>
       <x:c r="O274" s="34"/>
+      <x:c r="P274" s="32"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="34"/>
@@ -5622,6 +5917,7 @@
       <x:c r="M275" s="46"/>
       <x:c r="N275" s="46"/>
       <x:c r="O275" s="34"/>
+      <x:c r="P275" s="32"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="34"/>
@@ -5639,6 +5935,7 @@
       <x:c r="M276" s="46"/>
       <x:c r="N276" s="46"/>
       <x:c r="O276" s="34"/>
+      <x:c r="P276" s="32"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="34"/>
@@ -5656,6 +5953,7 @@
       <x:c r="M277" s="46"/>
       <x:c r="N277" s="46"/>
       <x:c r="O277" s="34"/>
+      <x:c r="P277" s="32"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="34"/>
@@ -5673,6 +5971,7 @@
       <x:c r="M278" s="46"/>
       <x:c r="N278" s="46"/>
       <x:c r="O278" s="34"/>
+      <x:c r="P278" s="32"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="34"/>
@@ -5690,6 +5989,7 @@
       <x:c r="M279" s="46"/>
       <x:c r="N279" s="46"/>
       <x:c r="O279" s="34"/>
+      <x:c r="P279" s="32"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="34"/>
@@ -5707,6 +6007,7 @@
       <x:c r="M280" s="46"/>
       <x:c r="N280" s="46"/>
       <x:c r="O280" s="34"/>
+      <x:c r="P280" s="32"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="34"/>
@@ -5724,6 +6025,7 @@
       <x:c r="M281" s="46"/>
       <x:c r="N281" s="46"/>
       <x:c r="O281" s="34"/>
+      <x:c r="P281" s="32"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="34"/>
@@ -5741,6 +6043,7 @@
       <x:c r="M282" s="46"/>
       <x:c r="N282" s="46"/>
       <x:c r="O282" s="34"/>
+      <x:c r="P282" s="32"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="34"/>
@@ -5758,6 +6061,7 @@
       <x:c r="M283" s="46"/>
       <x:c r="N283" s="46"/>
       <x:c r="O283" s="34"/>
+      <x:c r="P283" s="32"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="34"/>
@@ -5775,6 +6079,7 @@
       <x:c r="M284" s="46"/>
       <x:c r="N284" s="46"/>
       <x:c r="O284" s="34"/>
+      <x:c r="P284" s="32"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="34"/>
@@ -5792,6 +6097,7 @@
       <x:c r="M285" s="46"/>
       <x:c r="N285" s="46"/>
       <x:c r="O285" s="34"/>
+      <x:c r="P285" s="32"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="34"/>
@@ -5809,6 +6115,7 @@
       <x:c r="M286" s="46"/>
       <x:c r="N286" s="46"/>
       <x:c r="O286" s="34"/>
+      <x:c r="P286" s="32"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="34"/>
@@ -5826,6 +6133,7 @@
       <x:c r="M287" s="46"/>
       <x:c r="N287" s="46"/>
       <x:c r="O287" s="34"/>
+      <x:c r="P287" s="32"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="34"/>
@@ -5843,6 +6151,7 @@
       <x:c r="M288" s="46"/>
       <x:c r="N288" s="46"/>
       <x:c r="O288" s="34"/>
+      <x:c r="P288" s="32"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="34"/>
@@ -5860,6 +6169,7 @@
       <x:c r="M289" s="46"/>
       <x:c r="N289" s="46"/>
       <x:c r="O289" s="34"/>
+      <x:c r="P289" s="32"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="34"/>
@@ -5877,6 +6187,7 @@
       <x:c r="M290" s="46"/>
       <x:c r="N290" s="46"/>
       <x:c r="O290" s="34"/>
+      <x:c r="P290" s="32"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="34"/>
@@ -5894,6 +6205,7 @@
       <x:c r="M291" s="46"/>
       <x:c r="N291" s="46"/>
       <x:c r="O291" s="34"/>
+      <x:c r="P291" s="32"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="34"/>
@@ -5911,6 +6223,7 @@
       <x:c r="M292" s="46"/>
       <x:c r="N292" s="46"/>
       <x:c r="O292" s="34"/>
+      <x:c r="P292" s="32"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="34"/>
@@ -5928,6 +6241,7 @@
       <x:c r="M293" s="46"/>
       <x:c r="N293" s="46"/>
       <x:c r="O293" s="34"/>
+      <x:c r="P293" s="32"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="34"/>
@@ -5945,6 +6259,7 @@
       <x:c r="M294" s="46"/>
       <x:c r="N294" s="46"/>
       <x:c r="O294" s="34"/>
+      <x:c r="P294" s="32"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="34"/>
@@ -5962,6 +6277,7 @@
       <x:c r="M295" s="46"/>
       <x:c r="N295" s="46"/>
       <x:c r="O295" s="34"/>
+      <x:c r="P295" s="32"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="34"/>
@@ -5979,6 +6295,7 @@
       <x:c r="M296" s="46"/>
       <x:c r="N296" s="46"/>
       <x:c r="O296" s="34"/>
+      <x:c r="P296" s="32"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="34"/>
@@ -5996,6 +6313,7 @@
       <x:c r="M297" s="46"/>
       <x:c r="N297" s="46"/>
       <x:c r="O297" s="34"/>
+      <x:c r="P297" s="32"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="34"/>
@@ -6013,6 +6331,7 @@
       <x:c r="M298" s="46"/>
       <x:c r="N298" s="46"/>
       <x:c r="O298" s="34"/>
+      <x:c r="P298" s="32"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="34"/>
@@ -6030,6 +6349,7 @@
       <x:c r="M299" s="46"/>
       <x:c r="N299" s="46"/>
       <x:c r="O299" s="34"/>
+      <x:c r="P299" s="32"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="34"/>
@@ -6047,6 +6367,7 @@
       <x:c r="M300" s="46"/>
       <x:c r="N300" s="46"/>
       <x:c r="O300" s="34"/>
+      <x:c r="P300" s="32"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="34"/>
@@ -6064,6 +6385,7 @@
       <x:c r="M301" s="46"/>
       <x:c r="N301" s="46"/>
       <x:c r="O301" s="34"/>
+      <x:c r="P301" s="32"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="34"/>
@@ -6081,6 +6403,7 @@
       <x:c r="M302" s="46"/>
       <x:c r="N302" s="46"/>
       <x:c r="O302" s="34"/>
+      <x:c r="P302" s="32"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="34"/>
@@ -6098,6 +6421,7 @@
       <x:c r="M303" s="46"/>
       <x:c r="N303" s="46"/>
       <x:c r="O303" s="34"/>
+      <x:c r="P303" s="32"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="34"/>
@@ -6115,6 +6439,7 @@
       <x:c r="M304" s="46"/>
       <x:c r="N304" s="46"/>
       <x:c r="O304" s="34"/>
+      <x:c r="P304" s="32"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="34"/>
@@ -6132,6 +6457,7 @@
       <x:c r="M305" s="46"/>
       <x:c r="N305" s="46"/>
       <x:c r="O305" s="34"/>
+      <x:c r="P305" s="32"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="34"/>
@@ -6149,6 +6475,7 @@
       <x:c r="M306" s="46"/>
       <x:c r="N306" s="46"/>
       <x:c r="O306" s="34"/>
+      <x:c r="P306" s="32"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="34"/>
@@ -6166,6 +6493,7 @@
       <x:c r="M307" s="46"/>
       <x:c r="N307" s="46"/>
       <x:c r="O307" s="34"/>
+      <x:c r="P307" s="32"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="34"/>
@@ -6183,6 +6511,7 @@
       <x:c r="M308" s="46"/>
       <x:c r="N308" s="46"/>
       <x:c r="O308" s="34"/>
+      <x:c r="P308" s="32"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="34"/>
@@ -6200,6 +6529,7 @@
       <x:c r="M309" s="46"/>
       <x:c r="N309" s="46"/>
       <x:c r="O309" s="34"/>
+      <x:c r="P309" s="32"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="34"/>
@@ -6217,6 +6547,7 @@
       <x:c r="M310" s="46"/>
       <x:c r="N310" s="46"/>
       <x:c r="O310" s="34"/>
+      <x:c r="P310" s="32"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="34"/>
@@ -6234,6 +6565,7 @@
       <x:c r="M311" s="46"/>
       <x:c r="N311" s="46"/>
       <x:c r="O311" s="34"/>
+      <x:c r="P311" s="32"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="34"/>
@@ -6251,6 +6583,7 @@
       <x:c r="M312" s="46"/>
       <x:c r="N312" s="46"/>
       <x:c r="O312" s="34"/>
+      <x:c r="P312" s="32"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="34"/>
@@ -6268,6 +6601,7 @@
       <x:c r="M313" s="46"/>
       <x:c r="N313" s="46"/>
       <x:c r="O313" s="34"/>
+      <x:c r="P313" s="32"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="34"/>
@@ -6285,6 +6619,7 @@
       <x:c r="M314" s="46"/>
       <x:c r="N314" s="46"/>
       <x:c r="O314" s="34"/>
+      <x:c r="P314" s="32"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="34"/>
@@ -6302,6 +6637,7 @@
       <x:c r="M315" s="46"/>
       <x:c r="N315" s="46"/>
       <x:c r="O315" s="34"/>
+      <x:c r="P315" s="32"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="34"/>
@@ -6319,6 +6655,7 @@
       <x:c r="M316" s="46"/>
       <x:c r="N316" s="46"/>
       <x:c r="O316" s="34"/>
+      <x:c r="P316" s="32"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="34"/>
@@ -6336,6 +6673,7 @@
       <x:c r="M317" s="46"/>
       <x:c r="N317" s="46"/>
       <x:c r="O317" s="34"/>
+      <x:c r="P317" s="32"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="34"/>
@@ -6353,6 +6691,7 @@
       <x:c r="M318" s="46"/>
       <x:c r="N318" s="46"/>
       <x:c r="O318" s="34"/>
+      <x:c r="P318" s="32"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="34"/>
@@ -6370,6 +6709,7 @@
       <x:c r="M319" s="46"/>
       <x:c r="N319" s="46"/>
       <x:c r="O319" s="34"/>
+      <x:c r="P319" s="32"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="34"/>
@@ -6387,6 +6727,7 @@
       <x:c r="M320" s="46"/>
       <x:c r="N320" s="46"/>
       <x:c r="O320" s="34"/>
+      <x:c r="P320" s="32"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="34"/>
@@ -6404,6 +6745,7 @@
       <x:c r="M321" s="46"/>
       <x:c r="N321" s="46"/>
       <x:c r="O321" s="34"/>
+      <x:c r="P321" s="32"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="34"/>
@@ -6421,6 +6763,7 @@
       <x:c r="M322" s="46"/>
       <x:c r="N322" s="46"/>
       <x:c r="O322" s="34"/>
+      <x:c r="P322" s="32"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="34"/>
@@ -6438,6 +6781,7 @@
       <x:c r="M323" s="46"/>
       <x:c r="N323" s="46"/>
       <x:c r="O323" s="34"/>
+      <x:c r="P323" s="32"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="34"/>
@@ -6455,6 +6799,7 @@
       <x:c r="M324" s="46"/>
       <x:c r="N324" s="46"/>
       <x:c r="O324" s="34"/>
+      <x:c r="P324" s="32"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="34"/>
@@ -6472,6 +6817,7 @@
       <x:c r="M325" s="46"/>
       <x:c r="N325" s="46"/>
       <x:c r="O325" s="34"/>
+      <x:c r="P325" s="32"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="34"/>
@@ -6489,6 +6835,7 @@
       <x:c r="M326" s="46"/>
       <x:c r="N326" s="46"/>
       <x:c r="O326" s="34"/>
+      <x:c r="P326" s="32"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="34"/>
@@ -6506,6 +6853,7 @@
       <x:c r="M327" s="46"/>
       <x:c r="N327" s="46"/>
       <x:c r="O327" s="34"/>
+      <x:c r="P327" s="32"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="34"/>
@@ -6523,6 +6871,7 @@
       <x:c r="M328" s="46"/>
       <x:c r="N328" s="46"/>
       <x:c r="O328" s="34"/>
+      <x:c r="P328" s="32"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="34"/>
@@ -6540,6 +6889,7 @@
       <x:c r="M329" s="46"/>
       <x:c r="N329" s="46"/>
       <x:c r="O329" s="34"/>
+      <x:c r="P329" s="32"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="34"/>
@@ -6557,6 +6907,7 @@
       <x:c r="M330" s="46"/>
       <x:c r="N330" s="46"/>
       <x:c r="O330" s="34"/>
+      <x:c r="P330" s="32"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="34"/>
@@ -6574,6 +6925,7 @@
       <x:c r="M331" s="46"/>
       <x:c r="N331" s="46"/>
       <x:c r="O331" s="34"/>
+      <x:c r="P331" s="32"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="34"/>
@@ -6591,6 +6943,7 @@
       <x:c r="M332" s="46"/>
       <x:c r="N332" s="46"/>
       <x:c r="O332" s="34"/>
+      <x:c r="P332" s="32"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="34"/>
@@ -6608,6 +6961,7 @@
       <x:c r="M333" s="46"/>
       <x:c r="N333" s="46"/>
       <x:c r="O333" s="34"/>
+      <x:c r="P333" s="32"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="34"/>
@@ -6625,6 +6979,7 @@
       <x:c r="M334" s="46"/>
       <x:c r="N334" s="46"/>
       <x:c r="O334" s="34"/>
+      <x:c r="P334" s="32"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="34"/>
@@ -6642,6 +6997,7 @@
       <x:c r="M335" s="46"/>
       <x:c r="N335" s="46"/>
       <x:c r="O335" s="34"/>
+      <x:c r="P335" s="32"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="34"/>
@@ -6659,6 +7015,7 @@
       <x:c r="M336" s="46"/>
       <x:c r="N336" s="46"/>
       <x:c r="O336" s="34"/>
+      <x:c r="P336" s="32"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="34"/>
@@ -6676,6 +7033,7 @@
       <x:c r="M337" s="46"/>
       <x:c r="N337" s="46"/>
       <x:c r="O337" s="34"/>
+      <x:c r="P337" s="32"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="34"/>
@@ -6693,6 +7051,7 @@
       <x:c r="M338" s="46"/>
       <x:c r="N338" s="46"/>
       <x:c r="O338" s="34"/>
+      <x:c r="P338" s="32"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="34"/>
@@ -6710,6 +7069,7 @@
       <x:c r="M339" s="46"/>
       <x:c r="N339" s="46"/>
       <x:c r="O339" s="34"/>
+      <x:c r="P339" s="32"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="34"/>
@@ -6727,6 +7087,7 @@
       <x:c r="M340" s="46"/>
       <x:c r="N340" s="46"/>
       <x:c r="O340" s="34"/>
+      <x:c r="P340" s="32"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="34"/>
@@ -6744,6 +7105,7 @@
       <x:c r="M341" s="46"/>
       <x:c r="N341" s="46"/>
       <x:c r="O341" s="34"/>
+      <x:c r="P341" s="32"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="34"/>
@@ -6761,6 +7123,7 @@
       <x:c r="M342" s="46"/>
       <x:c r="N342" s="46"/>
       <x:c r="O342" s="34"/>
+      <x:c r="P342" s="32"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="34"/>
@@ -6778,6 +7141,7 @@
       <x:c r="M343" s="46"/>
       <x:c r="N343" s="46"/>
       <x:c r="O343" s="34"/>
+      <x:c r="P343" s="32"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="34"/>
@@ -6795,6 +7159,7 @@
       <x:c r="M344" s="46"/>
       <x:c r="N344" s="46"/>
       <x:c r="O344" s="34"/>
+      <x:c r="P344" s="32"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="34"/>
@@ -6812,6 +7177,7 @@
       <x:c r="M345" s="46"/>
       <x:c r="N345" s="46"/>
       <x:c r="O345" s="34"/>
+      <x:c r="P345" s="32"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="34"/>
@@ -6829,6 +7195,7 @@
       <x:c r="M346" s="46"/>
       <x:c r="N346" s="46"/>
       <x:c r="O346" s="34"/>
+      <x:c r="P346" s="32"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="34"/>
@@ -6846,6 +7213,7 @@
       <x:c r="M347" s="46"/>
       <x:c r="N347" s="46"/>
       <x:c r="O347" s="34"/>
+      <x:c r="P347" s="32"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="34"/>
@@ -6863,6 +7231,7 @@
       <x:c r="M348" s="46"/>
       <x:c r="N348" s="46"/>
       <x:c r="O348" s="34"/>
+      <x:c r="P348" s="32"/>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="34"/>
@@ -6880,6 +7249,7 @@
       <x:c r="M349" s="46"/>
       <x:c r="N349" s="46"/>
       <x:c r="O349" s="34"/>
+      <x:c r="P349" s="32"/>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="34"/>
@@ -6897,6 +7267,7 @@
       <x:c r="M350" s="46"/>
       <x:c r="N350" s="46"/>
       <x:c r="O350" s="34"/>
+      <x:c r="P350" s="32"/>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="34"/>
@@ -6914,6 +7285,7 @@
       <x:c r="M351" s="46"/>
       <x:c r="N351" s="46"/>
       <x:c r="O351" s="34"/>
+      <x:c r="P351" s="32"/>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="34"/>
@@ -6931,6 +7303,7 @@
       <x:c r="M352" s="46"/>
       <x:c r="N352" s="46"/>
       <x:c r="O352" s="34"/>
+      <x:c r="P352" s="32"/>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="34"/>
@@ -6948,6 +7321,7 @@
       <x:c r="M353" s="46"/>
       <x:c r="N353" s="46"/>
       <x:c r="O353" s="34"/>
+      <x:c r="P353" s="32"/>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="34"/>
@@ -6965,6 +7339,7 @@
       <x:c r="M354" s="46"/>
       <x:c r="N354" s="46"/>
       <x:c r="O354" s="34"/>
+      <x:c r="P354" s="32"/>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="34"/>
@@ -6982,6 +7357,7 @@
       <x:c r="M355" s="46"/>
       <x:c r="N355" s="46"/>
       <x:c r="O355" s="34"/>
+      <x:c r="P355" s="32"/>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="34"/>
@@ -6999,6 +7375,7 @@
       <x:c r="M356" s="46"/>
       <x:c r="N356" s="46"/>
       <x:c r="O356" s="34"/>
+      <x:c r="P356" s="32"/>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="34"/>
@@ -7016,6 +7393,7 @@
       <x:c r="M357" s="46"/>
       <x:c r="N357" s="46"/>
       <x:c r="O357" s="34"/>
+      <x:c r="P357" s="32"/>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="34"/>
@@ -7033,6 +7411,7 @@
       <x:c r="M358" s="46"/>
       <x:c r="N358" s="46"/>
       <x:c r="O358" s="34"/>
+      <x:c r="P358" s="32"/>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="34"/>
@@ -7050,6 +7429,7 @@
       <x:c r="M359" s="46"/>
       <x:c r="N359" s="46"/>
       <x:c r="O359" s="34"/>
+      <x:c r="P359" s="32"/>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="34"/>
@@ -7067,6 +7447,7 @@
       <x:c r="M360" s="46"/>
       <x:c r="N360" s="46"/>
       <x:c r="O360" s="34"/>
+      <x:c r="P360" s="32"/>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="34"/>
@@ -7084,6 +7465,7 @@
       <x:c r="M361" s="46"/>
       <x:c r="N361" s="46"/>
       <x:c r="O361" s="34"/>
+      <x:c r="P361" s="32"/>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="34"/>
@@ -7101,6 +7483,7 @@
       <x:c r="M362" s="46"/>
       <x:c r="N362" s="46"/>
       <x:c r="O362" s="34"/>
+      <x:c r="P362" s="32"/>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="34"/>
@@ -7118,6 +7501,7 @@
       <x:c r="M363" s="46"/>
       <x:c r="N363" s="46"/>
       <x:c r="O363" s="34"/>
+      <x:c r="P363" s="32"/>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="34"/>
@@ -7135,6 +7519,7 @@
       <x:c r="M364" s="46"/>
       <x:c r="N364" s="46"/>
       <x:c r="O364" s="34"/>
+      <x:c r="P364" s="32"/>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="34"/>
@@ -7152,6 +7537,7 @@
       <x:c r="M365" s="46"/>
       <x:c r="N365" s="46"/>
       <x:c r="O365" s="34"/>
+      <x:c r="P365" s="32"/>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="34"/>
@@ -7169,6 +7555,7 @@
       <x:c r="M366" s="46"/>
       <x:c r="N366" s="46"/>
       <x:c r="O366" s="34"/>
+      <x:c r="P366" s="32"/>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="34"/>
@@ -7186,6 +7573,7 @@
       <x:c r="M367" s="46"/>
       <x:c r="N367" s="46"/>
       <x:c r="O367" s="34"/>
+      <x:c r="P367" s="32"/>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="34"/>
@@ -7203,6 +7591,7 @@
       <x:c r="M368" s="46"/>
       <x:c r="N368" s="46"/>
       <x:c r="O368" s="34"/>
+      <x:c r="P368" s="32"/>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="34"/>
@@ -7220,6 +7609,7 @@
       <x:c r="M369" s="46"/>
       <x:c r="N369" s="46"/>
       <x:c r="O369" s="34"/>
+      <x:c r="P369" s="32"/>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="34"/>
@@ -7237,6 +7627,7 @@
       <x:c r="M370" s="46"/>
       <x:c r="N370" s="46"/>
       <x:c r="O370" s="34"/>
+      <x:c r="P370" s="32"/>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="34"/>
@@ -7254,6 +7645,7 @@
       <x:c r="M371" s="46"/>
       <x:c r="N371" s="46"/>
       <x:c r="O371" s="34"/>
+      <x:c r="P371" s="32"/>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="34"/>
@@ -7271,6 +7663,7 @@
       <x:c r="M372" s="46"/>
       <x:c r="N372" s="46"/>
       <x:c r="O372" s="34"/>
+      <x:c r="P372" s="32"/>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="34"/>
@@ -7288,6 +7681,7 @@
       <x:c r="M373" s="46"/>
       <x:c r="N373" s="46"/>
       <x:c r="O373" s="34"/>
+      <x:c r="P373" s="32"/>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="34"/>
@@ -7305,6 +7699,7 @@
       <x:c r="M374" s="46"/>
       <x:c r="N374" s="46"/>
       <x:c r="O374" s="34"/>
+      <x:c r="P374" s="32"/>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="34"/>
@@ -7322,6 +7717,7 @@
       <x:c r="M375" s="46"/>
       <x:c r="N375" s="46"/>
       <x:c r="O375" s="34"/>
+      <x:c r="P375" s="32"/>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="34"/>
@@ -7339,6 +7735,7 @@
       <x:c r="M376" s="46"/>
       <x:c r="N376" s="46"/>
       <x:c r="O376" s="34"/>
+      <x:c r="P376" s="32"/>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="34"/>
@@ -7356,6 +7753,7 @@
       <x:c r="M377" s="46"/>
       <x:c r="N377" s="46"/>
       <x:c r="O377" s="34"/>
+      <x:c r="P377" s="32"/>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="34"/>
@@ -7373,6 +7771,7 @@
       <x:c r="M378" s="46"/>
       <x:c r="N378" s="46"/>
       <x:c r="O378" s="34"/>
+      <x:c r="P378" s="32"/>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="34"/>
@@ -7390,6 +7789,7 @@
       <x:c r="M379" s="46"/>
       <x:c r="N379" s="46"/>
       <x:c r="O379" s="34"/>
+      <x:c r="P379" s="32"/>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="34"/>
@@ -7407,6 +7807,7 @@
       <x:c r="M380" s="46"/>
       <x:c r="N380" s="46"/>
       <x:c r="O380" s="34"/>
+      <x:c r="P380" s="32"/>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="34"/>
@@ -7424,6 +7825,7 @@
       <x:c r="M381" s="46"/>
       <x:c r="N381" s="46"/>
       <x:c r="O381" s="34"/>
+      <x:c r="P381" s="32"/>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="34"/>
@@ -7441,6 +7843,7 @@
       <x:c r="M382" s="46"/>
       <x:c r="N382" s="46"/>
       <x:c r="O382" s="34"/>
+      <x:c r="P382" s="32"/>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="34"/>
@@ -7458,6 +7861,7 @@
       <x:c r="M383" s="46"/>
       <x:c r="N383" s="46"/>
       <x:c r="O383" s="34"/>
+      <x:c r="P383" s="32"/>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="34"/>
@@ -7475,6 +7879,7 @@
       <x:c r="M384" s="46"/>
       <x:c r="N384" s="46"/>
       <x:c r="O384" s="34"/>
+      <x:c r="P384" s="32"/>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="34"/>
@@ -7492,6 +7897,7 @@
       <x:c r="M385" s="46"/>
       <x:c r="N385" s="46"/>
       <x:c r="O385" s="34"/>
+      <x:c r="P385" s="32"/>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="34"/>
@@ -7509,6 +7915,7 @@
       <x:c r="M386" s="46"/>
       <x:c r="N386" s="46"/>
       <x:c r="O386" s="34"/>
+      <x:c r="P386" s="32"/>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="34"/>
@@ -7526,6 +7933,7 @@
       <x:c r="M387" s="46"/>
       <x:c r="N387" s="46"/>
       <x:c r="O387" s="34"/>
+      <x:c r="P387" s="32"/>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="34"/>
@@ -7543,6 +7951,7 @@
       <x:c r="M388" s="46"/>
       <x:c r="N388" s="46"/>
       <x:c r="O388" s="34"/>
+      <x:c r="P388" s="32"/>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="34"/>
@@ -7560,6 +7969,7 @@
       <x:c r="M389" s="46"/>
       <x:c r="N389" s="46"/>
       <x:c r="O389" s="34"/>
+      <x:c r="P389" s="32"/>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="34"/>
@@ -7577,6 +7987,7 @@
       <x:c r="M390" s="46"/>
       <x:c r="N390" s="46"/>
       <x:c r="O390" s="34"/>
+      <x:c r="P390" s="32"/>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="34"/>
@@ -7594,6 +8005,7 @@
       <x:c r="M391" s="46"/>
       <x:c r="N391" s="46"/>
       <x:c r="O391" s="34"/>
+      <x:c r="P391" s="32"/>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="34"/>
@@ -7611,6 +8023,7 @@
       <x:c r="M392" s="46"/>
       <x:c r="N392" s="46"/>
       <x:c r="O392" s="34"/>
+      <x:c r="P392" s="32"/>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="34"/>
@@ -7628,6 +8041,7 @@
       <x:c r="M393" s="46"/>
       <x:c r="N393" s="46"/>
       <x:c r="O393" s="34"/>
+      <x:c r="P393" s="32"/>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="34"/>
@@ -7645,6 +8059,7 @@
       <x:c r="M394" s="46"/>
       <x:c r="N394" s="46"/>
       <x:c r="O394" s="34"/>
+      <x:c r="P394" s="32"/>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="34"/>
@@ -7662,6 +8077,7 @@
       <x:c r="M395" s="46"/>
       <x:c r="N395" s="46"/>
       <x:c r="O395" s="34"/>
+      <x:c r="P395" s="32"/>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="34"/>
@@ -7679,6 +8095,7 @@
       <x:c r="M396" s="46"/>
       <x:c r="N396" s="46"/>
       <x:c r="O396" s="34"/>
+      <x:c r="P396" s="32"/>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="34"/>
@@ -7696,6 +8113,7 @@
       <x:c r="M397" s="46"/>
       <x:c r="N397" s="46"/>
       <x:c r="O397" s="34"/>
+      <x:c r="P397" s="32"/>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="34"/>
@@ -7713,6 +8131,7 @@
       <x:c r="M398" s="46"/>
       <x:c r="N398" s="46"/>
       <x:c r="O398" s="34"/>
+      <x:c r="P398" s="32"/>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="34"/>
@@ -7730,6 +8149,7 @@
       <x:c r="M399" s="46"/>
       <x:c r="N399" s="46"/>
       <x:c r="O399" s="34"/>
+      <x:c r="P399" s="32"/>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="34"/>
@@ -7747,6 +8167,7 @@
       <x:c r="M400" s="46"/>
       <x:c r="N400" s="46"/>
       <x:c r="O400" s="34"/>
+      <x:c r="P400" s="32"/>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="34"/>
@@ -7764,6 +8185,7 @@
       <x:c r="M401" s="46"/>
       <x:c r="N401" s="46"/>
       <x:c r="O401" s="34"/>
+      <x:c r="P401" s="32"/>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="34"/>
@@ -7781,6 +8203,7 @@
       <x:c r="M402" s="46"/>
       <x:c r="N402" s="46"/>
       <x:c r="O402" s="34"/>
+      <x:c r="P402" s="32"/>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="34"/>
@@ -7798,6 +8221,7 @@
       <x:c r="M403" s="46"/>
       <x:c r="N403" s="46"/>
       <x:c r="O403" s="34"/>
+      <x:c r="P403" s="32"/>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="34"/>
@@ -7815,6 +8239,7 @@
       <x:c r="M404" s="46"/>
       <x:c r="N404" s="46"/>
       <x:c r="O404" s="34"/>
+      <x:c r="P404" s="32"/>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="34"/>
@@ -7832,6 +8257,7 @@
       <x:c r="M405" s="46"/>
       <x:c r="N405" s="46"/>
       <x:c r="O405" s="34"/>
+      <x:c r="P405" s="32"/>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="34"/>
@@ -7849,6 +8275,7 @@
       <x:c r="M406" s="46"/>
       <x:c r="N406" s="46"/>
       <x:c r="O406" s="34"/>
+      <x:c r="P406" s="32"/>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="34"/>
@@ -7866,6 +8293,7 @@
       <x:c r="M407" s="46"/>
       <x:c r="N407" s="46"/>
       <x:c r="O407" s="34"/>
+      <x:c r="P407" s="32"/>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="34"/>
@@ -7883,6 +8311,7 @@
       <x:c r="M408" s="46"/>
       <x:c r="N408" s="46"/>
       <x:c r="O408" s="34"/>
+      <x:c r="P408" s="32"/>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="34"/>
@@ -7900,6 +8329,7 @@
       <x:c r="M409" s="46"/>
       <x:c r="N409" s="46"/>
       <x:c r="O409" s="34"/>
+      <x:c r="P409" s="32"/>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="34"/>
@@ -7917,6 +8347,7 @@
       <x:c r="M410" s="46"/>
       <x:c r="N410" s="46"/>
       <x:c r="O410" s="34"/>
+      <x:c r="P410" s="32"/>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="34"/>
@@ -7934,6 +8365,7 @@
       <x:c r="M411" s="46"/>
       <x:c r="N411" s="46"/>
       <x:c r="O411" s="34"/>
+      <x:c r="P411" s="32"/>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="34"/>
@@ -7951,6 +8383,7 @@
       <x:c r="M412" s="46"/>
       <x:c r="N412" s="46"/>
       <x:c r="O412" s="34"/>
+      <x:c r="P412" s="32"/>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="34"/>
@@ -7968,6 +8401,7 @@
       <x:c r="M413" s="46"/>
       <x:c r="N413" s="46"/>
       <x:c r="O413" s="34"/>
+      <x:c r="P413" s="32"/>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="34"/>
@@ -7985,6 +8419,7 @@
       <x:c r="M414" s="46"/>
       <x:c r="N414" s="46"/>
       <x:c r="O414" s="34"/>
+      <x:c r="P414" s="32"/>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="34"/>
@@ -8002,6 +8437,7 @@
       <x:c r="M415" s="46"/>
       <x:c r="N415" s="46"/>
       <x:c r="O415" s="34"/>
+      <x:c r="P415" s="32"/>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="34"/>
@@ -8019,6 +8455,7 @@
       <x:c r="M416" s="46"/>
       <x:c r="N416" s="46"/>
       <x:c r="O416" s="34"/>
+      <x:c r="P416" s="32"/>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="34"/>
@@ -8036,6 +8473,7 @@
       <x:c r="M417" s="46"/>
       <x:c r="N417" s="46"/>
       <x:c r="O417" s="34"/>
+      <x:c r="P417" s="32"/>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="34"/>
@@ -8053,6 +8491,7 @@
       <x:c r="M418" s="46"/>
       <x:c r="N418" s="46"/>
       <x:c r="O418" s="34"/>
+      <x:c r="P418" s="32"/>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="34"/>
@@ -8070,6 +8509,7 @@
       <x:c r="M419" s="46"/>
       <x:c r="N419" s="46"/>
       <x:c r="O419" s="34"/>
+      <x:c r="P419" s="32"/>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="34"/>
@@ -8087,6 +8527,7 @@
       <x:c r="M420" s="46"/>
       <x:c r="N420" s="46"/>
       <x:c r="O420" s="34"/>
+      <x:c r="P420" s="32"/>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="34"/>
@@ -8104,6 +8545,7 @@
       <x:c r="M421" s="46"/>
       <x:c r="N421" s="46"/>
       <x:c r="O421" s="34"/>
+      <x:c r="P421" s="32"/>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="34"/>
@@ -8121,6 +8563,7 @@
       <x:c r="M422" s="46"/>
       <x:c r="N422" s="46"/>
       <x:c r="O422" s="34"/>
+      <x:c r="P422" s="32"/>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="34"/>
@@ -8138,6 +8581,7 @@
       <x:c r="M423" s="46"/>
       <x:c r="N423" s="46"/>
       <x:c r="O423" s="34"/>
+      <x:c r="P423" s="32"/>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="34"/>
@@ -8155,6 +8599,7 @@
       <x:c r="M424" s="46"/>
       <x:c r="N424" s="46"/>
       <x:c r="O424" s="34"/>
+      <x:c r="P424" s="32"/>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="34"/>
@@ -8172,6 +8617,7 @@
       <x:c r="M425" s="46"/>
       <x:c r="N425" s="46"/>
       <x:c r="O425" s="34"/>
+      <x:c r="P425" s="32"/>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="34"/>
@@ -8189,6 +8635,7 @@
       <x:c r="M426" s="46"/>
       <x:c r="N426" s="46"/>
       <x:c r="O426" s="34"/>
+      <x:c r="P426" s="32"/>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="34"/>
@@ -8206,6 +8653,7 @@
       <x:c r="M427" s="46"/>
       <x:c r="N427" s="46"/>
       <x:c r="O427" s="34"/>
+      <x:c r="P427" s="32"/>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="34"/>
@@ -8223,6 +8671,7 @@
       <x:c r="M428" s="46"/>
       <x:c r="N428" s="46"/>
       <x:c r="O428" s="34"/>
+      <x:c r="P428" s="32"/>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="34"/>
@@ -8240,6 +8689,7 @@
       <x:c r="M429" s="46"/>
       <x:c r="N429" s="46"/>
       <x:c r="O429" s="34"/>
+      <x:c r="P429" s="32"/>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="34"/>
@@ -8257,6 +8707,7 @@
       <x:c r="M430" s="46"/>
       <x:c r="N430" s="46"/>
       <x:c r="O430" s="34"/>
+      <x:c r="P430" s="32"/>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="34"/>
@@ -8274,6 +8725,7 @@
       <x:c r="M431" s="46"/>
       <x:c r="N431" s="46"/>
       <x:c r="O431" s="34"/>
+      <x:c r="P431" s="32"/>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="34"/>
@@ -8291,6 +8743,7 @@
       <x:c r="M432" s="46"/>
       <x:c r="N432" s="46"/>
       <x:c r="O432" s="34"/>
+      <x:c r="P432" s="32"/>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="34"/>
@@ -8308,6 +8761,7 @@
       <x:c r="M433" s="46"/>
       <x:c r="N433" s="46"/>
       <x:c r="O433" s="34"/>
+      <x:c r="P433" s="32"/>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="34"/>
@@ -8325,6 +8779,7 @@
       <x:c r="M434" s="46"/>
       <x:c r="N434" s="46"/>
       <x:c r="O434" s="34"/>
+      <x:c r="P434" s="32"/>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="34"/>
@@ -8342,6 +8797,7 @@
       <x:c r="M435" s="46"/>
       <x:c r="N435" s="46"/>
       <x:c r="O435" s="34"/>
+      <x:c r="P435" s="32"/>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="34"/>
@@ -8359,6 +8815,7 @@
       <x:c r="M436" s="46"/>
       <x:c r="N436" s="46"/>
       <x:c r="O436" s="34"/>
+      <x:c r="P436" s="32"/>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="34"/>
@@ -8376,6 +8833,7 @@
       <x:c r="M437" s="46"/>
       <x:c r="N437" s="46"/>
       <x:c r="O437" s="34"/>
+      <x:c r="P437" s="32"/>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="34"/>
@@ -8393,6 +8851,7 @@
       <x:c r="M438" s="46"/>
       <x:c r="N438" s="46"/>
       <x:c r="O438" s="34"/>
+      <x:c r="P438" s="32"/>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="34"/>
@@ -8410,6 +8869,7 @@
       <x:c r="M439" s="46"/>
       <x:c r="N439" s="46"/>
       <x:c r="O439" s="34"/>
+      <x:c r="P439" s="32"/>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="34"/>
@@ -8427,6 +8887,7 @@
       <x:c r="M440" s="46"/>
       <x:c r="N440" s="46"/>
       <x:c r="O440" s="34"/>
+      <x:c r="P440" s="32"/>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="34"/>
@@ -8444,6 +8905,7 @@
       <x:c r="M441" s="46"/>
       <x:c r="N441" s="46"/>
       <x:c r="O441" s="34"/>
+      <x:c r="P441" s="32"/>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="34"/>
@@ -8461,6 +8923,7 @@
       <x:c r="M442" s="46"/>
       <x:c r="N442" s="46"/>
       <x:c r="O442" s="34"/>
+      <x:c r="P442" s="32"/>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="34"/>
@@ -8478,6 +8941,7 @@
       <x:c r="M443" s="46"/>
       <x:c r="N443" s="46"/>
       <x:c r="O443" s="34"/>
+      <x:c r="P443" s="32"/>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="34"/>
@@ -8495,6 +8959,7 @@
       <x:c r="M444" s="46"/>
       <x:c r="N444" s="46"/>
       <x:c r="O444" s="34"/>
+      <x:c r="P444" s="32"/>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="34"/>
@@ -8512,6 +8977,7 @@
       <x:c r="M445" s="46"/>
       <x:c r="N445" s="46"/>
       <x:c r="O445" s="34"/>
+      <x:c r="P445" s="32"/>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="34"/>
@@ -8529,6 +8995,7 @@
       <x:c r="M446" s="46"/>
       <x:c r="N446" s="46"/>
       <x:c r="O446" s="34"/>
+      <x:c r="P446" s="32"/>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="34"/>
@@ -8546,6 +9013,7 @@
       <x:c r="M447" s="46"/>
       <x:c r="N447" s="46"/>
       <x:c r="O447" s="34"/>
+      <x:c r="P447" s="32"/>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="34"/>
@@ -8563,6 +9031,7 @@
       <x:c r="M448" s="46"/>
       <x:c r="N448" s="46"/>
       <x:c r="O448" s="34"/>
+      <x:c r="P448" s="32"/>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="34"/>
@@ -8580,6 +9049,7 @@
       <x:c r="M449" s="46"/>
       <x:c r="N449" s="46"/>
       <x:c r="O449" s="34"/>
+      <x:c r="P449" s="32"/>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="34"/>
@@ -8597,6 +9067,7 @@
       <x:c r="M450" s="46"/>
       <x:c r="N450" s="46"/>
       <x:c r="O450" s="34"/>
+      <x:c r="P450" s="32"/>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="34"/>
@@ -8614,6 +9085,7 @@
       <x:c r="M451" s="46"/>
       <x:c r="N451" s="46"/>
       <x:c r="O451" s="34"/>
+      <x:c r="P451" s="32"/>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="34"/>
@@ -8631,6 +9103,7 @@
       <x:c r="M452" s="46"/>
       <x:c r="N452" s="46"/>
       <x:c r="O452" s="34"/>
+      <x:c r="P452" s="32"/>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="34"/>
@@ -8648,6 +9121,7 @@
       <x:c r="M453" s="46"/>
       <x:c r="N453" s="46"/>
       <x:c r="O453" s="34"/>
+      <x:c r="P453" s="32"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="34"/>
@@ -8665,6 +9139,7 @@
       <x:c r="M454" s="46"/>
       <x:c r="N454" s="46"/>
       <x:c r="O454" s="34"/>
+      <x:c r="P454" s="32"/>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="34"/>
@@ -8682,6 +9157,7 @@
       <x:c r="M455" s="46"/>
       <x:c r="N455" s="46"/>
       <x:c r="O455" s="34"/>
+      <x:c r="P455" s="32"/>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="34"/>
@@ -8699,6 +9175,7 @@
       <x:c r="M456" s="46"/>
       <x:c r="N456" s="46"/>
       <x:c r="O456" s="34"/>
+      <x:c r="P456" s="32"/>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="34"/>
@@ -8716,6 +9193,7 @@
       <x:c r="M457" s="46"/>
       <x:c r="N457" s="46"/>
       <x:c r="O457" s="34"/>
+      <x:c r="P457" s="32"/>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="34"/>
@@ -8733,6 +9211,7 @@
       <x:c r="M458" s="46"/>
       <x:c r="N458" s="46"/>
       <x:c r="O458" s="34"/>
+      <x:c r="P458" s="32"/>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="34"/>
@@ -8750,6 +9229,7 @@
       <x:c r="M459" s="46"/>
       <x:c r="N459" s="46"/>
       <x:c r="O459" s="34"/>
+      <x:c r="P459" s="32"/>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="34"/>
@@ -8767,6 +9247,7 @@
       <x:c r="M460" s="46"/>
       <x:c r="N460" s="46"/>
       <x:c r="O460" s="34"/>
+      <x:c r="P460" s="32"/>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="34"/>
@@ -8784,6 +9265,7 @@
       <x:c r="M461" s="46"/>
       <x:c r="N461" s="46"/>
       <x:c r="O461" s="34"/>
+      <x:c r="P461" s="32"/>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="34"/>
@@ -8801,6 +9283,7 @@
       <x:c r="M462" s="46"/>
       <x:c r="N462" s="46"/>
       <x:c r="O462" s="34"/>
+      <x:c r="P462" s="32"/>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="34"/>
@@ -8818,6 +9301,7 @@
       <x:c r="M463" s="46"/>
       <x:c r="N463" s="46"/>
       <x:c r="O463" s="34"/>
+      <x:c r="P463" s="32"/>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="34"/>
@@ -8835,6 +9319,7 @@
       <x:c r="M464" s="46"/>
       <x:c r="N464" s="46"/>
       <x:c r="O464" s="34"/>
+      <x:c r="P464" s="32"/>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="34"/>
@@ -8852,6 +9337,7 @@
       <x:c r="M465" s="46"/>
       <x:c r="N465" s="46"/>
       <x:c r="O465" s="34"/>
+      <x:c r="P465" s="32"/>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="34"/>
@@ -8869,6 +9355,7 @@
       <x:c r="M466" s="46"/>
       <x:c r="N466" s="46"/>
       <x:c r="O466" s="34"/>
+      <x:c r="P466" s="32"/>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="34"/>
@@ -8886,6 +9373,7 @@
       <x:c r="M467" s="46"/>
       <x:c r="N467" s="46"/>
       <x:c r="O467" s="34"/>
+      <x:c r="P467" s="32"/>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="34"/>
@@ -8903,6 +9391,7 @@
       <x:c r="M468" s="46"/>
       <x:c r="N468" s="46"/>
       <x:c r="O468" s="34"/>
+      <x:c r="P468" s="32"/>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="34"/>
@@ -8920,6 +9409,7 @@
       <x:c r="M469" s="46"/>
       <x:c r="N469" s="46"/>
       <x:c r="O469" s="34"/>
+      <x:c r="P469" s="32"/>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="34"/>
@@ -8937,6 +9427,7 @@
       <x:c r="M470" s="46"/>
       <x:c r="N470" s="46"/>
       <x:c r="O470" s="34"/>
+      <x:c r="P470" s="32"/>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="34"/>
@@ -8954,6 +9445,7 @@
       <x:c r="M471" s="46"/>
       <x:c r="N471" s="46"/>
       <x:c r="O471" s="34"/>
+      <x:c r="P471" s="32"/>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="34"/>
@@ -8971,6 +9463,7 @@
       <x:c r="M472" s="46"/>
       <x:c r="N472" s="46"/>
       <x:c r="O472" s="34"/>
+      <x:c r="P472" s="32"/>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="34"/>
@@ -8988,6 +9481,7 @@
       <x:c r="M473" s="46"/>
       <x:c r="N473" s="46"/>
       <x:c r="O473" s="34"/>
+      <x:c r="P473" s="32"/>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="34"/>
@@ -9005,6 +9499,7 @@
       <x:c r="M474" s="46"/>
       <x:c r="N474" s="46"/>
       <x:c r="O474" s="34"/>
+      <x:c r="P474" s="32"/>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="34"/>
@@ -9022,6 +9517,7 @@
       <x:c r="M475" s="46"/>
       <x:c r="N475" s="46"/>
       <x:c r="O475" s="34"/>
+      <x:c r="P475" s="32"/>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="34"/>
@@ -9039,6 +9535,7 @@
       <x:c r="M476" s="46"/>
       <x:c r="N476" s="46"/>
       <x:c r="O476" s="34"/>
+      <x:c r="P476" s="32"/>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="34"/>
@@ -9056,6 +9553,7 @@
       <x:c r="M477" s="46"/>
       <x:c r="N477" s="46"/>
       <x:c r="O477" s="34"/>
+      <x:c r="P477" s="32"/>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="34"/>
@@ -9073,6 +9571,7 @@
       <x:c r="M478" s="46"/>
       <x:c r="N478" s="46"/>
       <x:c r="O478" s="34"/>
+      <x:c r="P478" s="32"/>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="34"/>
@@ -9090,6 +9589,7 @@
       <x:c r="M479" s="46"/>
       <x:c r="N479" s="46"/>
       <x:c r="O479" s="34"/>
+      <x:c r="P479" s="32"/>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="34"/>
@@ -9107,6 +9607,7 @@
       <x:c r="M480" s="46"/>
       <x:c r="N480" s="46"/>
       <x:c r="O480" s="34"/>
+      <x:c r="P480" s="32"/>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="34"/>
@@ -9124,6 +9625,7 @@
       <x:c r="M481" s="46"/>
       <x:c r="N481" s="46"/>
       <x:c r="O481" s="34"/>
+      <x:c r="P481" s="32"/>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="34"/>
@@ -9141,6 +9643,7 @@
       <x:c r="M482" s="46"/>
       <x:c r="N482" s="46"/>
       <x:c r="O482" s="34"/>
+      <x:c r="P482" s="32"/>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="34"/>
@@ -9158,6 +9661,7 @@
       <x:c r="M483" s="46"/>
       <x:c r="N483" s="46"/>
       <x:c r="O483" s="34"/>
+      <x:c r="P483" s="32"/>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="34"/>
@@ -9175,6 +9679,7 @@
       <x:c r="M484" s="46"/>
       <x:c r="N484" s="46"/>
       <x:c r="O484" s="34"/>
+      <x:c r="P484" s="32"/>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="34"/>
@@ -9192,6 +9697,7 @@
       <x:c r="M485" s="46"/>
       <x:c r="N485" s="46"/>
       <x:c r="O485" s="34"/>
+      <x:c r="P485" s="32"/>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="34"/>
@@ -9209,6 +9715,7 @@
       <x:c r="M486" s="46"/>
       <x:c r="N486" s="46"/>
       <x:c r="O486" s="34"/>
+      <x:c r="P486" s="32"/>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="34"/>
@@ -9226,6 +9733,7 @@
       <x:c r="M487" s="46"/>
       <x:c r="N487" s="46"/>
       <x:c r="O487" s="34"/>
+      <x:c r="P487" s="32"/>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="34"/>
@@ -9243,6 +9751,7 @@
       <x:c r="M488" s="46"/>
       <x:c r="N488" s="46"/>
       <x:c r="O488" s="34"/>
+      <x:c r="P488" s="32"/>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="34"/>
@@ -9260,6 +9769,7 @@
       <x:c r="M489" s="46"/>
       <x:c r="N489" s="46"/>
       <x:c r="O489" s="34"/>
+      <x:c r="P489" s="32"/>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="34"/>
@@ -9277,6 +9787,7 @@
       <x:c r="M490" s="46"/>
       <x:c r="N490" s="46"/>
       <x:c r="O490" s="34"/>
+      <x:c r="P490" s="32"/>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="34"/>
@@ -9294,6 +9805,7 @@
       <x:c r="M491" s="46"/>
       <x:c r="N491" s="46"/>
       <x:c r="O491" s="34"/>
+      <x:c r="P491" s="32"/>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="34"/>
@@ -9311,6 +9823,7 @@
       <x:c r="M492" s="46"/>
       <x:c r="N492" s="46"/>
       <x:c r="O492" s="34"/>
+      <x:c r="P492" s="32"/>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="34"/>
@@ -9328,6 +9841,7 @@
       <x:c r="M493" s="46"/>
       <x:c r="N493" s="46"/>
       <x:c r="O493" s="34"/>
+      <x:c r="P493" s="32"/>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="34"/>
@@ -9345,6 +9859,7 @@
       <x:c r="M494" s="46"/>
       <x:c r="N494" s="46"/>
       <x:c r="O494" s="34"/>
+      <x:c r="P494" s="32"/>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="34"/>
@@ -9362,6 +9877,7 @@
       <x:c r="M495" s="46"/>
       <x:c r="N495" s="46"/>
       <x:c r="O495" s="34"/>
+      <x:c r="P495" s="32"/>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="34"/>
@@ -9379,6 +9895,7 @@
       <x:c r="M496" s="46"/>
       <x:c r="N496" s="46"/>
       <x:c r="O496" s="34"/>
+      <x:c r="P496" s="32"/>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="34"/>
@@ -9396,6 +9913,7 @@
       <x:c r="M497" s="46"/>
       <x:c r="N497" s="46"/>
       <x:c r="O497" s="34"/>
+      <x:c r="P497" s="32"/>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="34"/>
@@ -9413,6 +9931,7 @@
       <x:c r="M498" s="46"/>
       <x:c r="N498" s="46"/>
       <x:c r="O498" s="34"/>
+      <x:c r="P498" s="32"/>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="34"/>
@@ -9430,6 +9949,7 @@
       <x:c r="M499" s="46"/>
       <x:c r="N499" s="46"/>
       <x:c r="O499" s="34"/>
+      <x:c r="P499" s="32"/>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="34"/>
@@ -9447,6 +9967,7 @@
       <x:c r="M500" s="46"/>
       <x:c r="N500" s="46"/>
       <x:c r="O500" s="34"/>
+      <x:c r="P500" s="32"/>
     </x:row>
     <x:row r="501">
       <x:c r="A501" s="34"/>
@@ -9464,6 +9985,7 @@
       <x:c r="M501" s="46"/>
       <x:c r="N501" s="46"/>
       <x:c r="O501" s="34"/>
+      <x:c r="P501" s="32"/>
     </x:row>
     <x:row r="502">
       <x:c r="A502" s="34"/>
@@ -9481,6 +10003,7 @@
       <x:c r="M502" s="46"/>
       <x:c r="N502" s="46"/>
       <x:c r="O502" s="34"/>
+      <x:c r="P502" s="32"/>
     </x:row>
     <x:row r="503">
       <x:c r="A503" s="34"/>
@@ -9498,6 +10021,7 @@
       <x:c r="M503" s="46"/>
       <x:c r="N503" s="46"/>
       <x:c r="O503" s="34"/>
+      <x:c r="P503" s="32"/>
     </x:row>
     <x:row r="504">
       <x:c r="A504" s="34"/>
@@ -9515,6 +10039,7 @@
       <x:c r="M504" s="46"/>
       <x:c r="N504" s="46"/>
       <x:c r="O504" s="34"/>
+      <x:c r="P504" s="32"/>
     </x:row>
     <x:row r="505">
       <x:c r="A505" s="34"/>
@@ -9532,6 +10057,7 @@
       <x:c r="M505" s="46"/>
       <x:c r="N505" s="46"/>
       <x:c r="O505" s="34"/>
+      <x:c r="P505" s="32"/>
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="34"/>
@@ -9549,6 +10075,7 @@
       <x:c r="M506" s="46"/>
       <x:c r="N506" s="46"/>
       <x:c r="O506" s="34"/>
+      <x:c r="P506" s="32"/>
     </x:row>
     <x:row r="507">
       <x:c r="A507" s="34"/>
@@ -9566,6 +10093,7 @@
       <x:c r="M507" s="46"/>
       <x:c r="N507" s="46"/>
       <x:c r="O507" s="34"/>
+      <x:c r="P507" s="32"/>
     </x:row>
     <x:row r="508">
       <x:c r="A508" s="34"/>
@@ -9583,6 +10111,7 @@
       <x:c r="M508" s="46"/>
       <x:c r="N508" s="46"/>
       <x:c r="O508" s="34"/>
+      <x:c r="P508" s="32"/>
     </x:row>
     <x:row r="509">
       <x:c r="A509" s="34"/>
@@ -9600,6 +10129,7 @@
       <x:c r="M509" s="46"/>
       <x:c r="N509" s="46"/>
       <x:c r="O509" s="34"/>
+      <x:c r="P509" s="32"/>
     </x:row>
     <x:row r="510">
       <x:c r="A510" s="34"/>
@@ -9617,6 +10147,7 @@
       <x:c r="M510" s="46"/>
       <x:c r="N510" s="46"/>
       <x:c r="O510" s="34"/>
+      <x:c r="P510" s="32"/>
     </x:row>
     <x:row r="511">
       <x:c r="A511" s="34"/>
@@ -9634,6 +10165,7 @@
       <x:c r="M511" s="46"/>
       <x:c r="N511" s="46"/>
       <x:c r="O511" s="34"/>
+      <x:c r="P511" s="32"/>
     </x:row>
     <x:row r="512">
       <x:c r="A512" s="34"/>
@@ -9651,6 +10183,7 @@
       <x:c r="M512" s="46"/>
       <x:c r="N512" s="46"/>
       <x:c r="O512" s="34"/>
+      <x:c r="P512" s="32"/>
     </x:row>
     <x:row r="513">
       <x:c r="A513" s="34"/>
@@ -9668,6 +10201,7 @@
       <x:c r="M513" s="46"/>
       <x:c r="N513" s="46"/>
       <x:c r="O513" s="34"/>
+      <x:c r="P513" s="32"/>
     </x:row>
     <x:row r="514">
       <x:c r="A514" s="34"/>
@@ -9685,6 +10219,7 @@
       <x:c r="M514" s="46"/>
       <x:c r="N514" s="46"/>
       <x:c r="O514" s="34"/>
+      <x:c r="P514" s="32"/>
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="34"/>
@@ -9702,6 +10237,7 @@
       <x:c r="M515" s="46"/>
       <x:c r="N515" s="46"/>
       <x:c r="O515" s="34"/>
+      <x:c r="P515" s="32"/>
     </x:row>
     <x:row r="516">
       <x:c r="A516" s="34"/>
@@ -9719,6 +10255,7 @@
       <x:c r="M516" s="46"/>
       <x:c r="N516" s="46"/>
       <x:c r="O516" s="34"/>
+      <x:c r="P516" s="32"/>
     </x:row>
     <x:row r="517">
       <x:c r="A517" s="34"/>
@@ -9736,6 +10273,7 @@
       <x:c r="M517" s="46"/>
       <x:c r="N517" s="46"/>
       <x:c r="O517" s="34"/>
+      <x:c r="P517" s="32"/>
     </x:row>
     <x:row r="518">
       <x:c r="A518" s="34"/>
@@ -9753,6 +10291,7 @@
       <x:c r="M518" s="46"/>
       <x:c r="N518" s="46"/>
       <x:c r="O518" s="34"/>
+      <x:c r="P518" s="32"/>
     </x:row>
     <x:row r="519">
       <x:c r="A519" s="34"/>
@@ -9770,6 +10309,7 @@
       <x:c r="M519" s="46"/>
       <x:c r="N519" s="46"/>
       <x:c r="O519" s="34"/>
+      <x:c r="P519" s="32"/>
     </x:row>
     <x:row r="520">
       <x:c r="A520" s="34"/>
@@ -9787,6 +10327,7 @@
       <x:c r="M520" s="46"/>
       <x:c r="N520" s="46"/>
       <x:c r="O520" s="34"/>
+      <x:c r="P520" s="32"/>
     </x:row>
     <x:row r="521">
       <x:c r="A521" s="34"/>
@@ -9804,6 +10345,7 @@
       <x:c r="M521" s="46"/>
       <x:c r="N521" s="46"/>
       <x:c r="O521" s="34"/>
+      <x:c r="P521" s="32"/>
     </x:row>
     <x:row r="522">
       <x:c r="A522" s="34"/>
@@ -9821,6 +10363,7 @@
       <x:c r="M522" s="46"/>
       <x:c r="N522" s="46"/>
       <x:c r="O522" s="34"/>
+      <x:c r="P522" s="32"/>
     </x:row>
     <x:row r="523">
       <x:c r="A523" s="34"/>
@@ -9838,6 +10381,7 @@
       <x:c r="M523" s="46"/>
       <x:c r="N523" s="46"/>
       <x:c r="O523" s="34"/>
+      <x:c r="P523" s="32"/>
     </x:row>
     <x:row r="524">
       <x:c r="A524" s="34"/>
@@ -9855,6 +10399,7 @@
       <x:c r="M524" s="46"/>
       <x:c r="N524" s="46"/>
       <x:c r="O524" s="34"/>
+      <x:c r="P524" s="32"/>
     </x:row>
     <x:row r="525">
       <x:c r="A525" s="34"/>
@@ -9872,6 +10417,7 @@
       <x:c r="M525" s="46"/>
       <x:c r="N525" s="46"/>
       <x:c r="O525" s="34"/>
+      <x:c r="P525" s="32"/>
     </x:row>
     <x:row r="526">
       <x:c r="A526" s="34"/>
@@ -9889,6 +10435,7 @@
       <x:c r="M526" s="46"/>
       <x:c r="N526" s="46"/>
       <x:c r="O526" s="34"/>
+      <x:c r="P526" s="32"/>
     </x:row>
     <x:row r="527">
       <x:c r="A527" s="34"/>
@@ -9906,6 +10453,7 @@
       <x:c r="M527" s="46"/>
       <x:c r="N527" s="46"/>
       <x:c r="O527" s="34"/>
+      <x:c r="P527" s="32"/>
     </x:row>
     <x:row r="528">
       <x:c r="A528" s="34"/>
@@ -9923,6 +10471,7 @@
       <x:c r="M528" s="46"/>
       <x:c r="N528" s="46"/>
       <x:c r="O528" s="34"/>
+      <x:c r="P528" s="32"/>
     </x:row>
     <x:row r="529">
       <x:c r="A529" s="34"/>
@@ -9940,6 +10489,7 @@
       <x:c r="M529" s="46"/>
       <x:c r="N529" s="46"/>
       <x:c r="O529" s="34"/>
+      <x:c r="P529" s="32"/>
     </x:row>
     <x:row r="530">
       <x:c r="A530" s="34"/>
@@ -9957,6 +10507,7 @@
       <x:c r="M530" s="46"/>
       <x:c r="N530" s="46"/>
       <x:c r="O530" s="34"/>
+      <x:c r="P530" s="32"/>
     </x:row>
     <x:row r="531">
       <x:c r="A531" s="34"/>
@@ -9974,6 +10525,7 @@
       <x:c r="M531" s="46"/>
       <x:c r="N531" s="46"/>
       <x:c r="O531" s="34"/>
+      <x:c r="P531" s="32"/>
     </x:row>
     <x:row r="532">
       <x:c r="A532" s="34"/>
@@ -9991,6 +10543,7 @@
       <x:c r="M532" s="46"/>
       <x:c r="N532" s="46"/>
       <x:c r="O532" s="34"/>
+      <x:c r="P532" s="32"/>
     </x:row>
     <x:row r="533">
       <x:c r="A533" s="34"/>
@@ -10008,6 +10561,7 @@
       <x:c r="M533" s="46"/>
       <x:c r="N533" s="46"/>
       <x:c r="O533" s="34"/>
+      <x:c r="P533" s="32"/>
     </x:row>
     <x:row r="534">
       <x:c r="A534" s="34"/>
@@ -10025,6 +10579,7 @@
       <x:c r="M534" s="46"/>
       <x:c r="N534" s="46"/>
       <x:c r="O534" s="34"/>
+      <x:c r="P534" s="32"/>
     </x:row>
     <x:row r="535">
       <x:c r="A535" s="34"/>
@@ -10042,6 +10597,7 @@
       <x:c r="M535" s="46"/>
       <x:c r="N535" s="46"/>
       <x:c r="O535" s="34"/>
+      <x:c r="P535" s="32"/>
     </x:row>
     <x:row r="536">
       <x:c r="A536" s="34"/>
@@ -10059,6 +10615,7 @@
       <x:c r="M536" s="46"/>
       <x:c r="N536" s="46"/>
       <x:c r="O536" s="34"/>
+      <x:c r="P536" s="32"/>
     </x:row>
     <x:row r="537">
       <x:c r="A537" s="34"/>
@@ -10076,6 +10633,7 @@
       <x:c r="M537" s="46"/>
       <x:c r="N537" s="46"/>
       <x:c r="O537" s="34"/>
+      <x:c r="P537" s="32"/>
     </x:row>
     <x:row r="538">
       <x:c r="A538" s="34"/>
@@ -10093,6 +10651,7 @@
       <x:c r="M538" s="46"/>
       <x:c r="N538" s="46"/>
       <x:c r="O538" s="34"/>
+      <x:c r="P538" s="32"/>
     </x:row>
     <x:row r="539">
       <x:c r="A539" s="34"/>
@@ -10110,6 +10669,7 @@
       <x:c r="M539" s="46"/>
       <x:c r="N539" s="46"/>
       <x:c r="O539" s="34"/>
+      <x:c r="P539" s="32"/>
     </x:row>
     <x:row r="540">
       <x:c r="A540" s="34"/>
@@ -10127,6 +10687,7 @@
       <x:c r="M540" s="46"/>
       <x:c r="N540" s="46"/>
       <x:c r="O540" s="34"/>
+      <x:c r="P540" s="32"/>
     </x:row>
     <x:row r="541">
       <x:c r="A541" s="34"/>
@@ -10144,6 +10705,7 @@
       <x:c r="M541" s="46"/>
       <x:c r="N541" s="46"/>
       <x:c r="O541" s="34"/>
+      <x:c r="P541" s="32"/>
     </x:row>
     <x:row r="542">
       <x:c r="A542" s="34"/>
@@ -10161,6 +10723,7 @@
       <x:c r="M542" s="46"/>
       <x:c r="N542" s="46"/>
       <x:c r="O542" s="34"/>
+      <x:c r="P542" s="32"/>
     </x:row>
     <x:row r="543">
       <x:c r="A543" s="34"/>
@@ -10178,6 +10741,7 @@
       <x:c r="M543" s="46"/>
       <x:c r="N543" s="46"/>
       <x:c r="O543" s="34"/>
+      <x:c r="P543" s="32"/>
     </x:row>
     <x:row r="544">
       <x:c r="A544" s="34"/>
@@ -10195,6 +10759,7 @@
       <x:c r="M544" s="46"/>
       <x:c r="N544" s="46"/>
       <x:c r="O544" s="34"/>
+      <x:c r="P544" s="32"/>
     </x:row>
     <x:row r="545">
       <x:c r="A545" s="34"/>
@@ -10212,6 +10777,7 @@
       <x:c r="M545" s="46"/>
       <x:c r="N545" s="46"/>
       <x:c r="O545" s="34"/>
+      <x:c r="P545" s="32"/>
     </x:row>
     <x:row r="546">
       <x:c r="A546" s="34"/>
@@ -10229,6 +10795,7 @@
       <x:c r="M546" s="46"/>
       <x:c r="N546" s="46"/>
       <x:c r="O546" s="34"/>
+      <x:c r="P546" s="32"/>
     </x:row>
     <x:row r="547">
       <x:c r="A547" s="34"/>
@@ -10246,6 +10813,7 @@
       <x:c r="M547" s="46"/>
       <x:c r="N547" s="46"/>
       <x:c r="O547" s="34"/>
+      <x:c r="P547" s="32"/>
     </x:row>
     <x:row r="548">
       <x:c r="A548" s="34"/>
@@ -10263,6 +10831,7 @@
       <x:c r="M548" s="46"/>
       <x:c r="N548" s="46"/>
       <x:c r="O548" s="34"/>
+      <x:c r="P548" s="32"/>
     </x:row>
     <x:row r="549">
       <x:c r="A549" s="34"/>
@@ -10280,6 +10849,7 @@
       <x:c r="M549" s="46"/>
       <x:c r="N549" s="46"/>
       <x:c r="O549" s="34"/>
+      <x:c r="P549" s="32"/>
     </x:row>
     <x:row r="550">
       <x:c r="A550" s="34"/>
@@ -10297,6 +10867,7 @@
       <x:c r="M550" s="46"/>
       <x:c r="N550" s="46"/>
       <x:c r="O550" s="34"/>
+      <x:c r="P550" s="32"/>
     </x:row>
     <x:row r="551">
       <x:c r="A551" s="34"/>
@@ -10314,6 +10885,7 @@
       <x:c r="M551" s="46"/>
       <x:c r="N551" s="46"/>
       <x:c r="O551" s="34"/>
+      <x:c r="P551" s="32"/>
     </x:row>
     <x:row r="552">
       <x:c r="A552" s="34"/>
@@ -10331,6 +10903,7 @@
       <x:c r="M552" s="46"/>
       <x:c r="N552" s="46"/>
       <x:c r="O552" s="34"/>
+      <x:c r="P552" s="32"/>
     </x:row>
     <x:row r="553">
       <x:c r="A553" s="34"/>
@@ -10348,6 +10921,7 @@
       <x:c r="M553" s="46"/>
       <x:c r="N553" s="46"/>
       <x:c r="O553" s="34"/>
+      <x:c r="P553" s="32"/>
     </x:row>
     <x:row r="554">
       <x:c r="A554" s="34"/>
@@ -10365,6 +10939,7 @@
       <x:c r="M554" s="46"/>
       <x:c r="N554" s="46"/>
       <x:c r="O554" s="34"/>
+      <x:c r="P554" s="32"/>
     </x:row>
     <x:row r="555">
       <x:c r="A555" s="34"/>
@@ -10382,6 +10957,7 @@
       <x:c r="M555" s="46"/>
       <x:c r="N555" s="46"/>
       <x:c r="O555" s="34"/>
+      <x:c r="P555" s="32"/>
     </x:row>
     <x:row r="556">
       <x:c r="A556" s="34"/>
@@ -10399,6 +10975,7 @@
       <x:c r="M556" s="46"/>
       <x:c r="N556" s="46"/>
       <x:c r="O556" s="34"/>
+      <x:c r="P556" s="32"/>
     </x:row>
     <x:row r="557">
       <x:c r="A557" s="34"/>
@@ -10416,6 +10993,7 @@
       <x:c r="M557" s="46"/>
       <x:c r="N557" s="46"/>
       <x:c r="O557" s="34"/>
+      <x:c r="P557" s="32"/>
     </x:row>
     <x:row r="558">
       <x:c r="A558" s="34"/>
@@ -10433,6 +11011,7 @@
       <x:c r="M558" s="46"/>
       <x:c r="N558" s="46"/>
       <x:c r="O558" s="34"/>
+      <x:c r="P558" s="32"/>
     </x:row>
     <x:row r="559">
       <x:c r="A559" s="34"/>
@@ -10450,6 +11029,7 @@
       <x:c r="M559" s="46"/>
       <x:c r="N559" s="46"/>
       <x:c r="O559" s="34"/>
+      <x:c r="P559" s="32"/>
     </x:row>
     <x:row r="560">
       <x:c r="A560" s="34"/>
@@ -10467,6 +11047,7 @@
       <x:c r="M560" s="46"/>
       <x:c r="N560" s="46"/>
       <x:c r="O560" s="34"/>
+      <x:c r="P560" s="32"/>
     </x:row>
     <x:row r="561">
       <x:c r="A561" s="34"/>
@@ -10484,6 +11065,7 @@
       <x:c r="M561" s="46"/>
       <x:c r="N561" s="46"/>
       <x:c r="O561" s="34"/>
+      <x:c r="P561" s="32"/>
     </x:row>
     <x:row r="562">
       <x:c r="A562" s="34"/>
@@ -10501,6 +11083,7 @@
       <x:c r="M562" s="46"/>
       <x:c r="N562" s="46"/>
       <x:c r="O562" s="34"/>
+      <x:c r="P562" s="32"/>
     </x:row>
     <x:row r="563">
       <x:c r="A563" s="34"/>
@@ -10518,6 +11101,7 @@
       <x:c r="M563" s="46"/>
       <x:c r="N563" s="46"/>
       <x:c r="O563" s="34"/>
+      <x:c r="P563" s="32"/>
     </x:row>
     <x:row r="564">
       <x:c r="A564" s="34"/>
@@ -10535,6 +11119,7 @@
       <x:c r="M564" s="46"/>
       <x:c r="N564" s="46"/>
       <x:c r="O564" s="34"/>
+      <x:c r="P564" s="32"/>
     </x:row>
     <x:row r="565">
       <x:c r="A565" s="34"/>
@@ -10552,6 +11137,7 @@
       <x:c r="M565" s="46"/>
       <x:c r="N565" s="46"/>
       <x:c r="O565" s="34"/>
+      <x:c r="P565" s="32"/>
     </x:row>
     <x:row r="566">
       <x:c r="A566" s="34"/>
@@ -10569,6 +11155,7 @@
       <x:c r="M566" s="46"/>
       <x:c r="N566" s="46"/>
       <x:c r="O566" s="34"/>
+      <x:c r="P566" s="32"/>
     </x:row>
     <x:row r="567">
       <x:c r="A567" s="34"/>
@@ -10586,6 +11173,7 @@
       <x:c r="M567" s="46"/>
       <x:c r="N567" s="46"/>
       <x:c r="O567" s="34"/>
+      <x:c r="P567" s="32"/>
     </x:row>
     <x:row r="568">
       <x:c r="A568" s="34"/>
@@ -10603,6 +11191,7 @@
       <x:c r="M568" s="46"/>
       <x:c r="N568" s="46"/>
       <x:c r="O568" s="34"/>
+      <x:c r="P568" s="32"/>
     </x:row>
     <x:row r="569">
       <x:c r="A569" s="34"/>
@@ -10620,6 +11209,7 @@
       <x:c r="M569" s="46"/>
       <x:c r="N569" s="46"/>
       <x:c r="O569" s="34"/>
+      <x:c r="P569" s="32"/>
     </x:row>
     <x:row r="570">
       <x:c r="A570" s="34"/>
@@ -10637,6 +11227,7 @@
       <x:c r="M570" s="46"/>
       <x:c r="N570" s="46"/>
       <x:c r="O570" s="34"/>
+      <x:c r="P570" s="32"/>
     </x:row>
     <x:row r="571">
       <x:c r="A571" s="34"/>
@@ -10654,6 +11245,7 @@
       <x:c r="M571" s="46"/>
       <x:c r="N571" s="46"/>
       <x:c r="O571" s="34"/>
+      <x:c r="P571" s="32"/>
     </x:row>
     <x:row r="572">
       <x:c r="A572" s="34"/>
@@ -10671,6 +11263,7 @@
       <x:c r="M572" s="46"/>
       <x:c r="N572" s="46"/>
       <x:c r="O572" s="34"/>
+      <x:c r="P572" s="32"/>
     </x:row>
     <x:row r="573">
       <x:c r="A573" s="34"/>
@@ -10688,6 +11281,7 @@
       <x:c r="M573" s="46"/>
       <x:c r="N573" s="46"/>
       <x:c r="O573" s="34"/>
+      <x:c r="P573" s="32"/>
     </x:row>
     <x:row r="574">
       <x:c r="A574" s="34"/>
@@ -10705,6 +11299,7 @@
       <x:c r="M574" s="46"/>
       <x:c r="N574" s="46"/>
       <x:c r="O574" s="34"/>
+      <x:c r="P574" s="32"/>
     </x:row>
     <x:row r="575">
       <x:c r="A575" s="34"/>
@@ -10722,6 +11317,7 @@
       <x:c r="M575" s="46"/>
       <x:c r="N575" s="46"/>
       <x:c r="O575" s="34"/>
+      <x:c r="P575" s="32"/>
     </x:row>
     <x:row r="576">
       <x:c r="A576" s="34"/>
@@ -10739,6 +11335,7 @@
       <x:c r="M576" s="46"/>
       <x:c r="N576" s="46"/>
       <x:c r="O576" s="34"/>
+      <x:c r="P576" s="32"/>
     </x:row>
     <x:row r="577">
       <x:c r="A577" s="34"/>
@@ -10756,6 +11353,7 @@
       <x:c r="M577" s="46"/>
       <x:c r="N577" s="46"/>
       <x:c r="O577" s="34"/>
+      <x:c r="P577" s="32"/>
     </x:row>
     <x:row r="578">
       <x:c r="A578" s="34"/>
@@ -10773,6 +11371,7 @@
       <x:c r="M578" s="46"/>
       <x:c r="N578" s="46"/>
       <x:c r="O578" s="34"/>
+      <x:c r="P578" s="32"/>
     </x:row>
     <x:row r="579">
       <x:c r="A579" s="34"/>
@@ -10790,6 +11389,7 @@
       <x:c r="M579" s="46"/>
       <x:c r="N579" s="46"/>
       <x:c r="O579" s="34"/>
+      <x:c r="P579" s="32"/>
     </x:row>
     <x:row r="580">
       <x:c r="A580" s="34"/>
@@ -10807,6 +11407,7 @@
       <x:c r="M580" s="46"/>
       <x:c r="N580" s="46"/>
       <x:c r="O580" s="34"/>
+      <x:c r="P580" s="32"/>
     </x:row>
     <x:row r="581">
       <x:c r="A581" s="34"/>
@@ -10824,6 +11425,7 @@
       <x:c r="M581" s="46"/>
       <x:c r="N581" s="46"/>
       <x:c r="O581" s="34"/>
+      <x:c r="P581" s="32"/>
     </x:row>
     <x:row r="582">
       <x:c r="A582" s="34"/>
@@ -10841,6 +11443,7 @@
       <x:c r="M582" s="46"/>
       <x:c r="N582" s="46"/>
       <x:c r="O582" s="34"/>
+      <x:c r="P582" s="32"/>
     </x:row>
     <x:row r="583">
       <x:c r="A583" s="34"/>
@@ -10858,6 +11461,7 @@
       <x:c r="M583" s="46"/>
       <x:c r="N583" s="46"/>
       <x:c r="O583" s="34"/>
+      <x:c r="P583" s="32"/>
     </x:row>
     <x:row r="584">
       <x:c r="A584" s="34"/>
@@ -10875,6 +11479,7 @@
       <x:c r="M584" s="46"/>
       <x:c r="N584" s="46"/>
       <x:c r="O584" s="34"/>
+      <x:c r="P584" s="32"/>
     </x:row>
     <x:row r="585">
       <x:c r="A585" s="34"/>
@@ -10892,6 +11497,7 @@
       <x:c r="M585" s="46"/>
       <x:c r="N585" s="46"/>
       <x:c r="O585" s="34"/>
+      <x:c r="P585" s="32"/>
     </x:row>
     <x:row r="586">
       <x:c r="A586" s="34"/>
@@ -10909,6 +11515,7 @@
       <x:c r="M586" s="46"/>
       <x:c r="N586" s="46"/>
       <x:c r="O586" s="34"/>
+      <x:c r="P586" s="32"/>
     </x:row>
     <x:row r="587">
       <x:c r="A587" s="34"/>
@@ -10926,6 +11533,7 @@
       <x:c r="M587" s="46"/>
       <x:c r="N587" s="46"/>
       <x:c r="O587" s="34"/>
+      <x:c r="P587" s="32"/>
     </x:row>
     <x:row r="588">
       <x:c r="A588" s="34"/>
@@ -10943,6 +11551,7 @@
       <x:c r="M588" s="46"/>
       <x:c r="N588" s="46"/>
       <x:c r="O588" s="34"/>
+      <x:c r="P588" s="32"/>
     </x:row>
     <x:row r="589">
       <x:c r="A589" s="34"/>
@@ -10960,6 +11569,7 @@
       <x:c r="M589" s="46"/>
       <x:c r="N589" s="46"/>
       <x:c r="O589" s="34"/>
+      <x:c r="P589" s="32"/>
     </x:row>
     <x:row r="590">
       <x:c r="A590" s="34"/>
@@ -10977,6 +11587,7 @@
       <x:c r="M590" s="46"/>
       <x:c r="N590" s="46"/>
       <x:c r="O590" s="34"/>
+      <x:c r="P590" s="32"/>
     </x:row>
     <x:row r="591">
       <x:c r="A591" s="34"/>
@@ -10994,6 +11605,7 @@
       <x:c r="M591" s="46"/>
       <x:c r="N591" s="46"/>
       <x:c r="O591" s="34"/>
+      <x:c r="P591" s="32"/>
     </x:row>
     <x:row r="592">
       <x:c r="A592" s="34"/>
@@ -11011,6 +11623,7 @@
       <x:c r="M592" s="46"/>
       <x:c r="N592" s="46"/>
       <x:c r="O592" s="34"/>
+      <x:c r="P592" s="32"/>
     </x:row>
     <x:row r="593">
       <x:c r="A593" s="34"/>
@@ -11028,6 +11641,7 @@
       <x:c r="M593" s="46"/>
       <x:c r="N593" s="46"/>
       <x:c r="O593" s="34"/>
+      <x:c r="P593" s="32"/>
     </x:row>
     <x:row r="594">
       <x:c r="A594" s="34"/>
@@ -11045,6 +11659,7 @@
       <x:c r="M594" s="46"/>
       <x:c r="N594" s="46"/>
       <x:c r="O594" s="34"/>
+      <x:c r="P594" s="32"/>
     </x:row>
     <x:row r="595">
       <x:c r="A595" s="34"/>
@@ -11062,6 +11677,7 @@
       <x:c r="M595" s="46"/>
       <x:c r="N595" s="46"/>
       <x:c r="O595" s="34"/>
+      <x:c r="P595" s="32"/>
     </x:row>
     <x:row r="596">
       <x:c r="A596" s="34"/>
@@ -11079,6 +11695,7 @@
       <x:c r="M596" s="46"/>
       <x:c r="N596" s="46"/>
       <x:c r="O596" s="34"/>
+      <x:c r="P596" s="32"/>
     </x:row>
     <x:row r="597">
       <x:c r="A597" s="34"/>
@@ -11096,6 +11713,7 @@
       <x:c r="M597" s="46"/>
       <x:c r="N597" s="46"/>
       <x:c r="O597" s="34"/>
+      <x:c r="P597" s="32"/>
     </x:row>
     <x:row r="598">
       <x:c r="A598" s="34"/>
@@ -11113,6 +11731,7 @@
       <x:c r="M598" s="46"/>
       <x:c r="N598" s="46"/>
       <x:c r="O598" s="34"/>
+      <x:c r="P598" s="32"/>
     </x:row>
     <x:row r="599">
       <x:c r="A599" s="34"/>
@@ -11130,6 +11749,7 @@
       <x:c r="M599" s="46"/>
       <x:c r="N599" s="46"/>
       <x:c r="O599" s="34"/>
+      <x:c r="P599" s="32"/>
     </x:row>
     <x:row r="600">
       <x:c r="A600" s="34"/>
@@ -11147,6 +11767,7 @@
       <x:c r="M600" s="46"/>
       <x:c r="N600" s="46"/>
       <x:c r="O600" s="34"/>
+      <x:c r="P600" s="32"/>
     </x:row>
     <x:row r="601">
       <x:c r="A601" s="34"/>
@@ -11164,6 +11785,7 @@
       <x:c r="M601" s="46"/>
       <x:c r="N601" s="46"/>
       <x:c r="O601" s="34"/>
+      <x:c r="P601" s="32"/>
     </x:row>
     <x:row r="602">
       <x:c r="A602" s="34"/>
@@ -11181,6 +11803,7 @@
       <x:c r="M602" s="46"/>
       <x:c r="N602" s="46"/>
       <x:c r="O602" s="34"/>
+      <x:c r="P602" s="32"/>
     </x:row>
     <x:row r="603">
       <x:c r="A603" s="34"/>
@@ -11198,6 +11821,7 @@
       <x:c r="M603" s="46"/>
       <x:c r="N603" s="46"/>
       <x:c r="O603" s="34"/>
+      <x:c r="P603" s="32"/>
     </x:row>
     <x:row r="604">
       <x:c r="A604" s="34"/>
@@ -11215,6 +11839,7 @@
       <x:c r="M604" s="46"/>
       <x:c r="N604" s="46"/>
       <x:c r="O604" s="34"/>
+      <x:c r="P604" s="32"/>
     </x:row>
     <x:row r="605">
       <x:c r="A605" s="34"/>
@@ -11232,6 +11857,7 @@
       <x:c r="M605" s="46"/>
       <x:c r="N605" s="46"/>
       <x:c r="O605" s="34"/>
+      <x:c r="P605" s="32"/>
     </x:row>
     <x:row r="606">
       <x:c r="A606" s="34"/>
@@ -11249,6 +11875,7 @@
       <x:c r="M606" s="46"/>
       <x:c r="N606" s="46"/>
       <x:c r="O606" s="34"/>
+      <x:c r="P606" s="32"/>
     </x:row>
     <x:row r="607">
       <x:c r="A607" s="34"/>
@@ -11266,6 +11893,7 @@
       <x:c r="M607" s="46"/>
       <x:c r="N607" s="46"/>
       <x:c r="O607" s="34"/>
+      <x:c r="P607" s="32"/>
     </x:row>
     <x:row r="608">
       <x:c r="A608" s="34"/>
@@ -11283,6 +11911,7 @@
       <x:c r="M608" s="46"/>
       <x:c r="N608" s="46"/>
       <x:c r="O608" s="34"/>
+      <x:c r="P608" s="32"/>
     </x:row>
     <x:row r="609">
       <x:c r="A609" s="34"/>
@@ -11300,6 +11929,7 @@
       <x:c r="M609" s="46"/>
       <x:c r="N609" s="46"/>
       <x:c r="O609" s="34"/>
+      <x:c r="P609" s="32"/>
     </x:row>
     <x:row r="610">
       <x:c r="A610" s="34"/>
@@ -11317,6 +11947,7 @@
       <x:c r="M610" s="46"/>
       <x:c r="N610" s="46"/>
       <x:c r="O610" s="34"/>
+      <x:c r="P610" s="32"/>
     </x:row>
     <x:row r="611">
       <x:c r="A611" s="34"/>
@@ -11334,6 +11965,7 @@
       <x:c r="M611" s="46"/>
       <x:c r="N611" s="46"/>
       <x:c r="O611" s="34"/>
+      <x:c r="P611" s="32"/>
     </x:row>
     <x:row r="612">
       <x:c r="A612" s="34"/>
@@ -11351,6 +11983,7 @@
       <x:c r="M612" s="46"/>
       <x:c r="N612" s="46"/>
       <x:c r="O612" s="34"/>
+      <x:c r="P612" s="32"/>
     </x:row>
     <x:row r="613">
       <x:c r="A613" s="34"/>
@@ -11368,6 +12001,7 @@
       <x:c r="M613" s="46"/>
       <x:c r="N613" s="46"/>
       <x:c r="O613" s="34"/>
+      <x:c r="P613" s="32"/>
     </x:row>
     <x:row r="614">
       <x:c r="A614" s="34"/>
@@ -11385,6 +12019,7 @@
       <x:c r="M614" s="46"/>
       <x:c r="N614" s="46"/>
       <x:c r="O614" s="34"/>
+      <x:c r="P614" s="32"/>
     </x:row>
     <x:row r="615">
       <x:c r="A615" s="34"/>
@@ -11402,6 +12037,7 @@
       <x:c r="M615" s="46"/>
       <x:c r="N615" s="46"/>
       <x:c r="O615" s="34"/>
+      <x:c r="P615" s="32"/>
     </x:row>
     <x:row r="616">
       <x:c r="A616" s="34"/>
@@ -11419,6 +12055,7 @@
       <x:c r="M616" s="46"/>
       <x:c r="N616" s="46"/>
       <x:c r="O616" s="34"/>
+      <x:c r="P616" s="32"/>
     </x:row>
     <x:row r="617">
       <x:c r="A617" s="34"/>
@@ -11436,6 +12073,7 @@
       <x:c r="M617" s="46"/>
       <x:c r="N617" s="46"/>
       <x:c r="O617" s="34"/>
+      <x:c r="P617" s="32"/>
     </x:row>
     <x:row r="618">
       <x:c r="A618" s="34"/>
@@ -11453,6 +12091,7 @@
       <x:c r="M618" s="46"/>
       <x:c r="N618" s="46"/>
       <x:c r="O618" s="34"/>
+      <x:c r="P618" s="32"/>
     </x:row>
     <x:row r="619">
       <x:c r="A619" s="34"/>
@@ -11470,6 +12109,7 @@
       <x:c r="M619" s="46"/>
       <x:c r="N619" s="46"/>
       <x:c r="O619" s="34"/>
+      <x:c r="P619" s="32"/>
     </x:row>
     <x:row r="620">
       <x:c r="A620" s="34"/>
@@ -11487,6 +12127,7 @@
       <x:c r="M620" s="46"/>
       <x:c r="N620" s="46"/>
       <x:c r="O620" s="34"/>
+      <x:c r="P620" s="32"/>
     </x:row>
     <x:row r="621">
       <x:c r="A621" s="34"/>
@@ -11504,6 +12145,7 @@
       <x:c r="M621" s="46"/>
       <x:c r="N621" s="46"/>
       <x:c r="O621" s="34"/>
+      <x:c r="P621" s="32"/>
     </x:row>
     <x:row r="622">
       <x:c r="A622" s="34"/>
@@ -11521,6 +12163,7 @@
       <x:c r="M622" s="46"/>
       <x:c r="N622" s="46"/>
       <x:c r="O622" s="34"/>
+      <x:c r="P622" s="32"/>
     </x:row>
     <x:row r="623">
       <x:c r="A623" s="34"/>
@@ -11538,6 +12181,7 @@
       <x:c r="M623" s="46"/>
       <x:c r="N623" s="46"/>
       <x:c r="O623" s="34"/>
+      <x:c r="P623" s="32"/>
     </x:row>
     <x:row r="624">
       <x:c r="A624" s="34"/>
@@ -11555,6 +12199,7 @@
       <x:c r="M624" s="46"/>
       <x:c r="N624" s="46"/>
       <x:c r="O624" s="34"/>
+      <x:c r="P624" s="32"/>
     </x:row>
     <x:row r="625">
       <x:c r="A625" s="34"/>
@@ -11572,6 +12217,7 @@
       <x:c r="M625" s="46"/>
       <x:c r="N625" s="46"/>
       <x:c r="O625" s="34"/>
+      <x:c r="P625" s="32"/>
     </x:row>
     <x:row r="626">
       <x:c r="A626" s="34"/>
@@ -11589,6 +12235,7 @@
       <x:c r="M626" s="46"/>
       <x:c r="N626" s="46"/>
       <x:c r="O626" s="34"/>
+      <x:c r="P626" s="32"/>
     </x:row>
     <x:row r="627">
       <x:c r="A627" s="34"/>
@@ -11606,6 +12253,7 @@
       <x:c r="M627" s="46"/>
       <x:c r="N627" s="46"/>
       <x:c r="O627" s="34"/>
+      <x:c r="P627" s="32"/>
     </x:row>
     <x:row r="628">
       <x:c r="A628" s="34"/>
@@ -11623,6 +12271,7 @@
       <x:c r="M628" s="46"/>
       <x:c r="N628" s="46"/>
       <x:c r="O628" s="34"/>
+      <x:c r="P628" s="32"/>
     </x:row>
     <x:row r="629">
       <x:c r="A629" s="34"/>
@@ -11640,6 +12289,7 @@
       <x:c r="M629" s="46"/>
       <x:c r="N629" s="46"/>
       <x:c r="O629" s="34"/>
+      <x:c r="P629" s="32"/>
     </x:row>
     <x:row r="630">
       <x:c r="A630" s="34"/>
@@ -11657,6 +12307,7 @@
       <x:c r="M630" s="46"/>
       <x:c r="N630" s="46"/>
       <x:c r="O630" s="34"/>
+      <x:c r="P630" s="32"/>
     </x:row>
     <x:row r="631">
       <x:c r="A631" s="34"/>
@@ -11674,6 +12325,7 @@
       <x:c r="M631" s="46"/>
       <x:c r="N631" s="46"/>
       <x:c r="O631" s="34"/>
+      <x:c r="P631" s="32"/>
     </x:row>
     <x:row r="632">
       <x:c r="A632" s="34"/>
@@ -11691,6 +12343,7 @@
       <x:c r="M632" s="46"/>
       <x:c r="N632" s="46"/>
       <x:c r="O632" s="34"/>
+      <x:c r="P632" s="32"/>
     </x:row>
     <x:row r="633">
       <x:c r="A633" s="34"/>
@@ -11708,6 +12361,7 @@
       <x:c r="M633" s="46"/>
       <x:c r="N633" s="46"/>
       <x:c r="O633" s="34"/>
+      <x:c r="P633" s="32"/>
     </x:row>
     <x:row r="634">
       <x:c r="A634" s="34"/>
@@ -11725,6 +12379,7 @@
       <x:c r="M634" s="46"/>
       <x:c r="N634" s="46"/>
       <x:c r="O634" s="34"/>
+      <x:c r="P634" s="32"/>
     </x:row>
     <x:row r="635">
       <x:c r="A635" s="34"/>
@@ -11742,6 +12397,7 @@
       <x:c r="M635" s="46"/>
       <x:c r="N635" s="46"/>
       <x:c r="O635" s="34"/>
+      <x:c r="P635" s="32"/>
     </x:row>
     <x:row r="636">
       <x:c r="A636" s="34"/>
@@ -11759,6 +12415,7 @@
       <x:c r="M636" s="46"/>
       <x:c r="N636" s="46"/>
       <x:c r="O636" s="34"/>
+      <x:c r="P636" s="32"/>
     </x:row>
     <x:row r="637">
       <x:c r="A637" s="34"/>
@@ -11776,6 +12433,7 @@
       <x:c r="M637" s="46"/>
       <x:c r="N637" s="46"/>
       <x:c r="O637" s="34"/>
+      <x:c r="P637" s="32"/>
     </x:row>
     <x:row r="638">
       <x:c r="A638" s="34"/>
@@ -11793,6 +12451,7 @@
       <x:c r="M638" s="46"/>
       <x:c r="N638" s="46"/>
       <x:c r="O638" s="34"/>
+      <x:c r="P638" s="32"/>
     </x:row>
     <x:row r="639">
       <x:c r="A639" s="34"/>
@@ -11810,6 +12469,7 @@
       <x:c r="M639" s="46"/>
       <x:c r="N639" s="46"/>
       <x:c r="O639" s="34"/>
+      <x:c r="P639" s="32"/>
     </x:row>
     <x:row r="640">
       <x:c r="A640" s="34"/>
@@ -11827,6 +12487,7 @@
       <x:c r="M640" s="46"/>
       <x:c r="N640" s="46"/>
       <x:c r="O640" s="34"/>
+      <x:c r="P640" s="32"/>
     </x:row>
     <x:row r="641">
       <x:c r="A641" s="34"/>
@@ -11844,6 +12505,7 @@
       <x:c r="M641" s="46"/>
       <x:c r="N641" s="46"/>
       <x:c r="O641" s="34"/>
+      <x:c r="P641" s="32"/>
     </x:row>
     <x:row r="642">
       <x:c r="A642" s="34"/>
@@ -11861,6 +12523,7 @@
       <x:c r="M642" s="46"/>
       <x:c r="N642" s="46"/>
       <x:c r="O642" s="34"/>
+      <x:c r="P642" s="32"/>
     </x:row>
     <x:row r="643">
       <x:c r="A643" s="34"/>
@@ -11878,6 +12541,7 @@
       <x:c r="M643" s="46"/>
       <x:c r="N643" s="46"/>
       <x:c r="O643" s="34"/>
+      <x:c r="P643" s="32"/>
     </x:row>
     <x:row r="644">
       <x:c r="A644" s="34"/>
@@ -11895,6 +12559,7 @@
       <x:c r="M644" s="46"/>
       <x:c r="N644" s="46"/>
       <x:c r="O644" s="34"/>
+      <x:c r="P644" s="32"/>
     </x:row>
     <x:row r="645">
       <x:c r="A645" s="34"/>
@@ -11912,6 +12577,7 @@
       <x:c r="M645" s="46"/>
       <x:c r="N645" s="46"/>
       <x:c r="O645" s="34"/>
+      <x:c r="P645" s="32"/>
     </x:row>
     <x:row r="646">
       <x:c r="A646" s="34"/>
@@ -11929,6 +12595,7 @@
       <x:c r="M646" s="46"/>
       <x:c r="N646" s="46"/>
       <x:c r="O646" s="34"/>
+      <x:c r="P646" s="32"/>
     </x:row>
     <x:row r="647">
       <x:c r="A647" s="34"/>
@@ -11946,6 +12613,7 @@
       <x:c r="M647" s="46"/>
       <x:c r="N647" s="46"/>
       <x:c r="O647" s="34"/>
+      <x:c r="P647" s="32"/>
     </x:row>
     <x:row r="648">
       <x:c r="A648" s="34"/>
@@ -11963,6 +12631,7 @@
       <x:c r="M648" s="46"/>
       <x:c r="N648" s="46"/>
       <x:c r="O648" s="34"/>
+      <x:c r="P648" s="32"/>
     </x:row>
     <x:row r="649">
       <x:c r="A649" s="34"/>
@@ -11980,6 +12649,7 @@
       <x:c r="M649" s="46"/>
       <x:c r="N649" s="46"/>
       <x:c r="O649" s="34"/>
+      <x:c r="P649" s="32"/>
     </x:row>
     <x:row r="650">
       <x:c r="A650" s="34"/>
@@ -11997,6 +12667,7 @@
       <x:c r="M650" s="46"/>
       <x:c r="N650" s="46"/>
       <x:c r="O650" s="34"/>
+      <x:c r="P650" s="32"/>
     </x:row>
     <x:row r="651">
       <x:c r="A651" s="34"/>
@@ -12014,6 +12685,7 @@
       <x:c r="M651" s="46"/>
       <x:c r="N651" s="46"/>
       <x:c r="O651" s="34"/>
+      <x:c r="P651" s="32"/>
     </x:row>
     <x:row r="652">
       <x:c r="A652" s="34"/>
@@ -12031,6 +12703,7 @@
       <x:c r="M652" s="46"/>
       <x:c r="N652" s="46"/>
       <x:c r="O652" s="34"/>
+      <x:c r="P652" s="32"/>
     </x:row>
     <x:row r="653">
       <x:c r="A653" s="34"/>
@@ -12048,6 +12721,7 @@
       <x:c r="M653" s="46"/>
       <x:c r="N653" s="46"/>
       <x:c r="O653" s="34"/>
+      <x:c r="P653" s="32"/>
     </x:row>
     <x:row r="654">
       <x:c r="A654" s="34"/>
@@ -12065,6 +12739,7 @@
       <x:c r="M654" s="46"/>
       <x:c r="N654" s="46"/>
       <x:c r="O654" s="34"/>
+      <x:c r="P654" s="32"/>
     </x:row>
     <x:row r="655">
       <x:c r="A655" s="34"/>
@@ -12082,6 +12757,7 @@
       <x:c r="M655" s="46"/>
       <x:c r="N655" s="46"/>
       <x:c r="O655" s="34"/>
+      <x:c r="P655" s="32"/>
     </x:row>
     <x:row r="656">
       <x:c r="A656" s="34"/>
@@ -12099,6 +12775,7 @@
       <x:c r="M656" s="46"/>
       <x:c r="N656" s="46"/>
       <x:c r="O656" s="34"/>
+      <x:c r="P656" s="32"/>
     </x:row>
     <x:row r="657">
       <x:c r="A657" s="34"/>
@@ -12116,6 +12793,7 @@
       <x:c r="M657" s="46"/>
       <x:c r="N657" s="46"/>
       <x:c r="O657" s="34"/>
+      <x:c r="P657" s="32"/>
     </x:row>
     <x:row r="658">
       <x:c r="A658" s="34"/>
@@ -12133,6 +12811,7 @@
       <x:c r="M658" s="46"/>
       <x:c r="N658" s="46"/>
       <x:c r="O658" s="34"/>
+      <x:c r="P658" s="32"/>
     </x:row>
     <x:row r="659">
       <x:c r="A659" s="34"/>
@@ -12150,6 +12829,7 @@
       <x:c r="M659" s="46"/>
       <x:c r="N659" s="46"/>
       <x:c r="O659" s="34"/>
+      <x:c r="P659" s="32"/>
     </x:row>
     <x:row r="660">
       <x:c r="A660" s="34"/>
@@ -12167,6 +12847,7 @@
       <x:c r="M660" s="46"/>
       <x:c r="N660" s="46"/>
       <x:c r="O660" s="34"/>
+      <x:c r="P660" s="32"/>
     </x:row>
     <x:row r="661">
       <x:c r="A661" s="34"/>
@@ -12184,6 +12865,7 @@
       <x:c r="M661" s="46"/>
       <x:c r="N661" s="46"/>
       <x:c r="O661" s="34"/>
+      <x:c r="P661" s="32"/>
     </x:row>
     <x:row r="662">
       <x:c r="A662" s="34"/>
@@ -12201,6 +12883,7 @@
       <x:c r="M662" s="46"/>
       <x:c r="N662" s="46"/>
       <x:c r="O662" s="34"/>
+      <x:c r="P662" s="32"/>
     </x:row>
     <x:row r="663">
       <x:c r="A663" s="34"/>
@@ -12218,6 +12901,7 @@
       <x:c r="M663" s="46"/>
       <x:c r="N663" s="46"/>
       <x:c r="O663" s="34"/>
+      <x:c r="P663" s="32"/>
     </x:row>
     <x:row r="664">
       <x:c r="A664" s="34"/>
@@ -12235,6 +12919,7 @@
       <x:c r="M664" s="46"/>
       <x:c r="N664" s="46"/>
       <x:c r="O664" s="34"/>
+      <x:c r="P664" s="32"/>
     </x:row>
     <x:row r="665">
       <x:c r="A665" s="34"/>
@@ -12252,6 +12937,7 @@
       <x:c r="M665" s="46"/>
       <x:c r="N665" s="46"/>
       <x:c r="O665" s="34"/>
+      <x:c r="P665" s="32"/>
     </x:row>
     <x:row r="666">
       <x:c r="A666" s="34"/>
@@ -12269,6 +12955,7 @@
       <x:c r="M666" s="46"/>
       <x:c r="N666" s="46"/>
       <x:c r="O666" s="34"/>
+      <x:c r="P666" s="32"/>
     </x:row>
     <x:row r="667">
       <x:c r="A667" s="34"/>
@@ -12286,6 +12973,7 @@
       <x:c r="M667" s="46"/>
       <x:c r="N667" s="46"/>
       <x:c r="O667" s="34"/>
+      <x:c r="P667" s="32"/>
     </x:row>
     <x:row r="668">
       <x:c r="A668" s="34"/>
@@ -12303,6 +12991,7 @@
       <x:c r="M668" s="46"/>
       <x:c r="N668" s="46"/>
       <x:c r="O668" s="34"/>
+      <x:c r="P668" s="32"/>
     </x:row>
     <x:row r="669">
       <x:c r="A669" s="34"/>
@@ -12320,6 +13009,7 @@
       <x:c r="M669" s="46"/>
       <x:c r="N669" s="46"/>
       <x:c r="O669" s="34"/>
+      <x:c r="P669" s="32"/>
     </x:row>
     <x:row r="670">
       <x:c r="A670" s="34"/>
@@ -12337,6 +13027,7 @@
       <x:c r="M670" s="46"/>
       <x:c r="N670" s="46"/>
       <x:c r="O670" s="34"/>
+      <x:c r="P670" s="32"/>
     </x:row>
     <x:row r="671">
       <x:c r="A671" s="34"/>
@@ -12354,6 +13045,7 @@
       <x:c r="M671" s="46"/>
       <x:c r="N671" s="46"/>
       <x:c r="O671" s="34"/>
+      <x:c r="P671" s="32"/>
     </x:row>
     <x:row r="672">
       <x:c r="A672" s="34"/>
@@ -12371,6 +13063,7 @@
       <x:c r="M672" s="46"/>
       <x:c r="N672" s="46"/>
       <x:c r="O672" s="34"/>
+      <x:c r="P672" s="32"/>
     </x:row>
     <x:row r="673">
       <x:c r="A673" s="34"/>
@@ -12388,6 +13081,7 @@
       <x:c r="M673" s="46"/>
       <x:c r="N673" s="46"/>
       <x:c r="O673" s="34"/>
+      <x:c r="P673" s="32"/>
     </x:row>
     <x:row r="674">
       <x:c r="A674" s="34"/>
@@ -12405,6 +13099,7 @@
       <x:c r="M674" s="46"/>
       <x:c r="N674" s="46"/>
       <x:c r="O674" s="34"/>
+      <x:c r="P674" s="32"/>
     </x:row>
     <x:row r="675">
       <x:c r="A675" s="34"/>
@@ -12422,6 +13117,7 @@
       <x:c r="M675" s="46"/>
       <x:c r="N675" s="46"/>
       <x:c r="O675" s="34"/>
+      <x:c r="P675" s="32"/>
     </x:row>
     <x:row r="676">
       <x:c r="A676" s="34"/>
@@ -12439,6 +13135,7 @@
       <x:c r="M676" s="46"/>
       <x:c r="N676" s="46"/>
       <x:c r="O676" s="34"/>
+      <x:c r="P676" s="32"/>
     </x:row>
     <x:row r="677">
       <x:c r="A677" s="34"/>
@@ -12456,6 +13153,7 @@
       <x:c r="M677" s="46"/>
       <x:c r="N677" s="46"/>
       <x:c r="O677" s="34"/>
+      <x:c r="P677" s="32"/>
     </x:row>
     <x:row r="678">
       <x:c r="A678" s="34"/>
@@ -12473,6 +13171,7 @@
       <x:c r="M678" s="46"/>
       <x:c r="N678" s="46"/>
       <x:c r="O678" s="34"/>
+      <x:c r="P678" s="32"/>
     </x:row>
     <x:row r="679">
       <x:c r="A679" s="34"/>
@@ -12490,6 +13189,7 @@
       <x:c r="M679" s="46"/>
       <x:c r="N679" s="46"/>
       <x:c r="O679" s="34"/>
+      <x:c r="P679" s="32"/>
     </x:row>
     <x:row r="680">
       <x:c r="A680" s="34"/>
@@ -12507,6 +13207,7 @@
       <x:c r="M680" s="46"/>
       <x:c r="N680" s="46"/>
       <x:c r="O680" s="34"/>
+      <x:c r="P680" s="32"/>
     </x:row>
     <x:row r="681">
       <x:c r="A681" s="34"/>
@@ -12524,6 +13225,7 @@
       <x:c r="M681" s="46"/>
       <x:c r="N681" s="46"/>
       <x:c r="O681" s="34"/>
+      <x:c r="P681" s="32"/>
     </x:row>
     <x:row r="682">
       <x:c r="A682" s="34"/>
@@ -12541,6 +13243,7 @@
       <x:c r="M682" s="46"/>
       <x:c r="N682" s="46"/>
       <x:c r="O682" s="34"/>
+      <x:c r="P682" s="32"/>
     </x:row>
     <x:row r="683">
       <x:c r="A683" s="34"/>
@@ -12558,6 +13261,7 @@
       <x:c r="M683" s="46"/>
       <x:c r="N683" s="46"/>
       <x:c r="O683" s="34"/>
+      <x:c r="P683" s="32"/>
     </x:row>
     <x:row r="684">
       <x:c r="A684" s="34"/>
@@ -12575,6 +13279,7 @@
       <x:c r="M684" s="46"/>
       <x:c r="N684" s="46"/>
       <x:c r="O684" s="34"/>
+      <x:c r="P684" s="32"/>
     </x:row>
     <x:row r="685">
       <x:c r="A685" s="34"/>
@@ -12592,6 +13297,7 @@
       <x:c r="M685" s="46"/>
       <x:c r="N685" s="46"/>
       <x:c r="O685" s="34"/>
+      <x:c r="P685" s="32"/>
     </x:row>
     <x:row r="686">
       <x:c r="A686" s="34"/>
@@ -12609,6 +13315,7 @@
       <x:c r="M686" s="46"/>
       <x:c r="N686" s="46"/>
       <x:c r="O686" s="34"/>
+      <x:c r="P686" s="32"/>
     </x:row>
     <x:row r="687">
       <x:c r="A687" s="34"/>
@@ -12626,6 +13333,7 @@
       <x:c r="M687" s="46"/>
       <x:c r="N687" s="46"/>
       <x:c r="O687" s="34"/>
+      <x:c r="P687" s="32"/>
     </x:row>
     <x:row r="688">
       <x:c r="A688" s="34"/>
@@ -12643,6 +13351,7 @@
       <x:c r="M688" s="46"/>
       <x:c r="N688" s="46"/>
       <x:c r="O688" s="34"/>
+      <x:c r="P688" s="32"/>
     </x:row>
     <x:row r="689">
       <x:c r="A689" s="34"/>
@@ -12660,6 +13369,7 @@
       <x:c r="M689" s="46"/>
       <x:c r="N689" s="46"/>
       <x:c r="O689" s="34"/>
+      <x:c r="P689" s="32"/>
     </x:row>
     <x:row r="690">
       <x:c r="A690" s="34"/>
@@ -12677,6 +13387,7 @@
       <x:c r="M690" s="46"/>
       <x:c r="N690" s="46"/>
       <x:c r="O690" s="34"/>
+      <x:c r="P690" s="32"/>
     </x:row>
     <x:row r="691">
       <x:c r="A691" s="34"/>
@@ -12694,6 +13405,7 @@
       <x:c r="M691" s="46"/>
       <x:c r="N691" s="46"/>
       <x:c r="O691" s="34"/>
+      <x:c r="P691" s="32"/>
     </x:row>
     <x:row r="692">
       <x:c r="A692" s="34"/>
@@ -12711,6 +13423,7 @@
       <x:c r="M692" s="46"/>
       <x:c r="N692" s="46"/>
       <x:c r="O692" s="34"/>
+      <x:c r="P692" s="32"/>
     </x:row>
     <x:row r="693">
       <x:c r="A693" s="34"/>
@@ -12728,6 +13441,7 @@
       <x:c r="M693" s="46"/>
       <x:c r="N693" s="46"/>
       <x:c r="O693" s="34"/>
+      <x:c r="P693" s="32"/>
     </x:row>
     <x:row r="694">
       <x:c r="A694" s="34"/>
@@ -12745,6 +13459,7 @@
       <x:c r="M694" s="46"/>
       <x:c r="N694" s="46"/>
       <x:c r="O694" s="34"/>
+      <x:c r="P694" s="32"/>
     </x:row>
     <x:row r="695">
       <x:c r="A695" s="34"/>
@@ -12762,6 +13477,7 @@
       <x:c r="M695" s="46"/>
       <x:c r="N695" s="46"/>
       <x:c r="O695" s="34"/>
+      <x:c r="P695" s="32"/>
     </x:row>
     <x:row r="696">
       <x:c r="A696" s="34"/>
@@ -12779,6 +13495,7 @@
       <x:c r="M696" s="46"/>
       <x:c r="N696" s="46"/>
       <x:c r="O696" s="34"/>
+      <x:c r="P696" s="32"/>
     </x:row>
     <x:row r="697">
       <x:c r="A697" s="34"/>
@@ -12796,6 +13513,7 @@
       <x:c r="M697" s="46"/>
       <x:c r="N697" s="46"/>
       <x:c r="O697" s="34"/>
+      <x:c r="P697" s="32"/>
     </x:row>
     <x:row r="698">
       <x:c r="A698" s="34"/>
@@ -12813,6 +13531,7 @@
       <x:c r="M698" s="46"/>
       <x:c r="N698" s="46"/>
       <x:c r="O698" s="34"/>
+      <x:c r="P698" s="32"/>
     </x:row>
     <x:row r="699">
       <x:c r="A699" s="34"/>
@@ -12830,6 +13549,7 @@
       <x:c r="M699" s="46"/>
       <x:c r="N699" s="46"/>
       <x:c r="O699" s="34"/>
+      <x:c r="P699" s="32"/>
     </x:row>
     <x:row r="700">
       <x:c r="A700" s="34"/>
@@ -12847,6 +13567,7 @@
       <x:c r="M700" s="46"/>
       <x:c r="N700" s="46"/>
       <x:c r="O700" s="34"/>
+      <x:c r="P700" s="32"/>
     </x:row>
     <x:row r="701">
       <x:c r="A701" s="34"/>
@@ -12864,6 +13585,7 @@
       <x:c r="M701" s="46"/>
       <x:c r="N701" s="46"/>
       <x:c r="O701" s="34"/>
+      <x:c r="P701" s="32"/>
     </x:row>
     <x:row r="702">
       <x:c r="A702" s="34"/>
@@ -12881,6 +13603,7 @@
       <x:c r="M702" s="46"/>
       <x:c r="N702" s="46"/>
       <x:c r="O702" s="34"/>
+      <x:c r="P702" s="32"/>
     </x:row>
     <x:row r="703">
       <x:c r="A703" s="34"/>
@@ -12898,6 +13621,7 @@
       <x:c r="M703" s="46"/>
       <x:c r="N703" s="46"/>
       <x:c r="O703" s="34"/>
+      <x:c r="P703" s="32"/>
     </x:row>
     <x:row r="704">
       <x:c r="A704" s="34"/>
@@ -12915,6 +13639,7 @@
       <x:c r="M704" s="46"/>
       <x:c r="N704" s="46"/>
       <x:c r="O704" s="34"/>
+      <x:c r="P704" s="32"/>
     </x:row>
     <x:row r="705">
       <x:c r="A705" s="34"/>
@@ -12932,6 +13657,7 @@
       <x:c r="M705" s="46"/>
       <x:c r="N705" s="46"/>
       <x:c r="O705" s="34"/>
+      <x:c r="P705" s="32"/>
     </x:row>
     <x:row r="706">
       <x:c r="A706" s="34"/>
@@ -12949,6 +13675,7 @@
       <x:c r="M706" s="46"/>
       <x:c r="N706" s="46"/>
       <x:c r="O706" s="34"/>
+      <x:c r="P706" s="32"/>
     </x:row>
     <x:row r="707">
       <x:c r="A707" s="34"/>
@@ -12966,6 +13693,7 @@
       <x:c r="M707" s="46"/>
       <x:c r="N707" s="46"/>
       <x:c r="O707" s="34"/>
+      <x:c r="P707" s="32"/>
     </x:row>
     <x:row r="708">
       <x:c r="A708" s="34"/>
@@ -12983,6 +13711,7 @@
       <x:c r="M708" s="46"/>
       <x:c r="N708" s="46"/>
       <x:c r="O708" s="34"/>
+      <x:c r="P708" s="32"/>
     </x:row>
     <x:row r="709">
       <x:c r="A709" s="34"/>
@@ -13000,6 +13729,7 @@
       <x:c r="M709" s="46"/>
       <x:c r="N709" s="46"/>
       <x:c r="O709" s="34"/>
+      <x:c r="P709" s="32"/>
     </x:row>
     <x:row r="710">
       <x:c r="A710" s="34"/>
@@ -13017,6 +13747,7 @@
       <x:c r="M710" s="46"/>
       <x:c r="N710" s="46"/>
       <x:c r="O710" s="34"/>
+      <x:c r="P710" s="32"/>
     </x:row>
     <x:row r="711">
       <x:c r="A711" s="34"/>
@@ -13034,6 +13765,7 @@
       <x:c r="M711" s="46"/>
       <x:c r="N711" s="46"/>
       <x:c r="O711" s="34"/>
+      <x:c r="P711" s="32"/>
     </x:row>
     <x:row r="712">
       <x:c r="A712" s="34"/>
@@ -13051,6 +13783,7 @@
       <x:c r="M712" s="46"/>
       <x:c r="N712" s="46"/>
       <x:c r="O712" s="34"/>
+      <x:c r="P712" s="32"/>
     </x:row>
     <x:row r="713">
       <x:c r="A713" s="34"/>
@@ -13068,6 +13801,7 @@
       <x:c r="M713" s="46"/>
       <x:c r="N713" s="46"/>
       <x:c r="O713" s="34"/>
+      <x:c r="P713" s="32"/>
     </x:row>
     <x:row r="714">
       <x:c r="A714" s="34"/>
@@ -13085,6 +13819,7 @@
       <x:c r="M714" s="46"/>
       <x:c r="N714" s="46"/>
       <x:c r="O714" s="34"/>
+      <x:c r="P714" s="32"/>
     </x:row>
     <x:row r="715">
       <x:c r="A715" s="34"/>
@@ -13102,6 +13837,7 @@
       <x:c r="M715" s="46"/>
       <x:c r="N715" s="46"/>
       <x:c r="O715" s="34"/>
+      <x:c r="P715" s="32"/>
     </x:row>
     <x:row r="716">
       <x:c r="A716" s="34"/>
@@ -13119,6 +13855,7 @@
       <x:c r="M716" s="46"/>
       <x:c r="N716" s="46"/>
       <x:c r="O716" s="34"/>
+      <x:c r="P716" s="32"/>
     </x:row>
     <x:row r="717">
       <x:c r="A717" s="34"/>
@@ -13136,6 +13873,7 @@
       <x:c r="M717" s="46"/>
       <x:c r="N717" s="46"/>
       <x:c r="O717" s="34"/>
+      <x:c r="P717" s="32"/>
     </x:row>
     <x:row r="718">
       <x:c r="A718" s="34"/>
@@ -13153,6 +13891,7 @@
       <x:c r="M718" s="46"/>
       <x:c r="N718" s="46"/>
       <x:c r="O718" s="34"/>
+      <x:c r="P718" s="32"/>
     </x:row>
     <x:row r="719">
       <x:c r="A719" s="34"/>
@@ -13170,6 +13909,7 @@
       <x:c r="M719" s="46"/>
       <x:c r="N719" s="46"/>
       <x:c r="O719" s="34"/>
+      <x:c r="P719" s="32"/>
     </x:row>
     <x:row r="720">
       <x:c r="A720" s="34"/>
@@ -13187,6 +13927,7 @@
       <x:c r="M720" s="46"/>
       <x:c r="N720" s="46"/>
       <x:c r="O720" s="34"/>
+      <x:c r="P720" s="32"/>
     </x:row>
     <x:row r="721">
       <x:c r="A721" s="34"/>
@@ -13204,6 +13945,7 @@
       <x:c r="M721" s="46"/>
       <x:c r="N721" s="46"/>
       <x:c r="O721" s="34"/>
+      <x:c r="P721" s="32"/>
     </x:row>
     <x:row r="722">
       <x:c r="A722" s="34"/>
@@ -13221,6 +13963,7 @@
       <x:c r="M722" s="46"/>
       <x:c r="N722" s="46"/>
       <x:c r="O722" s="34"/>
+      <x:c r="P722" s="32"/>
     </x:row>
     <x:row r="723">
       <x:c r="A723" s="34"/>
@@ -13238,6 +13981,7 @@
       <x:c r="M723" s="46"/>
       <x:c r="N723" s="46"/>
       <x:c r="O723" s="34"/>
+      <x:c r="P723" s="32"/>
     </x:row>
     <x:row r="724">
       <x:c r="A724" s="34"/>
@@ -13255,6 +13999,7 @@
       <x:c r="M724" s="46"/>
       <x:c r="N724" s="46"/>
       <x:c r="O724" s="34"/>
+      <x:c r="P724" s="32"/>
     </x:row>
     <x:row r="725">
       <x:c r="A725" s="34"/>
@@ -13272,6 +14017,7 @@
       <x:c r="M725" s="46"/>
       <x:c r="N725" s="46"/>
       <x:c r="O725" s="34"/>
+      <x:c r="P725" s="32"/>
     </x:row>
     <x:row r="726">
       <x:c r="A726" s="34"/>
@@ -13289,6 +14035,7 @@
       <x:c r="M726" s="46"/>
       <x:c r="N726" s="46"/>
       <x:c r="O726" s="34"/>
+      <x:c r="P726" s="32"/>
     </x:row>
     <x:row r="727">
       <x:c r="A727" s="34"/>
@@ -13306,6 +14053,7 @@
       <x:c r="M727" s="46"/>
       <x:c r="N727" s="46"/>
       <x:c r="O727" s="34"/>
+      <x:c r="P727" s="32"/>
     </x:row>
     <x:row r="728">
       <x:c r="A728" s="34"/>
@@ -13323,6 +14071,7 @@
       <x:c r="M728" s="46"/>
       <x:c r="N728" s="46"/>
       <x:c r="O728" s="34"/>
+      <x:c r="P728" s="32"/>
     </x:row>
     <x:row r="729">
       <x:c r="A729" s="34"/>
@@ -13340,6 +14089,7 @@
       <x:c r="M729" s="46"/>
       <x:c r="N729" s="46"/>
       <x:c r="O729" s="34"/>
+      <x:c r="P729" s="32"/>
     </x:row>
     <x:row r="730">
       <x:c r="A730" s="34"/>
@@ -13357,6 +14107,7 @@
       <x:c r="M730" s="46"/>
       <x:c r="N730" s="46"/>
       <x:c r="O730" s="34"/>
+      <x:c r="P730" s="32"/>
     </x:row>
     <x:row r="731">
       <x:c r="A731" s="34"/>
@@ -13374,6 +14125,7 @@
       <x:c r="M731" s="46"/>
       <x:c r="N731" s="46"/>
       <x:c r="O731" s="34"/>
+      <x:c r="P731" s="32"/>
     </x:row>
     <x:row r="732">
       <x:c r="A732" s="34"/>
@@ -13391,6 +14143,7 @@
       <x:c r="M732" s="46"/>
       <x:c r="N732" s="46"/>
       <x:c r="O732" s="34"/>
+      <x:c r="P732" s="32"/>
     </x:row>
     <x:row r="733">
       <x:c r="A733" s="34"/>
@@ -13408,6 +14161,7 @@
       <x:c r="M733" s="46"/>
       <x:c r="N733" s="46"/>
       <x:c r="O733" s="34"/>
+      <x:c r="P733" s="32"/>
     </x:row>
     <x:row r="734">
       <x:c r="A734" s="34"/>
@@ -13425,6 +14179,7 @@
       <x:c r="M734" s="46"/>
       <x:c r="N734" s="46"/>
       <x:c r="O734" s="34"/>
+      <x:c r="P734" s="32"/>
     </x:row>
     <x:row r="735">
       <x:c r="A735" s="34"/>
@@ -13442,6 +14197,7 @@
       <x:c r="M735" s="46"/>
       <x:c r="N735" s="46"/>
       <x:c r="O735" s="34"/>
+      <x:c r="P735" s="32"/>
     </x:row>
     <x:row r="736">
       <x:c r="A736" s="34"/>
@@ -13459,6 +14215,7 @@
       <x:c r="M736" s="46"/>
       <x:c r="N736" s="46"/>
       <x:c r="O736" s="34"/>
+      <x:c r="P736" s="32"/>
     </x:row>
     <x:row r="737">
       <x:c r="A737" s="34"/>
@@ -13476,6 +14233,7 @@
       <x:c r="M737" s="46"/>
       <x:c r="N737" s="46"/>
       <x:c r="O737" s="34"/>
+      <x:c r="P737" s="32"/>
     </x:row>
     <x:row r="738">
       <x:c r="A738" s="34"/>
@@ -13493,6 +14251,7 @@
       <x:c r="M738" s="46"/>
       <x:c r="N738" s="46"/>
       <x:c r="O738" s="34"/>
+      <x:c r="P738" s="32"/>
     </x:row>
     <x:row r="739">
       <x:c r="A739" s="34"/>
@@ -13510,6 +14269,7 @@
       <x:c r="M739" s="46"/>
       <x:c r="N739" s="46"/>
       <x:c r="O739" s="34"/>
+      <x:c r="P739" s="32"/>
     </x:row>
     <x:row r="740">
       <x:c r="A740" s="34"/>
@@ -13527,6 +14287,7 @@
       <x:c r="M740" s="46"/>
       <x:c r="N740" s="46"/>
       <x:c r="O740" s="34"/>
+      <x:c r="P740" s="32"/>
     </x:row>
     <x:row r="741">
       <x:c r="A741" s="34"/>
@@ -13544,6 +14305,7 @@
       <x:c r="M741" s="46"/>
       <x:c r="N741" s="46"/>
       <x:c r="O741" s="34"/>
+      <x:c r="P741" s="32"/>
     </x:row>
     <x:row r="742">
       <x:c r="A742" s="34"/>
@@ -13561,6 +14323,7 @@
       <x:c r="M742" s="46"/>
       <x:c r="N742" s="46"/>
       <x:c r="O742" s="34"/>
+      <x:c r="P742" s="32"/>
     </x:row>
     <x:row r="743">
       <x:c r="A743" s="34"/>
@@ -13578,6 +14341,7 @@
       <x:c r="M743" s="46"/>
       <x:c r="N743" s="46"/>
       <x:c r="O743" s="34"/>
+      <x:c r="P743" s="32"/>
     </x:row>
     <x:row r="744">
       <x:c r="A744" s="34"/>
@@ -13595,6 +14359,7 @@
       <x:c r="M744" s="46"/>
       <x:c r="N744" s="46"/>
       <x:c r="O744" s="34"/>
+      <x:c r="P744" s="32"/>
     </x:row>
     <x:row r="745">
       <x:c r="A745" s="34"/>
@@ -13612,6 +14377,7 @@
       <x:c r="M745" s="46"/>
       <x:c r="N745" s="46"/>
       <x:c r="O745" s="34"/>
+      <x:c r="P745" s="32"/>
     </x:row>
     <x:row r="746">
       <x:c r="A746" s="34"/>
@@ -13629,6 +14395,7 @@
       <x:c r="M746" s="46"/>
       <x:c r="N746" s="46"/>
       <x:c r="O746" s="34"/>
+      <x:c r="P746" s="32"/>
     </x:row>
     <x:row r="747">
       <x:c r="A747" s="34"/>
@@ -13646,6 +14413,7 @@
       <x:c r="M747" s="46"/>
       <x:c r="N747" s="46"/>
       <x:c r="O747" s="34"/>
+      <x:c r="P747" s="32"/>
     </x:row>
     <x:row r="748">
       <x:c r="A748" s="34"/>
@@ -13663,6 +14431,7 @@
       <x:c r="M748" s="46"/>
       <x:c r="N748" s="46"/>
       <x:c r="O748" s="34"/>
+      <x:c r="P748" s="32"/>
     </x:row>
     <x:row r="749">
       <x:c r="A749" s="34"/>
@@ -13680,6 +14449,7 @@
       <x:c r="M749" s="46"/>
       <x:c r="N749" s="46"/>
       <x:c r="O749" s="34"/>
+      <x:c r="P749" s="32"/>
     </x:row>
     <x:row r="750">
       <x:c r="A750" s="34"/>
@@ -13697,6 +14467,7 @@
       <x:c r="M750" s="46"/>
       <x:c r="N750" s="46"/>
       <x:c r="O750" s="34"/>
+      <x:c r="P750" s="32"/>
     </x:row>
     <x:row r="751">
       <x:c r="A751" s="34"/>
@@ -13714,6 +14485,7 @@
       <x:c r="M751" s="46"/>
       <x:c r="N751" s="46"/>
       <x:c r="O751" s="34"/>
+      <x:c r="P751" s="32"/>
     </x:row>
     <x:row r="752">
       <x:c r="A752" s="34"/>
@@ -13731,6 +14503,7 @@
       <x:c r="M752" s="46"/>
       <x:c r="N752" s="46"/>
       <x:c r="O752" s="34"/>
+      <x:c r="P752" s="32"/>
     </x:row>
     <x:row r="753">
       <x:c r="A753" s="34"/>
@@ -13748,6 +14521,7 @@
       <x:c r="M753" s="46"/>
       <x:c r="N753" s="46"/>
       <x:c r="O753" s="34"/>
+      <x:c r="P753" s="32"/>
     </x:row>
     <x:row r="754">
       <x:c r="A754" s="34"/>
@@ -13765,6 +14539,7 @@
       <x:c r="M754" s="46"/>
       <x:c r="N754" s="46"/>
       <x:c r="O754" s="34"/>
+      <x:c r="P754" s="32"/>
     </x:row>
     <x:row r="755">
       <x:c r="A755" s="34"/>
@@ -13782,6 +14557,7 @@
       <x:c r="M755" s="46"/>
       <x:c r="N755" s="46"/>
       <x:c r="O755" s="34"/>
+      <x:c r="P755" s="32"/>
     </x:row>
     <x:row r="756">
       <x:c r="A756" s="34"/>
@@ -13799,6 +14575,7 @@
       <x:c r="M756" s="46"/>
       <x:c r="N756" s="46"/>
       <x:c r="O756" s="34"/>
+      <x:c r="P756" s="32"/>
     </x:row>
     <x:row r="757">
       <x:c r="A757" s="34"/>
@@ -13816,6 +14593,7 @@
       <x:c r="M757" s="46"/>
       <x:c r="N757" s="46"/>
       <x:c r="O757" s="34"/>
+      <x:c r="P757" s="32"/>
     </x:row>
     <x:row r="758">
       <x:c r="A758" s="34"/>
@@ -13833,6 +14611,7 @@
       <x:c r="M758" s="46"/>
       <x:c r="N758" s="46"/>
       <x:c r="O758" s="34"/>
+      <x:c r="P758" s="32"/>
     </x:row>
     <x:row r="759">
       <x:c r="A759" s="34"/>
@@ -13850,6 +14629,7 @@
       <x:c r="M759" s="46"/>
       <x:c r="N759" s="46"/>
       <x:c r="O759" s="34"/>
+      <x:c r="P759" s="32"/>
     </x:row>
     <x:row r="760">
       <x:c r="A760" s="34"/>
@@ -13867,6 +14647,7 @@
       <x:c r="M760" s="46"/>
       <x:c r="N760" s="46"/>
       <x:c r="O760" s="34"/>
+      <x:c r="P760" s="32"/>
     </x:row>
     <x:row r="761">
       <x:c r="A761" s="34"/>
@@ -13884,6 +14665,7 @@
       <x:c r="M761" s="46"/>
       <x:c r="N761" s="46"/>
       <x:c r="O761" s="34"/>
+      <x:c r="P761" s="32"/>
     </x:row>
     <x:row r="762">
       <x:c r="A762" s="34"/>
@@ -13901,6 +14683,7 @@
       <x:c r="M762" s="46"/>
       <x:c r="N762" s="46"/>
       <x:c r="O762" s="34"/>
+      <x:c r="P762" s="32"/>
     </x:row>
     <x:row r="763">
       <x:c r="A763" s="34"/>
@@ -13918,6 +14701,7 @@
       <x:c r="M763" s="46"/>
       <x:c r="N763" s="46"/>
       <x:c r="O763" s="34"/>
+      <x:c r="P763" s="32"/>
     </x:row>
     <x:row r="764">
       <x:c r="A764" s="34"/>
@@ -13935,6 +14719,7 @@
       <x:c r="M764" s="46"/>
       <x:c r="N764" s="46"/>
       <x:c r="O764" s="34"/>
+      <x:c r="P764" s="32"/>
     </x:row>
     <x:row r="765">
       <x:c r="A765" s="34"/>
@@ -13952,6 +14737,7 @@
       <x:c r="M765" s="46"/>
       <x:c r="N765" s="46"/>
       <x:c r="O765" s="34"/>
+      <x:c r="P765" s="32"/>
     </x:row>
     <x:row r="766">
       <x:c r="A766" s="34"/>
@@ -13969,6 +14755,7 @@
       <x:c r="M766" s="46"/>
       <x:c r="N766" s="46"/>
       <x:c r="O766" s="34"/>
+      <x:c r="P766" s="32"/>
     </x:row>
     <x:row r="767">
       <x:c r="A767" s="34"/>
@@ -13986,6 +14773,7 @@
       <x:c r="M767" s="46"/>
       <x:c r="N767" s="46"/>
       <x:c r="O767" s="34"/>
+      <x:c r="P767" s="32"/>
     </x:row>
     <x:row r="768">
       <x:c r="A768" s="34"/>
@@ -14003,6 +14791,7 @@
       <x:c r="M768" s="46"/>
       <x:c r="N768" s="46"/>
       <x:c r="O768" s="34"/>
+      <x:c r="P768" s="32"/>
     </x:row>
     <x:row r="769">
       <x:c r="A769" s="34"/>
@@ -14020,6 +14809,7 @@
       <x:c r="M769" s="46"/>
       <x:c r="N769" s="46"/>
       <x:c r="O769" s="34"/>
+      <x:c r="P769" s="32"/>
     </x:row>
     <x:row r="770">
       <x:c r="A770" s="34"/>
@@ -14037,6 +14827,7 @@
       <x:c r="M770" s="46"/>
       <x:c r="N770" s="46"/>
       <x:c r="O770" s="34"/>
+      <x:c r="P770" s="32"/>
     </x:row>
     <x:row r="771">
       <x:c r="A771" s="34"/>
@@ -14054,6 +14845,7 @@
       <x:c r="M771" s="46"/>
       <x:c r="N771" s="46"/>
       <x:c r="O771" s="34"/>
+      <x:c r="P771" s="32"/>
     </x:row>
     <x:row r="772">
       <x:c r="A772" s="34"/>
@@ -14071,6 +14863,7 @@
       <x:c r="M772" s="46"/>
       <x:c r="N772" s="46"/>
       <x:c r="O772" s="34"/>
+      <x:c r="P772" s="32"/>
     </x:row>
     <x:row r="773">
       <x:c r="A773" s="34"/>
@@ -14088,6 +14881,7 @@
       <x:c r="M773" s="46"/>
       <x:c r="N773" s="46"/>
       <x:c r="O773" s="34"/>
+      <x:c r="P773" s="32"/>
     </x:row>
     <x:row r="774">
       <x:c r="A774" s="34"/>
@@ -14105,6 +14899,7 @@
       <x:c r="M774" s="46"/>
       <x:c r="N774" s="46"/>
       <x:c r="O774" s="34"/>
+      <x:c r="P774" s="32"/>
     </x:row>
     <x:row r="775">
       <x:c r="A775" s="34"/>
@@ -14122,6 +14917,7 @@
       <x:c r="M775" s="46"/>
       <x:c r="N775" s="46"/>
       <x:c r="O775" s="34"/>
+      <x:c r="P775" s="32"/>
     </x:row>
     <x:row r="776">
       <x:c r="A776" s="34"/>
@@ -14139,6 +14935,7 @@
       <x:c r="M776" s="46"/>
       <x:c r="N776" s="46"/>
       <x:c r="O776" s="34"/>
+      <x:c r="P776" s="32"/>
     </x:row>
     <x:row r="777">
       <x:c r="A777" s="34"/>
@@ -14156,6 +14953,7 @@
       <x:c r="M777" s="46"/>
       <x:c r="N777" s="46"/>
       <x:c r="O777" s="34"/>
+      <x:c r="P777" s="32"/>
     </x:row>
     <x:row r="778">
       <x:c r="A778" s="34"/>
@@ -14173,6 +14971,7 @@
       <x:c r="M778" s="46"/>
       <x:c r="N778" s="46"/>
       <x:c r="O778" s="34"/>
+      <x:c r="P778" s="32"/>
     </x:row>
     <x:row r="779">
       <x:c r="A779" s="34"/>
@@ -14190,6 +14989,7 @@
       <x:c r="M779" s="46"/>
       <x:c r="N779" s="46"/>
       <x:c r="O779" s="34"/>
+      <x:c r="P779" s="32"/>
     </x:row>
     <x:row r="780">
       <x:c r="A780" s="34"/>
@@ -14207,6 +15007,7 @@
       <x:c r="M780" s="46"/>
       <x:c r="N780" s="46"/>
       <x:c r="O780" s="34"/>
+      <x:c r="P780" s="32"/>
     </x:row>
     <x:row r="781">
       <x:c r="A781" s="34"/>
@@ -14224,6 +15025,7 @@
       <x:c r="M781" s="46"/>
       <x:c r="N781" s="46"/>
       <x:c r="O781" s="34"/>
+      <x:c r="P781" s="32"/>
     </x:row>
     <x:row r="782">
       <x:c r="A782" s="34"/>
@@ -14241,6 +15043,7 @@
       <x:c r="M782" s="46"/>
       <x:c r="N782" s="46"/>
       <x:c r="O782" s="34"/>
+      <x:c r="P782" s="32"/>
     </x:row>
     <x:row r="783">
       <x:c r="A783" s="34"/>
@@ -14258,6 +15061,7 @@
       <x:c r="M783" s="46"/>
       <x:c r="N783" s="46"/>
       <x:c r="O783" s="34"/>
+      <x:c r="P783" s="32"/>
     </x:row>
     <x:row r="784">
       <x:c r="A784" s="34"/>
@@ -14275,6 +15079,7 @@
       <x:c r="M784" s="46"/>
       <x:c r="N784" s="46"/>
       <x:c r="O784" s="34"/>
+      <x:c r="P784" s="32"/>
     </x:row>
     <x:row r="785">
       <x:c r="A785" s="34"/>
@@ -14292,6 +15097,7 @@
       <x:c r="M785" s="46"/>
       <x:c r="N785" s="46"/>
       <x:c r="O785" s="34"/>
+      <x:c r="P785" s="32"/>
     </x:row>
     <x:row r="786">
       <x:c r="A786" s="34"/>
@@ -14309,6 +15115,7 @@
       <x:c r="M786" s="46"/>
       <x:c r="N786" s="46"/>
       <x:c r="O786" s="34"/>
+      <x:c r="P786" s="32"/>
     </x:row>
     <x:row r="787">
       <x:c r="A787" s="34"/>
@@ -14326,6 +15133,7 @@
       <x:c r="M787" s="46"/>
       <x:c r="N787" s="46"/>
       <x:c r="O787" s="34"/>
+      <x:c r="P787" s="32"/>
     </x:row>
     <x:row r="788">
       <x:c r="A788" s="34"/>
@@ -14343,6 +15151,7 @@
       <x:c r="M788" s="46"/>
       <x:c r="N788" s="46"/>
       <x:c r="O788" s="34"/>
+      <x:c r="P788" s="32"/>
     </x:row>
     <x:row r="789">
       <x:c r="A789" s="34"/>
@@ -14360,6 +15169,7 @@
       <x:c r="M789" s="46"/>
       <x:c r="N789" s="46"/>
       <x:c r="O789" s="34"/>
+      <x:c r="P789" s="32"/>
     </x:row>
     <x:row r="790">
       <x:c r="A790" s="34"/>
@@ -14377,6 +15187,7 @@
       <x:c r="M790" s="46"/>
       <x:c r="N790" s="46"/>
       <x:c r="O790" s="34"/>
+      <x:c r="P790" s="32"/>
     </x:row>
     <x:row r="791">
       <x:c r="A791" s="34"/>
@@ -14394,6 +15205,7 @@
       <x:c r="M791" s="46"/>
       <x:c r="N791" s="46"/>
       <x:c r="O791" s="34"/>
+      <x:c r="P791" s="32"/>
     </x:row>
     <x:row r="792">
       <x:c r="A792" s="34"/>
@@ -14411,6 +15223,7 @@
       <x:c r="M792" s="46"/>
       <x:c r="N792" s="46"/>
       <x:c r="O792" s="34"/>
+      <x:c r="P792" s="32"/>
     </x:row>
     <x:row r="793">
       <x:c r="A793" s="34"/>
@@ -14428,6 +15241,7 @@
       <x:c r="M793" s="46"/>
       <x:c r="N793" s="46"/>
       <x:c r="O793" s="34"/>
+      <x:c r="P793" s="32"/>
     </x:row>
     <x:row r="794">
       <x:c r="A794" s="34"/>
@@ -14445,6 +15259,7 @@
       <x:c r="M794" s="46"/>
       <x:c r="N794" s="46"/>
       <x:c r="O794" s="34"/>
+      <x:c r="P794" s="32"/>
     </x:row>
     <x:row r="795">
       <x:c r="A795" s="34"/>
@@ -14462,6 +15277,7 @@
       <x:c r="M795" s="46"/>
       <x:c r="N795" s="46"/>
       <x:c r="O795" s="34"/>
+      <x:c r="P795" s="32"/>
     </x:row>
     <x:row r="796">
       <x:c r="A796" s="34"/>
@@ -14479,6 +15295,7 @@
       <x:c r="M796" s="46"/>
       <x:c r="N796" s="46"/>
       <x:c r="O796" s="34"/>
+      <x:c r="P796" s="32"/>
     </x:row>
     <x:row r="797">
       <x:c r="A797" s="34"/>
@@ -14496,6 +15313,7 @@
       <x:c r="M797" s="46"/>
       <x:c r="N797" s="46"/>
       <x:c r="O797" s="34"/>
+      <x:c r="P797" s="32"/>
     </x:row>
     <x:row r="798">
       <x:c r="A798" s="34"/>
@@ -14513,6 +15331,7 @@
       <x:c r="M798" s="46"/>
       <x:c r="N798" s="46"/>
       <x:c r="O798" s="34"/>
+      <x:c r="P798" s="32"/>
     </x:row>
     <x:row r="799">
       <x:c r="A799" s="34"/>
@@ -14530,6 +15349,7 @@
       <x:c r="M799" s="46"/>
       <x:c r="N799" s="46"/>
       <x:c r="O799" s="34"/>
+      <x:c r="P799" s="32"/>
     </x:row>
     <x:row r="800">
       <x:c r="A800" s="34"/>
@@ -14547,6 +15367,7 @@
       <x:c r="M800" s="46"/>
       <x:c r="N800" s="46"/>
       <x:c r="O800" s="34"/>
+      <x:c r="P800" s="32"/>
     </x:row>
     <x:row r="801">
       <x:c r="A801" s="34"/>
@@ -14564,6 +15385,7 @@
       <x:c r="M801" s="46"/>
       <x:c r="N801" s="46"/>
       <x:c r="O801" s="34"/>
+      <x:c r="P801" s="32"/>
     </x:row>
     <x:row r="802">
       <x:c r="A802" s="34"/>
@@ -14581,6 +15403,7 @@
       <x:c r="M802" s="46"/>
       <x:c r="N802" s="46"/>
       <x:c r="O802" s="34"/>
+      <x:c r="P802" s="32"/>
     </x:row>
     <x:row r="803">
       <x:c r="A803" s="34"/>
@@ -14598,6 +15421,7 @@
       <x:c r="M803" s="46"/>
       <x:c r="N803" s="46"/>
       <x:c r="O803" s="34"/>
+      <x:c r="P803" s="32"/>
     </x:row>
     <x:row r="804">
       <x:c r="A804" s="34"/>
@@ -14615,6 +15439,7 @@
       <x:c r="M804" s="46"/>
       <x:c r="N804" s="46"/>
       <x:c r="O804" s="34"/>
+      <x:c r="P804" s="32"/>
     </x:row>
     <x:row r="805">
       <x:c r="A805" s="34"/>
@@ -14632,6 +15457,7 @@
       <x:c r="M805" s="46"/>
       <x:c r="N805" s="46"/>
       <x:c r="O805" s="34"/>
+      <x:c r="P805" s="32"/>
     </x:row>
     <x:row r="806">
       <x:c r="A806" s="34"/>
@@ -14649,6 +15475,7 @@
       <x:c r="M806" s="46"/>
       <x:c r="N806" s="46"/>
       <x:c r="O806" s="34"/>
+      <x:c r="P806" s="32"/>
     </x:row>
     <x:row r="807">
       <x:c r="A807" s="34"/>
@@ -14666,6 +15493,7 @@
       <x:c r="M807" s="46"/>
       <x:c r="N807" s="46"/>
       <x:c r="O807" s="34"/>
+      <x:c r="P807" s="32"/>
     </x:row>
     <x:row r="808">
       <x:c r="A808" s="34"/>
@@ -14683,6 +15511,7 @@
       <x:c r="M808" s="46"/>
       <x:c r="N808" s="46"/>
       <x:c r="O808" s="34"/>
+      <x:c r="P808" s="32"/>
     </x:row>
     <x:row r="809">
       <x:c r="A809" s="34"/>
@@ -14700,6 +15529,7 @@
       <x:c r="M809" s="46"/>
       <x:c r="N809" s="46"/>
       <x:c r="O809" s="34"/>
+      <x:c r="P809" s="32"/>
     </x:row>
     <x:row r="810">
       <x:c r="A810" s="34"/>
@@ -14717,6 +15547,7 @@
       <x:c r="M810" s="46"/>
       <x:c r="N810" s="46"/>
       <x:c r="O810" s="34"/>
+      <x:c r="P810" s="32"/>
     </x:row>
     <x:row r="811">
       <x:c r="A811" s="34"/>
@@ -14734,6 +15565,7 @@
       <x:c r="M811" s="46"/>
       <x:c r="N811" s="46"/>
       <x:c r="O811" s="34"/>
+      <x:c r="P811" s="32"/>
     </x:row>
     <x:row r="812">
       <x:c r="A812" s="34"/>
@@ -14751,6 +15583,7 @@
       <x:c r="M812" s="46"/>
       <x:c r="N812" s="46"/>
       <x:c r="O812" s="34"/>
+      <x:c r="P812" s="32"/>
     </x:row>
     <x:row r="813">
       <x:c r="A813" s="34"/>
@@ -14768,6 +15601,7 @@
       <x:c r="M813" s="46"/>
       <x:c r="N813" s="46"/>
       <x:c r="O813" s="34"/>
+      <x:c r="P813" s="32"/>
     </x:row>
     <x:row r="814">
       <x:c r="A814" s="34"/>
@@ -14785,6 +15619,7 @@
       <x:c r="M814" s="46"/>
       <x:c r="N814" s="46"/>
       <x:c r="O814" s="34"/>
+      <x:c r="P814" s="32"/>
     </x:row>
     <x:row r="815">
       <x:c r="A815" s="34"/>
@@ -14802,6 +15637,7 @@
       <x:c r="M815" s="46"/>
       <x:c r="N815" s="46"/>
       <x:c r="O815" s="34"/>
+      <x:c r="P815" s="32"/>
     </x:row>
     <x:row r="816">
       <x:c r="A816" s="34"/>
@@ -14819,6 +15655,7 @@
       <x:c r="M816" s="46"/>
       <x:c r="N816" s="46"/>
       <x:c r="O816" s="34"/>
+      <x:c r="P816" s="32"/>
     </x:row>
     <x:row r="817">
       <x:c r="A817" s="34"/>
@@ -14836,6 +15673,7 @@
       <x:c r="M817" s="46"/>
       <x:c r="N817" s="46"/>
       <x:c r="O817" s="34"/>
+      <x:c r="P817" s="32"/>
     </x:row>
     <x:row r="818">
       <x:c r="A818" s="34"/>
@@ -14853,6 +15691,7 @@
       <x:c r="M818" s="46"/>
       <x:c r="N818" s="46"/>
       <x:c r="O818" s="34"/>
+      <x:c r="P818" s="32"/>
     </x:row>
     <x:row r="819">
       <x:c r="A819" s="34"/>
@@ -14870,6 +15709,7 @@
       <x:c r="M819" s="46"/>
       <x:c r="N819" s="46"/>
       <x:c r="O819" s="34"/>
+      <x:c r="P819" s="32"/>
     </x:row>
     <x:row r="820">
       <x:c r="A820" s="34"/>
@@ -14887,6 +15727,7 @@
       <x:c r="M820" s="46"/>
       <x:c r="N820" s="46"/>
       <x:c r="O820" s="34"/>
+      <x:c r="P820" s="32"/>
     </x:row>
     <x:row r="821">
       <x:c r="A821" s="34"/>
@@ -14904,6 +15745,7 @@
       <x:c r="M821" s="46"/>
       <x:c r="N821" s="46"/>
       <x:c r="O821" s="34"/>
+      <x:c r="P821" s="32"/>
     </x:row>
     <x:row r="822">
       <x:c r="A822" s="34"/>
@@ -14921,6 +15763,7 @@
       <x:c r="M822" s="46"/>
       <x:c r="N822" s="46"/>
       <x:c r="O822" s="34"/>
+      <x:c r="P822" s="32"/>
     </x:row>
     <x:row r="823">
       <x:c r="A823" s="34"/>
@@ -14938,6 +15781,7 @@
       <x:c r="M823" s="46"/>
       <x:c r="N823" s="46"/>
       <x:c r="O823" s="34"/>
+      <x:c r="P823" s="32"/>
     </x:row>
     <x:row r="824">
       <x:c r="A824" s="34"/>
@@ -14955,6 +15799,7 @@
       <x:c r="M824" s="46"/>
       <x:c r="N824" s="46"/>
       <x:c r="O824" s="34"/>
+      <x:c r="P824" s="32"/>
     </x:row>
     <x:row r="825">
       <x:c r="A825" s="34"/>
@@ -14972,6 +15817,7 @@
       <x:c r="M825" s="46"/>
       <x:c r="N825" s="46"/>
       <x:c r="O825" s="34"/>
+      <x:c r="P825" s="32"/>
     </x:row>
     <x:row r="826">
       <x:c r="A826" s="34"/>
@@ -14989,6 +15835,7 @@
       <x:c r="M826" s="46"/>
       <x:c r="N826" s="46"/>
       <x:c r="O826" s="34"/>
+      <x:c r="P826" s="32"/>
     </x:row>
     <x:row r="827">
       <x:c r="A827" s="34"/>
@@ -15006,6 +15853,7 @@
       <x:c r="M827" s="46"/>
       <x:c r="N827" s="46"/>
       <x:c r="O827" s="34"/>
+      <x:c r="P827" s="32"/>
     </x:row>
     <x:row r="828">
       <x:c r="A828" s="34"/>
@@ -15023,6 +15871,7 @@
       <x:c r="M828" s="46"/>
       <x:c r="N828" s="46"/>
       <x:c r="O828" s="34"/>
+      <x:c r="P828" s="32"/>
     </x:row>
     <x:row r="829">
       <x:c r="A829" s="34"/>
@@ -15040,6 +15889,7 @@
       <x:c r="M829" s="46"/>
       <x:c r="N829" s="46"/>
       <x:c r="O829" s="34"/>
+      <x:c r="P829" s="32"/>
     </x:row>
     <x:row r="830">
       <x:c r="A830" s="34"/>
@@ -15057,6 +15907,7 @@
       <x:c r="M830" s="46"/>
       <x:c r="N830" s="46"/>
       <x:c r="O830" s="34"/>
+      <x:c r="P830" s="32"/>
     </x:row>
     <x:row r="831">
       <x:c r="A831" s="34"/>
@@ -15074,6 +15925,7 @@
       <x:c r="M831" s="46"/>
       <x:c r="N831" s="46"/>
       <x:c r="O831" s="34"/>
+      <x:c r="P831" s="32"/>
     </x:row>
     <x:row r="832">
       <x:c r="A832" s="34"/>
@@ -15091,6 +15943,7 @@
       <x:c r="M832" s="46"/>
       <x:c r="N832" s="46"/>
       <x:c r="O832" s="34"/>
+      <x:c r="P832" s="32"/>
     </x:row>
     <x:row r="833">
       <x:c r="A833" s="34"/>
@@ -15108,6 +15961,7 @@
       <x:c r="M833" s="46"/>
       <x:c r="N833" s="46"/>
       <x:c r="O833" s="34"/>
+      <x:c r="P833" s="32"/>
     </x:row>
     <x:row r="834">
       <x:c r="A834" s="34"/>
@@ -15125,6 +15979,7 @@
       <x:c r="M834" s="46"/>
       <x:c r="N834" s="46"/>
       <x:c r="O834" s="34"/>
+      <x:c r="P834" s="32"/>
     </x:row>
     <x:row r="835">
       <x:c r="A835" s="34"/>
@@ -15142,6 +15997,7 @@
       <x:c r="M835" s="46"/>
       <x:c r="N835" s="46"/>
       <x:c r="O835" s="34"/>
+      <x:c r="P835" s="32"/>
     </x:row>
     <x:row r="836">
       <x:c r="A836" s="34"/>
@@ -15159,6 +16015,7 @@
       <x:c r="M836" s="46"/>
       <x:c r="N836" s="46"/>
       <x:c r="O836" s="34"/>
+      <x:c r="P836" s="32"/>
     </x:row>
     <x:row r="837">
       <x:c r="A837" s="34"/>
@@ -15176,6 +16033,7 @@
       <x:c r="M837" s="46"/>
       <x:c r="N837" s="46"/>
       <x:c r="O837" s="34"/>
+      <x:c r="P837" s="32"/>
     </x:row>
     <x:row r="838">
       <x:c r="A838" s="34"/>
@@ -15193,6 +16051,7 @@
       <x:c r="M838" s="46"/>
       <x:c r="N838" s="46"/>
       <x:c r="O838" s="34"/>
+      <x:c r="P838" s="32"/>
     </x:row>
     <x:row r="839">
       <x:c r="A839" s="34"/>
@@ -15210,6 +16069,7 @@
       <x:c r="M839" s="46"/>
       <x:c r="N839" s="46"/>
       <x:c r="O839" s="34"/>
+      <x:c r="P839" s="32"/>
     </x:row>
     <x:row r="840">
       <x:c r="A840" s="34"/>
@@ -15227,6 +16087,7 @@
       <x:c r="M840" s="46"/>
       <x:c r="N840" s="46"/>
       <x:c r="O840" s="34"/>
+      <x:c r="P840" s="32"/>
     </x:row>
     <x:row r="841">
       <x:c r="A841" s="34"/>
@@ -15244,6 +16105,7 @@
       <x:c r="M841" s="46"/>
       <x:c r="N841" s="46"/>
       <x:c r="O841" s="34"/>
+      <x:c r="P841" s="32"/>
     </x:row>
     <x:row r="842">
       <x:c r="A842" s="34"/>
@@ -15261,6 +16123,7 @@
       <x:c r="M842" s="46"/>
       <x:c r="N842" s="46"/>
       <x:c r="O842" s="34"/>
+      <x:c r="P842" s="32"/>
     </x:row>
     <x:row r="843">
       <x:c r="A843" s="34"/>
@@ -15278,6 +16141,7 @@
       <x:c r="M843" s="46"/>
       <x:c r="N843" s="46"/>
       <x:c r="O843" s="34"/>
+      <x:c r="P843" s="32"/>
     </x:row>
     <x:row r="844">
       <x:c r="A844" s="34"/>
@@ -15295,6 +16159,7 @@
       <x:c r="M844" s="46"/>
       <x:c r="N844" s="46"/>
       <x:c r="O844" s="34"/>
+      <x:c r="P844" s="32"/>
     </x:row>
     <x:row r="845">
       <x:c r="A845" s="34"/>
@@ -15312,6 +16177,7 @@
       <x:c r="M845" s="46"/>
       <x:c r="N845" s="46"/>
       <x:c r="O845" s="34"/>
+      <x:c r="P845" s="32"/>
     </x:row>
     <x:row r="846">
       <x:c r="A846" s="34"/>
@@ -15329,6 +16195,7 @@
       <x:c r="M846" s="46"/>
       <x:c r="N846" s="46"/>
       <x:c r="O846" s="34"/>
+      <x:c r="P846" s="32"/>
     </x:row>
     <x:row r="847">
       <x:c r="A847" s="34"/>
@@ -15346,6 +16213,7 @@
       <x:c r="M847" s="46"/>
       <x:c r="N847" s="46"/>
       <x:c r="O847" s="34"/>
+      <x:c r="P847" s="32"/>
     </x:row>
     <x:row r="848">
       <x:c r="A848" s="34"/>
@@ -15363,6 +16231,7 @@
       <x:c r="M848" s="46"/>
       <x:c r="N848" s="46"/>
       <x:c r="O848" s="34"/>
+      <x:c r="P848" s="32"/>
     </x:row>
     <x:row r="849">
       <x:c r="A849" s="34"/>
@@ -15380,6 +16249,7 @@
       <x:c r="M849" s="46"/>
       <x:c r="N849" s="46"/>
       <x:c r="O849" s="34"/>
+      <x:c r="P849" s="32"/>
     </x:row>
     <x:row r="850">
       <x:c r="A850" s="34"/>
@@ -15397,6 +16267,7 @@
       <x:c r="M850" s="46"/>
       <x:c r="N850" s="46"/>
       <x:c r="O850" s="34"/>
+      <x:c r="P850" s="32"/>
     </x:row>
     <x:row r="851">
       <x:c r="A851" s="34"/>
@@ -15414,6 +16285,7 @@
       <x:c r="M851" s="46"/>
       <x:c r="N851" s="46"/>
       <x:c r="O851" s="34"/>
+      <x:c r="P851" s="32"/>
     </x:row>
     <x:row r="852">
       <x:c r="A852" s="34"/>
@@ -15431,6 +16303,7 @@
       <x:c r="M852" s="46"/>
       <x:c r="N852" s="46"/>
       <x:c r="O852" s="34"/>
+      <x:c r="P852" s="32"/>
     </x:row>
     <x:row r="853">
       <x:c r="A853" s="34"/>
@@ -15448,6 +16321,7 @@
       <x:c r="M853" s="46"/>
       <x:c r="N853" s="46"/>
       <x:c r="O853" s="34"/>
+      <x:c r="P853" s="32"/>
     </x:row>
     <x:row r="854">
       <x:c r="A854" s="34"/>
@@ -15465,6 +16339,7 @@
       <x:c r="M854" s="46"/>
       <x:c r="N854" s="46"/>
       <x:c r="O854" s="34"/>
+      <x:c r="P854" s="32"/>
     </x:row>
     <x:row r="855">
       <x:c r="A855" s="34"/>
@@ -15482,6 +16357,7 @@
       <x:c r="M855" s="46"/>
       <x:c r="N855" s="46"/>
       <x:c r="O855" s="34"/>
+      <x:c r="P855" s="32"/>
     </x:row>
     <x:row r="856">
       <x:c r="A856" s="34"/>
@@ -15499,6 +16375,7 @@
       <x:c r="M856" s="46"/>
       <x:c r="N856" s="46"/>
       <x:c r="O856" s="34"/>
+      <x:c r="P856" s="32"/>
     </x:row>
     <x:row r="857">
       <x:c r="A857" s="34"/>
@@ -15516,6 +16393,7 @@
       <x:c r="M857" s="46"/>
       <x:c r="N857" s="46"/>
       <x:c r="O857" s="34"/>
+      <x:c r="P857" s="32"/>
     </x:row>
     <x:row r="858">
       <x:c r="A858" s="34"/>
@@ -15533,6 +16411,7 @@
       <x:c r="M858" s="46"/>
       <x:c r="N858" s="46"/>
       <x:c r="O858" s="34"/>
+      <x:c r="P858" s="32"/>
     </x:row>
     <x:row r="859">
       <x:c r="A859" s="34"/>
@@ -15550,6 +16429,7 @@
       <x:c r="M859" s="46"/>
       <x:c r="N859" s="46"/>
       <x:c r="O859" s="34"/>
+      <x:c r="P859" s="32"/>
     </x:row>
     <x:row r="860">
       <x:c r="A860" s="34"/>
@@ -15567,6 +16447,7 @@
       <x:c r="M860" s="46"/>
       <x:c r="N860" s="46"/>
       <x:c r="O860" s="34"/>
+      <x:c r="P860" s="32"/>
     </x:row>
     <x:row r="861">
       <x:c r="A861" s="34"/>
@@ -15584,6 +16465,7 @@
       <x:c r="M861" s="46"/>
       <x:c r="N861" s="46"/>
       <x:c r="O861" s="34"/>
+      <x:c r="P861" s="32"/>
     </x:row>
     <x:row r="862">
       <x:c r="A862" s="34"/>
@@ -15601,6 +16483,7 @@
       <x:c r="M862" s="46"/>
       <x:c r="N862" s="46"/>
       <x:c r="O862" s="34"/>
+      <x:c r="P862" s="32"/>
     </x:row>
     <x:row r="863">
       <x:c r="A863" s="34"/>
@@ -15618,6 +16501,7 @@
       <x:c r="M863" s="46"/>
       <x:c r="N863" s="46"/>
       <x:c r="O863" s="34"/>
+      <x:c r="P863" s="32"/>
     </x:row>
     <x:row r="864">
       <x:c r="A864" s="34"/>
@@ -15635,6 +16519,7 @@
       <x:c r="M864" s="46"/>
       <x:c r="N864" s="46"/>
       <x:c r="O864" s="34"/>
+      <x:c r="P864" s="32"/>
     </x:row>
     <x:row r="865">
       <x:c r="A865" s="34"/>
@@ -15652,6 +16537,7 @@
       <x:c r="M865" s="46"/>
       <x:c r="N865" s="46"/>
       <x:c r="O865" s="34"/>
+      <x:c r="P865" s="32"/>
     </x:row>
     <x:row r="866">
       <x:c r="A866" s="34"/>
@@ -15669,6 +16555,7 @@
       <x:c r="M866" s="46"/>
       <x:c r="N866" s="46"/>
       <x:c r="O866" s="34"/>
+      <x:c r="P866" s="32"/>
     </x:row>
     <x:row r="867">
       <x:c r="A867" s="34"/>
@@ -15686,6 +16573,7 @@
       <x:c r="M867" s="46"/>
       <x:c r="N867" s="46"/>
       <x:c r="O867" s="34"/>
+      <x:c r="P867" s="32"/>
     </x:row>
     <x:row r="868">
       <x:c r="A868" s="34"/>
@@ -15703,6 +16591,7 @@
       <x:c r="M868" s="46"/>
       <x:c r="N868" s="46"/>
       <x:c r="O868" s="34"/>
+      <x:c r="P868" s="32"/>
     </x:row>
     <x:row r="869">
       <x:c r="A869" s="34"/>
@@ -15720,6 +16609,7 @@
       <x:c r="M869" s="46"/>
       <x:c r="N869" s="46"/>
       <x:c r="O869" s="34"/>
+      <x:c r="P869" s="32"/>
     </x:row>
     <x:row r="870">
       <x:c r="A870" s="34"/>
@@ -15737,6 +16627,7 @@
       <x:c r="M870" s="46"/>
       <x:c r="N870" s="46"/>
       <x:c r="O870" s="34"/>
+      <x:c r="P870" s="32"/>
     </x:row>
     <x:row r="871">
       <x:c r="A871" s="34"/>
@@ -15754,6 +16645,7 @@
       <x:c r="M871" s="46"/>
       <x:c r="N871" s="46"/>
       <x:c r="O871" s="34"/>
+      <x:c r="P871" s="32"/>
     </x:row>
     <x:row r="872">
       <x:c r="A872" s="34"/>
@@ -15771,6 +16663,7 @@
       <x:c r="M872" s="46"/>
       <x:c r="N872" s="46"/>
       <x:c r="O872" s="34"/>
+      <x:c r="P872" s="32"/>
     </x:row>
     <x:row r="873">
       <x:c r="A873" s="34"/>
@@ -15788,6 +16681,7 @@
       <x:c r="M873" s="46"/>
       <x:c r="N873" s="46"/>
       <x:c r="O873" s="34"/>
+      <x:c r="P873" s="32"/>
     </x:row>
     <x:row r="874">
       <x:c r="A874" s="34"/>
@@ -15805,6 +16699,7 @@
       <x:c r="M874" s="46"/>
       <x:c r="N874" s="46"/>
       <x:c r="O874" s="34"/>
+      <x:c r="P874" s="32"/>
     </x:row>
     <x:row r="875">
       <x:c r="A875" s="34"/>
@@ -15822,6 +16717,7 @@
       <x:c r="M875" s="46"/>
       <x:c r="N875" s="46"/>
       <x:c r="O875" s="34"/>
+      <x:c r="P875" s="32"/>
     </x:row>
     <x:row r="876">
       <x:c r="A876" s="34"/>
@@ -15839,6 +16735,7 @@
       <x:c r="M876" s="46"/>
       <x:c r="N876" s="46"/>
       <x:c r="O876" s="34"/>
+      <x:c r="P876" s="32"/>
     </x:row>
     <x:row r="877">
       <x:c r="A877" s="34"/>
@@ -15856,6 +16753,7 @@
       <x:c r="M877" s="46"/>
       <x:c r="N877" s="46"/>
       <x:c r="O877" s="34"/>
+      <x:c r="P877" s="32"/>
     </x:row>
     <x:row r="878">
       <x:c r="A878" s="34"/>
@@ -15873,6 +16771,7 @@
       <x:c r="M878" s="46"/>
       <x:c r="N878" s="46"/>
       <x:c r="O878" s="34"/>
+      <x:c r="P878" s="32"/>
     </x:row>
     <x:row r="879">
       <x:c r="A879" s="34"/>
@@ -15890,6 +16789,7 @@
       <x:c r="M879" s="46"/>
       <x:c r="N879" s="46"/>
       <x:c r="O879" s="34"/>
+      <x:c r="P879" s="32"/>
     </x:row>
     <x:row r="880">
       <x:c r="A880" s="34"/>
@@ -15907,6 +16807,7 @@
       <x:c r="M880" s="46"/>
       <x:c r="N880" s="46"/>
       <x:c r="O880" s="34"/>
+      <x:c r="P880" s="32"/>
     </x:row>
     <x:row r="881">
       <x:c r="A881" s="34"/>
@@ -15924,6 +16825,7 @@
       <x:c r="M881" s="46"/>
       <x:c r="N881" s="46"/>
       <x:c r="O881" s="34"/>
+      <x:c r="P881" s="32"/>
     </x:row>
     <x:row r="882">
       <x:c r="A882" s="34"/>
@@ -15941,6 +16843,7 @@
       <x:c r="M882" s="46"/>
       <x:c r="N882" s="46"/>
       <x:c r="O882" s="34"/>
+      <x:c r="P882" s="32"/>
     </x:row>
     <x:row r="883">
       <x:c r="A883" s="34"/>
@@ -15958,6 +16861,7 @@
       <x:c r="M883" s="46"/>
       <x:c r="N883" s="46"/>
       <x:c r="O883" s="34"/>
+      <x:c r="P883" s="32"/>
     </x:row>
     <x:row r="884">
       <x:c r="A884" s="34"/>
@@ -15975,6 +16879,7 @@
       <x:c r="M884" s="46"/>
       <x:c r="N884" s="46"/>
       <x:c r="O884" s="34"/>
+      <x:c r="P884" s="32"/>
     </x:row>
     <x:row r="885">
       <x:c r="A885" s="34"/>
@@ -15992,6 +16897,7 @@
       <x:c r="M885" s="46"/>
       <x:c r="N885" s="46"/>
       <x:c r="O885" s="34"/>
+      <x:c r="P885" s="32"/>
     </x:row>
     <x:row r="886">
       <x:c r="A886" s="34"/>
@@ -16009,6 +16915,7 @@
       <x:c r="M886" s="46"/>
       <x:c r="N886" s="46"/>
       <x:c r="O886" s="34"/>
+      <x:c r="P886" s="32"/>
     </x:row>
     <x:row r="887">
       <x:c r="A887" s="34"/>
@@ -16026,6 +16933,7 @@
       <x:c r="M887" s="46"/>
       <x:c r="N887" s="46"/>
       <x:c r="O887" s="34"/>
+      <x:c r="P887" s="32"/>
     </x:row>
     <x:row r="888">
       <x:c r="A888" s="34"/>
@@ -16043,6 +16951,7 @@
       <x:c r="M888" s="46"/>
       <x:c r="N888" s="46"/>
       <x:c r="O888" s="34"/>
+      <x:c r="P888" s="32"/>
     </x:row>
     <x:row r="889">
       <x:c r="A889" s="34"/>
@@ -16060,6 +16969,7 @@
       <x:c r="M889" s="46"/>
       <x:c r="N889" s="46"/>
       <x:c r="O889" s="34"/>
+      <x:c r="P889" s="32"/>
     </x:row>
     <x:row r="890">
       <x:c r="A890" s="34"/>
@@ -16077,6 +16987,7 @@
       <x:c r="M890" s="46"/>
       <x:c r="N890" s="46"/>
       <x:c r="O890" s="34"/>
+      <x:c r="P890" s="32"/>
     </x:row>
     <x:row r="891">
       <x:c r="A891" s="34"/>
@@ -16094,6 +17005,7 @@
       <x:c r="M891" s="46"/>
       <x:c r="N891" s="46"/>
       <x:c r="O891" s="34"/>
+      <x:c r="P891" s="32"/>
     </x:row>
     <x:row r="892">
       <x:c r="A892" s="34"/>
@@ -16111,6 +17023,7 @@
       <x:c r="M892" s="46"/>
       <x:c r="N892" s="46"/>
       <x:c r="O892" s="34"/>
+      <x:c r="P892" s="32"/>
     </x:row>
     <x:row r="893">
       <x:c r="A893" s="34"/>
@@ -16128,6 +17041,7 @@
       <x:c r="M893" s="46"/>
       <x:c r="N893" s="46"/>
       <x:c r="O893" s="34"/>
+      <x:c r="P893" s="32"/>
     </x:row>
     <x:row r="894">
       <x:c r="A894" s="34"/>
@@ -16145,6 +17059,7 @@
       <x:c r="M894" s="46"/>
       <x:c r="N894" s="46"/>
       <x:c r="O894" s="34"/>
+      <x:c r="P894" s="32"/>
     </x:row>
     <x:row r="895">
       <x:c r="A895" s="34"/>
@@ -16162,6 +17077,7 @@
       <x:c r="M895" s="46"/>
       <x:c r="N895" s="46"/>
       <x:c r="O895" s="34"/>
+      <x:c r="P895" s="32"/>
     </x:row>
     <x:row r="896">
       <x:c r="A896" s="34"/>
@@ -16179,6 +17095,7 @@
       <x:c r="M896" s="46"/>
       <x:c r="N896" s="46"/>
       <x:c r="O896" s="34"/>
+      <x:c r="P896" s="32"/>
     </x:row>
     <x:row r="897">
       <x:c r="A897" s="34"/>
@@ -16196,6 +17113,7 @@
       <x:c r="M897" s="46"/>
       <x:c r="N897" s="46"/>
       <x:c r="O897" s="34"/>
+      <x:c r="P897" s="32"/>
     </x:row>
     <x:row r="898">
       <x:c r="A898" s="34"/>
@@ -16213,6 +17131,7 @@
       <x:c r="M898" s="46"/>
       <x:c r="N898" s="46"/>
       <x:c r="O898" s="34"/>
+      <x:c r="P898" s="32"/>
     </x:row>
     <x:row r="899">
       <x:c r="A899" s="34"/>
@@ -16230,6 +17149,7 @@
       <x:c r="M899" s="46"/>
       <x:c r="N899" s="46"/>
       <x:c r="O899" s="34"/>
+      <x:c r="P899" s="32"/>
     </x:row>
     <x:row r="900">
       <x:c r="A900" s="34"/>
@@ -16247,6 +17167,7 @@
       <x:c r="M900" s="46"/>
       <x:c r="N900" s="46"/>
       <x:c r="O900" s="34"/>
+      <x:c r="P900" s="32"/>
     </x:row>
     <x:row r="901">
       <x:c r="A901" s="34"/>
@@ -16264,6 +17185,7 @@
       <x:c r="M901" s="46"/>
       <x:c r="N901" s="46"/>
       <x:c r="O901" s="34"/>
+      <x:c r="P901" s="32"/>
     </x:row>
     <x:row r="902">
       <x:c r="A902" s="34"/>
@@ -16281,6 +17203,7 @@
       <x:c r="M902" s="46"/>
       <x:c r="N902" s="46"/>
       <x:c r="O902" s="34"/>
+      <x:c r="P902" s="32"/>
     </x:row>
     <x:row r="903">
       <x:c r="A903" s="34"/>
@@ -16298,6 +17221,7 @@
       <x:c r="M903" s="46"/>
       <x:c r="N903" s="46"/>
       <x:c r="O903" s="34"/>
+      <x:c r="P903" s="32"/>
     </x:row>
     <x:row r="904">
       <x:c r="A904" s="34"/>
@@ -16315,6 +17239,7 @@
       <x:c r="M904" s="46"/>
       <x:c r="N904" s="46"/>
       <x:c r="O904" s="34"/>
+      <x:c r="P904" s="32"/>
     </x:row>
     <x:row r="905">
       <x:c r="A905" s="34"/>
@@ -16332,6 +17257,7 @@
       <x:c r="M905" s="46"/>
       <x:c r="N905" s="46"/>
       <x:c r="O905" s="34"/>
+      <x:c r="P905" s="32"/>
     </x:row>
     <x:row r="906">
       <x:c r="A906" s="34"/>
@@ -16349,6 +17275,7 @@
       <x:c r="M906" s="46"/>
       <x:c r="N906" s="46"/>
       <x:c r="O906" s="34"/>
+      <x:c r="P906" s="32"/>
     </x:row>
     <x:row r="907">
       <x:c r="A907" s="34"/>
@@ -16366,6 +17293,7 @@
       <x:c r="M907" s="46"/>
       <x:c r="N907" s="46"/>
       <x:c r="O907" s="34"/>
+      <x:c r="P907" s="32"/>
     </x:row>
     <x:row r="908">
       <x:c r="A908" s="34"/>
@@ -16383,6 +17311,7 @@
       <x:c r="M908" s="46"/>
       <x:c r="N908" s="46"/>
       <x:c r="O908" s="34"/>
+      <x:c r="P908" s="32"/>
     </x:row>
     <x:row r="909">
       <x:c r="A909" s="34"/>
@@ -16400,6 +17329,7 @@
       <x:c r="M909" s="46"/>
       <x:c r="N909" s="46"/>
       <x:c r="O909" s="34"/>
+      <x:c r="P909" s="32"/>
     </x:row>
     <x:row r="910">
       <x:c r="A910" s="34"/>
@@ -16417,6 +17347,7 @@
       <x:c r="M910" s="46"/>
       <x:c r="N910" s="46"/>
       <x:c r="O910" s="34"/>
+      <x:c r="P910" s="32"/>
     </x:row>
     <x:row r="911">
       <x:c r="A911" s="34"/>
@@ -16434,6 +17365,7 @@
       <x:c r="M911" s="46"/>
       <x:c r="N911" s="46"/>
       <x:c r="O911" s="34"/>
+      <x:c r="P911" s="32"/>
     </x:row>
     <x:row r="912">
       <x:c r="A912" s="34"/>
@@ -16451,6 +17383,7 @@
       <x:c r="M912" s="46"/>
       <x:c r="N912" s="46"/>
       <x:c r="O912" s="34"/>
+      <x:c r="P912" s="32"/>
     </x:row>
     <x:row r="913">
       <x:c r="A913" s="34"/>
@@ -16468,6 +17401,7 @@
       <x:c r="M913" s="46"/>
       <x:c r="N913" s="46"/>
       <x:c r="O913" s="34"/>
+      <x:c r="P913" s="32"/>
     </x:row>
     <x:row r="914">
       <x:c r="A914" s="34"/>
@@ -16485,6 +17419,7 @@
       <x:c r="M914" s="46"/>
       <x:c r="N914" s="46"/>
       <x:c r="O914" s="34"/>
+      <x:c r="P914" s="32"/>
     </x:row>
     <x:row r="915">
       <x:c r="A915" s="34"/>
@@ -16502,6 +17437,7 @@
       <x:c r="M915" s="46"/>
       <x:c r="N915" s="46"/>
       <x:c r="O915" s="34"/>
+      <x:c r="P915" s="32"/>
     </x:row>
     <x:row r="916">
       <x:c r="A916" s="34"/>
@@ -16519,6 +17455,7 @@
       <x:c r="M916" s="46"/>
       <x:c r="N916" s="46"/>
       <x:c r="O916" s="34"/>
+      <x:c r="P916" s="32"/>
     </x:row>
     <x:row r="917">
       <x:c r="A917" s="34"/>
@@ -16536,6 +17473,7 @@
       <x:c r="M917" s="46"/>
       <x:c r="N917" s="46"/>
       <x:c r="O917" s="34"/>
+      <x:c r="P917" s="32"/>
     </x:row>
     <x:row r="918">
       <x:c r="A918" s="34"/>
@@ -16553,6 +17491,7 @@
       <x:c r="M918" s="46"/>
       <x:c r="N918" s="46"/>
       <x:c r="O918" s="34"/>
+      <x:c r="P918" s="32"/>
     </x:row>
     <x:row r="919">
       <x:c r="A919" s="34"/>
@@ -16570,6 +17509,7 @@
       <x:c r="M919" s="46"/>
       <x:c r="N919" s="46"/>
       <x:c r="O919" s="34"/>
+      <x:c r="P919" s="32"/>
     </x:row>
     <x:row r="920">
       <x:c r="A920" s="34"/>
@@ -16587,6 +17527,7 @@
       <x:c r="M920" s="46"/>
       <x:c r="N920" s="46"/>
       <x:c r="O920" s="34"/>
+      <x:c r="P920" s="32"/>
     </x:row>
     <x:row r="921">
       <x:c r="A921" s="34"/>
@@ -16604,6 +17545,7 @@
       <x:c r="M921" s="46"/>
       <x:c r="N921" s="46"/>
       <x:c r="O921" s="34"/>
+      <x:c r="P921" s="32"/>
     </x:row>
     <x:row r="922">
       <x:c r="A922" s="34"/>
@@ -16621,6 +17563,7 @@
       <x:c r="M922" s="46"/>
       <x:c r="N922" s="46"/>
       <x:c r="O922" s="34"/>
+      <x:c r="P922" s="32"/>
     </x:row>
     <x:row r="923">
       <x:c r="A923" s="34"/>
@@ -16638,6 +17581,7 @@
       <x:c r="M923" s="46"/>
       <x:c r="N923" s="46"/>
       <x:c r="O923" s="34"/>
+      <x:c r="P923" s="32"/>
     </x:row>
     <x:row r="924">
       <x:c r="A924" s="34"/>
@@ -16655,6 +17599,7 @@
       <x:c r="M924" s="46"/>
       <x:c r="N924" s="46"/>
       <x:c r="O924" s="34"/>
+      <x:c r="P924" s="32"/>
     </x:row>
     <x:row r="925">
       <x:c r="A925" s="34"/>
@@ -16672,6 +17617,7 @@
       <x:c r="M925" s="46"/>
       <x:c r="N925" s="46"/>
       <x:c r="O925" s="34"/>
+      <x:c r="P925" s="32"/>
     </x:row>
     <x:row r="926">
       <x:c r="A926" s="34"/>
@@ -16689,6 +17635,7 @@
       <x:c r="M926" s="46"/>
       <x:c r="N926" s="46"/>
       <x:c r="O926" s="34"/>
+      <x:c r="P926" s="32"/>
     </x:row>
     <x:row r="927">
       <x:c r="A927" s="34"/>
@@ -16706,6 +17653,7 @@
       <x:c r="M927" s="46"/>
       <x:c r="N927" s="46"/>
       <x:c r="O927" s="34"/>
+      <x:c r="P927" s="32"/>
     </x:row>
     <x:row r="928">
       <x:c r="A928" s="34"/>
@@ -16723,6 +17671,7 @@
       <x:c r="M928" s="46"/>
       <x:c r="N928" s="46"/>
       <x:c r="O928" s="34"/>
+      <x:c r="P928" s="32"/>
     </x:row>
     <x:row r="929">
       <x:c r="A929" s="34"/>
@@ -16740,6 +17689,7 @@
       <x:c r="M929" s="46"/>
       <x:c r="N929" s="46"/>
       <x:c r="O929" s="34"/>
+      <x:c r="P929" s="32"/>
     </x:row>
     <x:row r="930">
       <x:c r="A930" s="34"/>
@@ -16757,6 +17707,7 @@
       <x:c r="M930" s="46"/>
       <x:c r="N930" s="46"/>
       <x:c r="O930" s="34"/>
+      <x:c r="P930" s="32"/>
     </x:row>
     <x:row r="931">
       <x:c r="A931" s="34"/>
@@ -16774,6 +17725,7 @@
       <x:c r="M931" s="46"/>
       <x:c r="N931" s="46"/>
       <x:c r="O931" s="34"/>
+      <x:c r="P931" s="32"/>
     </x:row>
     <x:row r="932">
       <x:c r="A932" s="34"/>
@@ -16791,6 +17743,7 @@
       <x:c r="M932" s="46"/>
       <x:c r="N932" s="46"/>
       <x:c r="O932" s="34"/>
+      <x:c r="P932" s="32"/>
     </x:row>
     <x:row r="933">
       <x:c r="A933" s="34"/>
@@ -16808,6 +17761,7 @@
       <x:c r="M933" s="46"/>
       <x:c r="N933" s="46"/>
       <x:c r="O933" s="34"/>
+      <x:c r="P933" s="32"/>
     </x:row>
     <x:row r="934">
       <x:c r="A934" s="34"/>
@@ -16825,6 +17779,7 @@
       <x:c r="M934" s="46"/>
       <x:c r="N934" s="46"/>
       <x:c r="O934" s="34"/>
+      <x:c r="P934" s="32"/>
     </x:row>
     <x:row r="935">
       <x:c r="A935" s="34"/>
@@ -16842,6 +17797,7 @@
       <x:c r="M935" s="46"/>
       <x:c r="N935" s="46"/>
       <x:c r="O935" s="34"/>
+      <x:c r="P935" s="32"/>
     </x:row>
     <x:row r="936">
       <x:c r="A936" s="34"/>
@@ -16859,6 +17815,7 @@
       <x:c r="M936" s="46"/>
       <x:c r="N936" s="46"/>
       <x:c r="O936" s="34"/>
+      <x:c r="P936" s="32"/>
     </x:row>
     <x:row r="937">
       <x:c r="A937" s="34"/>
@@ -16876,6 +17833,7 @@
       <x:c r="M937" s="46"/>
       <x:c r="N937" s="46"/>
       <x:c r="O937" s="34"/>
+      <x:c r="P937" s="32"/>
     </x:row>
     <x:row r="938">
       <x:c r="A938" s="34"/>
@@ -16893,6 +17851,7 @@
       <x:c r="M938" s="46"/>
       <x:c r="N938" s="46"/>
       <x:c r="O938" s="34"/>
+      <x:c r="P938" s="32"/>
     </x:row>
     <x:row r="939">
       <x:c r="A939" s="34"/>
@@ -16910,6 +17869,7 @@
       <x:c r="M939" s="46"/>
       <x:c r="N939" s="46"/>
       <x:c r="O939" s="34"/>
+      <x:c r="P939" s="32"/>
     </x:row>
     <x:row r="940">
       <x:c r="A940" s="34"/>
@@ -16927,6 +17887,7 @@
       <x:c r="M940" s="46"/>
       <x:c r="N940" s="46"/>
       <x:c r="O940" s="34"/>
+      <x:c r="P940" s="32"/>
     </x:row>
     <x:row r="941">
       <x:c r="A941" s="34"/>
@@ -16944,6 +17905,7 @@
       <x:c r="M941" s="46"/>
       <x:c r="N941" s="46"/>
       <x:c r="O941" s="34"/>
+      <x:c r="P941" s="32"/>
     </x:row>
     <x:row r="942">
       <x:c r="A942" s="34"/>
@@ -16961,6 +17923,7 @@
       <x:c r="M942" s="46"/>
       <x:c r="N942" s="46"/>
       <x:c r="O942" s="34"/>
+      <x:c r="P942" s="32"/>
     </x:row>
     <x:row r="943">
       <x:c r="A943" s="34"/>
@@ -16978,6 +17941,7 @@
       <x:c r="M943" s="46"/>
       <x:c r="N943" s="46"/>
       <x:c r="O943" s="34"/>
+      <x:c r="P943" s="32"/>
     </x:row>
     <x:row r="944">
       <x:c r="A944" s="34"/>
@@ -16995,6 +17959,7 @@
       <x:c r="M944" s="46"/>
       <x:c r="N944" s="46"/>
       <x:c r="O944" s="34"/>
+      <x:c r="P944" s="32"/>
     </x:row>
     <x:row r="945">
       <x:c r="A945" s="34"/>
@@ -17012,6 +17977,7 @@
       <x:c r="M945" s="46"/>
       <x:c r="N945" s="46"/>
       <x:c r="O945" s="34"/>
+      <x:c r="P945" s="32"/>
     </x:row>
     <x:row r="946">
       <x:c r="A946" s="34"/>
@@ -17029,6 +17995,7 @@
       <x:c r="M946" s="46"/>
       <x:c r="N946" s="46"/>
       <x:c r="O946" s="34"/>
+      <x:c r="P946" s="32"/>
     </x:row>
     <x:row r="947">
       <x:c r="A947" s="34"/>
@@ -17046,6 +18013,7 @@
       <x:c r="M947" s="46"/>
       <x:c r="N947" s="46"/>
       <x:c r="O947" s="34"/>
+      <x:c r="P947" s="32"/>
     </x:row>
     <x:row r="948">
       <x:c r="A948" s="34"/>
@@ -17063,6 +18031,7 @@
       <x:c r="M948" s="46"/>
       <x:c r="N948" s="46"/>
       <x:c r="O948" s="34"/>
+      <x:c r="P948" s="32"/>
     </x:row>
     <x:row r="949">
       <x:c r="A949" s="34"/>
@@ -17080,6 +18049,7 @@
       <x:c r="M949" s="46"/>
       <x:c r="N949" s="46"/>
       <x:c r="O949" s="34"/>
+      <x:c r="P949" s="32"/>
     </x:row>
     <x:row r="950">
       <x:c r="A950" s="34"/>
@@ -17097,6 +18067,7 @@
       <x:c r="M950" s="46"/>
       <x:c r="N950" s="46"/>
       <x:c r="O950" s="34"/>
+      <x:c r="P950" s="32"/>
     </x:row>
     <x:row r="951">
       <x:c r="A951" s="34"/>
@@ -17114,6 +18085,7 @@
       <x:c r="M951" s="46"/>
       <x:c r="N951" s="46"/>
       <x:c r="O951" s="34"/>
+      <x:c r="P951" s="32"/>
     </x:row>
     <x:row r="952">
       <x:c r="A952" s="34"/>
@@ -17131,6 +18103,7 @@
       <x:c r="M952" s="46"/>
       <x:c r="N952" s="46"/>
       <x:c r="O952" s="34"/>
+      <x:c r="P952" s="32"/>
     </x:row>
     <x:row r="953">
       <x:c r="A953" s="34"/>
@@ -17148,6 +18121,7 @@
       <x:c r="M953" s="46"/>
       <x:c r="N953" s="46"/>
       <x:c r="O953" s="34"/>
+      <x:c r="P953" s="32"/>
     </x:row>
     <x:row r="954">
       <x:c r="A954" s="34"/>
@@ -17165,6 +18139,7 @@
       <x:c r="M954" s="46"/>
       <x:c r="N954" s="46"/>
       <x:c r="O954" s="34"/>
+      <x:c r="P954" s="32"/>
     </x:row>
     <x:row r="955">
       <x:c r="A955" s="34"/>
@@ -17182,6 +18157,7 @@
       <x:c r="M955" s="46"/>
       <x:c r="N955" s="46"/>
       <x:c r="O955" s="34"/>
+      <x:c r="P955" s="32"/>
     </x:row>
     <x:row r="956">
       <x:c r="A956" s="34"/>
@@ -17199,6 +18175,7 @@
       <x:c r="M956" s="46"/>
       <x:c r="N956" s="46"/>
       <x:c r="O956" s="34"/>
+      <x:c r="P956" s="32"/>
     </x:row>
     <x:row r="957">
       <x:c r="A957" s="34"/>
@@ -17216,6 +18193,7 @@
       <x:c r="M957" s="46"/>
       <x:c r="N957" s="46"/>
       <x:c r="O957" s="34"/>
+      <x:c r="P957" s="32"/>
     </x:row>
     <x:row r="958">
       <x:c r="A958" s="34"/>
@@ -17233,6 +18211,7 @@
       <x:c r="M958" s="46"/>
       <x:c r="N958" s="46"/>
       <x:c r="O958" s="34"/>
+      <x:c r="P958" s="32"/>
     </x:row>
     <x:row r="959">
       <x:c r="A959" s="34"/>
@@ -17250,6 +18229,7 @@
       <x:c r="M959" s="46"/>
       <x:c r="N959" s="46"/>
       <x:c r="O959" s="34"/>
+      <x:c r="P959" s="32"/>
     </x:row>
     <x:row r="960">
       <x:c r="A960" s="34"/>
@@ -17267,6 +18247,7 @@
       <x:c r="M960" s="46"/>
       <x:c r="N960" s="46"/>
       <x:c r="O960" s="34"/>
+      <x:c r="P960" s="32"/>
     </x:row>
     <x:row r="961">
       <x:c r="A961" s="34"/>
@@ -17284,6 +18265,7 @@
       <x:c r="M961" s="46"/>
       <x:c r="N961" s="46"/>
       <x:c r="O961" s="34"/>
+      <x:c r="P961" s="32"/>
     </x:row>
     <x:row r="962">
       <x:c r="A962" s="34"/>
@@ -17301,6 +18283,7 @@
       <x:c r="M962" s="46"/>
       <x:c r="N962" s="46"/>
       <x:c r="O962" s="34"/>
+      <x:c r="P962" s="32"/>
     </x:row>
     <x:row r="963">
       <x:c r="A963" s="34"/>
@@ -17318,6 +18301,7 @@
       <x:c r="M963" s="46"/>
       <x:c r="N963" s="46"/>
       <x:c r="O963" s="34"/>
+      <x:c r="P963" s="32"/>
     </x:row>
     <x:row r="964">
       <x:c r="A964" s="34"/>
@@ -17335,6 +18319,7 @@
       <x:c r="M964" s="46"/>
       <x:c r="N964" s="46"/>
       <x:c r="O964" s="34"/>
+      <x:c r="P964" s="32"/>
     </x:row>
     <x:row r="965">
       <x:c r="A965" s="34"/>
@@ -17352,6 +18337,7 @@
       <x:c r="M965" s="46"/>
       <x:c r="N965" s="46"/>
       <x:c r="O965" s="34"/>
+      <x:c r="P965" s="32"/>
     </x:row>
     <x:row r="966">
       <x:c r="A966" s="34"/>
@@ -17369,6 +18355,7 @@
       <x:c r="M966" s="46"/>
       <x:c r="N966" s="46"/>
       <x:c r="O966" s="34"/>
+      <x:c r="P966" s="32"/>
     </x:row>
     <x:row r="967">
       <x:c r="A967" s="34"/>
@@ -17386,6 +18373,7 @@
       <x:c r="M967" s="46"/>
       <x:c r="N967" s="46"/>
       <x:c r="O967" s="34"/>
+      <x:c r="P967" s="32"/>
     </x:row>
     <x:row r="968">
       <x:c r="A968" s="34"/>
@@ -17403,6 +18391,7 @@
       <x:c r="M968" s="46"/>
       <x:c r="N968" s="46"/>
       <x:c r="O968" s="34"/>
+      <x:c r="P968" s="32"/>
     </x:row>
     <x:row r="969">
       <x:c r="A969" s="34"/>
@@ -17420,6 +18409,7 @@
       <x:c r="M969" s="46"/>
       <x:c r="N969" s="46"/>
       <x:c r="O969" s="34"/>
+      <x:c r="P969" s="32"/>
     </x:row>
     <x:row r="970">
       <x:c r="A970" s="34"/>
@@ -17437,6 +18427,7 @@
       <x:c r="M970" s="46"/>
       <x:c r="N970" s="46"/>
       <x:c r="O970" s="34"/>
+      <x:c r="P970" s="32"/>
     </x:row>
     <x:row r="971">
       <x:c r="A971" s="34"/>
@@ -17454,6 +18445,7 @@
       <x:c r="M971" s="46"/>
       <x:c r="N971" s="46"/>
       <x:c r="O971" s="34"/>
+      <x:c r="P971" s="32"/>
     </x:row>
     <x:row r="972">
       <x:c r="A972" s="34"/>
@@ -17471,6 +18463,7 @@
       <x:c r="M972" s="46"/>
       <x:c r="N972" s="46"/>
       <x:c r="O972" s="34"/>
+      <x:c r="P972" s="32"/>
     </x:row>
     <x:row r="973">
       <x:c r="A973" s="34"/>
@@ -17488,6 +18481,7 @@
       <x:c r="M973" s="46"/>
       <x:c r="N973" s="46"/>
       <x:c r="O973" s="34"/>
+      <x:c r="P973" s="32"/>
     </x:row>
     <x:row r="974">
       <x:c r="A974" s="34"/>
@@ -17505,6 +18499,7 @@
       <x:c r="M974" s="46"/>
       <x:c r="N974" s="46"/>
       <x:c r="O974" s="34"/>
+      <x:c r="P974" s="32"/>
     </x:row>
     <x:row r="975">
       <x:c r="A975" s="34"/>
@@ -17522,6 +18517,7 @@
       <x:c r="M975" s="46"/>
       <x:c r="N975" s="46"/>
       <x:c r="O975" s="34"/>
+      <x:c r="P975" s="32"/>
     </x:row>
     <x:row r="976">
       <x:c r="A976" s="34"/>
@@ -17539,6 +18535,7 @@
       <x:c r="M976" s="46"/>
       <x:c r="N976" s="46"/>
       <x:c r="O976" s="34"/>
+      <x:c r="P976" s="32"/>
     </x:row>
     <x:row r="977">
       <x:c r="A977" s="34"/>
@@ -17556,6 +18553,7 @@
       <x:c r="M977" s="46"/>
       <x:c r="N977" s="46"/>
       <x:c r="O977" s="34"/>
+      <x:c r="P977" s="32"/>
     </x:row>
     <x:row r="978">
       <x:c r="A978" s="34"/>
@@ -17573,6 +18571,7 @@
       <x:c r="M978" s="46"/>
       <x:c r="N978" s="46"/>
       <x:c r="O978" s="34"/>
+      <x:c r="P978" s="32"/>
     </x:row>
     <x:row r="979">
       <x:c r="A979" s="34"/>
@@ -17590,6 +18589,7 @@
       <x:c r="M979" s="46"/>
       <x:c r="N979" s="46"/>
       <x:c r="O979" s="34"/>
+      <x:c r="P979" s="32"/>
     </x:row>
     <x:row r="980">
       <x:c r="A980" s="34"/>
@@ -17607,6 +18607,7 @@
       <x:c r="M980" s="46"/>
       <x:c r="N980" s="46"/>
       <x:c r="O980" s="34"/>
+      <x:c r="P980" s="32"/>
     </x:row>
     <x:row r="981">
       <x:c r="A981" s="34"/>
@@ -17624,6 +18625,7 @@
       <x:c r="M981" s="46"/>
       <x:c r="N981" s="46"/>
       <x:c r="O981" s="34"/>
+      <x:c r="P981" s="32"/>
     </x:row>
     <x:row r="982">
       <x:c r="A982" s="34"/>
@@ -17641,6 +18643,7 @@
       <x:c r="M982" s="46"/>
       <x:c r="N982" s="46"/>
       <x:c r="O982" s="34"/>
+      <x:c r="P982" s="32"/>
     </x:row>
     <x:row r="983">
       <x:c r="A983" s="34"/>
@@ -17658,6 +18661,7 @@
       <x:c r="M983" s="46"/>
       <x:c r="N983" s="46"/>
       <x:c r="O983" s="34"/>
+      <x:c r="P983" s="32"/>
     </x:row>
     <x:row r="984">
       <x:c r="A984" s="34"/>
@@ -17675,6 +18679,7 @@
       <x:c r="M984" s="46"/>
       <x:c r="N984" s="46"/>
       <x:c r="O984" s="34"/>
+      <x:c r="P984" s="32"/>
     </x:row>
     <x:row r="985">
       <x:c r="A985" s="34"/>
@@ -17692,6 +18697,7 @@
       <x:c r="M985" s="46"/>
       <x:c r="N985" s="46"/>
       <x:c r="O985" s="34"/>
+      <x:c r="P985" s="32"/>
     </x:row>
     <x:row r="986">
       <x:c r="A986" s="34"/>
@@ -17709,6 +18715,7 @@
       <x:c r="M986" s="46"/>
       <x:c r="N986" s="46"/>
       <x:c r="O986" s="34"/>
+      <x:c r="P986" s="32"/>
     </x:row>
     <x:row r="987">
       <x:c r="A987" s="34"/>
@@ -17726,6 +18733,7 @@
       <x:c r="M987" s="46"/>
       <x:c r="N987" s="46"/>
       <x:c r="O987" s="34"/>
+      <x:c r="P987" s="32"/>
     </x:row>
     <x:row r="988">
       <x:c r="A988" s="34"/>
@@ -17743,6 +18751,7 @@
       <x:c r="M988" s="46"/>
       <x:c r="N988" s="46"/>
       <x:c r="O988" s="34"/>
+      <x:c r="P988" s="32"/>
     </x:row>
     <x:row r="989">
       <x:c r="A989" s="34"/>
@@ -17760,6 +18769,7 @@
       <x:c r="M989" s="46"/>
       <x:c r="N989" s="46"/>
       <x:c r="O989" s="34"/>
+      <x:c r="P989" s="32"/>
     </x:row>
     <x:row r="990">
       <x:c r="A990" s="34"/>
@@ -17777,6 +18787,7 @@
       <x:c r="M990" s="46"/>
       <x:c r="N990" s="46"/>
       <x:c r="O990" s="34"/>
+      <x:c r="P990" s="32"/>
     </x:row>
     <x:row r="991">
       <x:c r="A991" s="34"/>
@@ -17794,6 +18805,7 @@
       <x:c r="M991" s="46"/>
       <x:c r="N991" s="46"/>
       <x:c r="O991" s="34"/>
+      <x:c r="P991" s="32"/>
     </x:row>
     <x:row r="992">
       <x:c r="A992" s="34"/>
@@ -17811,6 +18823,7 @@
       <x:c r="M992" s="46"/>
       <x:c r="N992" s="46"/>
       <x:c r="O992" s="34"/>
+      <x:c r="P992" s="32"/>
     </x:row>
     <x:row r="993">
       <x:c r="A993" s="34"/>
@@ -17828,6 +18841,7 @@
       <x:c r="M993" s="46"/>
       <x:c r="N993" s="46"/>
       <x:c r="O993" s="34"/>
+      <x:c r="P993" s="32"/>
     </x:row>
     <x:row r="994">
       <x:c r="A994" s="34"/>
@@ -17845,6 +18859,7 @@
       <x:c r="M994" s="46"/>
       <x:c r="N994" s="46"/>
       <x:c r="O994" s="34"/>
+      <x:c r="P994" s="32"/>
     </x:row>
     <x:row r="995">
       <x:c r="A995" s="34"/>
@@ -17862,6 +18877,7 @@
       <x:c r="M995" s="46"/>
       <x:c r="N995" s="46"/>
       <x:c r="O995" s="34"/>
+      <x:c r="P995" s="32"/>
     </x:row>
     <x:row r="996">
       <x:c r="A996" s="34"/>
@@ -17879,6 +18895,7 @@
       <x:c r="M996" s="46"/>
       <x:c r="N996" s="46"/>
       <x:c r="O996" s="34"/>
+      <x:c r="P996" s="32"/>
     </x:row>
     <x:row r="997">
       <x:c r="A997" s="34"/>
@@ -17896,6 +18913,7 @@
       <x:c r="M997" s="46"/>
       <x:c r="N997" s="46"/>
       <x:c r="O997" s="34"/>
+      <x:c r="P997" s="32"/>
     </x:row>
     <x:row r="998">
       <x:c r="A998" s="34"/>
@@ -17913,6 +18931,7 @@
       <x:c r="M998" s="46"/>
       <x:c r="N998" s="46"/>
       <x:c r="O998" s="34"/>
+      <x:c r="P998" s="32"/>
     </x:row>
     <x:row r="999">
       <x:c r="A999" s="34"/>
@@ -17930,6 +18949,7 @@
       <x:c r="M999" s="46"/>
       <x:c r="N999" s="46"/>
       <x:c r="O999" s="34"/>
+      <x:c r="P999" s="32"/>
     </x:row>
     <x:row r="1000">
       <x:c r="A1000" s="35"/>
@@ -17947,6 +18967,10 @@
       <x:c r="M1000" s="47"/>
       <x:c r="N1000" s="47"/>
       <x:c r="O1000" s="35"/>
+      <x:c r="P1000" s="32"/>
+    </x:row>
+    <x:row r="1001">
+      <x:c r="P1001" s="32"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A2:A1000">
@@ -17989,7 +19013,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b7c1df9fb64450b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc4527cd30e64f22"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Company_HTX586.xlsx
+++ b/src/HTX586CONTRACT.Web/wwwroot/templates/Template_Import_Company_HTX586.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_COMPANY" sheetId="1" r:id="R3963a5b682ed413a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="2" r:id="R7523141b2e4541a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMPORT_COMPANY" sheetId="1" r:id="Rb202c764b9d54a13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HUONG_DAN" sheetId="2" r:id="R2a04c95ba9974de6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -903,6 +903,7 @@
     <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="42" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
@@ -954,6 +955,9 @@
       <x:c r="P1" s="150" t="str">
         <x:v>ComplaintContact</x:v>
       </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>BusinessLicenseIssuedPlace</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="43" t="str">
@@ -1004,6 +1008,9 @@
       <x:c r="P2" s="32" t="str">
         <x:v>Sở GTVT Cần Thơ: 0939.984.333 - 0907.877.758</x:v>
       </x:c>
+      <x:c r="Q2" t="str">
+        <x:v>Sở Giao Thông Vận Tải Cần Thơ</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="34"/>
@@ -1022,6 +1029,7 @@
       <x:c r="N3" s="46"/>
       <x:c r="O3" s="34"/>
       <x:c r="P3" s="32"/>
+      <x:c r="Q3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="34"/>
@@ -1040,6 +1048,7 @@
       <x:c r="N4" s="46"/>
       <x:c r="O4" s="34"/>
       <x:c r="P4" s="32"/>
+      <x:c r="Q4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="34"/>
@@ -1058,6 +1067,7 @@
       <x:c r="N5" s="46"/>
       <x:c r="O5" s="34"/>
       <x:c r="P5" s="32"/>
+      <x:c r="Q5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="34"/>
@@ -1076,6 +1086,7 @@
       <x:c r="N6" s="46"/>
       <x:c r="O6" s="34"/>
       <x:c r="P6" s="32"/>
+      <x:c r="Q6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="34"/>
@@ -1094,6 +1105,7 @@
       <x:c r="N7" s="46"/>
       <x:c r="O7" s="34"/>
       <x:c r="P7" s="32"/>
+      <x:c r="Q7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="34"/>
@@ -1112,6 +1124,7 @@
       <x:c r="N8" s="46"/>
       <x:c r="O8" s="34"/>
       <x:c r="P8" s="32"/>
+      <x:c r="Q8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="34"/>
@@ -1130,6 +1143,7 @@
       <x:c r="N9" s="46"/>
       <x:c r="O9" s="34"/>
       <x:c r="P9" s="32"/>
+      <x:c r="Q9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="34"/>
@@ -1148,6 +1162,7 @@
       <x:c r="N10" s="46"/>
       <x:c r="O10" s="34"/>
       <x:c r="P10" s="32"/>
+      <x:c r="Q10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="34"/>
@@ -1166,6 +1181,7 @@
       <x:c r="N11" s="46"/>
       <x:c r="O11" s="34"/>
       <x:c r="P11" s="32"/>
+      <x:c r="Q11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="34"/>
@@ -1184,6 +1200,7 @@
       <x:c r="N12" s="46"/>
       <x:c r="O12" s="34"/>
       <x:c r="P12" s="32"/>
+      <x:c r="Q12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="34"/>
@@ -1202,6 +1219,7 @@
       <x:c r="N13" s="46"/>
       <x:c r="O13" s="34"/>
       <x:c r="P13" s="32"/>
+      <x:c r="Q13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="34"/>
@@ -1220,6 +1238,7 @@
       <x:c r="N14" s="46"/>
       <x:c r="O14" s="34"/>
       <x:c r="P14" s="32"/>
+      <x:c r="Q14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="34"/>
@@ -1238,6 +1257,7 @@
       <x:c r="N15" s="46"/>
       <x:c r="O15" s="34"/>
       <x:c r="P15" s="32"/>
+      <x:c r="Q15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="34"/>
@@ -1256,6 +1276,7 @@
       <x:c r="N16" s="46"/>
       <x:c r="O16" s="34"/>
       <x:c r="P16" s="32"/>
+      <x:c r="Q16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="34"/>
@@ -1274,6 +1295,7 @@
       <x:c r="N17" s="46"/>
       <x:c r="O17" s="34"/>
       <x:c r="P17" s="32"/>
+      <x:c r="Q17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="34"/>
@@ -1292,6 +1314,7 @@
       <x:c r="N18" s="46"/>
       <x:c r="O18" s="34"/>
       <x:c r="P18" s="32"/>
+      <x:c r="Q18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="34"/>
@@ -1310,6 +1333,7 @@
       <x:c r="N19" s="46"/>
       <x:c r="O19" s="34"/>
       <x:c r="P19" s="32"/>
+      <x:c r="Q19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="34"/>
@@ -1328,6 +1352,7 @@
       <x:c r="N20" s="46"/>
       <x:c r="O20" s="34"/>
       <x:c r="P20" s="32"/>
+      <x:c r="Q20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="34"/>
@@ -1346,6 +1371,7 @@
       <x:c r="N21" s="46"/>
       <x:c r="O21" s="34"/>
       <x:c r="P21" s="32"/>
+      <x:c r="Q21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="34"/>
@@ -1364,6 +1390,7 @@
       <x:c r="N22" s="46"/>
       <x:c r="O22" s="34"/>
       <x:c r="P22" s="32"/>
+      <x:c r="Q22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="34"/>
@@ -1382,6 +1409,7 @@
       <x:c r="N23" s="46"/>
       <x:c r="O23" s="34"/>
       <x:c r="P23" s="32"/>
+      <x:c r="Q23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="34"/>
@@ -1400,6 +1428,7 @@
       <x:c r="N24" s="46"/>
       <x:c r="O24" s="34"/>
       <x:c r="P24" s="32"/>
+      <x:c r="Q24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="34"/>
@@ -1418,6 +1447,7 @@
       <x:c r="N25" s="46"/>
       <x:c r="O25" s="34"/>
       <x:c r="P25" s="32"/>
+      <x:c r="Q25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="34"/>
@@ -1436,6 +1466,7 @@
       <x:c r="N26" s="46"/>
       <x:c r="O26" s="34"/>
       <x:c r="P26" s="32"/>
+      <x:c r="Q26"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="34"/>
@@ -1454,6 +1485,7 @@
       <x:c r="N27" s="46"/>
       <x:c r="O27" s="34"/>
       <x:c r="P27" s="32"/>
+      <x:c r="Q27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="34"/>
@@ -1472,6 +1504,7 @@
       <x:c r="N28" s="46"/>
       <x:c r="O28" s="34"/>
       <x:c r="P28" s="32"/>
+      <x:c r="Q28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="34"/>
@@ -1490,6 +1523,7 @@
       <x:c r="N29" s="46"/>
       <x:c r="O29" s="34"/>
       <x:c r="P29" s="32"/>
+      <x:c r="Q29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="34"/>
@@ -1508,6 +1542,7 @@
       <x:c r="N30" s="46"/>
       <x:c r="O30" s="34"/>
       <x:c r="P30" s="32"/>
+      <x:c r="Q30"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="34"/>
@@ -1526,6 +1561,7 @@
       <x:c r="N31" s="46"/>
       <x:c r="O31" s="34"/>
       <x:c r="P31" s="32"/>
+      <x:c r="Q31"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="34"/>
@@ -1544,6 +1580,7 @@
       <x:c r="N32" s="46"/>
       <x:c r="O32" s="34"/>
       <x:c r="P32" s="32"/>
+      <x:c r="Q32"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="34"/>
@@ -1562,6 +1599,7 @@
       <x:c r="N33" s="46"/>
       <x:c r="O33" s="34"/>
       <x:c r="P33" s="32"/>
+      <x:c r="Q33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="34"/>
@@ -1580,6 +1618,7 @@
       <x:c r="N34" s="46"/>
       <x:c r="O34" s="34"/>
       <x:c r="P34" s="32"/>
+      <x:c r="Q34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="34"/>
@@ -1598,6 +1637,7 @@
       <x:c r="N35" s="46"/>
       <x:c r="O35" s="34"/>
       <x:c r="P35" s="32"/>
+      <x:c r="Q35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="34"/>
@@ -1616,6 +1656,7 @@
       <x:c r="N36" s="46"/>
       <x:c r="O36" s="34"/>
       <x:c r="P36" s="32"/>
+      <x:c r="Q36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="34"/>
@@ -1634,6 +1675,7 @@
       <x:c r="N37" s="46"/>
       <x:c r="O37" s="34"/>
       <x:c r="P37" s="32"/>
+      <x:c r="Q37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="34"/>
@@ -1652,6 +1694,7 @@
       <x:c r="N38" s="46"/>
       <x:c r="O38" s="34"/>
       <x:c r="P38" s="32"/>
+      <x:c r="Q38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="34"/>
@@ -1670,6 +1713,7 @@
       <x:c r="N39" s="46"/>
       <x:c r="O39" s="34"/>
       <x:c r="P39" s="32"/>
+      <x:c r="Q39"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="34"/>
@@ -1688,6 +1732,7 @@
       <x:c r="N40" s="46"/>
       <x:c r="O40" s="34"/>
       <x:c r="P40" s="32"/>
+      <x:c r="Q40"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="34"/>
@@ -1706,6 +1751,7 @@
       <x:c r="N41" s="46"/>
       <x:c r="O41" s="34"/>
       <x:c r="P41" s="32"/>
+      <x:c r="Q41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="34"/>
@@ -1724,6 +1770,7 @@
       <x:c r="N42" s="46"/>
       <x:c r="O42" s="34"/>
       <x:c r="P42" s="32"/>
+      <x:c r="Q42"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="34"/>
@@ -1742,6 +1789,7 @@
       <x:c r="N43" s="46"/>
       <x:c r="O43" s="34"/>
       <x:c r="P43" s="32"/>
+      <x:c r="Q43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="34"/>
@@ -1760,6 +1808,7 @@
       <x:c r="N44" s="46"/>
       <x:c r="O44" s="34"/>
       <x:c r="P44" s="32"/>
+      <x:c r="Q44"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="34"/>
@@ -1778,6 +1827,7 @@
       <x:c r="N45" s="46"/>
       <x:c r="O45" s="34"/>
       <x:c r="P45" s="32"/>
+      <x:c r="Q45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="34"/>
@@ -1796,6 +1846,7 @@
       <x:c r="N46" s="46"/>
       <x:c r="O46" s="34"/>
       <x:c r="P46" s="32"/>
+      <x:c r="Q46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="34"/>
@@ -1814,6 +1865,7 @@
       <x:c r="N47" s="46"/>
       <x:c r="O47" s="34"/>
       <x:c r="P47" s="32"/>
+      <x:c r="Q47"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="34"/>
@@ -1832,6 +1884,7 @@
       <x:c r="N48" s="46"/>
       <x:c r="O48" s="34"/>
       <x:c r="P48" s="32"/>
+      <x:c r="Q48"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="34"/>
@@ -1850,6 +1903,7 @@
       <x:c r="N49" s="46"/>
       <x:c r="O49" s="34"/>
       <x:c r="P49" s="32"/>
+      <x:c r="Q49"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="34"/>
@@ -1868,6 +1922,7 @@
       <x:c r="N50" s="46"/>
       <x:c r="O50" s="34"/>
       <x:c r="P50" s="32"/>
+      <x:c r="Q50"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="34"/>
@@ -1886,6 +1941,7 @@
       <x:c r="N51" s="46"/>
       <x:c r="O51" s="34"/>
       <x:c r="P51" s="32"/>
+      <x:c r="Q51"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="34"/>
@@ -1904,6 +1960,7 @@
       <x:c r="N52" s="46"/>
       <x:c r="O52" s="34"/>
       <x:c r="P52" s="32"/>
+      <x:c r="Q52"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="34"/>
@@ -1922,6 +1979,7 @@
       <x:c r="N53" s="46"/>
       <x:c r="O53" s="34"/>
       <x:c r="P53" s="32"/>
+      <x:c r="Q53"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="34"/>
@@ -1940,6 +1998,7 @@
       <x:c r="N54" s="46"/>
       <x:c r="O54" s="34"/>
       <x:c r="P54" s="32"/>
+      <x:c r="Q54"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="34"/>
@@ -1958,6 +2017,7 @@
       <x:c r="N55" s="46"/>
       <x:c r="O55" s="34"/>
       <x:c r="P55" s="32"/>
+      <x:c r="Q55"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="34"/>
@@ -1976,6 +2036,7 @@
       <x:c r="N56" s="46"/>
       <x:c r="O56" s="34"/>
       <x:c r="P56" s="32"/>
+      <x:c r="Q56"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="34"/>
@@ -1994,6 +2055,7 @@
       <x:c r="N57" s="46"/>
       <x:c r="O57" s="34"/>
       <x:c r="P57" s="32"/>
+      <x:c r="Q57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="34"/>
@@ -2012,6 +2074,7 @@
       <x:c r="N58" s="46"/>
       <x:c r="O58" s="34"/>
       <x:c r="P58" s="32"/>
+      <x:c r="Q58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="34"/>
@@ -2030,6 +2093,7 @@
       <x:c r="N59" s="46"/>
       <x:c r="O59" s="34"/>
       <x:c r="P59" s="32"/>
+      <x:c r="Q59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="34"/>
@@ -2048,6 +2112,7 @@
       <x:c r="N60" s="46"/>
       <x:c r="O60" s="34"/>
       <x:c r="P60" s="32"/>
+      <x:c r="Q60"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="34"/>
@@ -2066,6 +2131,7 @@
       <x:c r="N61" s="46"/>
       <x:c r="O61" s="34"/>
       <x:c r="P61" s="32"/>
+      <x:c r="Q61"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="34"/>
@@ -2084,6 +2150,7 @@
       <x:c r="N62" s="46"/>
       <x:c r="O62" s="34"/>
       <x:c r="P62" s="32"/>
+      <x:c r="Q62"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="34"/>
@@ -2102,6 +2169,7 @@
       <x:c r="N63" s="46"/>
       <x:c r="O63" s="34"/>
       <x:c r="P63" s="32"/>
+      <x:c r="Q63"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="34"/>
@@ -2120,6 +2188,7 @@
       <x:c r="N64" s="46"/>
       <x:c r="O64" s="34"/>
       <x:c r="P64" s="32"/>
+      <x:c r="Q64"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="34"/>
@@ -2138,6 +2207,7 @@
       <x:c r="N65" s="46"/>
       <x:c r="O65" s="34"/>
       <x:c r="P65" s="32"/>
+      <x:c r="Q65"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="34"/>
@@ -2156,6 +2226,7 @@
       <x:c r="N66" s="46"/>
       <x:c r="O66" s="34"/>
       <x:c r="P66" s="32"/>
+      <x:c r="Q66"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="34"/>
@@ -2174,6 +2245,7 @@
       <x:c r="N67" s="46"/>
       <x:c r="O67" s="34"/>
       <x:c r="P67" s="32"/>
+      <x:c r="Q67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="34"/>
@@ -2192,6 +2264,7 @@
       <x:c r="N68" s="46"/>
       <x:c r="O68" s="34"/>
       <x:c r="P68" s="32"/>
+      <x:c r="Q68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="34"/>
@@ -2210,6 +2283,7 @@
       <x:c r="N69" s="46"/>
       <x:c r="O69" s="34"/>
       <x:c r="P69" s="32"/>
+      <x:c r="Q69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="34"/>
@@ -2228,6 +2302,7 @@
       <x:c r="N70" s="46"/>
       <x:c r="O70" s="34"/>
       <x:c r="P70" s="32"/>
+      <x:c r="Q70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="34"/>
@@ -2246,6 +2321,7 @@
       <x:c r="N71" s="46"/>
       <x:c r="O71" s="34"/>
       <x:c r="P71" s="32"/>
+      <x:c r="Q71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="34"/>
@@ -2264,6 +2340,7 @@
       <x:c r="N72" s="46"/>
       <x:c r="O72" s="34"/>
       <x:c r="P72" s="32"/>
+      <x:c r="Q72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="34"/>
@@ -2282,6 +2359,7 @@
       <x:c r="N73" s="46"/>
       <x:c r="O73" s="34"/>
       <x:c r="P73" s="32"/>
+      <x:c r="Q73"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="34"/>
@@ -2300,6 +2378,7 @@
       <x:c r="N74" s="46"/>
       <x:c r="O74" s="34"/>
       <x:c r="P74" s="32"/>
+      <x:c r="Q74"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="34"/>
@@ -2318,6 +2397,7 @@
       <x:c r="N75" s="46"/>
       <x:c r="O75" s="34"/>
       <x:c r="P75" s="32"/>
+      <x:c r="Q75"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="34"/>
@@ -2336,6 +2416,7 @@
       <x:c r="N76" s="46"/>
       <x:c r="O76" s="34"/>
       <x:c r="P76" s="32"/>
+      <x:c r="Q76"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="34"/>
@@ -2354,6 +2435,7 @@
       <x:c r="N77" s="46"/>
       <x:c r="O77" s="34"/>
       <x:c r="P77" s="32"/>
+      <x:c r="Q77"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="34"/>
@@ -2372,6 +2454,7 @@
       <x:c r="N78" s="46"/>
       <x:c r="O78" s="34"/>
       <x:c r="P78" s="32"/>
+      <x:c r="Q78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="34"/>
@@ -2390,6 +2473,7 @@
       <x:c r="N79" s="46"/>
       <x:c r="O79" s="34"/>
       <x:c r="P79" s="32"/>
+      <x:c r="Q79"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="34"/>
@@ -2408,6 +2492,7 @@
       <x:c r="N80" s="46"/>
       <x:c r="O80" s="34"/>
       <x:c r="P80" s="32"/>
+      <x:c r="Q80"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="34"/>
@@ -2426,6 +2511,7 @@
       <x:c r="N81" s="46"/>
       <x:c r="O81" s="34"/>
       <x:c r="P81" s="32"/>
+      <x:c r="Q81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="34"/>
@@ -2444,6 +2530,7 @@
       <x:c r="N82" s="46"/>
       <x:c r="O82" s="34"/>
       <x:c r="P82" s="32"/>
+      <x:c r="Q82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="34"/>
@@ -2462,6 +2549,7 @@
       <x:c r="N83" s="46"/>
       <x:c r="O83" s="34"/>
       <x:c r="P83" s="32"/>
+      <x:c r="Q83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="34"/>
@@ -2480,6 +2568,7 @@
       <x:c r="N84" s="46"/>
       <x:c r="O84" s="34"/>
       <x:c r="P84" s="32"/>
+      <x:c r="Q84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="34"/>
@@ -2498,6 +2587,7 @@
       <x:c r="N85" s="46"/>
       <x:c r="O85" s="34"/>
       <x:c r="P85" s="32"/>
+      <x:c r="Q85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="34"/>
@@ -2516,6 +2606,7 @@
       <x:c r="N86" s="46"/>
       <x:c r="O86" s="34"/>
       <x:c r="P86" s="32"/>
+      <x:c r="Q86"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="34"/>
@@ -2534,6 +2625,7 @@
       <x:c r="N87" s="46"/>
       <x:c r="O87" s="34"/>
       <x:c r="P87" s="32"/>
+      <x:c r="Q87"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="34"/>
@@ -2552,6 +2644,7 @@
       <x:c r="N88" s="46"/>
       <x:c r="O88" s="34"/>
       <x:c r="P88" s="32"/>
+      <x:c r="Q88"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="34"/>
@@ -2570,6 +2663,7 @@
       <x:c r="N89" s="46"/>
       <x:c r="O89" s="34"/>
       <x:c r="P89" s="32"/>
+      <x:c r="Q89"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="34"/>
@@ -2588,6 +2682,7 @@
       <x:c r="N90" s="46"/>
       <x:c r="O90" s="34"/>
       <x:c r="P90" s="32"/>
+      <x:c r="Q90"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="34"/>
@@ -2606,6 +2701,7 @@
       <x:c r="N91" s="46"/>
       <x:c r="O91" s="34"/>
       <x:c r="P91" s="32"/>
+      <x:c r="Q91"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="34"/>
@@ -2624,6 +2720,7 @@
       <x:c r="N92" s="46"/>
       <x:c r="O92" s="34"/>
       <x:c r="P92" s="32"/>
+      <x:c r="Q92"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="34"/>
@@ -2642,6 +2739,7 @@
       <x:c r="N93" s="46"/>
       <x:c r="O93" s="34"/>
       <x:c r="P93" s="32"/>
+      <x:c r="Q93"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="34"/>
@@ -2660,6 +2758,7 @@
       <x:c r="N94" s="46"/>
       <x:c r="O94" s="34"/>
       <x:c r="P94" s="32"/>
+      <x:c r="Q94"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="34"/>
@@ -2678,6 +2777,7 @@
       <x:c r="N95" s="46"/>
       <x:c r="O95" s="34"/>
       <x:c r="P95" s="32"/>
+      <x:c r="Q95"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="34"/>
@@ -2696,6 +2796,7 @@
       <x:c r="N96" s="46"/>
       <x:c r="O96" s="34"/>
       <x:c r="P96" s="32"/>
+      <x:c r="Q96"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="34"/>
@@ -2714,6 +2815,7 @@
       <x:c r="N97" s="46"/>
       <x:c r="O97" s="34"/>
       <x:c r="P97" s="32"/>
+      <x:c r="Q97"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="34"/>
@@ -2732,6 +2834,7 @@
       <x:c r="N98" s="46"/>
       <x:c r="O98" s="34"/>
       <x:c r="P98" s="32"/>
+      <x:c r="Q98"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="34"/>
@@ -2750,6 +2853,7 @@
       <x:c r="N99" s="46"/>
       <x:c r="O99" s="34"/>
       <x:c r="P99" s="32"/>
+      <x:c r="Q99"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="34"/>
@@ -2768,6 +2872,7 @@
       <x:c r="N100" s="46"/>
       <x:c r="O100" s="34"/>
       <x:c r="P100" s="32"/>
+      <x:c r="Q100"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="34"/>
@@ -2786,6 +2891,7 @@
       <x:c r="N101" s="46"/>
       <x:c r="O101" s="34"/>
       <x:c r="P101" s="32"/>
+      <x:c r="Q101"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="34"/>
@@ -2804,6 +2910,7 @@
       <x:c r="N102" s="46"/>
       <x:c r="O102" s="34"/>
       <x:c r="P102" s="32"/>
+      <x:c r="Q102"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="34"/>
@@ -2822,6 +2929,7 @@
       <x:c r="N103" s="46"/>
       <x:c r="O103" s="34"/>
       <x:c r="P103" s="32"/>
+      <x:c r="Q103"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="34"/>
@@ -2840,6 +2948,7 @@
       <x:c r="N104" s="46"/>
       <x:c r="O104" s="34"/>
       <x:c r="P104" s="32"/>
+      <x:c r="Q104"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="34"/>
@@ -2858,6 +2967,7 @@
       <x:c r="N105" s="46"/>
       <x:c r="O105" s="34"/>
       <x:c r="P105" s="32"/>
+      <x:c r="Q105"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="34"/>
@@ -2876,6 +2986,7 @@
       <x:c r="N106" s="46"/>
       <x:c r="O106" s="34"/>
       <x:c r="P106" s="32"/>
+      <x:c r="Q106"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="34"/>
@@ -2894,6 +3005,7 @@
       <x:c r="N107" s="46"/>
       <x:c r="O107" s="34"/>
       <x:c r="P107" s="32"/>
+      <x:c r="Q107"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="34"/>
@@ -2912,6 +3024,7 @@
       <x:c r="N108" s="46"/>
       <x:c r="O108" s="34"/>
       <x:c r="P108" s="32"/>
+      <x:c r="Q108"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="34"/>
@@ -2930,6 +3043,7 @@
       <x:c r="N109" s="46"/>
       <x:c r="O109" s="34"/>
       <x:c r="P109" s="32"/>
+      <x:c r="Q109"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="34"/>
@@ -2948,6 +3062,7 @@
       <x:c r="N110" s="46"/>
       <x:c r="O110" s="34"/>
       <x:c r="P110" s="32"/>
+      <x:c r="Q110"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="34"/>
@@ -2966,6 +3081,7 @@
       <x:c r="N111" s="46"/>
       <x:c r="O111" s="34"/>
       <x:c r="P111" s="32"/>
+      <x:c r="Q111"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="34"/>
@@ -2984,6 +3100,7 @@
       <x:c r="N112" s="46"/>
       <x:c r="O112" s="34"/>
       <x:c r="P112" s="32"/>
+      <x:c r="Q112"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="34"/>
@@ -3002,6 +3119,7 @@
       <x:c r="N113" s="46"/>
       <x:c r="O113" s="34"/>
       <x:c r="P113" s="32"/>
+      <x:c r="Q113"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="34"/>
@@ -3020,6 +3138,7 @@
       <x:c r="N114" s="46"/>
       <x:c r="O114" s="34"/>
       <x:c r="P114" s="32"/>
+      <x:c r="Q114"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="34"/>
@@ -3038,6 +3157,7 @@
       <x:c r="N115" s="46"/>
       <x:c r="O115" s="34"/>
       <x:c r="P115" s="32"/>
+      <x:c r="Q115"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="34"/>
@@ -3056,6 +3176,7 @@
       <x:c r="N116" s="46"/>
       <x:c r="O116" s="34"/>
       <x:c r="P116" s="32"/>
+      <x:c r="Q116"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="34"/>
@@ -3074,6 +3195,7 @@
       <x:c r="N117" s="46"/>
       <x:c r="O117" s="34"/>
       <x:c r="P117" s="32"/>
+      <x:c r="Q117"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="34"/>
@@ -3092,6 +3214,7 @@
       <x:c r="N118" s="46"/>
       <x:c r="O118" s="34"/>
       <x:c r="P118" s="32"/>
+      <x:c r="Q118"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="34"/>
@@ -3110,6 +3233,7 @@
       <x:c r="N119" s="46"/>
       <x:c r="O119" s="34"/>
       <x:c r="P119" s="32"/>
+      <x:c r="Q119"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="34"/>
@@ -3128,6 +3252,7 @@
       <x:c r="N120" s="46"/>
       <x:c r="O120" s="34"/>
       <x:c r="P120" s="32"/>
+      <x:c r="Q120"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="34"/>
@@ -3146,6 +3271,7 @@
       <x:c r="N121" s="46"/>
       <x:c r="O121" s="34"/>
       <x:c r="P121" s="32"/>
+      <x:c r="Q121"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="34"/>
@@ -3164,6 +3290,7 @@
       <x:c r="N122" s="46"/>
       <x:c r="O122" s="34"/>
       <x:c r="P122" s="32"/>
+      <x:c r="Q122"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="34"/>
@@ -3182,6 +3309,7 @@
       <x:c r="N123" s="46"/>
       <x:c r="O123" s="34"/>
       <x:c r="P123" s="32"/>
+      <x:c r="Q123"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="34"/>
@@ -3200,6 +3328,7 @@
       <x:c r="N124" s="46"/>
       <x:c r="O124" s="34"/>
       <x:c r="P124" s="32"/>
+      <x:c r="Q124"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="34"/>
@@ -3218,6 +3347,7 @@
       <x:c r="N125" s="46"/>
       <x:c r="O125" s="34"/>
       <x:c r="P125" s="32"/>
+      <x:c r="Q125"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="34"/>
@@ -3236,6 +3366,7 @@
       <x:c r="N126" s="46"/>
       <x:c r="O126" s="34"/>
       <x:c r="P126" s="32"/>
+      <x:c r="Q126"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="34"/>
@@ -3254,6 +3385,7 @@
       <x:c r="N127" s="46"/>
       <x:c r="O127" s="34"/>
       <x:c r="P127" s="32"/>
+      <x:c r="Q127"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="34"/>
@@ -3272,6 +3404,7 @@
       <x:c r="N128" s="46"/>
       <x:c r="O128" s="34"/>
       <x:c r="P128" s="32"/>
+      <x:c r="Q128"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="34"/>
@@ -3290,6 +3423,7 @@
       <x:c r="N129" s="46"/>
       <x:c r="O129" s="34"/>
       <x:c r="P129" s="32"/>
+      <x:c r="Q129"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="34"/>
@@ -3308,6 +3442,7 @@
       <x:c r="N130" s="46"/>
       <x:c r="O130" s="34"/>
       <x:c r="P130" s="32"/>
+      <x:c r="Q130"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="34"/>
@@ -3326,6 +3461,7 @@
       <x:c r="N131" s="46"/>
       <x:c r="O131" s="34"/>
       <x:c r="P131" s="32"/>
+      <x:c r="Q131"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="34"/>
@@ -3344,6 +3480,7 @@
       <x:c r="N132" s="46"/>
       <x:c r="O132" s="34"/>
       <x:c r="P132" s="32"/>
+      <x:c r="Q132"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="34"/>
@@ -3362,6 +3499,7 @@
       <x:c r="N133" s="46"/>
       <x:c r="O133" s="34"/>
       <x:c r="P133" s="32"/>
+      <x:c r="Q133"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="34"/>
@@ -3380,6 +3518,7 @@
       <x:c r="N134" s="46"/>
       <x:c r="O134" s="34"/>
       <x:c r="P134" s="32"/>
+      <x:c r="Q134"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="34"/>
@@ -3398,6 +3537,7 @@
       <x:c r="N135" s="46"/>
       <x:c r="O135" s="34"/>
       <x:c r="P135" s="32"/>
+      <x:c r="Q135"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="34"/>
@@ -3416,6 +3556,7 @@
       <x:c r="N136" s="46"/>
       <x:c r="O136" s="34"/>
       <x:c r="P136" s="32"/>
+      <x:c r="Q136"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="34"/>
@@ -3434,6 +3575,7 @@
       <x:c r="N137" s="46"/>
       <x:c r="O137" s="34"/>
       <x:c r="P137" s="32"/>
+      <x:c r="Q137"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="34"/>
@@ -3452,6 +3594,7 @@
       <x:c r="N138" s="46"/>
       <x:c r="O138" s="34"/>
       <x:c r="P138" s="32"/>
+      <x:c r="Q138"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="34"/>
@@ -3470,6 +3613,7 @@
       <x:c r="N139" s="46"/>
       <x:c r="O139" s="34"/>
       <x:c r="P139" s="32"/>
+      <x:c r="Q139"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="34"/>
@@ -3488,6 +3632,7 @@
       <x:c r="N140" s="46"/>
       <x:c r="O140" s="34"/>
       <x:c r="P140" s="32"/>
+      <x:c r="Q140"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="34"/>
@@ -3506,6 +3651,7 @@
       <x:c r="N141" s="46"/>
       <x:c r="O141" s="34"/>
       <x:c r="P141" s="32"/>
+      <x:c r="Q141"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="34"/>
@@ -3524,6 +3670,7 @@
       <x:c r="N142" s="46"/>
       <x:c r="O142" s="34"/>
       <x:c r="P142" s="32"/>
+      <x:c r="Q142"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="34"/>
@@ -3542,6 +3689,7 @@
       <x:c r="N143" s="46"/>
       <x:c r="O143" s="34"/>
       <x:c r="P143" s="32"/>
+      <x:c r="Q143"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="34"/>
@@ -3560,6 +3708,7 @@
       <x:c r="N144" s="46"/>
       <x:c r="O144" s="34"/>
       <x:c r="P144" s="32"/>
+      <x:c r="Q144"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="34"/>
@@ -3578,6 +3727,7 @@
       <x:c r="N145" s="46"/>
       <x:c r="O145" s="34"/>
       <x:c r="P145" s="32"/>
+      <x:c r="Q145"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="34"/>
@@ -3596,6 +3746,7 @@
       <x:c r="N146" s="46"/>
       <x:c r="O146" s="34"/>
       <x:c r="P146" s="32"/>
+      <x:c r="Q146"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="34"/>
@@ -3614,6 +3765,7 @@
       <x:c r="N147" s="46"/>
       <x:c r="O147" s="34"/>
       <x:c r="P147" s="32"/>
+      <x:c r="Q147"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="34"/>
@@ -3632,6 +3784,7 @@
       <x:c r="N148" s="46"/>
       <x:c r="O148" s="34"/>
       <x:c r="P148" s="32"/>
+      <x:c r="Q148"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="34"/>
@@ -3650,6 +3803,7 @@
       <x:c r="N149" s="46"/>
       <x:c r="O149" s="34"/>
       <x:c r="P149" s="32"/>
+      <x:c r="Q149"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="34"/>
@@ -3668,6 +3822,7 @@
       <x:c r="N150" s="46"/>
       <x:c r="O150" s="34"/>
       <x:c r="P150" s="32"/>
+      <x:c r="Q150"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="34"/>
@@ -3686,6 +3841,7 @@
       <x:c r="N151" s="46"/>
       <x:c r="O151" s="34"/>
       <x:c r="P151" s="32"/>
+      <x:c r="Q151"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="34"/>
@@ -3704,6 +3860,7 @@
       <x:c r="N152" s="46"/>
       <x:c r="O152" s="34"/>
       <x:c r="P152" s="32"/>
+      <x:c r="Q152"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="34"/>
@@ -3722,6 +3879,7 @@
       <x:c r="N153" s="46"/>
       <x:c r="O153" s="34"/>
       <x:c r="P153" s="32"/>
+      <x:c r="Q153"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="34"/>
@@ -3740,6 +3898,7 @@
       <x:c r="N154" s="46"/>
       <x:c r="O154" s="34"/>
       <x:c r="P154" s="32"/>
+      <x:c r="Q154"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="34"/>
@@ -3758,6 +3917,7 @@
       <x:c r="N155" s="46"/>
       <x:c r="O155" s="34"/>
       <x:c r="P155" s="32"/>
+      <x:c r="Q155"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="34"/>
@@ -3776,6 +3936,7 @@
       <x:c r="N156" s="46"/>
       <x:c r="O156" s="34"/>
       <x:c r="P156" s="32"/>
+      <x:c r="Q156"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="34"/>
@@ -3794,6 +3955,7 @@
       <x:c r="N157" s="46"/>
       <x:c r="O157" s="34"/>
       <x:c r="P157" s="32"/>
+      <x:c r="Q157"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="34"/>
@@ -3812,6 +3974,7 @@
       <x:c r="N158" s="46"/>
       <x:c r="O158" s="34"/>
       <x:c r="P158" s="32"/>
+      <x:c r="Q158"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="34"/>
@@ -3830,6 +3993,7 @@
       <x:c r="N159" s="46"/>
       <x:c r="O159" s="34"/>
       <x:c r="P159" s="32"/>
+      <x:c r="Q159"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="34"/>
@@ -3848,6 +4012,7 @@
       <x:c r="N160" s="46"/>
       <x:c r="O160" s="34"/>
       <x:c r="P160" s="32"/>
+      <x:c r="Q160"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="34"/>
@@ -3866,6 +4031,7 @@
       <x:c r="N161" s="46"/>
       <x:c r="O161" s="34"/>
       <x:c r="P161" s="32"/>
+      <x:c r="Q161"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="34"/>
@@ -3884,6 +4050,7 @@
       <x:c r="N162" s="46"/>
       <x:c r="O162" s="34"/>
       <x:c r="P162" s="32"/>
+      <x:c r="Q162"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="34"/>
@@ -3902,6 +4069,7 @@
       <x:c r="N163" s="46"/>
       <x:c r="O163" s="34"/>
       <x:c r="P163" s="32"/>
+      <x:c r="Q163"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="34"/>
@@ -3920,6 +4088,7 @@
       <x:c r="N164" s="46"/>
       <x:c r="O164" s="34"/>
       <x:c r="P164" s="32"/>
+      <x:c r="Q164"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="34"/>
@@ -3938,6 +4107,7 @@
       <x:c r="N165" s="46"/>
       <x:c r="O165" s="34"/>
       <x:c r="P165" s="32"/>
+      <x:c r="Q165"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="34"/>
@@ -3956,6 +4126,7 @@
       <x:c r="N166" s="46"/>
       <x:c r="O166" s="34"/>
       <x:c r="P166" s="32"/>
+      <x:c r="Q166"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="34"/>
@@ -3974,6 +4145,7 @@
       <x:c r="N167" s="46"/>
       <x:c r="O167" s="34"/>
       <x:c r="P167" s="32"/>
+      <x:c r="Q167"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="34"/>
@@ -3992,6 +4164,7 @@
       <x:c r="N168" s="46"/>
       <x:c r="O168" s="34"/>
       <x:c r="P168" s="32"/>
+      <x:c r="Q168"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="34"/>
@@ -4010,6 +4183,7 @@
       <x:c r="N169" s="46"/>
       <x:c r="O169" s="34"/>
       <x:c r="P169" s="32"/>
+      <x:c r="Q169"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="34"/>
@@ -4028,6 +4202,7 @@
       <x:c r="N170" s="46"/>
       <x:c r="O170" s="34"/>
       <x:c r="P170" s="32"/>
+      <x:c r="Q170"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="34"/>
@@ -4046,6 +4221,7 @@
       <x:c r="N171" s="46"/>
       <x:c r="O171" s="34"/>
       <x:c r="P171" s="32"/>
+      <x:c r="Q171"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="34"/>
@@ -4064,6 +4240,7 @@
       <x:c r="N172" s="46"/>
       <x:c r="O172" s="34"/>
       <x:c r="P172" s="32"/>
+      <x:c r="Q172"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="34"/>
@@ -4082,6 +4259,7 @@
       <x:c r="N173" s="46"/>
       <x:c r="O173" s="34"/>
       <x:c r="P173" s="32"/>
+      <x:c r="Q173"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="34"/>
@@ -4100,6 +4278,7 @@
       <x:c r="N174" s="46"/>
       <x:c r="O174" s="34"/>
       <x:c r="P174" s="32"/>
+      <x:c r="Q174"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="34"/>
@@ -4118,6 +4297,7 @@
       <x:c r="N175" s="46"/>
       <x:c r="O175" s="34"/>
       <x:c r="P175" s="32"/>
+      <x:c r="Q175"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="34"/>
@@ -4136,6 +4316,7 @@
       <x:c r="N176" s="46"/>
       <x:c r="O176" s="34"/>
       <x:c r="P176" s="32"/>
+      <x:c r="Q176"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="34"/>
@@ -4154,6 +4335,7 @@
       <x:c r="N177" s="46"/>
       <x:c r="O177" s="34"/>
       <x:c r="P177" s="32"/>
+      <x:c r="Q177"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="34"/>
@@ -4172,6 +4354,7 @@
       <x:c r="N178" s="46"/>
       <x:c r="O178" s="34"/>
       <x:c r="P178" s="32"/>
+      <x:c r="Q178"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="34"/>
@@ -4190,6 +4373,7 @@
       <x:c r="N179" s="46"/>
       <x:c r="O179" s="34"/>
       <x:c r="P179" s="32"/>
+      <x:c r="Q179"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="34"/>
@@ -4208,6 +4392,7 @@
       <x:c r="N180" s="46"/>
       <x:c r="O180" s="34"/>
       <x:c r="P180" s="32"/>
+      <x:c r="Q180"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="34"/>
@@ -4226,6 +4411,7 @@
       <x:c r="N181" s="46"/>
       <x:c r="O181" s="34"/>
       <x:c r="P181" s="32"/>
+      <x:c r="Q181"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="34"/>
@@ -4244,6 +4430,7 @@
       <x:c r="N182" s="46"/>
       <x:c r="O182" s="34"/>
       <x:c r="P182" s="32"/>
+      <x:c r="Q182"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="34"/>
@@ -4262,6 +4449,7 @@
       <x:c r="N183" s="46"/>
       <x:c r="O183" s="34"/>
       <x:c r="P183" s="32"/>
+      <x:c r="Q183"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="34"/>
@@ -4280,6 +4468,7 @@
       <x:c r="N184" s="46"/>
       <x:c r="O184" s="34"/>
       <x:c r="P184" s="32"/>
+      <x:c r="Q184"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="34"/>
@@ -4298,6 +4487,7 @@
       <x:c r="N185" s="46"/>
       <x:c r="O185" s="34"/>
       <x:c r="P185" s="32"/>
+      <x:c r="Q185"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="34"/>
@@ -4316,6 +4506,7 @@
       <x:c r="N186" s="46"/>
       <x:c r="O186" s="34"/>
       <x:c r="P186" s="32"/>
+      <x:c r="Q186"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="34"/>
@@ -4334,6 +4525,7 @@
       <x:c r="N187" s="46"/>
       <x:c r="O187" s="34"/>
       <x:c r="P187" s="32"/>
+      <x:c r="Q187"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="34"/>
@@ -4352,6 +4544,7 @@
       <x:c r="N188" s="46"/>
       <x:c r="O188" s="34"/>
       <x:c r="P188" s="32"/>
+      <x:c r="Q188"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="34"/>
@@ -4370,6 +4563,7 @@
       <x:c r="N189" s="46"/>
       <x:c r="O189" s="34"/>
       <x:c r="P189" s="32"/>
+      <x:c r="Q189"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="34"/>
@@ -4388,6 +4582,7 @@
       <x:c r="N190" s="46"/>
       <x:c r="O190" s="34"/>
       <x:c r="P190" s="32"/>
+      <x:c r="Q190"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="34"/>
@@ -4406,6 +4601,7 @@
       <x:c r="N191" s="46"/>
       <x:c r="O191" s="34"/>
       <x:c r="P191" s="32"/>
+      <x:c r="Q191"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="34"/>
@@ -4424,6 +4620,7 @@
       <x:c r="N192" s="46"/>
       <x:c r="O192" s="34"/>
       <x:c r="P192" s="32"/>
+      <x:c r="Q192"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="34"/>
@@ -4442,6 +4639,7 @@
       <x:c r="N193" s="46"/>
       <x:c r="O193" s="34"/>
       <x:c r="P193" s="32"/>
+      <x:c r="Q193"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="34"/>
@@ -4460,6 +4658,7 @@
       <x:c r="N194" s="46"/>
       <x:c r="O194" s="34"/>
       <x:c r="P194" s="32"/>
+      <x:c r="Q194"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="34"/>
@@ -4478,6 +4677,7 @@
       <x:c r="N195" s="46"/>
       <x:c r="O195" s="34"/>
       <x:c r="P195" s="32"/>
+      <x:c r="Q195"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="34"/>
@@ -4496,6 +4696,7 @@
       <x:c r="N196" s="46"/>
       <x:c r="O196" s="34"/>
       <x:c r="P196" s="32"/>
+      <x:c r="Q196"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="34"/>
@@ -4514,6 +4715,7 @@
       <x:c r="N197" s="46"/>
       <x:c r="O197" s="34"/>
       <x:c r="P197" s="32"/>
+      <x:c r="Q197"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="34"/>
@@ -4532,6 +4734,7 @@
       <x:c r="N198" s="46"/>
       <x:c r="O198" s="34"/>
       <x:c r="P198" s="32"/>
+      <x:c r="Q198"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="34"/>
@@ -4550,6 +4753,7 @@
       <x:c r="N199" s="46"/>
       <x:c r="O199" s="34"/>
       <x:c r="P199" s="32"/>
+      <x:c r="Q199"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="34"/>
@@ -4568,6 +4772,7 @@
       <x:c r="N200" s="46"/>
       <x:c r="O200" s="34"/>
       <x:c r="P200" s="32"/>
+      <x:c r="Q200"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="34"/>
@@ -4586,6 +4791,7 @@
       <x:c r="N201" s="46"/>
       <x:c r="O201" s="34"/>
       <x:c r="P201" s="32"/>
+      <x:c r="Q201"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="34"/>
@@ -4604,6 +4810,7 @@
       <x:c r="N202" s="46"/>
       <x:c r="O202" s="34"/>
       <x:c r="P202" s="32"/>
+      <x:c r="Q202"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="34"/>
@@ -4622,6 +4829,7 @@
       <x:c r="N203" s="46"/>
       <x:c r="O203" s="34"/>
       <x:c r="P203" s="32"/>
+      <x:c r="Q203"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="34"/>
@@ -4640,6 +4848,7 @@
       <x:c r="N204" s="46"/>
       <x:c r="O204" s="34"/>
       <x:c r="P204" s="32"/>
+      <x:c r="Q204"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="34"/>
@@ -4658,6 +4867,7 @@
       <x:c r="N205" s="46"/>
       <x:c r="O205" s="34"/>
       <x:c r="P205" s="32"/>
+      <x:c r="Q205"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="34"/>
@@ -4676,6 +4886,7 @@
       <x:c r="N206" s="46"/>
       <x:c r="O206" s="34"/>
       <x:c r="P206" s="32"/>
+      <x:c r="Q206"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="34"/>
@@ -4694,6 +4905,7 @@
       <x:c r="N207" s="46"/>
       <x:c r="O207" s="34"/>
       <x:c r="P207" s="32"/>
+      <x:c r="Q207"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="34"/>
@@ -4712,6 +4924,7 @@
       <x:c r="N208" s="46"/>
       <x:c r="O208" s="34"/>
       <x:c r="P208" s="32"/>
+      <x:c r="Q208"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="34"/>
@@ -4730,6 +4943,7 @@
       <x:c r="N209" s="46"/>
       <x:c r="O209" s="34"/>
       <x:c r="P209" s="32"/>
+      <x:c r="Q209"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="34"/>
@@ -4748,6 +4962,7 @@
       <x:c r="N210" s="46"/>
       <x:c r="O210" s="34"/>
       <x:c r="P210" s="32"/>
+      <x:c r="Q210"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="34"/>
@@ -4766,6 +4981,7 @@
       <x:c r="N211" s="46"/>
       <x:c r="O211" s="34"/>
       <x:c r="P211" s="32"/>
+      <x:c r="Q211"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="34"/>
@@ -4784,6 +5000,7 @@
       <x:c r="N212" s="46"/>
       <x:c r="O212" s="34"/>
       <x:c r="P212" s="32"/>
+      <x:c r="Q212"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="34"/>
@@ -4802,6 +5019,7 @@
       <x:c r="N213" s="46"/>
       <x:c r="O213" s="34"/>
       <x:c r="P213" s="32"/>
+      <x:c r="Q213"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="34"/>
@@ -4820,6 +5038,7 @@
       <x:c r="N214" s="46"/>
       <x:c r="O214" s="34"/>
       <x:c r="P214" s="32"/>
+      <x:c r="Q214"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="34"/>
@@ -4838,6 +5057,7 @@
       <x:c r="N215" s="46"/>
       <x:c r="O215" s="34"/>
       <x:c r="P215" s="32"/>
+      <x:c r="Q215"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="34"/>
@@ -4856,6 +5076,7 @@
       <x:c r="N216" s="46"/>
       <x:c r="O216" s="34"/>
       <x:c r="P216" s="32"/>
+      <x:c r="Q216"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="34"/>
@@ -4874,6 +5095,7 @@
       <x:c r="N217" s="46"/>
       <x:c r="O217" s="34"/>
       <x:c r="P217" s="32"/>
+      <x:c r="Q217"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="34"/>
@@ -4892,6 +5114,7 @@
       <x:c r="N218" s="46"/>
       <x:c r="O218" s="34"/>
       <x:c r="P218" s="32"/>
+      <x:c r="Q218"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="34"/>
@@ -4910,6 +5133,7 @@
       <x:c r="N219" s="46"/>
       <x:c r="O219" s="34"/>
       <x:c r="P219" s="32"/>
+      <x:c r="Q219"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="34"/>
@@ -4928,6 +5152,7 @@
       <x:c r="N220" s="46"/>
       <x:c r="O220" s="34"/>
       <x:c r="P220" s="32"/>
+      <x:c r="Q220"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="34"/>
@@ -4946,6 +5171,7 @@
       <x:c r="N221" s="46"/>
       <x:c r="O221" s="34"/>
       <x:c r="P221" s="32"/>
+      <x:c r="Q221"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="34"/>
@@ -4964,6 +5190,7 @@
       <x:c r="N222" s="46"/>
       <x:c r="O222" s="34"/>
       <x:c r="P222" s="32"/>
+      <x:c r="Q222"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="34"/>
@@ -4982,6 +5209,7 @@
       <x:c r="N223" s="46"/>
       <x:c r="O223" s="34"/>
       <x:c r="P223" s="32"/>
+      <x:c r="Q223"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="34"/>
@@ -5000,6 +5228,7 @@
       <x:c r="N224" s="46"/>
       <x:c r="O224" s="34"/>
       <x:c r="P224" s="32"/>
+      <x:c r="Q224"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="34"/>
@@ -5018,6 +5247,7 @@
       <x:c r="N225" s="46"/>
       <x:c r="O225" s="34"/>
       <x:c r="P225" s="32"/>
+      <x:c r="Q225"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="34"/>
@@ -5036,6 +5266,7 @@
       <x:c r="N226" s="46"/>
       <x:c r="O226" s="34"/>
       <x:c r="P226" s="32"/>
+      <x:c r="Q226"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="34"/>
@@ -5054,6 +5285,7 @@
       <x:c r="N227" s="46"/>
       <x:c r="O227" s="34"/>
       <x:c r="P227" s="32"/>
+      <x:c r="Q227"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="34"/>
@@ -5072,6 +5304,7 @@
       <x:c r="N228" s="46"/>
       <x:c r="O228" s="34"/>
       <x:c r="P228" s="32"/>
+      <x:c r="Q228"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="34"/>
@@ -5090,6 +5323,7 @@
       <x:c r="N229" s="46"/>
       <x:c r="O229" s="34"/>
       <x:c r="P229" s="32"/>
+      <x:c r="Q229"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="34"/>
@@ -5108,6 +5342,7 @@
       <x:c r="N230" s="46"/>
       <x:c r="O230" s="34"/>
       <x:c r="P230" s="32"/>
+      <x:c r="Q230"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="34"/>
@@ -5126,6 +5361,7 @@
       <x:c r="N231" s="46"/>
       <x:c r="O231" s="34"/>
       <x:c r="P231" s="32"/>
+      <x:c r="Q231"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="34"/>
@@ -5144,6 +5380,7 @@
       <x:c r="N232" s="46"/>
       <x:c r="O232" s="34"/>
       <x:c r="P232" s="32"/>
+      <x:c r="Q232"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="34"/>
@@ -5162,6 +5399,7 @@
       <x:c r="N233" s="46"/>
       <x:c r="O233" s="34"/>
       <x:c r="P233" s="32"/>
+      <x:c r="Q233"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="34"/>
@@ -5180,6 +5418,7 @@
       <x:c r="N234" s="46"/>
       <x:c r="O234" s="34"/>
       <x:c r="P234" s="32"/>
+      <x:c r="Q234"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="34"/>
@@ -5198,6 +5437,7 @@
       <x:c r="N235" s="46"/>
       <x:c r="O235" s="34"/>
       <x:c r="P235" s="32"/>
+      <x:c r="Q235"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="34"/>
@@ -5216,6 +5456,7 @@
       <x:c r="N236" s="46"/>
       <x:c r="O236" s="34"/>
       <x:c r="P236" s="32"/>
+      <x:c r="Q236"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="34"/>
@@ -5234,6 +5475,7 @@
       <x:c r="N237" s="46"/>
       <x:c r="O237" s="34"/>
       <x:c r="P237" s="32"/>
+      <x:c r="Q237"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="34"/>
@@ -5252,6 +5494,7 @@
       <x:c r="N238" s="46"/>
       <x:c r="O238" s="34"/>
       <x:c r="P238" s="32"/>
+      <x:c r="Q238"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="34"/>
@@ -5270,6 +5513,7 @@
       <x:c r="N239" s="46"/>
       <x:c r="O239" s="34"/>
       <x:c r="P239" s="32"/>
+      <x:c r="Q239"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="34"/>
@@ -5288,6 +5532,7 @@
       <x:c r="N240" s="46"/>
       <x:c r="O240" s="34"/>
       <x:c r="P240" s="32"/>
+      <x:c r="Q240"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="34"/>
@@ -5306,6 +5551,7 @@
       <x:c r="N241" s="46"/>
       <x:c r="O241" s="34"/>
       <x:c r="P241" s="32"/>
+      <x:c r="Q241"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="34"/>
@@ -5324,6 +5570,7 @@
       <x:c r="N242" s="46"/>
       <x:c r="O242" s="34"/>
       <x:c r="P242" s="32"/>
+      <x:c r="Q242"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="34"/>
@@ -5342,6 +5589,7 @@
       <x:c r="N243" s="46"/>
       <x:c r="O243" s="34"/>
       <x:c r="P243" s="32"/>
+      <x:c r="Q243"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="34"/>
@@ -5360,6 +5608,7 @@
       <x:c r="N244" s="46"/>
       <x:c r="O244" s="34"/>
       <x:c r="P244" s="32"/>
+      <x:c r="Q244"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="34"/>
@@ -5378,6 +5627,7 @@
       <x:c r="N245" s="46"/>
       <x:c r="O245" s="34"/>
       <x:c r="P245" s="32"/>
+      <x:c r="Q245"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="34"/>
@@ -5396,6 +5646,7 @@
       <x:c r="N246" s="46"/>
       <x:c r="O246" s="34"/>
       <x:c r="P246" s="32"/>
+      <x:c r="Q246"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="34"/>
@@ -5414,6 +5665,7 @@
       <x:c r="N247" s="46"/>
       <x:c r="O247" s="34"/>
       <x:c r="P247" s="32"/>
+      <x:c r="Q247"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="34"/>
@@ -5432,6 +5684,7 @@
       <x:c r="N248" s="46"/>
       <x:c r="O248" s="34"/>
       <x:c r="P248" s="32"/>
+      <x:c r="Q248"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="34"/>
@@ -5450,6 +5703,7 @@
       <x:c r="N249" s="46"/>
       <x:c r="O249" s="34"/>
       <x:c r="P249" s="32"/>
+      <x:c r="Q249"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="34"/>
@@ -5468,6 +5722,7 @@
       <x:c r="N250" s="46"/>
       <x:c r="O250" s="34"/>
       <x:c r="P250" s="32"/>
+      <x:c r="Q250"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="34"/>
@@ -5486,6 +5741,7 @@
       <x:c r="N251" s="46"/>
       <x:c r="O251" s="34"/>
       <x:c r="P251" s="32"/>
+      <x:c r="Q251"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="34"/>
@@ -5504,6 +5760,7 @@
       <x:c r="N252" s="46"/>
       <x:c r="O252" s="34"/>
       <x:c r="P252" s="32"/>
+      <x:c r="Q252"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="34"/>
@@ -5522,6 +5779,7 @@
       <x:c r="N253" s="46"/>
       <x:c r="O253" s="34"/>
       <x:c r="P253" s="32"/>
+      <x:c r="Q253"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="34"/>
@@ -5540,6 +5798,7 @@
       <x:c r="N254" s="46"/>
       <x:c r="O254" s="34"/>
       <x:c r="P254" s="32"/>
+      <x:c r="Q254"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="34"/>
@@ -5558,6 +5817,7 @@
       <x:c r="N255" s="46"/>
       <x:c r="O255" s="34"/>
       <x:c r="P255" s="32"/>
+      <x:c r="Q255"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="34"/>
@@ -5576,6 +5836,7 @@
       <x:c r="N256" s="46"/>
       <x:c r="O256" s="34"/>
       <x:c r="P256" s="32"/>
+      <x:c r="Q256"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="34"/>
@@ -5594,6 +5855,7 @@
       <x:c r="N257" s="46"/>
       <x:c r="O257" s="34"/>
       <x:c r="P257" s="32"/>
+      <x:c r="Q257"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="34"/>
@@ -5612,6 +5874,7 @@
       <x:c r="N258" s="46"/>
       <x:c r="O258" s="34"/>
       <x:c r="P258" s="32"/>
+      <x:c r="Q258"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="34"/>
@@ -5630,6 +5893,7 @@
       <x:c r="N259" s="46"/>
       <x:c r="O259" s="34"/>
       <x:c r="P259" s="32"/>
+      <x:c r="Q259"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="34"/>
@@ -5648,6 +5912,7 @@
       <x:c r="N260" s="46"/>
       <x:c r="O260" s="34"/>
       <x:c r="P260" s="32"/>
+      <x:c r="Q260"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="34"/>
@@ -5666,6 +5931,7 @@
       <x:c r="N261" s="46"/>
       <x:c r="O261" s="34"/>
       <x:c r="P261" s="32"/>
+      <x:c r="Q261"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="34"/>
@@ -5684,6 +5950,7 @@
       <x:c r="N262" s="46"/>
       <x:c r="O262" s="34"/>
       <x:c r="P262" s="32"/>
+      <x:c r="Q262"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="34"/>
@@ -5702,6 +5969,7 @@
       <x:c r="N263" s="46"/>
       <x:c r="O263" s="34"/>
       <x:c r="P263" s="32"/>
+      <x:c r="Q263"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="34"/>
@@ -5720,6 +5988,7 @@
       <x:c r="N264" s="46"/>
       <x:c r="O264" s="34"/>
       <x:c r="P264" s="32"/>
+      <x:c r="Q264"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="34"/>
@@ -5738,6 +6007,7 @@
       <x:c r="N265" s="46"/>
       <x:c r="O265" s="34"/>
       <x:c r="P265" s="32"/>
+      <x:c r="Q265"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="34"/>
@@ -5756,6 +6026,7 @@
       <x:c r="N266" s="46"/>
       <x:c r="O266" s="34"/>
       <x:c r="P266" s="32"/>
+      <x:c r="Q266"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="34"/>
@@ -5774,6 +6045,7 @@
       <x:c r="N267" s="46"/>
       <x:c r="O267" s="34"/>
       <x:c r="P267" s="32"/>
+      <x:c r="Q267"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="34"/>
@@ -5792,6 +6064,7 @@
       <x:c r="N268" s="46"/>
       <x:c r="O268" s="34"/>
       <x:c r="P268" s="32"/>
+      <x:c r="Q268"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="34"/>
@@ -5810,6 +6083,7 @@
       <x:c r="N269" s="46"/>
       <x:c r="O269" s="34"/>
       <x:c r="P269" s="32"/>
+      <x:c r="Q269"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="34"/>
@@ -5828,6 +6102,7 @@
       <x:c r="N270" s="46"/>
       <x:c r="O270" s="34"/>
       <x:c r="P270" s="32"/>
+      <x:c r="Q270"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="34"/>
@@ -5846,6 +6121,7 @@
       <x:c r="N271" s="46"/>
       <x:c r="O271" s="34"/>
       <x:c r="P271" s="32"/>
+      <x:c r="Q271"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="34"/>
@@ -5864,6 +6140,7 @@
       <x:c r="N272" s="46"/>
       <x:c r="O272" s="34"/>
       <x:c r="P272" s="32"/>
+      <x:c r="Q272"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="34"/>
@@ -5882,6 +6159,7 @@
       <x:c r="N273" s="46"/>
       <x:c r="O273" s="34"/>
       <x:c r="P273" s="32"/>
+      <x:c r="Q273"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="34"/>
@@ -5900,6 +6178,7 @@
       <x:c r="N274" s="46"/>
       <x:c r="O274" s="34"/>
       <x:c r="P274" s="32"/>
+      <x:c r="Q274"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="34"/>
@@ -5918,6 +6197,7 @@
       <x:c r="N275" s="46"/>
       <x:c r="O275" s="34"/>
       <x:c r="P275" s="32"/>
+      <x:c r="Q275"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="34"/>
@@ -5936,6 +6216,7 @@
       <x:c r="N276" s="46"/>
       <x:c r="O276" s="34"/>
       <x:c r="P276" s="32"/>
+      <x:c r="Q276"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="34"/>
@@ -5954,6 +6235,7 @@
       <x:c r="N277" s="46"/>
       <x:c r="O277" s="34"/>
       <x:c r="P277" s="32"/>
+      <x:c r="Q277"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="34"/>
@@ -5972,6 +6254,7 @@
       <x:c r="N278" s="46"/>
       <x:c r="O278" s="34"/>
       <x:c r="P278" s="32"/>
+      <x:c r="Q278"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="34"/>
@@ -5990,6 +6273,7 @@
       <x:c r="N279" s="46"/>
       <x:c r="O279" s="34"/>
       <x:c r="P279" s="32"/>
+      <x:c r="Q279"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="34"/>
@@ -6008,6 +6292,7 @@
       <x:c r="N280" s="46"/>
       <x:c r="O280" s="34"/>
       <x:c r="P280" s="32"/>
+      <x:c r="Q280"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="34"/>
@@ -6026,6 +6311,7 @@
       <x:c r="N281" s="46"/>
       <x:c r="O281" s="34"/>
       <x:c r="P281" s="32"/>
+      <x:c r="Q281"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="34"/>
@@ -6044,6 +6330,7 @@
       <x:c r="N282" s="46"/>
       <x:c r="O282" s="34"/>
       <x:c r="P282" s="32"/>
+      <x:c r="Q282"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="34"/>
@@ -6062,6 +6349,7 @@
       <x:c r="N283" s="46"/>
       <x:c r="O283" s="34"/>
       <x:c r="P283" s="32"/>
+      <x:c r="Q283"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="34"/>
@@ -6080,6 +6368,7 @@
       <x:c r="N284" s="46"/>
       <x:c r="O284" s="34"/>
       <x:c r="P284" s="32"/>
+      <x:c r="Q284"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="34"/>
@@ -6098,6 +6387,7 @@
       <x:c r="N285" s="46"/>
       <x:c r="O285" s="34"/>
       <x:c r="P285" s="32"/>
+      <x:c r="Q285"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="34"/>
@@ -6116,6 +6406,7 @@
       <x:c r="N286" s="46"/>
       <x:c r="O286" s="34"/>
       <x:c r="P286" s="32"/>
+      <x:c r="Q286"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="34"/>
@@ -6134,6 +6425,7 @@
       <x:c r="N287" s="46"/>
       <x:c r="O287" s="34"/>
       <x:c r="P287" s="32"/>
+      <x:c r="Q287"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="34"/>
@@ -6152,6 +6444,7 @@
       <x:c r="N288" s="46"/>
       <x:c r="O288" s="34"/>
       <x:c r="P288" s="32"/>
+      <x:c r="Q288"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="34"/>
@@ -6170,6 +6463,7 @@
       <x:c r="N289" s="46"/>
       <x:c r="O289" s="34"/>
       <x:c r="P289" s="32"/>
+      <x:c r="Q289"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="34"/>
@@ -6188,6 +6482,7 @@
       <x:c r="N290" s="46"/>
       <x:c r="O290" s="34"/>
       <x:c r="P290" s="32"/>
+      <x:c r="Q290"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="34"/>
@@ -6206,6 +6501,7 @@
       <x:c r="N291" s="46"/>
       <x:c r="O291" s="34"/>
       <x:c r="P291" s="32"/>
+      <x:c r="Q291"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="34"/>
@@ -6224,6 +6520,7 @@
       <x:c r="N292" s="46"/>
       <x:c r="O292" s="34"/>
       <x:c r="P292" s="32"/>
+      <x:c r="Q292"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="34"/>
@@ -6242,6 +6539,7 @@
       <x:c r="N293" s="46"/>
       <x:c r="O293" s="34"/>
       <x:c r="P293" s="32"/>
+      <x:c r="Q293"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="34"/>
@@ -6260,6 +6558,7 @@
       <x:c r="N294" s="46"/>
       <x:c r="O294" s="34"/>
       <x:c r="P294" s="32"/>
+      <x:c r="Q294"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="34"/>
@@ -6278,6 +6577,7 @@
       <x:c r="N295" s="46"/>
       <x:c r="O295" s="34"/>
       <x:c r="P295" s="32"/>
+      <x:c r="Q295"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="34"/>
@@ -6296,6 +6596,7 @@
       <x:c r="N296" s="46"/>
       <x:c r="O296" s="34"/>
       <x:c r="P296" s="32"/>
+      <x:c r="Q296"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="34"/>
@@ -6314,6 +6615,7 @@
       <x:c r="N297" s="46"/>
       <x:c r="O297" s="34"/>
       <x:c r="P297" s="32"/>
+      <x:c r="Q297"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="34"/>
@@ -6332,6 +6634,7 @@
       <x:c r="N298" s="46"/>
       <x:c r="O298" s="34"/>
       <x:c r="P298" s="32"/>
+      <x:c r="Q298"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="34"/>
@@ -6350,6 +6653,7 @@
       <x:c r="N299" s="46"/>
       <x:c r="O299" s="34"/>
       <x:c r="P299" s="32"/>
+      <x:c r="Q299"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="34"/>
@@ -6368,6 +6672,7 @@
       <x:c r="N300" s="46"/>
       <x:c r="O300" s="34"/>
       <x:c r="P300" s="32"/>
+      <x:c r="Q300"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="34"/>
@@ -6386,6 +6691,7 @@
       <x:c r="N301" s="46"/>
       <x:c r="O301" s="34"/>
       <x:c r="P301" s="32"/>
+      <x:c r="Q301"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="34"/>
@@ -6404,6 +6710,7 @@
       <x:c r="N302" s="46"/>
       <x:c r="O302" s="34"/>
       <x:c r="P302" s="32"/>
+      <x:c r="Q302"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="34"/>
@@ -6422,6 +6729,7 @@
       <x:c r="N303" s="46"/>
       <x:c r="O303" s="34"/>
       <x:c r="P303" s="32"/>
+      <x:c r="Q303"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="34"/>
@@ -6440,6 +6748,7 @@
       <x:c r="N304" s="46"/>
       <x:c r="O304" s="34"/>
       <x:c r="P304" s="32"/>
+      <x:c r="Q304"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="34"/>
@@ -6458,6 +6767,7 @@
       <x:c r="N305" s="46"/>
       <x:c r="O305" s="34"/>
       <x:c r="P305" s="32"/>
+      <x:c r="Q305"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="34"/>
@@ -6476,6 +6786,7 @@
       <x:c r="N306" s="46"/>
       <x:c r="O306" s="34"/>
       <x:c r="P306" s="32"/>
+      <x:c r="Q306"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="34"/>
@@ -6494,6 +6805,7 @@
       <x:c r="N307" s="46"/>
       <x:c r="O307" s="34"/>
       <x:c r="P307" s="32"/>
+      <x:c r="Q307"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="34"/>
@@ -6512,6 +6824,7 @@
       <x:c r="N308" s="46"/>
       <x:c r="O308" s="34"/>
       <x:c r="P308" s="32"/>
+      <x:c r="Q308"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="34"/>
@@ -6530,6 +6843,7 @@
       <x:c r="N309" s="46"/>
       <x:c r="O309" s="34"/>
       <x:c r="P309" s="32"/>
+      <x:c r="Q309"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="34"/>
@@ -6548,6 +6862,7 @@
       <x:c r="N310" s="46"/>
       <x:c r="O310" s="34"/>
       <x:c r="P310" s="32"/>
+      <x:c r="Q310"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="34"/>
@@ -6566,6 +6881,7 @@
       <x:c r="N311" s="46"/>
       <x:c r="O311" s="34"/>
       <x:c r="P311" s="32"/>
+      <x:c r="Q311"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="34"/>
@@ -6584,6 +6900,7 @@
       <x:c r="N312" s="46"/>
       <x:c r="O312" s="34"/>
       <x:c r="P312" s="32"/>
+      <x:c r="Q312"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="34"/>
@@ -6602,6 +6919,7 @@
       <x:c r="N313" s="46"/>
       <x:c r="O313" s="34"/>
       <x:c r="P313" s="32"/>
+      <x:c r="Q313"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="34"/>
@@ -6620,6 +6938,7 @@
       <x:c r="N314" s="46"/>
       <x:c r="O314" s="34"/>
       <x:c r="P314" s="32"/>
+      <x:c r="Q314"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="34"/>
@@ -6638,6 +6957,7 @@
       <x:c r="N315" s="46"/>
       <x:c r="O315" s="34"/>
       <x:c r="P315" s="32"/>
+      <x:c r="Q315"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="34"/>
@@ -6656,6 +6976,7 @@
       <x:c r="N316" s="46"/>
       <x:c r="O316" s="34"/>
       <x:c r="P316" s="32"/>
+      <x:c r="Q316"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="34"/>
@@ -6674,6 +6995,7 @@
       <x:c r="N317" s="46"/>
       <x:c r="O317" s="34"/>
       <x:c r="P317" s="32"/>
+      <x:c r="Q317"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="34"/>
@@ -6692,6 +7014,7 @@
       <x:c r="N318" s="46"/>
       <x:c r="O318" s="34"/>
       <x:c r="P318" s="32"/>
+      <x:c r="Q318"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="34"/>
@@ -6710,6 +7033,7 @@
       <x:c r="N319" s="46"/>
       <x:c r="O319" s="34"/>
       <x:c r="P319" s="32"/>
+      <x:c r="Q319"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="34"/>
@@ -6728,6 +7052,7 @@
       <x:c r="N320" s="46"/>
       <x:c r="O320" s="34"/>
       <x:c r="P320" s="32"/>
+      <x:c r="Q320"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="34"/>
@@ -6746,6 +7071,7 @@
       <x:c r="N321" s="46"/>
       <x:c r="O321" s="34"/>
       <x:c r="P321" s="32"/>
+      <x:c r="Q321"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="34"/>
@@ -6764,6 +7090,7 @@
       <x:c r="N322" s="46"/>
       <x:c r="O322" s="34"/>
       <x:c r="P322" s="32"/>
+      <x:c r="Q322"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="34"/>
@@ -6782,6 +7109,7 @@
       <x:c r="N323" s="46"/>
       <x:c r="O323" s="34"/>
       <x:c r="P323" s="32"/>
+      <x:c r="Q323"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="34"/>
@@ -6800,6 +7128,7 @@
       <x:c r="N324" s="46"/>
       <x:c r="O324" s="34"/>
       <x:c r="P324" s="32"/>
+      <x:c r="Q324"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="34"/>
@@ -6818,6 +7147,7 @@
       <x:c r="N325" s="46"/>
       <x:c r="O325" s="34"/>
       <x:c r="P325" s="32"/>
+      <x:c r="Q325"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="34"/>
@@ -6836,6 +7166,7 @@
       <x:c r="N326" s="46"/>
       <x:c r="O326" s="34"/>
       <x:c r="P326" s="32"/>
+      <x:c r="Q326"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="34"/>
@@ -6854,6 +7185,7 @@
       <x:c r="N327" s="46"/>
       <x:c r="O327" s="34"/>
       <x:c r="P327" s="32"/>
+      <x:c r="Q327"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="34"/>
@@ -6872,6 +7204,7 @@
       <x:c r="N328" s="46"/>
       <x:c r="O328" s="34"/>
       <x:c r="P328" s="32"/>
+      <x:c r="Q328"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="34"/>
@@ -6890,6 +7223,7 @@
       <x:c r="N329" s="46"/>
       <x:c r="O329" s="34"/>
       <x:c r="P329" s="32"/>
+      <x:c r="Q329"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="34"/>
@@ -6908,6 +7242,7 @@
       <x:c r="N330" s="46"/>
       <x:c r="O330" s="34"/>
       <x:c r="P330" s="32"/>
+      <x:c r="Q330"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="34"/>
@@ -6926,6 +7261,7 @@
       <x:c r="N331" s="46"/>
       <x:c r="O331" s="34"/>
       <x:c r="P331" s="32"/>
+      <x:c r="Q331"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="34"/>
@@ -6944,6 +7280,7 @@
       <x:c r="N332" s="46"/>
       <x:c r="O332" s="34"/>
       <x:c r="P332" s="32"/>
+      <x:c r="Q332"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="34"/>
@@ -6962,6 +7299,7 @@
       <x:c r="N333" s="46"/>
       <x:c r="O333" s="34"/>
       <x:c r="P333" s="32"/>
+      <x:c r="Q333"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="34"/>
@@ -6980,6 +7318,7 @@
       <x:c r="N334" s="46"/>
       <x:c r="O334" s="34"/>
       <x:c r="P334" s="32"/>
+      <x:c r="Q334"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="34"/>
@@ -6998,6 +7337,7 @@
       <x:c r="N335" s="46"/>
       <x:c r="O335" s="34"/>
       <x:c r="P335" s="32"/>
+      <x:c r="Q335"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="34"/>
@@ -7016,6 +7356,7 @@
       <x:c r="N336" s="46"/>
       <x:c r="O336" s="34"/>
       <x:c r="P336" s="32"/>
+      <x:c r="Q336"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="34"/>
@@ -7034,6 +7375,7 @@
       <x:c r="N337" s="46"/>
       <x:c r="O337" s="34"/>
       <x:c r="P337" s="32"/>
+      <x:c r="Q337"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="34"/>
@@ -7052,6 +7394,7 @@
       <x:c r="N338" s="46"/>
       <x:c r="O338" s="34"/>
       <x:c r="P338" s="32"/>
+      <x:c r="Q338"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="34"/>
@@ -7070,6 +7413,7 @@
       <x:c r="N339" s="46"/>
       <x:c r="O339" s="34"/>
       <x:c r="P339" s="32"/>
+      <x:c r="Q339"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="34"/>
@@ -7088,6 +7432,7 @@
       <x:c r="N340" s="46"/>
       <x:c r="O340" s="34"/>
       <x:c r="P340" s="32"/>
+      <x:c r="Q340"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="34"/>
@@ -7106,6 +7451,7 @@
       <x:c r="N341" s="46"/>
       <x:c r="O341" s="34"/>
       <x:c r="P341" s="32"/>
+      <x:c r="Q341"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="34"/>
@@ -7124,6 +7470,7 @@
       <x:c r="N342" s="46"/>
       <x:c r="O342" s="34"/>
       <x:c r="P342" s="32"/>
+      <x:c r="Q342"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="34"/>
@@ -7142,6 +7489,7 @@
       <x:c r="N343" s="46"/>
       <x:c r="O343" s="34"/>
       <x:c r="P343" s="32"/>
+      <x:c r="Q343"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="34"/>
@@ -7160,6 +7508,7 @@
       <x:c r="N344" s="46"/>
       <x:c r="O344" s="34"/>
       <x:c r="P344" s="32"/>
+      <x:c r="Q344"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="34"/>
@@ -7178,6 +7527,7 @@
       <x:c r="N345" s="46"/>
       <x:c r="O345" s="34"/>
       <x:c r="P345" s="32"/>
+      <x:c r="Q345"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="34"/>
@@ -7196,6 +7546,7 @@
       <x:c r="N346" s="46"/>
       <x:c r="O346" s="34"/>
       <x:c r="P346" s="32"/>
+      <x:c r="Q346"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="34"/>
@@ -7214,6 +7565,7 @@
       <x:c r="N347" s="46"/>
       <x:c r="O347" s="34"/>
       <x:c r="P347" s="32"/>
+      <x:c r="Q347"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="34"/>
@@ -7232,6 +7584,7 @@
       <x:c r="N348" s="46"/>
       <x:c r="O348" s="34"/>
       <x:c r="P348" s="32"/>
+      <x:c r="Q348"/>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="34"/>
@@ -7250,6 +7603,7 @@
       <x:c r="N349" s="46"/>
       <x:c r="O349" s="34"/>
       <x:c r="P349" s="32"/>
+      <x:c r="Q349"/>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="34"/>
@@ -7268,6 +7622,7 @@
       <x:c r="N350" s="46"/>
       <x:c r="O350" s="34"/>
       <x:c r="P350" s="32"/>
+      <x:c r="Q350"/>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="34"/>
@@ -7286,6 +7641,7 @@
       <x:c r="N351" s="46"/>
       <x:c r="O351" s="34"/>
       <x:c r="P351" s="32"/>
+      <x:c r="Q351"/>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="34"/>
@@ -7304,6 +7660,7 @@
       <x:c r="N352" s="46"/>
       <x:c r="O352" s="34"/>
       <x:c r="P352" s="32"/>
+      <x:c r="Q352"/>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="34"/>
@@ -7322,6 +7679,7 @@
       <x:c r="N353" s="46"/>
       <x:c r="O353" s="34"/>
       <x:c r="P353" s="32"/>
+      <x:c r="Q353"/>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="34"/>
@@ -7340,6 +7698,7 @@
       <x:c r="N354" s="46"/>
       <x:c r="O354" s="34"/>
       <x:c r="P354" s="32"/>
+      <x:c r="Q354"/>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="34"/>
@@ -7358,6 +7717,7 @@
       <x:c r="N355" s="46"/>
       <x:c r="O355" s="34"/>
       <x:c r="P355" s="32"/>
+      <x:c r="Q355"/>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="34"/>
@@ -7376,6 +7736,7 @@
       <x:c r="N356" s="46"/>
       <x:c r="O356" s="34"/>
       <x:c r="P356" s="32"/>
+      <x:c r="Q356"/>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="34"/>
@@ -7394,6 +7755,7 @@
       <x:c r="N357" s="46"/>
       <x:c r="O357" s="34"/>
       <x:c r="P357" s="32"/>
+      <x:c r="Q357"/>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="34"/>
@@ -7412,6 +7774,7 @@
       <x:c r="N358" s="46"/>
       <x:c r="O358" s="34"/>
       <x:c r="P358" s="32"/>
+      <x:c r="Q358"/>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="34"/>
@@ -7430,6 +7793,7 @@
       <x:c r="N359" s="46"/>
       <x:c r="O359" s="34"/>
       <x:c r="P359" s="32"/>
+      <x:c r="Q359"/>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="34"/>
@@ -7448,6 +7812,7 @@
       <x:c r="N360" s="46"/>
       <x:c r="O360" s="34"/>
       <x:c r="P360" s="32"/>
+      <x:c r="Q360"/>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="34"/>
@@ -7466,6 +7831,7 @@
       <x:c r="N361" s="46"/>
       <x:c r="O361" s="34"/>
       <x:c r="P361" s="32"/>
+      <x:c r="Q361"/>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="34"/>
@@ -7484,6 +7850,7 @@
       <x:c r="N362" s="46"/>
       <x:c r="O362" s="34"/>
       <x:c r="P362" s="32"/>
+      <x:c r="Q362"/>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="34"/>
@@ -7502,6 +7869,7 @@
       <x:c r="N363" s="46"/>
       <x:c r="O363" s="34"/>
       <x:c r="P363" s="32"/>
+      <x:c r="Q363"/>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="34"/>
@@ -7520,6 +7888,7 @@
       <x:c r="N364" s="46"/>
       <x:c r="O364" s="34"/>
       <x:c r="P364" s="32"/>
+      <x:c r="Q364"/>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="34"/>
@@ -7538,6 +7907,7 @@
       <x:c r="N365" s="46"/>
       <x:c r="O365" s="34"/>
       <x:c r="P365" s="32"/>
+      <x:c r="Q365"/>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="34"/>
@@ -7556,6 +7926,7 @@
       <x:c r="N366" s="46"/>
       <x:c r="O366" s="34"/>
       <x:c r="P366" s="32"/>
+      <x:c r="Q366"/>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="34"/>
@@ -7574,6 +7945,7 @@
       <x:c r="N367" s="46"/>
       <x:c r="O367" s="34"/>
       <x:c r="P367" s="32"/>
+      <x:c r="Q367"/>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="34"/>
@@ -7592,6 +7964,7 @@
       <x:c r="N368" s="46"/>
       <x:c r="O368" s="34"/>
       <x:c r="P368" s="32"/>
+      <x:c r="Q368"/>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="34"/>
@@ -7610,6 +7983,7 @@
       <x:c r="N369" s="46"/>
       <x:c r="O369" s="34"/>
       <x:c r="P369" s="32"/>
+      <x:c r="Q369"/>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="34"/>
@@ -7628,6 +8002,7 @@
       <x:c r="N370" s="46"/>
       <x:c r="O370" s="34"/>
       <x:c r="P370" s="32"/>
+      <x:c r="Q370"/>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="34"/>
@@ -7646,6 +8021,7 @@
       <x:c r="N371" s="46"/>
       <x:c r="O371" s="34"/>
       <x:c r="P371" s="32"/>
+      <x:c r="Q371"/>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="34"/>
@@ -7664,6 +8040,7 @@
       <x:c r="N372" s="46"/>
       <x:c r="O372" s="34"/>
       <x:c r="P372" s="32"/>
+      <x:c r="Q372"/>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="34"/>
@@ -7682,6 +8059,7 @@
       <x:c r="N373" s="46"/>
       <x:c r="O373" s="34"/>
       <x:c r="P373" s="32"/>
+      <x:c r="Q373"/>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="34"/>
@@ -7700,6 +8078,7 @@
       <x:c r="N374" s="46"/>
       <x:c r="O374" s="34"/>
       <x:c r="P374" s="32"/>
+      <x:c r="Q374"/>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="34"/>
@@ -7718,6 +8097,7 @@
       <x:c r="N375" s="46"/>
       <x:c r="O375" s="34"/>
       <x:c r="P375" s="32"/>
+      <x:c r="Q375"/>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="34"/>
@@ -7736,6 +8116,7 @@
       <x:c r="N376" s="46"/>
       <x:c r="O376" s="34"/>
       <x:c r="P376" s="32"/>
+      <x:c r="Q376"/>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="34"/>
@@ -7754,6 +8135,7 @@
       <x:c r="N377" s="46"/>
       <x:c r="O377" s="34"/>
       <x:c r="P377" s="32"/>
+      <x:c r="Q377"/>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="34"/>
@@ -7772,6 +8154,7 @@
       <x:c r="N378" s="46"/>
       <x:c r="O378" s="34"/>
       <x:c r="P378" s="32"/>
+      <x:c r="Q378"/>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="34"/>
@@ -7790,6 +8173,7 @@
       <x:c r="N379" s="46"/>
       <x:c r="O379" s="34"/>
       <x:c r="P379" s="32"/>
+      <x:c r="Q379"/>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="34"/>
@@ -7808,6 +8192,7 @@
       <x:c r="N380" s="46"/>
       <x:c r="O380" s="34"/>
       <x:c r="P380" s="32"/>
+      <x:c r="Q380"/>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="34"/>
@@ -7826,6 +8211,7 @@
       <x:c r="N381" s="46"/>
       <x:c r="O381" s="34"/>
       <x:c r="P381" s="32"/>
+      <x:c r="Q381"/>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="34"/>
@@ -7844,6 +8230,7 @@
       <x:c r="N382" s="46"/>
       <x:c r="O382" s="34"/>
       <x:c r="P382" s="32"/>
+      <x:c r="Q382"/>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="34"/>
@@ -7862,6 +8249,7 @@
       <x:c r="N383" s="46"/>
       <x:c r="O383" s="34"/>
       <x:c r="P383" s="32"/>
+      <x:c r="Q383"/>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="34"/>
@@ -7880,6 +8268,7 @@
       <x:c r="N384" s="46"/>
       <x:c r="O384" s="34"/>
       <x:c r="P384" s="32"/>
+      <x:c r="Q384"/>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="34"/>
@@ -7898,6 +8287,7 @@
       <x:c r="N385" s="46"/>
       <x:c r="O385" s="34"/>
       <x:c r="P385" s="32"/>
+      <x:c r="Q385"/>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="34"/>
@@ -7916,6 +8306,7 @@
       <x:c r="N386" s="46"/>
       <x:c r="O386" s="34"/>
       <x:c r="P386" s="32"/>
+      <x:c r="Q386"/>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="34"/>
@@ -7934,6 +8325,7 @@
       <x:c r="N387" s="46"/>
       <x:c r="O387" s="34"/>
       <x:c r="P387" s="32"/>
+      <x:c r="Q387"/>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="34"/>
@@ -7952,6 +8344,7 @@
       <x:c r="N388" s="46"/>
       <x:c r="O388" s="34"/>
       <x:c r="P388" s="32"/>
+      <x:c r="Q388"/>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="34"/>
@@ -7970,6 +8363,7 @@
       <x:c r="N389" s="46"/>
       <x:c r="O389" s="34"/>
       <x:c r="P389" s="32"/>
+      <x:c r="Q389"/>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="34"/>
@@ -7988,6 +8382,7 @@
       <x:c r="N390" s="46"/>
       <x:c r="O390" s="34"/>
       <x:c r="P390" s="32"/>
+      <x:c r="Q390"/>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="34"/>
@@ -8006,6 +8401,7 @@
       <x:c r="N391" s="46"/>
       <x:c r="O391" s="34"/>
       <x:c r="P391" s="32"/>
+      <x:c r="Q391"/>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="34"/>
@@ -8024,6 +8420,7 @@
       <x:c r="N392" s="46"/>
       <x:c r="O392" s="34"/>
       <x:c r="P392" s="32"/>
+      <x:c r="Q392"/>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="34"/>
@@ -8042,6 +8439,7 @@
       <x:c r="N393" s="46"/>
       <x:c r="O393" s="34"/>
       <x:c r="P393" s="32"/>
+      <x:c r="Q393"/>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="34"/>
@@ -8060,6 +8458,7 @@
       <x:c r="N394" s="46"/>
       <x:c r="O394" s="34"/>
       <x:c r="P394" s="32"/>
+      <x:c r="Q394"/>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="34"/>
@@ -8078,6 +8477,7 @@
       <x:c r="N395" s="46"/>
       <x:c r="O395" s="34"/>
       <x:c r="P395" s="32"/>
+      <x:c r="Q395"/>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="34"/>
@@ -8096,6 +8496,7 @@
       <x:c r="N396" s="46"/>
       <x:c r="O396" s="34"/>
       <x:c r="P396" s="32"/>
+      <x:c r="Q396"/>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="34"/>
@@ -8114,6 +8515,7 @@
       <x:c r="N397" s="46"/>
       <x:c r="O397" s="34"/>
       <x:c r="P397" s="32"/>
+      <x:c r="Q397"/>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="34"/>
@@ -8132,6 +8534,7 @@
       <x:c r="N398" s="46"/>
       <x:c r="O398" s="34"/>
       <x:c r="P398" s="32"/>
+      <x:c r="Q398"/>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="34"/>
@@ -8150,6 +8553,7 @@
       <x:c r="N399" s="46"/>
       <x:c r="O399" s="34"/>
       <x:c r="P399" s="32"/>
+      <x:c r="Q399"/>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="34"/>
@@ -8168,6 +8572,7 @@
       <x:c r="N400" s="46"/>
       <x:c r="O400" s="34"/>
       <x:c r="P400" s="32"/>
+      <x:c r="Q400"/>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="34"/>
@@ -8186,6 +8591,7 @@
       <x:c r="N401" s="46"/>
       <x:c r="O401" s="34"/>
       <x:c r="P401" s="32"/>
+      <x:c r="Q401"/>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="34"/>
@@ -8204,6 +8610,7 @@
       <x:c r="N402" s="46"/>
       <x:c r="O402" s="34"/>
       <x:c r="P402" s="32"/>
+      <x:c r="Q402"/>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="34"/>
@@ -8222,6 +8629,7 @@
       <x:c r="N403" s="46"/>
       <x:c r="O403" s="34"/>
       <x:c r="P403" s="32"/>
+      <x:c r="Q403"/>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="34"/>
@@ -8240,6 +8648,7 @@
       <x:c r="N404" s="46"/>
       <x:c r="O404" s="34"/>
       <x:c r="P404" s="32"/>
+      <x:c r="Q404"/>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="34"/>
@@ -8258,6 +8667,7 @@
       <x:c r="N405" s="46"/>
       <x:c r="O405" s="34"/>
       <x:c r="P405" s="32"/>
+      <x:c r="Q405"/>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="34"/>
@@ -8276,6 +8686,7 @@
       <x:c r="N406" s="46"/>
       <x:c r="O406" s="34"/>
       <x:c r="P406" s="32"/>
+      <x:c r="Q406"/>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="34"/>
@@ -8294,6 +8705,7 @@
       <x:c r="N407" s="46"/>
       <x:c r="O407" s="34"/>
       <x:c r="P407" s="32"/>
+      <x:c r="Q407"/>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="34"/>
@@ -8312,6 +8724,7 @@
       <x:c r="N408" s="46"/>
       <x:c r="O408" s="34"/>
       <x:c r="P408" s="32"/>
+      <x:c r="Q408"/>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="34"/>
@@ -8330,6 +8743,7 @@
       <x:c r="N409" s="46"/>
       <x:c r="O409" s="34"/>
       <x:c r="P409" s="32"/>
+      <x:c r="Q409"/>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="34"/>
@@ -8348,6 +8762,7 @@
       <x:c r="N410" s="46"/>
       <x:c r="O410" s="34"/>
       <x:c r="P410" s="32"/>
+      <x:c r="Q410"/>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="34"/>
@@ -8366,6 +8781,7 @@
       <x:c r="N411" s="46"/>
       <x:c r="O411" s="34"/>
       <x:c r="P411" s="32"/>
+      <x:c r="Q411"/>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="34"/>
@@ -8384,6 +8800,7 @@
       <x:c r="N412" s="46"/>
       <x:c r="O412" s="34"/>
       <x:c r="P412" s="32"/>
+      <x:c r="Q412"/>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="34"/>
@@ -8402,6 +8819,7 @@
       <x:c r="N413" s="46"/>
       <x:c r="O413" s="34"/>
       <x:c r="P413" s="32"/>
+      <x:c r="Q413"/>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="34"/>
@@ -8420,6 +8838,7 @@
       <x:c r="N414" s="46"/>
       <x:c r="O414" s="34"/>
       <x:c r="P414" s="32"/>
+      <x:c r="Q414"/>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="34"/>
@@ -8438,6 +8857,7 @@
       <x:c r="N415" s="46"/>
       <x:c r="O415" s="34"/>
       <x:c r="P415" s="32"/>
+      <x:c r="Q415"/>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="34"/>
@@ -8456,6 +8876,7 @@
       <x:c r="N416" s="46"/>
       <x:c r="O416" s="34"/>
       <x:c r="P416" s="32"/>
+      <x:c r="Q416"/>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="34"/>
@@ -8474,6 +8895,7 @@
       <x:c r="N417" s="46"/>
       <x:c r="O417" s="34"/>
       <x:c r="P417" s="32"/>
+      <x:c r="Q417"/>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="34"/>
@@ -8492,6 +8914,7 @@
       <x:c r="N418" s="46"/>
       <x:c r="O418" s="34"/>
       <x:c r="P418" s="32"/>
+      <x:c r="Q418"/>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="34"/>
@@ -8510,6 +8933,7 @@
       <x:c r="N419" s="46"/>
       <x:c r="O419" s="34"/>
       <x:c r="P419" s="32"/>
+      <x:c r="Q419"/>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="34"/>
@@ -8528,6 +8952,7 @@
       <x:c r="N420" s="46"/>
       <x:c r="O420" s="34"/>
       <x:c r="P420" s="32"/>
+      <x:c r="Q420"/>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="34"/>
@@ -8546,6 +8971,7 @@
       <x:c r="N421" s="46"/>
       <x:c r="O421" s="34"/>
       <x:c r="P421" s="32"/>
+      <x:c r="Q421"/>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="34"/>
@@ -8564,6 +8990,7 @@
       <x:c r="N422" s="46"/>
       <x:c r="O422" s="34"/>
       <x:c r="P422" s="32"/>
+      <x:c r="Q422"/>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="34"/>
@@ -8582,6 +9009,7 @@
       <x:c r="N423" s="46"/>
       <x:c r="O423" s="34"/>
       <x:c r="P423" s="32"/>
+      <x:c r="Q423"/>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="34"/>
@@ -8600,6 +9028,7 @@
       <x:c r="N424" s="46"/>
       <x:c r="O424" s="34"/>
       <x:c r="P424" s="32"/>
+      <x:c r="Q424"/>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="34"/>
@@ -8618,6 +9047,7 @@
       <x:c r="N425" s="46"/>
       <x:c r="O425" s="34"/>
       <x:c r="P425" s="32"/>
+      <x:c r="Q425"/>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="34"/>
@@ -8636,6 +9066,7 @@
       <x:c r="N426" s="46"/>
       <x:c r="O426" s="34"/>
       <x:c r="P426" s="32"/>
+      <x:c r="Q426"/>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="34"/>
@@ -8654,6 +9085,7 @@
       <x:c r="N427" s="46"/>
       <x:c r="O427" s="34"/>
       <x:c r="P427" s="32"/>
+      <x:c r="Q427"/>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="34"/>
@@ -8672,6 +9104,7 @@
       <x:c r="N428" s="46"/>
       <x:c r="O428" s="34"/>
       <x:c r="P428" s="32"/>
+      <x:c r="Q428"/>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="34"/>
@@ -8690,6 +9123,7 @@
       <x:c r="N429" s="46"/>
       <x:c r="O429" s="34"/>
       <x:c r="P429" s="32"/>
+      <x:c r="Q429"/>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="34"/>
@@ -8708,6 +9142,7 @@
       <x:c r="N430" s="46"/>
       <x:c r="O430" s="34"/>
       <x:c r="P430" s="32"/>
+      <x:c r="Q430"/>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="34"/>
@@ -8726,6 +9161,7 @@
       <x:c r="N431" s="46"/>
       <x:c r="O431" s="34"/>
       <x:c r="P431" s="32"/>
+      <x:c r="Q431"/>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="34"/>
@@ -8744,6 +9180,7 @@
       <x:c r="N432" s="46"/>
       <x:c r="O432" s="34"/>
       <x:c r="P432" s="32"/>
+      <x:c r="Q432"/>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="34"/>
@@ -8762,6 +9199,7 @@
       <x:c r="N433" s="46"/>
       <x:c r="O433" s="34"/>
       <x:c r="P433" s="32"/>
+      <x:c r="Q433"/>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="34"/>
@@ -8780,6 +9218,7 @@
       <x:c r="N434" s="46"/>
       <x:c r="O434" s="34"/>
       <x:c r="P434" s="32"/>
+      <x:c r="Q434"/>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="34"/>
@@ -8798,6 +9237,7 @@
       <x:c r="N435" s="46"/>
       <x:c r="O435" s="34"/>
       <x:c r="P435" s="32"/>
+      <x:c r="Q435"/>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="34"/>
@@ -8816,6 +9256,7 @@
       <x:c r="N436" s="46"/>
       <x:c r="O436" s="34"/>
       <x:c r="P436" s="32"/>
+      <x:c r="Q436"/>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="34"/>
@@ -8834,6 +9275,7 @@
       <x:c r="N437" s="46"/>
       <x:c r="O437" s="34"/>
       <x:c r="P437" s="32"/>
+      <x:c r="Q437"/>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="34"/>
@@ -8852,6 +9294,7 @@
       <x:c r="N438" s="46"/>
       <x:c r="O438" s="34"/>
       <x:c r="P438" s="32"/>
+      <x:c r="Q438"/>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="34"/>
@@ -8870,6 +9313,7 @@
       <x:c r="N439" s="46"/>
       <x:c r="O439" s="34"/>
       <x:c r="P439" s="32"/>
+      <x:c r="Q439"/>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="34"/>
@@ -8888,6 +9332,7 @@
       <x:c r="N440" s="46"/>
       <x:c r="O440" s="34"/>
       <x:c r="P440" s="32"/>
+      <x:c r="Q440"/>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="34"/>
@@ -8906,6 +9351,7 @@
       <x:c r="N441" s="46"/>
       <x:c r="O441" s="34"/>
       <x:c r="P441" s="32"/>
+      <x:c r="Q441"/>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="34"/>
@@ -8924,6 +9370,7 @@
       <x:c r="N442" s="46"/>
       <x:c r="O442" s="34"/>
       <x:c r="P442" s="32"/>
+      <x:c r="Q442"/>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="34"/>
@@ -8942,6 +9389,7 @@
       <x:c r="N443" s="46"/>
       <x:c r="O443" s="34"/>
       <x:c r="P443" s="32"/>
+      <x:c r="Q443"/>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="34"/>
@@ -8960,6 +9408,7 @@
       <x:c r="N444" s="46"/>
       <x:c r="O444" s="34"/>
       <x:c r="P444" s="32"/>
+      <x:c r="Q444"/>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="34"/>
@@ -8978,6 +9427,7 @@
       <x:c r="N445" s="46"/>
       <x:c r="O445" s="34"/>
       <x:c r="P445" s="32"/>
+      <x:c r="Q445"/>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="34"/>
@@ -8996,6 +9446,7 @@
       <x:c r="N446" s="46"/>
       <x:c r="O446" s="34"/>
       <x:c r="P446" s="32"/>
+      <x:c r="Q446"/>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="34"/>
@@ -9014,6 +9465,7 @@
       <x:c r="N447" s="46"/>
       <x:c r="O447" s="34"/>
       <x:c r="P447" s="32"/>
+      <x:c r="Q447"/>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="34"/>
@@ -9032,6 +9484,7 @@
       <x:c r="N448" s="46"/>
       <x:c r="O448" s="34"/>
       <x:c r="P448" s="32"/>
+      <x:c r="Q448"/>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="34"/>
@@ -9050,6 +9503,7 @@
       <x:c r="N449" s="46"/>
       <x:c r="O449" s="34"/>
       <x:c r="P449" s="32"/>
+      <x:c r="Q449"/>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="34"/>
@@ -9068,6 +9522,7 @@
       <x:c r="N450" s="46"/>
       <x:c r="O450" s="34"/>
       <x:c r="P450" s="32"/>
+      <x:c r="Q450"/>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="34"/>
@@ -9086,6 +9541,7 @@
       <x:c r="N451" s="46"/>
       <x:c r="O451" s="34"/>
       <x:c r="P451" s="32"/>
+      <x:c r="Q451"/>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="34"/>
@@ -9104,6 +9560,7 @@
       <x:c r="N452" s="46"/>
       <x:c r="O452" s="34"/>
       <x:c r="P452" s="32"/>
+      <x:c r="Q452"/>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="34"/>
@@ -9122,6 +9579,7 @@
       <x:c r="N453" s="46"/>
       <x:c r="O453" s="34"/>
       <x:c r="P453" s="32"/>
+      <x:c r="Q453"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="34"/>
@@ -9140,6 +9598,7 @@
       <x:c r="N454" s="46"/>
       <x:c r="O454" s="34"/>
       <x:c r="P454" s="32"/>
+      <x:c r="Q454"/>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="34"/>
@@ -9158,6 +9617,7 @@
       <x:c r="N455" s="46"/>
       <x:c r="O455" s="34"/>
       <x:c r="P455" s="32"/>
+      <x:c r="Q455"/>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="34"/>
@@ -9176,6 +9636,7 @@
       <x:c r="N456" s="46"/>
       <x:c r="O456" s="34"/>
       <x:c r="P456" s="32"/>
+      <x:c r="Q456"/>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="34"/>
@@ -9194,6 +9655,7 @@
       <x:c r="N457" s="46"/>
       <x:c r="O457" s="34"/>
       <x:c r="P457" s="32"/>
+      <x:c r="Q457"/>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="34"/>
@@ -9212,6 +9674,7 @@
       <x:c r="N458" s="46"/>
       <x:c r="O458" s="34"/>
       <x:c r="P458" s="32"/>
+      <x:c r="Q458"/>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="34"/>
@@ -9230,6 +9693,7 @@
       <x:c r="N459" s="46"/>
       <x:c r="O459" s="34"/>
       <x:c r="P459" s="32"/>
+      <x:c r="Q459"/>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="34"/>
@@ -9248,6 +9712,7 @@
       <x:c r="N460" s="46"/>
       <x:c r="O460" s="34"/>
       <x:c r="P460" s="32"/>
+      <x:c r="Q460"/>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="34"/>
@@ -9266,6 +9731,7 @@
       <x:c r="N461" s="46"/>
       <x:c r="O461" s="34"/>
       <x:c r="P461" s="32"/>
+      <x:c r="Q461"/>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="34"/>
@@ -9284,6 +9750,7 @@
       <x:c r="N462" s="46"/>
       <x:c r="O462" s="34"/>
       <x:c r="P462" s="32"/>
+      <x:c r="Q462"/>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="34"/>
@@ -9302,6 +9769,7 @@
       <x:c r="N463" s="46"/>
       <x:c r="O463" s="34"/>
       <x:c r="P463" s="32"/>
+      <x:c r="Q463"/>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="34"/>
@@ -9320,6 +9788,7 @@
       <x:c r="N464" s="46"/>
       <x:c r="O464" s="34"/>
       <x:c r="P464" s="32"/>
+      <x:c r="Q464"/>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="34"/>
@@ -9338,6 +9807,7 @@
       <x:c r="N465" s="46"/>
       <x:c r="O465" s="34"/>
       <x:c r="P465" s="32"/>
+      <x:c r="Q465"/>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="34"/>
@@ -9356,6 +9826,7 @@
       <x:c r="N466" s="46"/>
       <x:c r="O466" s="34"/>
       <x:c r="P466" s="32"/>
+      <x:c r="Q466"/>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="34"/>
@@ -9374,6 +9845,7 @@
       <x:c r="N467" s="46"/>
       <x:c r="O467" s="34"/>
       <x:c r="P467" s="32"/>
+      <x:c r="Q467"/>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="34"/>
@@ -9392,6 +9864,7 @@
       <x:c r="N468" s="46"/>
       <x:c r="O468" s="34"/>
       <x:c r="P468" s="32"/>
+      <x:c r="Q468"/>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="34"/>
@@ -9410,6 +9883,7 @@
       <x:c r="N469" s="46"/>
       <x:c r="O469" s="34"/>
       <x:c r="P469" s="32"/>
+      <x:c r="Q469"/>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="34"/>
@@ -9428,6 +9902,7 @@
       <x:c r="N470" s="46"/>
       <x:c r="O470" s="34"/>
       <x:c r="P470" s="32"/>
+      <x:c r="Q470"/>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="34"/>
@@ -9446,6 +9921,7 @@
       <x:c r="N471" s="46"/>
       <x:c r="O471" s="34"/>
       <x:c r="P471" s="32"/>
+      <x:c r="Q471"/>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="34"/>
@@ -9464,6 +9940,7 @@
       <x:c r="N472" s="46"/>
       <x:c r="O472" s="34"/>
       <x:c r="P472" s="32"/>
+      <x:c r="Q472"/>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="34"/>
@@ -9482,6 +9959,7 @@
       <x:c r="N473" s="46"/>
       <x:c r="O473" s="34"/>
       <x:c r="P473" s="32"/>
+      <x:c r="Q473"/>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="34"/>
@@ -9500,6 +9978,7 @@
       <x:c r="N474" s="46"/>
       <x:c r="O474" s="34"/>
       <x:c r="P474" s="32"/>
+      <x:c r="Q474"/>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="34"/>
@@ -9518,6 +9997,7 @@
       <x:c r="N475" s="46"/>
       <x:c r="O475" s="34"/>
       <x:c r="P475" s="32"/>
+      <x:c r="Q475"/>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="34"/>
@@ -9536,6 +10016,7 @@
       <x:c r="N476" s="46"/>
       <x:c r="O476" s="34"/>
       <x:c r="P476" s="32"/>
+      <x:c r="Q476"/>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="34"/>
@@ -9554,6 +10035,7 @@
       <x:c r="N477" s="46"/>
       <x:c r="O477" s="34"/>
       <x:c r="P477" s="32"/>
+      <x:c r="Q477"/>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="34"/>
@@ -9572,6 +10054,7 @@
       <x:c r="N478" s="46"/>
       <x:c r="O478" s="34"/>
       <x:c r="P478" s="32"/>
+      <x:c r="Q478"/>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="34"/>
@@ -9590,6 +10073,7 @@
       <x:c r="N479" s="46"/>
       <x:c r="O479" s="34"/>
       <x:c r="P479" s="32"/>
+      <x:c r="Q479"/>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="34"/>
@@ -9608,6 +10092,7 @@
       <x:c r="N480" s="46"/>
       <x:c r="O480" s="34"/>
       <x:c r="P480" s="32"/>
+      <x:c r="Q480"/>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="34"/>
@@ -9626,6 +10111,7 @@
       <x:c r="N481" s="46"/>
       <x:c r="O481" s="34"/>
       <x:c r="P481" s="32"/>
+      <x:c r="Q481"/>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="34"/>
@@ -9644,6 +10130,7 @@
       <x:c r="N482" s="46"/>
       <x:c r="O482" s="34"/>
       <x:c r="P482" s="32"/>
+      <x:c r="Q482"/>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="34"/>
@@ -9662,6 +10149,7 @@
       <x:c r="N483" s="46"/>
       <x:c r="O483" s="34"/>
       <x:c r="P483" s="32"/>
+      <x:c r="Q483"/>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="34"/>
@@ -9680,6 +10168,7 @@
       <x:c r="N484" s="46"/>
       <x:c r="O484" s="34"/>
       <x:c r="P484" s="32"/>
+      <x:c r="Q484"/>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="34"/>
@@ -9698,6 +10187,7 @@
       <x:c r="N485" s="46"/>
       <x:c r="O485" s="34"/>
       <x:c r="P485" s="32"/>
+      <x:c r="Q485"/>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="34"/>
@@ -9716,6 +10206,7 @@
       <x:c r="N486" s="46"/>
       <x:c r="O486" s="34"/>
       <x:c r="P486" s="32"/>
+      <x:c r="Q486"/>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="34"/>
@@ -9734,6 +10225,7 @@
       <x:c r="N487" s="46"/>
       <x:c r="O487" s="34"/>
       <x:c r="P487" s="32"/>
+      <x:c r="Q487"/>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="34"/>
@@ -9752,6 +10244,7 @@
       <x:c r="N488" s="46"/>
       <x:c r="O488" s="34"/>
       <x:c r="P488" s="32"/>
+      <x:c r="Q488"/>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="34"/>
@@ -9770,6 +10263,7 @@
       <x:c r="N489" s="46"/>
       <x:c r="O489" s="34"/>
       <x:c r="P489" s="32"/>
+      <x:c r="Q489"/>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="34"/>
@@ -9788,6 +10282,7 @@
       <x:c r="N490" s="46"/>
       <x:c r="O490" s="34"/>
       <x:c r="P490" s="32"/>
+      <x:c r="Q490"/>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="34"/>
@@ -9806,6 +10301,7 @@
       <x:c r="N491" s="46"/>
       <x:c r="O491" s="34"/>
       <x:c r="P491" s="32"/>
+      <x:c r="Q491"/>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="34"/>
@@ -9824,6 +10320,7 @@
       <x:c r="N492" s="46"/>
       <x:c r="O492" s="34"/>
       <x:c r="P492" s="32"/>
+      <x:c r="Q492"/>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="34"/>
@@ -9842,6 +10339,7 @@
       <x:c r="N493" s="46"/>
       <x:c r="O493" s="34"/>
       <x:c r="P493" s="32"/>
+      <x:c r="Q493"/>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="34"/>
@@ -9860,6 +10358,7 @@
       <x:c r="N494" s="46"/>
       <x:c r="O494" s="34"/>
       <x:c r="P494" s="32"/>
+      <x:c r="Q494"/>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="34"/>
@@ -9878,6 +10377,7 @@
       <x:c r="N495" s="46"/>
       <x:c r="O495" s="34"/>
       <x:c r="P495" s="32"/>
+      <x:c r="Q495"/>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="34"/>
@@ -9896,6 +10396,7 @@
       <x:c r="N496" s="46"/>
       <x:c r="O496" s="34"/>
       <x:c r="P496" s="32"/>
+      <x:c r="Q496"/>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="34"/>
@@ -9914,6 +10415,7 @@
       <x:c r="N497" s="46"/>
       <x:c r="O497" s="34"/>
       <x:c r="P497" s="32"/>
+      <x:c r="Q497"/>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="34"/>
@@ -9932,6 +10434,7 @@
       <x:c r="N498" s="46"/>
       <x:c r="O498" s="34"/>
       <x:c r="P498" s="32"/>
+      <x:c r="Q498"/>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="34"/>
@@ -9950,6 +10453,7 @@
       <x:c r="N499" s="46"/>
       <x:c r="O499" s="34"/>
       <x:c r="P499" s="32"/>
+      <x:c r="Q499"/>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="34"/>
@@ -9968,6 +10472,7 @@
       <x:c r="N500" s="46"/>
       <x:c r="O500" s="34"/>
       <x:c r="P500" s="32"/>
+      <x:c r="Q500"/>
     </x:row>
     <x:row r="501">
       <x:c r="A501" s="34"/>
@@ -9986,6 +10491,7 @@
       <x:c r="N501" s="46"/>
       <x:c r="O501" s="34"/>
       <x:c r="P501" s="32"/>
+      <x:c r="Q501"/>
     </x:row>
     <x:row r="502">
       <x:c r="A502" s="34"/>
@@ -10004,6 +10510,7 @@
       <x:c r="N502" s="46"/>
       <x:c r="O502" s="34"/>
       <x:c r="P502" s="32"/>
+      <x:c r="Q502"/>
     </x:row>
     <x:row r="503">
       <x:c r="A503" s="34"/>
@@ -10022,6 +10529,7 @@
       <x:c r="N503" s="46"/>
       <x:c r="O503" s="34"/>
       <x:c r="P503" s="32"/>
+      <x:c r="Q503"/>
     </x:row>
     <x:row r="504">
       <x:c r="A504" s="34"/>
@@ -10040,6 +10548,7 @@
       <x:c r="N504" s="46"/>
       <x:c r="O504" s="34"/>
       <x:c r="P504" s="32"/>
+      <x:c r="Q504"/>
     </x:row>
     <x:row r="505">
       <x:c r="A505" s="34"/>
@@ -10058,6 +10567,7 @@
       <x:c r="N505" s="46"/>
       <x:c r="O505" s="34"/>
       <x:c r="P505" s="32"/>
+      <x:c r="Q505"/>
     </x:row>
     <x:row r="506">
       <x:c r="A506" s="34"/>
@@ -10076,6 +10586,7 @@
       <x:c r="N506" s="46"/>
       <x:c r="O506" s="34"/>
       <x:c r="P506" s="32"/>
+      <x:c r="Q506"/>
     </x:row>
     <x:row r="507">
       <x:c r="A507" s="34"/>
@@ -10094,6 +10605,7 @@
       <x:c r="N507" s="46"/>
       <x:c r="O507" s="34"/>
       <x:c r="P507" s="32"/>
+      <x:c r="Q507"/>
     </x:row>
     <x:row r="508">
       <x:c r="A508" s="34"/>
@@ -10112,6 +10624,7 @@
       <x:c r="N508" s="46"/>
       <x:c r="O508" s="34"/>
       <x:c r="P508" s="32"/>
+      <x:c r="Q508"/>
     </x:row>
     <x:row r="509">
       <x:c r="A509" s="34"/>
@@ -10130,6 +10643,7 @@
       <x:c r="N509" s="46"/>
       <x:c r="O509" s="34"/>
       <x:c r="P509" s="32"/>
+      <x:c r="Q509"/>
     </x:row>
     <x:row r="510">
       <x:c r="A510" s="34"/>
@@ -10148,6 +10662,7 @@
       <x:c r="N510" s="46"/>
       <x:c r="O510" s="34"/>
       <x:c r="P510" s="32"/>
+      <x:c r="Q510"/>
     </x:row>
     <x:row r="511">
       <x:c r="A511" s="34"/>
@@ -10166,6 +10681,7 @@
       <x:c r="N511" s="46"/>
       <x:c r="O511" s="34"/>
       <x:c r="P511" s="32"/>
+      <x:c r="Q511"/>
     </x:row>
     <x:row r="512">
       <x:c r="A512" s="34"/>
@@ -10184,6 +10700,7 @@
       <x:c r="N512" s="46"/>
       <x:c r="O512" s="34"/>
       <x:c r="P512" s="32"/>
+      <x:c r="Q512"/>
     </x:row>
     <x:row r="513">
       <x:c r="A513" s="34"/>
@@ -10202,6 +10719,7 @@
       <x:c r="N513" s="46"/>
       <x:c r="O513" s="34"/>
       <x:c r="P513" s="32"/>
+      <x:c r="Q513"/>
     </x:row>
     <x:row r="514">
       <x:c r="A514" s="34"/>
@@ -10220,6 +10738,7 @@
       <x:c r="N514" s="46"/>
       <x:c r="O514" s="34"/>
       <x:c r="P514" s="32"/>
+      <x:c r="Q514"/>
     </x:row>
     <x:row r="515">
       <x:c r="A515" s="34"/>
@@ -10238,6 +10757,7 @@
       <x:c r="N515" s="46"/>
       <x:c r="O515" s="34"/>
       <x:c r="P515" s="32"/>
+      <x:c r="Q515"/>
     </x:row>
     <x:row r="516">
       <x:c r="A516" s="34"/>
@@ -10256,6 +10776,7 @@
       <x:c r="N516" s="46"/>
       <x:c r="O516" s="34"/>
       <x:c r="P516" s="32"/>
+      <x:c r="Q516"/>
     </x:row>
     <x:row r="517">
       <x:c r="A517" s="34"/>
@@ -10274,6 +10795,7 @@
       <x:c r="N517" s="46"/>
       <x:c r="O517" s="34"/>
       <x:c r="P517" s="32"/>
+      <x:c r="Q517"/>
     </x:row>
     <x:row r="518">
       <x:c r="A518" s="34"/>
@@ -10292,6 +10814,7 @@
       <x:c r="N518" s="46"/>
       <x:c r="O518" s="34"/>
       <x:c r="P518" s="32"/>
+      <x:c r="Q518"/>
     </x:row>
     <x:row r="519">
       <x:c r="A519" s="34"/>
@@ -10310,6 +10833,7 @@
       <x:c r="N519" s="46"/>
       <x:c r="O519" s="34"/>
       <x:c r="P519" s="32"/>
+      <x:c r="Q519"/>
     </x:row>
     <x:row r="520">
       <x:c r="A520" s="34"/>
@@ -10328,6 +10852,7 @@
       <x:c r="N520" s="46"/>
       <x:c r="O520" s="34"/>
       <x:c r="P520" s="32"/>
+      <x:c r="Q520"/>
     </x:row>
     <x:row r="521">
       <x:c r="A521" s="34"/>
@@ -10346,6 +10871,7 @@
       <x:c r="N521" s="46"/>
       <x:c r="O521" s="34"/>
       <x:c r="P521" s="32"/>
+      <x:c r="Q521"/>
     </x:row>
     <x:row r="522">
       <x:c r="A522" s="34"/>
@@ -10364,6 +10890,7 @@
       <x:c r="N522" s="46"/>
       <x:c r="O522" s="34"/>
       <x:c r="P522" s="32"/>
+      <x:c r="Q522"/>
     </x:row>
     <x:row r="523">
       <x:c r="A523" s="34"/>
@@ -10382,6 +10909,7 @@
       <x:c r="N523" s="46"/>
       <x:c r="O523" s="34"/>
       <x:c r="P523" s="32"/>
+      <x:c r="Q523"/>
     </x:row>
     <x:row r="524">
       <x:c r="A524" s="34"/>
@@ -10400,6 +10928,7 @@
       <x:c r="N524" s="46"/>
       <x:c r="O524" s="34"/>
       <x:c r="P524" s="32"/>
+      <x:c r="Q524"/>
     </x:row>
     <x:row r="525">
       <x:c r="A525" s="34"/>
@@ -10418,6 +10947,7 @@
       <x:c r="N525" s="46"/>
       <x:c r="O525" s="34"/>
       <x:c r="P525" s="32"/>
+      <x:c r="Q525"/>
     </x:row>
     <x:row r="526">
       <x:c r="A526" s="34"/>
@@ -10436,6 +10966,7 @@
       <x:c r="N526" s="46"/>
       <x:c r="O526" s="34"/>
       <x:c r="P526" s="32"/>
+      <x:c r="Q526"/>
     </x:row>
     <x:row r="527">
       <x:c r="A527" s="34"/>
@@ -10454,6 +10985,7 @@
       <x:c r="N527" s="46"/>
       <x:c r="O527" s="34"/>
       <x:c r="P527" s="32"/>
+      <x:c r="Q527"/>
     </x:row>
     <x:row r="528">
       <x:c r="A528" s="34"/>
@@ -10472,6 +11004,7 @@
       <x:c r="N528" s="46"/>
       <x:c r="O528" s="34"/>
       <x:c r="P528" s="32"/>
+      <x:c r="Q528"/>
     </x:row>
     <x:row r="529">
       <x:c r="A529" s="34"/>
@@ -10490,6 +11023,7 @@
       <x:c r="N529" s="46"/>
       <x:c r="O529" s="34"/>
       <x:c r="P529" s="32"/>
+      <x:c r="Q529"/>
     </x:row>
     <x:row r="530">
       <x:c r="A530" s="34"/>
@@ -10508,6 +11042,7 @@
       <x:c r="N530" s="46"/>
       <x:c r="O530" s="34"/>
       <x:c r="P530" s="32"/>
+      <x:c r="Q530"/>
     </x:row>
     <x:row r="531">
       <x:c r="A531" s="34"/>
@@ -10526,6 +11061,7 @@
       <x:c r="N531" s="46"/>
       <x:c r="O531" s="34"/>
       <x:c r="P531" s="32"/>
+      <x:c r="Q531"/>
     </x:row>
     <x:row r="532">
       <x:c r="A532" s="34"/>
@@ -10544,6 +11080,7 @@
       <x:c r="N532" s="46"/>
       <x:c r="O532" s="34"/>
       <x:c r="P532" s="32"/>
+      <x:c r="Q532"/>
     </x:row>
     <x:row r="533">
       <x:c r="A533" s="34"/>
@@ -10562,6 +11099,7 @@
       <x:c r="N533" s="46"/>
       <x:c r="O533" s="34"/>
       <x:c r="P533" s="32"/>
+      <x:c r="Q533"/>
     </x:row>
     <x:row r="534">
       <x:c r="A534" s="34"/>
@@ -10580,6 +11118,7 @@
       <x:c r="N534" s="46"/>
       <x:c r="O534" s="34"/>
       <x:c r="P534" s="32"/>
+      <x:c r="Q534"/>
     </x:row>
     <x:row r="535">
       <x:c r="A535" s="34"/>
@@ -10598,6 +11137,7 @@
       <x:c r="N535" s="46"/>
       <x:c r="O535" s="34"/>
       <x:c r="P535" s="32"/>
+      <x:c r="Q535"/>
     </x:row>
     <x:row r="536">
       <x:c r="A536" s="34"/>
@@ -10616,6 +11156,7 @@
       <x:c r="N536" s="46"/>
       <x:c r="O536" s="34"/>
       <x:c r="P536" s="32"/>
+      <x:c r="Q536"/>
     </x:row>
     <x:row r="537">
       <x:c r="A537" s="34"/>
@@ -10634,6 +11175,7 @@
       <x:c r="N537" s="46"/>
       <x:c r="O537" s="34"/>
       <x:c r="P537" s="32"/>
+      <x:c r="Q537"/>
     </x:row>
     <x:row r="538">
       <x:c r="A538" s="34"/>
@@ -10652,6 +11194,7 @@
       <x:c r="N538" s="46"/>
       <x:c r="O538" s="34"/>
       <x:c r="P538" s="32"/>
+      <x:c r="Q538"/>
     </x:row>
     <x:row r="539">
       <x:c r="A539" s="34"/>
@@ -10670,6 +11213,7 @@
       <x:c r="N539" s="46"/>
       <x:c r="O539" s="34"/>
       <x:c r="P539" s="32"/>
+      <x:c r="Q539"/>
     </x:row>
     <x:row r="540">
       <x:c r="A540" s="34"/>
@@ -10688,6 +11232,7 @@
       <x:c r="N540" s="46"/>
       <x:c r="O540" s="34"/>
       <x:c r="P540" s="32"/>
+      <x:c r="Q540"/>
     </x:row>
     <x:row r="541">
       <x:c r="A541" s="34"/>
@@ -10706,6 +11251,7 @@
       <x:c r="N541" s="46"/>
       <x:c r="O541" s="34"/>
       <x:c r="P541" s="32"/>
+      <x:c r="Q541"/>
     </x:row>
     <x:row r="542">
       <x:c r="A542" s="34"/>
@@ -10724,6 +11270,7 @@
       <x:c r="N542" s="46"/>
       <x:c r="O542" s="34"/>
       <x:c r="P542" s="32"/>
+      <x:c r="Q542"/>
     </x:row>
     <x:row r="543">
       <x:c r="A543" s="34"/>
@@ -10742,6 +11289,7 @@
       <x:c r="N543" s="46"/>
       <x:c r="O543" s="34"/>
       <x:c r="P543" s="32"/>
+      <x:c r="Q543"/>
     </x:row>
     <x:row r="544">
       <x:c r="A544" s="34"/>
@@ -10760,6 +11308,7 @@
       <x:c r="N544" s="46"/>
       <x:c r="O544" s="34"/>
       <x:c r="P544" s="32"/>
+      <x:c r="Q544"/>
     </x:row>
     <x:row r="545">
       <x:c r="A545" s="34"/>
@@ -10778,6 +11327,7 @@
       <x:c r="N545" s="46"/>
       <x:c r="O545" s="34"/>
       <x:c r="P545" s="32"/>
+      <x:c r="Q545"/>
     </x:row>
     <x:row r="546">
       <x:c r="A546" s="34"/>
@@ -10796,6 +11346,7 @@
       <x:c r="N546" s="46"/>
       <x:c r="O546" s="34"/>
       <x:c r="P546" s="32"/>
+      <x:c r="Q546"/>
     </x:row>
     <x:row r="547">
       <x:c r="A547" s="34"/>
@@ -10814,6 +11365,7 @@
       <x:c r="N547" s="46"/>
       <x:c r="O547" s="34"/>
       <x:c r="P547" s="32"/>
+      <x:c r="Q547"/>
     </x:row>
     <x:row r="548">
       <x:c r="A548" s="34"/>
@@ -10832,6 +11384,7 @@
       <x:c r="N548" s="46"/>
       <x:c r="O548" s="34"/>
       <x:c r="P548" s="32"/>
+      <x:c r="Q548"/>
     </x:row>
     <x:row r="549">
       <x:c r="A549" s="34"/>
@@ -10850,6 +11403,7 @@
       <x:c r="N549" s="46"/>
       <x:c r="O549" s="34"/>
       <x:c r="P549" s="32"/>
+      <x:c r="Q549"/>
     </x:row>
     <x:row r="550">
       <x:c r="A550" s="34"/>
@@ -10868,6 +11422,7 @@
       <x:c r="N550" s="46"/>
       <x:c r="O550" s="34"/>
       <x:c r="P550" s="32"/>
+      <x:c r="Q550"/>
     </x:row>
     <x:row r="551">
       <x:c r="A551" s="34"/>
@@ -10886,6 +11441,7 @@
       <x:c r="N551" s="46"/>
       <x:c r="O551" s="34"/>
       <x:c r="P551" s="32"/>
+      <x:c r="Q551"/>
     </x:row>
     <x:row r="552">
       <x:c r="A552" s="34"/>
@@ -10904,6 +11460,7 @@
       <x:c r="N552" s="46"/>
       <x:c r="O552" s="34"/>
       <x:c r="P552" s="32"/>
+      <x:c r="Q552"/>
     </x:row>
     <x:row r="553">
       <x:c r="A553" s="34"/>
@@ -10922,6 +11479,7 @@
       <x:c r="N553" s="46"/>
       <x:c r="O553" s="34"/>
       <x:c r="P553" s="32"/>
+      <x:c r="Q553"/>
     </x:row>
     <x:row r="554">
       <x:c r="A554" s="34"/>
@@ -10940,6 +11498,7 @@
       <x:c r="N554" s="46"/>
       <x:c r="O554" s="34"/>
       <x:c r="P554" s="32"/>
+      <x:c r="Q554"/>
     </x:row>
     <x:row r="555">
       <x:c r="A555" s="34"/>
@@ -10958,6 +11517,7 @@
       <x:c r="N555" s="46"/>
       <x:c r="O555" s="34"/>
       <x:c r="P555" s="32"/>
+      <x:c r="Q555"/>
     </x:row>
     <x:row r="556">
       <x:c r="A556" s="34"/>
@@ -10976,6 +11536,7 @@
       <x:c r="N556" s="46"/>
       <x:c r="O556" s="34"/>
       <x:c r="P556" s="32"/>
+      <x:c r="Q556"/>
     </x:row>
     <x:row r="557">
       <x:c r="A557" s="34"/>
@@ -10994,6 +11555,7 @@
       <x:c r="N557" s="46"/>
       <x:c r="O557" s="34"/>
       <x:c r="P557" s="32"/>
+      <x:c r="Q557"/>
     </x:row>
     <x:row r="558">
       <x:c r="A558" s="34"/>
@@ -11012,6 +11574,7 @@
       <x:c r="N558" s="46"/>
       <x:c r="O558" s="34"/>
       <x:c r="P558" s="32"/>
+      <x:c r="Q558"/>
     </x:row>
     <x:row r="559">
       <x:c r="A559" s="34"/>
@@ -11030,6 +11593,7 @@
       <x:c r="N559" s="46"/>
       <x:c r="O559" s="34"/>
       <x:c r="P559" s="32"/>
+      <x:c r="Q559"/>
     </x:row>
     <x:row r="560">
       <x:c r="A560" s="34"/>
@@ -11048,6 +11612,7 @@
       <x:c r="N560" s="46"/>
       <x:c r="O560" s="34"/>
       <x:c r="P560" s="32"/>
+      <x:c r="Q560"/>
     </x:row>
     <x:row r="561">
       <x:c r="A561" s="34"/>
@@ -11066,6 +11631,7 @@
       <x:c r="N561" s="46"/>
       <x:c r="O561" s="34"/>
       <x:c r="P561" s="32"/>
+      <x:c r="Q561"/>
     </x:row>
     <x:row r="562">
       <x:c r="A562" s="34"/>
@@ -11084,6 +11650,7 @@
       <x:c r="N562" s="46"/>
       <x:c r="O562" s="34"/>
       <x:c r="P562" s="32"/>
+      <x:c r="Q562"/>
     </x:row>
     <x:row r="563">
       <x:c r="A563" s="34"/>
@@ -11102,6 +11669,7 @@
       <x:c r="N563" s="46"/>
       <x:c r="O563" s="34"/>
       <x:c r="P563" s="32"/>
+      <x:c r="Q563"/>
     </x:row>
     <x:row r="564">
       <x:c r="A564" s="34"/>
@@ -11120,6 +11688,7 @@
       <x:c r="N564" s="46"/>
       <x:c r="O564" s="34"/>
       <x:c r="P564" s="32"/>
+      <x:c r="Q564"/>
     </x:row>
     <x:row r="565">
       <x:c r="A565" s="34"/>
@@ -11138,6 +11707,7 @@
       <x:c r="N565" s="46"/>
       <x:c r="O565" s="34"/>
       <x:c r="P565" s="32"/>
+      <x:c r="Q565"/>
     </x:row>
     <x:row r="566">
       <x:c r="A566" s="34"/>
@@ -11156,6 +11726,7 @@
       <x:c r="N566" s="46"/>
       <x:c r="O566" s="34"/>
       <x:c r="P566" s="32"/>
+      <x:c r="Q566"/>
     </x:row>
     <x:row r="567">
       <x:c r="A567" s="34"/>
@@ -11174,6 +11745,7 @@
       <x:c r="N567" s="46"/>
       <x:c r="O567" s="34"/>
       <x:c r="P567" s="32"/>
+      <x:c r="Q567"/>
     </x:row>
     <x:row r="568">
       <x:c r="A568" s="34"/>
@@ -11192,6 +11764,7 @@
       <x:c r="N568" s="46"/>
       <x:c r="O568" s="34"/>
       <x:c r="P568" s="32"/>
+      <x:c r="Q568"/>
     </x:row>
     <x:row r="569">
       <x:c r="A569" s="34"/>
@@ -11210,6 +11783,7 @@
       <x:c r="N569" s="46"/>
       <x:c r="O569" s="34"/>
       <x:c r="P569" s="32"/>
+      <x:c r="Q569"/>
     </x:row>
     <x:row r="570">
       <x:c r="A570" s="34"/>
@@ -11228,6 +11802,7 @@
       <x:c r="N570" s="46"/>
       <x:c r="O570" s="34"/>
       <x:c r="P570" s="32"/>
+      <x:c r="Q570"/>
     </x:row>
     <x:row r="571">
       <x:c r="A571" s="34"/>
@@ -11246,6 +11821,7 @@
       <x:c r="N571" s="46"/>
       <x:c r="O571" s="34"/>
       <x:c r="P571" s="32"/>
+      <x:c r="Q571"/>
     </x:row>
     <x:row r="572">
       <x:c r="A572" s="34"/>
@@ -11264,6 +11840,7 @@
       <x:c r="N572" s="46"/>
       <x:c r="O572" s="34"/>
       <x:c r="P572" s="32"/>
+      <x:c r="Q572"/>
     </x:row>
     <x:row r="573">
       <x:c r="A573" s="34"/>
@@ -11282,6 +11859,7 @@
       <x:c r="N573" s="46"/>
       <x:c r="O573" s="34"/>
       <x:c r="P573" s="32"/>
+      <x:c r="Q573"/>
     </x:row>
     <x:row r="574">
       <x:c r="A574" s="34"/>
@@ -11300,6 +11878,7 @@
       <x:c r="N574" s="46"/>
       <x:c r="O574" s="34"/>
       <x:c r="P574" s="32"/>
+      <x:c r="Q574"/>
     </x:row>
     <x:row r="575">
       <x:c r="A575" s="34"/>
@@ -11318,6 +11897,7 @@
       <x:c r="N575" s="46"/>
       <x:c r="O575" s="34"/>
       <x:c r="P575" s="32"/>
+      <x:c r="Q575"/>
     </x:row>
     <x:row r="576">
       <x:c r="A576" s="34"/>
@@ -11336,6 +11916,7 @@
       <x:c r="N576" s="46"/>
       <x:c r="O576" s="34"/>
       <x:c r="P576" s="32"/>
+      <x:c r="Q576"/>
     </x:row>
     <x:row r="577">
       <x:c r="A577" s="34"/>
@@ -11354,6 +11935,7 @@
       <x:c r="N577" s="46"/>
       <x:c r="O577" s="34"/>
       <x:c r="P577" s="32"/>
+      <x:c r="Q577"/>
     </x:row>
     <x:row r="578">
       <x:c r="A578" s="34"/>
@@ -11372,6 +11954,7 @@
       <x:c r="N578" s="46"/>
       <x:c r="O578" s="34"/>
       <x:c r="P578" s="32"/>
+      <x:c r="Q578"/>
     </x:row>
     <x:row r="579">
       <x:c r="A579" s="34"/>
@@ -11390,6 +11973,7 @@
       <x:c r="N579" s="46"/>
       <x:c r="O579" s="34"/>
       <x:c r="P579" s="32"/>
+      <x:c r="Q579"/>
     </x:row>
     <x:row r="580">
       <x:c r="A580" s="34"/>
@@ -11408,6 +11992,7 @@
       <x:c r="N580" s="46"/>
       <x:c r="O580" s="34"/>
       <x:c r="P580" s="32"/>
+      <x:c r="Q580"/>
     </x:row>
     <x:row r="581">
       <x:c r="A581" s="34"/>
@@ -11426,6 +12011,7 @@
       <x:c r="N581" s="46"/>
       <x:c r="O581" s="34"/>
       <x:c r="P581" s="32"/>
+      <x:c r="Q581"/>
     </x:row>
     <x:row r="582">
       <x:c r="A582" s="34"/>
@@ -11444,6 +12030,7 @@
       <x:c r="N582" s="46"/>
       <x:c r="O582" s="34"/>
       <x:c r="P582" s="32"/>
+      <x:c r="Q582"/>
     </x:row>
     <x:row r="583">
       <x:c r="A583" s="34"/>
@@ -11462,6 +12049,7 @@
       <x:c r="N583" s="46"/>
       <x:c r="O583" s="34"/>
       <x:c r="P583" s="32"/>
+      <x:c r="Q583"/>
     </x:row>
     <x:row r="584">
       <x:c r="A584" s="34"/>
@@ -11480,6 +12068,7 @@
       <x:c r="N584" s="46"/>
       <x:c r="O584" s="34"/>
       <x:c r="P584" s="32"/>
+      <x:c r="Q584"/>
     </x:row>
     <x:row r="585">
       <x:c r="A585" s="34"/>
@@ -11498,6 +12087,7 @@
       <x:c r="N585" s="46"/>
       <x:c r="O585" s="34"/>
       <x:c r="P585" s="32"/>
+      <x:c r="Q585"/>
     </x:row>
     <x:row r="586">
       <x:c r="A586" s="34"/>
@@ -11516,6 +12106,7 @@
       <x:c r="N586" s="46"/>
       <x:c r="O586" s="34"/>
       <x:c r="P586" s="32"/>
+      <x:c r="Q586"/>
     </x:row>
     <x:row r="587">
       <x:c r="A587" s="34"/>
@@ -11534,6 +12125,7 @@
       <x:c r="N587" s="46"/>
       <x:c r="O587" s="34"/>
       <x:c r="P587" s="32"/>
+      <x:c r="Q587"/>
     </x:row>
     <x:row r="588">
       <x:c r="A588" s="34"/>
@@ -11552,6 +12144,7 @@
       <x:c r="N588" s="46"/>
       <x:c r="O588" s="34"/>
       <x:c r="P588" s="32"/>
+      <x:c r="Q588"/>
     </x:row>
     <x:row r="589">
       <x:c r="A589" s="34"/>
@@ -11570,6 +12163,7 @@
       <x:c r="N589" s="46"/>
       <x:c r="O589" s="34"/>
       <x:c r="P589" s="32"/>
+      <x:c r="Q589"/>
     </x:row>
     <x:row r="590">
       <x:c r="A590" s="34"/>
@@ -11588,6 +12182,7 @@
       <x:c r="N590" s="46"/>
       <x:c r="O590" s="34"/>
       <x:c r="P590" s="32"/>
+      <x:c r="Q590"/>
     </x:row>
     <x:row r="591">
       <x:c r="A591" s="34"/>
@@ -11606,6 +12201,7 @@
       <x:c r="N591" s="46"/>
       <x:c r="O591" s="34"/>
       <x:c r="P591" s="32"/>
+      <x:c r="Q591"/>
     </x:row>
     <x:row r="592">
       <x:c r="A592" s="34"/>
@@ -11624,6 +12220,7 @@
       <x:c r="N592" s="46"/>
       <x:c r="O592" s="34"/>
       <x:c r="P592" s="32"/>
+      <x:c r="Q592"/>
     </x:row>
     <x:row r="593">
       <x:c r="A593" s="34"/>
@@ -11642,6 +12239,7 @@
       <x:c r="N593" s="46"/>
       <x:c r="O593" s="34"/>
       <x:c r="P593" s="32"/>
+      <x:c r="Q593"/>
     </x:row>
     <x:row r="594">
       <x:c r="A594" s="34"/>
@@ -11660,6 +12258,7 @@
       <x:c r="N594" s="46"/>
       <x:c r="O594" s="34"/>
       <x:c r="P594" s="32"/>
+      <x:c r="Q594"/>
     </x:row>
     <x:row r="595">
       <x:c r="A595" s="34"/>
@@ -11678,6 +12277,7 @@
       <x:c r="N595" s="46"/>
       <x:c r="O595" s="34"/>
       <x:c r="P595" s="32"/>
+      <x:c r="Q595"/>
     </x:row>
     <x:row r="596">
       <x:c r="A596" s="34"/>
@@ -11696,6 +12296,7 @@
       <x:c r="N596" s="46"/>
       <x:c r="O596" s="34"/>
       <x:c r="P596" s="32"/>
+      <x:c r="Q596"/>
     </x:row>
     <x:row r="597">
       <x:c r="A597" s="34"/>
@@ -11714,6 +12315,7 @@
       <x:c r="N597" s="46"/>
       <x:c r="O597" s="34"/>
       <x:c r="P597" s="32"/>
+      <x:c r="Q597"/>
     </x:row>
     <x:row r="598">
       <x:c r="A598" s="34"/>
@@ -11732,6 +12334,7 @@
       <x:c r="N598" s="46"/>
       <x:c r="O598" s="34"/>
       <x:c r="P598" s="32"/>
+      <x:c r="Q598"/>
     </x:row>
     <x:row r="599">
       <x:c r="A599" s="34"/>
@@ -11750,6 +12353,7 @@
       <x:c r="N599" s="46"/>
       <x:c r="O599" s="34"/>
       <x:c r="P599" s="32"/>
+      <x:c r="Q599"/>
     </x:row>
     <x:row r="600">
       <x:c r="A600" s="34"/>
@@ -11768,6 +12372,7 @@
       <x:c r="N600" s="46"/>
       <x:c r="O600" s="34"/>
       <x:c r="P600" s="32"/>
+      <x:c r="Q600"/>
     </x:row>
     <x:row r="601">
       <x:c r="A601" s="34"/>
@@ -11786,6 +12391,7 @@
       <x:c r="N601" s="46"/>
       <x:c r="O601" s="34"/>
       <x:c r="P601" s="32"/>
+      <x:c r="Q601"/>
     </x:row>
     <x:row r="602">
       <x:c r="A602" s="34"/>
@@ -11804,6 +12410,7 @@
       <x:c r="N602" s="46"/>
       <x:c r="O602" s="34"/>
       <x:c r="P602" s="32"/>
+      <x:c r="Q602"/>
     </x:row>
     <x:row r="603">
       <x:c r="A603" s="34"/>
@@ -11822,6 +12429,7 @@
       <x:c r="N603" s="46"/>
       <x:c r="O603" s="34"/>
       <x:c r="P603" s="32"/>
+      <x:c r="Q603"/>
     </x:row>
     <x:row r="604">
       <x:c r="A604" s="34"/>
@@ -11840,6 +12448,7 @@
       <x:c r="N604" s="46"/>
       <x:c r="O604" s="34"/>
       <x:c r="P604" s="32"/>
+      <x:c r="Q604"/>
     </x:row>
     <x:row r="605">
       <x:c r="A605" s="34"/>
@@ -11858,6 +12467,7 @@
       <x:c r="N605" s="46"/>
       <x:c r="O605" s="34"/>
       <x:c r="P605" s="32"/>
+      <x:c r="Q605"/>
     </x:row>
     <x:row r="606">
       <x:c r="A606" s="34"/>
@@ -11876,6 +12486,7 @@
       <x:c r="N606" s="46"/>
       <x:c r="O606" s="34"/>
       <x:c r="P606" s="32"/>
+      <x:c r="Q606"/>
     </x:row>
     <x:row r="607">
       <x:c r="A607" s="34"/>
@@ -11894,6 +12505,7 @@
       <x:c r="N607" s="46"/>
       <x:c r="O607" s="34"/>
       <x:c r="P607" s="32"/>
+      <x:c r="Q607"/>
     </x:row>
     <x:row r="608">
       <x:c r="A608" s="34"/>
@@ -11912,6 +12524,7 @@
       <x:c r="N608" s="46"/>
       <x:c r="O608" s="34"/>
       <x:c r="P608" s="32"/>
+      <x:c r="Q608"/>
     </x:row>
     <x:row r="609">
       <x:c r="A609" s="34"/>
@@ -11930,6 +12543,7 @@
       <x:c r="N609" s="46"/>
       <x:c r="O609" s="34"/>
       <x:c r="P609" s="32"/>
+      <x:c r="Q609"/>
     </x:row>
     <x:row r="610">
       <x:c r="A610" s="34"/>
@@ -11948,6 +12562,7 @@
       <x:c r="N610" s="46"/>
       <x:c r="O610" s="34"/>
       <x:c r="P610" s="32"/>
+      <x:c r="Q610"/>
     </x:row>
     <x:row r="611">
       <x:c r="A611" s="34"/>
@@ -11966,6 +12581,7 @@
       <x:c r="N611" s="46"/>
       <x:c r="O611" s="34"/>
       <x:c r="P611" s="32"/>
+      <x:c r="Q611"/>
     </x:row>
     <x:row r="612">
       <x:c r="A612" s="34"/>
@@ -11984,6 +12600,7 @@
       <x:c r="N612" s="46"/>
       <x:c r="O612" s="34"/>
       <x:c r="P612" s="32"/>
+      <x:c r="Q612"/>
     </x:row>
     <x:row r="613">
       <x:c r="A613" s="34"/>
@@ -12002,6 +12619,7 @@
       <x:c r="N613" s="46"/>
       <x:c r="O613" s="34"/>
       <x:c r="P613" s="32"/>
+      <x:c r="Q613"/>
     </x:row>
     <x:row r="614">
       <x:c r="A614" s="34"/>
@@ -12020,6 +12638,7 @@
       <x:c r="N614" s="46"/>
       <x:c r="O614" s="34"/>
       <x:c r="P614" s="32"/>
+      <x:c r="Q614"/>
     </x:row>
     <x:row r="615">
       <x:c r="A615" s="34"/>
@@ -12038,6 +12657,7 @@
       <x:c r="N615" s="46"/>
       <x:c r="O615" s="34"/>
       <x:c r="P615" s="32"/>
+      <x:c r="Q615"/>
     </x:row>
     <x:row r="616">
       <x:c r="A616" s="34"/>
@@ -12056,6 +12676,7 @@
       <x:c r="N616" s="46"/>
       <x:c r="O616" s="34"/>
       <x:c r="P616" s="32"/>
+      <x:c r="Q616"/>
     </x:row>
     <x:row r="617">
       <x:c r="A617" s="34"/>
@@ -12074,6 +12695,7 @@
       <x:c r="N617" s="46"/>
       <x:c r="O617" s="34"/>
       <x:c r="P617" s="32"/>
+      <x:c r="Q617"/>
     </x:row>
     <x:row r="618">
       <x:c r="A618" s="34"/>
@@ -12092,6 +12714,7 @@
       <x:c r="N618" s="46"/>
       <x:c r="O618" s="34"/>
       <x:c r="P618" s="32"/>
+      <x:c r="Q618"/>
     </x:row>
     <x:row r="619">
       <x:c r="A619" s="34"/>
@@ -12110,6 +12733,7 @@
       <x:c r="N619" s="46"/>
       <x:c r="O619" s="34"/>
       <x:c r="P619" s="32"/>
+      <x:c r="Q619"/>
     </x:row>
     <x:row r="620">
       <x:c r="A620" s="34"/>
@@ -12128,6 +12752,7 @@
       <x:c r="N620" s="46"/>
       <x:c r="O620" s="34"/>
       <x:c r="P620" s="32"/>
+      <x:c r="Q620"/>
     </x:row>
     <x:row r="621">
       <x:c r="A621" s="34"/>
@@ -12146,6 +12771,7 @@
       <x:c r="N621" s="46"/>
       <x:c r="O621" s="34"/>
       <x:c r="P621" s="32"/>
+      <x:c r="Q621"/>
     </x:row>
     <x:row r="622">
       <x:c r="A622" s="34"/>
@@ -12164,6 +12790,7 @@
       <x:c r="N622" s="46"/>
       <x:c r="O622" s="34"/>
       <x:c r="P622" s="32"/>
+      <x:c r="Q622"/>
     </x:row>
     <x:row r="623">
       <x:c r="A623" s="34"/>
@@ -12182,6 +12809,7 @@
       <x:c r="N623" s="46"/>
       <x:c r="O623" s="34"/>
       <x:c r="P623" s="32"/>
+      <x:c r="Q623"/>
     </x:row>
     <x:row r="624">
       <x:c r="A624" s="34"/>
@@ -12200,6 +12828,7 @@
       <x:c r="N624" s="46"/>
       <x:c r="O624" s="34"/>
       <x:c r="P624" s="32"/>
+      <x:c r="Q624"/>
     </x:row>
     <x:row r="625">
       <x:c r="A625" s="34"/>
@@ -12218,6 +12847,7 @@
       <x:c r="N625" s="46"/>
       <x:c r="O625" s="34"/>
       <x:c r="P625" s="32"/>
+      <x:c r="Q625"/>
     </x:row>
     <x:row r="626">
       <x:c r="A626" s="34"/>
@@ -12236,6 +12866,7 @@
       <x:c r="N626" s="46"/>
       <x:c r="O626" s="34"/>
       <x:c r="P626" s="32"/>
+      <x:c r="Q626"/>
     </x:row>
     <x:row r="627">
       <x:c r="A627" s="34"/>
@@ -12254,6 +12885,7 @@
       <x:c r="N627" s="46"/>
       <x:c r="O627" s="34"/>
       <x:c r="P627" s="32"/>
+      <x:c r="Q627"/>
     </x:row>
     <x:row r="628">
       <x:c r="A628" s="34"/>
@@ -12272,6 +12904,7 @@
       <x:c r="N628" s="46"/>
       <x:c r="O628" s="34"/>
       <x:c r="P628" s="32"/>
+      <x:c r="Q628"/>
     </x:row>
     <x:row r="629">
       <x:c r="A629" s="34"/>
@@ -12290,6 +12923,7 @@
       <x:c r="N629" s="46"/>
       <x:c r="O629" s="34"/>
       <x:c r="P629" s="32"/>
+      <x:c r="Q629"/>
     </x:row>
     <x:row r="630">
       <x:c r="A630" s="34"/>
@@ -12308,6 +12942,7 @@
       <x:c r="N630" s="46"/>
       <x:c r="O630" s="34"/>
       <x:c r="P630" s="32"/>
+      <x:c r="Q630"/>
     </x:row>
     <x:row r="631">
       <x:c r="A631" s="34"/>
@@ -12326,6 +12961,7 @@
       <x:c r="N631" s="46"/>
       <x:c r="O631" s="34"/>
       <x:c r="P631" s="32"/>
+      <x:c r="Q631"/>
     </x:row>
     <x:row r="632">
       <x:c r="A632" s="34"/>
@@ -12344,6 +12980,7 @@
       <x:c r="N632" s="46"/>
       <x:c r="O632" s="34"/>
       <x:c r="P632" s="32"/>
+      <x:c r="Q632"/>
     </x:row>
     <x:row r="633">
       <x:c r="A633" s="34"/>
@@ -12362,6 +12999,7 @@
       <x:c r="N633" s="46"/>
       <x:c r="O633" s="34"/>
       <x:c r="P633" s="32"/>
+      <x:c r="Q633"/>
     </x:row>
     <x:row r="634">
       <x:c r="A634" s="34"/>
@@ -12380,6 +13018,7 @@
       <x:c r="N634" s="46"/>
       <x:c r="O634" s="34"/>
       <x:c r="P634" s="32"/>
+      <x:c r="Q634"/>
     </x:row>
     <x:row r="635">
       <x:c r="A635" s="34"/>
@@ -12398,6 +13037,7 @@
       <x:c r="N635" s="46"/>
       <x:c r="O635" s="34"/>
       <x:c r="P635" s="32"/>
+      <x:c r="Q635"/>
     </x:row>
     <x:row r="636">
       <x:c r="A636" s="34"/>
@@ -12416,6 +13056,7 @@
       <x:c r="N636" s="46"/>
       <x:c r="O636" s="34"/>
       <x:c r="P636" s="32"/>
+      <x:c r="Q636"/>
     </x:row>
     <x:row r="637">
       <x:c r="A637" s="34"/>
@@ -12434,6 +13075,7 @@
       <x:c r="N637" s="46"/>
       <x:c r="O637" s="34"/>
       <x:c r="P637" s="32"/>
+      <x:c r="Q637"/>
     </x:row>
     <x:row r="638">
       <x:c r="A638" s="34"/>
@@ -12452,6 +13094,7 @@
       <x:c r="N638" s="46"/>
       <x:c r="O638" s="34"/>
       <x:c r="P638" s="32"/>
+      <x:c r="Q638"/>
     </x:row>
     <x:row r="639">
       <x:c r="A639" s="34"/>
@@ -12470,6 +13113,7 @@
       <x:c r="N639" s="46"/>
       <x:c r="O639" s="34"/>
       <x:c r="P639" s="32"/>
+      <x:c r="Q639"/>
     </x:row>
     <x:row r="640">
       <x:c r="A640" s="34"/>
@@ -12488,6 +13132,7 @@
       <x:c r="N640" s="46"/>
       <x:c r="O640" s="34"/>
       <x:c r="P640" s="32"/>
+      <x:c r="Q640"/>
     </x:row>
     <x:row r="641">
       <x:c r="A641" s="34"/>
@@ -12506,6 +13151,7 @@
       <x:c r="N641" s="46"/>
       <x:c r="O641" s="34"/>
       <x:c r="P641" s="32"/>
+      <x:c r="Q641"/>
     </x:row>
     <x:row r="642">
       <x:c r="A642" s="34"/>
@@ -12524,6 +13170,7 @@
       <x:c r="N642" s="46"/>
       <x:c r="O642" s="34"/>
       <x:c r="P642" s="32"/>
+      <x:c r="Q642"/>
     </x:row>
     <x:row r="643">
       <x:c r="A643" s="34"/>
@@ -12542,6 +13189,7 @@
       <x:c r="N643" s="46"/>
       <x:c r="O643" s="34"/>
       <x:c r="P643" s="32"/>
+      <x:c r="Q643"/>
     </x:row>
     <x:row r="644">
       <x:c r="A644" s="34"/>
@@ -12560,6 +13208,7 @@
       <x:c r="N644" s="46"/>
       <x:c r="O644" s="34"/>
       <x:c r="P644" s="32"/>
+      <x:c r="Q644"/>
     </x:row>
     <x:row r="645">
       <x:c r="A645" s="34"/>
@@ -12578,6 +13227,7 @@
       <x:c r="N645" s="46"/>
       <x:c r="O645" s="34"/>
       <x:c r="P645" s="32"/>
+      <x:c r="Q645"/>
     </x:row>
     <x:row r="646">
       <x:c r="A646" s="34"/>
@@ -12596,6 +13246,7 @@
       <x:c r="N646" s="46"/>
       <x:c r="O646" s="34"/>
       <x:c r="P646" s="32"/>
+      <x:c r="Q646"/>
     </x:row>
     <x:row r="647">
       <x:c r="A647" s="34"/>
@@ -12614,6 +13265,7 @@
       <x:c r="N647" s="46"/>
       <x:c r="O647" s="34"/>
       <x:c r="P647" s="32"/>
+      <x:c r="Q647"/>
     </x:row>
     <x:row r="648">
       <x:c r="A648" s="34"/>
@@ -12632,6 +13284,7 @@
       <x:c r="N648" s="46"/>
       <x:c r="O648" s="34"/>
       <x:c r="P648" s="32"/>
+      <x:c r="Q648"/>
     </x:row>
     <x:row r="649">
       <x:c r="A649" s="34"/>
@@ -12650,6 +13303,7 @@
       <x:c r="N649" s="46"/>
       <x:c r="O649" s="34"/>
       <x:c r="P649" s="32"/>
+      <x:c r="Q649"/>
     </x:row>
     <x:row r="650">
       <x:c r="A650" s="34"/>
@@ -12668,6 +13322,7 @@
       <x:c r="N650" s="46"/>
       <x:c r="O650" s="34"/>
       <x:c r="P650" s="32"/>
+      <x:c r="Q650"/>
     </x:row>
     <x:row r="651">
       <x:c r="A651" s="34"/>
@@ -12686,6 +13341,7 @@
       <x:c r="N651" s="46"/>
       <x:c r="O651" s="34"/>
       <x:c r="P651" s="32"/>
+      <x:c r="Q651"/>
     </x:row>
     <x:row r="652">
       <x:c r="A652" s="34"/>
@@ -12704,6 +13360,7 @@
       <x:c r="N652" s="46"/>
       <x:c r="O652" s="34"/>
       <x:c r="P652" s="32"/>
+      <x:c r="Q652"/>
     </x:row>
     <x:row r="653">
       <x:c r="A653" s="34"/>
@@ -12722,6 +13379,7 @@
       <x:c r="N653" s="46"/>
       <x:c r="O653" s="34"/>
       <x:c r="P653" s="32"/>
+      <x:c r="Q653"/>
     </x:row>
     <x:row r="654">
       <x:c r="A654" s="34"/>
@@ -12740,6 +13398,7 @@
       <x:c r="N654" s="46"/>
       <x:c r="O654" s="34"/>
       <x:c r="P654" s="32"/>
+      <x:c r="Q654"/>
     </x:row>
     <x:row r="655">
       <x:c r="A655" s="34"/>
@@ -12758,6 +13417,7 @@
       <x:c r="N655" s="46"/>
       <x:c r="O655" s="34"/>
       <x:c r="P655" s="32"/>
+      <x:c r="Q655"/>
     </x:row>
     <x:row r="656">
       <x:c r="A656" s="34"/>
@@ -12776,6 +13436,7 @@
       <x:c r="N656" s="46"/>
       <x:c r="O656" s="34"/>
       <x:c r="P656" s="32"/>
+      <x:c r="Q656"/>
     </x:row>
     <x:row r="657">
       <x:c r="A657" s="34"/>
@@ -12794,6 +13455,7 @@
       <x:c r="N657" s="46"/>
       <x:c r="O657" s="34"/>
       <x:c r="P657" s="32"/>
+      <x:c r="Q657"/>
     </x:row>
     <x:row r="658">
       <x:c r="A658" s="34"/>
@@ -12812,6 +13474,7 @@
       <x:c r="N658" s="46"/>
       <x:c r="O658" s="34"/>
       <x:c r="P658" s="32"/>
+      <x:c r="Q658"/>
     </x:row>
     <x:row r="659">
       <x:c r="A659" s="34"/>
@@ -12830,6 +13493,7 @@
       <x:c r="N659" s="46"/>
       <x:c r="O659" s="34"/>
       <x:c r="P659" s="32"/>
+      <x:c r="Q659"/>
     </x:row>
     <x:row r="660">
       <x:c r="A660" s="34"/>
@@ -12848,6 +13512,7 @@
       <x:c r="N660" s="46"/>
       <x:c r="O660" s="34"/>
       <x:c r="P660" s="32"/>
+      <x:c r="Q660"/>
     </x:row>
     <x:row r="661">
       <x:c r="A661" s="34"/>
@@ -12866,6 +13531,7 @@
       <x:c r="N661" s="46"/>
       <x:c r="O661" s="34"/>
       <x:c r="P661" s="32"/>
+      <x:c r="Q661"/>
     </x:row>
     <x:row r="662">
       <x:c r="A662" s="34"/>
@@ -12884,6 +13550,7 @@
       <x:c r="N662" s="46"/>
       <x:c r="O662" s="34"/>
       <x:c r="P662" s="32"/>
+      <x:c r="Q662"/>
     </x:row>
     <x:row r="663">
       <x:c r="A663" s="34"/>
@@ -12902,6 +13569,7 @@
       <x:c r="N663" s="46"/>
       <x:c r="O663" s="34"/>
       <x:c r="P663" s="32"/>
+      <x:c r="Q663"/>
     </x:row>
     <x:row r="664">
       <x:c r="A664" s="34"/>
@@ -12920,6 +13588,7 @@
       <x:c r="N664" s="46"/>
       <x:c r="O664" s="34"/>
       <x:c r="P664" s="32"/>
+      <x:c r="Q664"/>
     </x:row>
     <x:row r="665">
       <x:c r="A665" s="34"/>
@@ -12938,6 +13607,7 @@
       <x:c r="N665" s="46"/>
       <x:c r="O665" s="34"/>
       <x:c r="P665" s="32"/>
+      <x:c r="Q665"/>
     </x:row>
     <x:row r="666">
       <x:c r="A666" s="34"/>
@@ -12956,6 +13626,7 @@
       <x:c r="N666" s="46"/>
       <x:c r="O666" s="34"/>
       <x:c r="P666" s="32"/>
+      <x:c r="Q666"/>
     </x:row>
     <x:row r="667">
       <x:c r="A667" s="34"/>
@@ -12974,6 +13645,7 @@
       <x:c r="N667" s="46"/>
       <x:c r="O667" s="34"/>
       <x:c r="P667" s="32"/>
+      <x:c r="Q667"/>
     </x:row>
     <x:row r="668">
       <x:c r="A668" s="34"/>
@@ -12992,6 +13664,7 @@
       <x:c r="N668" s="46"/>
       <x:c r="O668" s="34"/>
       <x:c r="P668" s="32"/>
+      <x:c r="Q668"/>
     </x:row>
     <x:row r="669">
       <x:c r="A669" s="34"/>
@@ -13010,6 +13683,7 @@
       <x:c r="N669" s="46"/>
       <x:c r="O669" s="34"/>
       <x:c r="P669" s="32"/>
+      <x:c r="Q669"/>
     </x:row>
     <x:row r="670">
       <x:c r="A670" s="34"/>
@@ -13028,6 +13702,7 @@
       <x:c r="N670" s="46"/>
       <x:c r="O670" s="34"/>
       <x:c r="P670" s="32"/>
+      <x:c r="Q670"/>
     </x:row>
     <x:row r="671">
       <x:c r="A671" s="34"/>
@@ -13046,6 +13721,7 @@
       <x:c r="N671" s="46"/>
       <x:c r="O671" s="34"/>
       <x:c r="P671" s="32"/>
+      <x:c r="Q671"/>
     </x:row>
     <x:row r="672">
       <x:c r="A672" s="34"/>
@@ -13064,6 +13740,7 @@
       <x:c r="N672" s="46"/>
       <x:c r="O672" s="34"/>
       <x:c r="P672" s="32"/>
+      <x:c r="Q672"/>
     </x:row>
     <x:row r="673">
       <x:c r="A673" s="34"/>
@@ -13082,6 +13759,7 @@
       <x:c r="N673" s="46"/>
       <x:c r="O673" s="34"/>
       <x:c r="P673" s="32"/>
+      <x:c r="Q673"/>
     </x:row>
     <x:row r="674">
       <x:c r="A674" s="34"/>
@@ -13100,6 +13778,7 @@
       <x:c r="N674" s="46"/>
       <x:c r="O674" s="34"/>
       <x:c r="P674" s="32"/>
+      <x:c r="Q674"/>
     </x:row>
     <x:row r="675">
       <x:c r="A675" s="34"/>
@@ -13118,6 +13797,7 @@
       <x:c r="N675" s="46"/>
       <x:c r="O675" s="34"/>
       <x:c r="P675" s="32"/>
+      <x:c r="Q675"/>
     </x:row>
     <x:row r="676">
       <x:c r="A676" s="34"/>
@@ -13136,6 +13816,7 @@
       <x:c r="N676" s="46"/>
       <x:c r="O676" s="34"/>
       <x:c r="P676" s="32"/>
+      <x:c r="Q676"/>
     </x:row>
     <x:row r="677">
       <x:c r="A677" s="34"/>
@@ -13154,6 +13835,7 @@
       <x:c r="N677" s="46"/>
       <x:c r="O677" s="34"/>
       <x:c r="P677" s="32"/>
+      <x:c r="Q677"/>
     </x:row>
     <x:row r="678">
       <x:c r="A678" s="34"/>
@@ -13172,6 +13854,7 @@
       <x:c r="N678" s="46"/>
       <x:c r="O678" s="34"/>
       <x:c r="P678" s="32"/>
+      <x:c r="Q678"/>
     </x:row>
     <x:row r="679">
       <x:c r="A679" s="34"/>
@@ -13190,6 +13873,7 @@
       <x:c r="N679" s="46"/>
       <x:c r="O679" s="34"/>
       <x:c r="P679" s="32"/>
+      <x:c r="Q679"/>
     </x:row>
     <x:row r="680">
       <x:c r="A680" s="34"/>
@@ -13208,6 +13892,7 @@
       <x:c r="N680" s="46"/>
       <x:c r="O680" s="34"/>
       <x:c r="P680" s="32"/>
+      <x:c r="Q680"/>
     </x:row>
     <x:row r="681">
       <x:c r="A681" s="34"/>
@@ -13226,6 +13911,7 @@
       <x:c r="N681" s="46"/>
       <x:c r="O681" s="34"/>
       <x:c r="P681" s="32"/>
+      <x:c r="Q681"/>
     </x:row>
     <x:row r="682">
       <x:c r="A682" s="34"/>
@@ -13244,6 +13930,7 @@
       <x:c r="N682" s="46"/>
       <x:c r="O682" s="34"/>
       <x:c r="P682" s="32"/>
+      <x:c r="Q682"/>
     </x:row>
     <x:row r="683">
       <x:c r="A683" s="34"/>
@@ -13262,6 +13949,7 @@
       <x:c r="N683" s="46"/>
       <x:c r="O683" s="34"/>
       <x:c r="P683" s="32"/>
+      <x:c r="Q683"/>
     </x:row>
     <x:row r="684">
       <x:c r="A684" s="34"/>
@@ -13280,6 +13968,7 @@
       <x:c r="N684" s="46"/>
       <x:c r="O684" s="34"/>
       <x:c r="P684" s="32"/>
+      <x:c r="Q684"/>
     </x:row>
     <x:row r="685">
       <x:c r="A685" s="34"/>
@@ -13298,6 +13987,7 @@
       <x:c r="N685" s="46"/>
       <x:c r="O685" s="34"/>
       <x:c r="P685" s="32"/>
+      <x:c r="Q685"/>
     </x:row>
     <x:row r="686">
       <x:c r="A686" s="34"/>
@@ -13316,6 +14006,7 @@
       <x:c r="N686" s="46"/>
       <x:c r="O686" s="34"/>
       <x:c r="P686" s="32"/>
+      <x:c r="Q686"/>
     </x:row>
     <x:row r="687">
       <x:c r="A687" s="34"/>
@@ -13334,6 +14025,7 @@
       <x:c r="N687" s="46"/>
       <x:c r="O687" s="34"/>
       <x:c r="P687" s="32"/>
+      <x:c r="Q687"/>
     </x:row>
     <x:row r="688">
       <x:c r="A688" s="34"/>
@@ -13352,6 +14044,7 @@
       <x:c r="N688" s="46"/>
       <x:c r="O688" s="34"/>
       <x:c r="P688" s="32"/>
+      <x:c r="Q688"/>
     </x:row>
     <x:row r="689">
       <x:c r="A689" s="34"/>
@@ -13370,6 +14063,7 @@
       <x:c r="N689" s="46"/>
       <x:c r="O689" s="34"/>
       <x:c r="P689" s="32"/>
+      <x:c r="Q689"/>
     </x:row>
     <x:row r="690">
       <x:c r="A690" s="34"/>
@@ -13388,6 +14082,7 @@
       <x:c r="N690" s="46"/>
       <x:c r="O690" s="34"/>
       <x:c r="P690" s="32"/>
+      <x:c r="Q690"/>
     </x:row>
     <x:row r="691">
       <x:c r="A691" s="34"/>
@@ -13406,6 +14101,7 @@
       <x:c r="N691" s="46"/>
       <x:c r="O691" s="34"/>
       <x:c r="P691" s="32"/>
+      <x:c r="Q691"/>
     </x:row>
     <x:row r="692">
       <x:c r="A692" s="34"/>
@@ -13424,6 +14120,7 @@
       <x:c r="N692" s="46"/>
       <x:c r="O692" s="34"/>
       <x:c r="P692" s="32"/>
+      <x:c r="Q692"/>
     </x:row>
     <x:row r="693">
       <x:c r="A693" s="34"/>
@@ -13442,6 +14139,7 @@
       <x:c r="N693" s="46"/>
       <x:c r="O693" s="34"/>
       <x:c r="P693" s="32"/>
+      <x:c r="Q693"/>
     </x:row>
     <x:row r="694">
       <x:c r="A694" s="34"/>
@@ -13460,6 +14158,7 @@
       <x:c r="N694" s="46"/>
       <x:c r="O694" s="34"/>
       <x:c r="P694" s="32"/>
+      <x:c r="Q694"/>
     </x:row>
     <x:row r="695">
       <x:c r="A695" s="34"/>
@@ -13478,6 +14177,7 @@
       <x:c r="N695" s="46"/>
       <x:c r="O695" s="34"/>
       <x:c r="P695" s="32"/>
+      <x:c r="Q695"/>
     </x:row>
     <x:row r="696">
       <x:c r="A696" s="34"/>
@@ -13496,6 +14196,7 @@
       <x:c r="N696" s="46"/>
       <x:c r="O696" s="34"/>
       <x:c r="P696" s="32"/>
+      <x:c r="Q696"/>
     </x:row>
     <x:row r="697">
       <x:c r="A697" s="34"/>
@@ -13514,6 +14215,7 @@
       <x:c r="N697" s="46"/>
       <x:c r="O697" s="34"/>
       <x:c r="P697" s="32"/>
+      <x:c r="Q697"/>
     </x:row>
     <x:row r="698">
       <x:c r="A698" s="34"/>
@@ -13532,6 +14234,7 @@
       <x:c r="N698" s="46"/>
       <x:c r="O698" s="34"/>
       <x:c r="P698" s="32"/>
+      <x:c r="Q698"/>
     </x:row>
     <x:row r="699">
       <x:c r="A699" s="34"/>
@@ -13550,6 +14253,7 @@
       <x:c r="N699" s="46"/>
       <x:c r="O699" s="34"/>
       <x:c r="P699" s="32"/>
+      <x:c r="Q699"/>
     </x:row>
     <x:row r="700">
       <x:c r="A700" s="34"/>
@@ -13568,6 +14272,7 @@
       <x:c r="N700" s="46"/>
       <x:c r="O700" s="34"/>
       <x:c r="P700" s="32"/>
+      <x:c r="Q700"/>
     </x:row>
     <x:row r="701">
       <x:c r="A701" s="34"/>
@@ -13586,6 +14291,7 @@
       <x:c r="N701" s="46"/>
       <x:c r="O701" s="34"/>
       <x:c r="P701" s="32"/>
+      <x:c r="Q701"/>
     </x:row>
     <x:row r="702">
       <x:c r="A702" s="34"/>
@@ -13604,6 +14310,7 @@
       <x:c r="N702" s="46"/>
       <x:c r="O702" s="34"/>
       <x:c r="P702" s="32"/>
+      <x:c r="Q702"/>
     </x:row>
     <x:row r="703">
       <x:c r="A703" s="34"/>
@@ -13622,6 +14329,7 @@
       <x:c r="N703" s="46"/>
       <x:c r="O703" s="34"/>
       <x:c r="P703" s="32"/>
+      <x:c r="Q703"/>
     </x:row>
     <x:row r="704">
       <x:c r="A704" s="34"/>
@@ -13640,6 +14348,7 @@
       <x:c r="N704" s="46"/>
       <x:c r="O704" s="34"/>
       <x:c r="P704" s="32"/>
+      <x:c r="Q704"/>
     </x:row>
     <x:row r="705">
       <x:c r="A705" s="34"/>
@@ -13658,6 +14367,7 @@
       <x:c r="N705" s="46"/>
       <x:c r="O705" s="34"/>
       <x:c r="P705" s="32"/>
+      <x:c r="Q705"/>
     </x:row>
     <x:row r="706">
       <x:c r="A706" s="34"/>
@@ -13676,6 +14386,7 @@
       <x:c r="N706" s="46"/>
       <x:c r="O706" s="34"/>
       <x:c r="P706" s="32"/>
+      <x:c r="Q706"/>
     </x:row>
     <x:row r="707">
       <x:c r="A707" s="34"/>
@@ -13694,6 +14405,7 @@
       <x:c r="N707" s="46"/>
       <x:c r="O707" s="34"/>
       <x:c r="P707" s="32"/>
+      <x:c r="Q707"/>
     </x:row>
     <x:row r="708">
       <x:c r="A708" s="34"/>
@@ -13712,6 +14424,7 @@
       <x:c r="N708" s="46"/>
       <x:c r="O708" s="34"/>
       <x:c r="P708" s="32"/>
+      <x:c r="Q708"/>
     </x:row>
     <x:row r="709">
       <x:c r="A709" s="34"/>
@@ -13730,6 +14443,7 @@
       <x:c r="N709" s="46"/>
       <x:c r="O709" s="34"/>
       <x:c r="P709" s="32"/>
+      <x:c r="Q709"/>
     </x:row>
     <x:row r="710">
       <x:c r="A710" s="34"/>
@@ -13748,6 +14462,7 @@
       <x:c r="N710" s="46"/>
       <x:c r="O710" s="34"/>
       <x:c r="P710" s="32"/>
+      <x:c r="Q710"/>
     </x:row>
     <x:row r="711">
       <x:c r="A711" s="34"/>
@@ -13766,6 +14481,7 @@
       <x:c r="N711" s="46"/>
       <x:c r="O711" s="34"/>
       <x:c r="P711" s="32"/>
+      <x:c r="Q711"/>
     </x:row>
     <x:row r="712">
       <x:c r="A712" s="34"/>
@@ -13784,6 +14500,7 @@
       <x:c r="N712" s="46"/>
       <x:c r="O712" s="34"/>
       <x:c r="P712" s="32"/>
+      <x:c r="Q712"/>
     </x:row>
     <x:row r="713">
       <x:c r="A713" s="34"/>
@@ -13802,6 +14519,7 @@
       <x:c r="N713" s="46"/>
       <x:c r="O713" s="34"/>
       <x:c r="P713" s="32"/>
+      <x:c r="Q713"/>
     </x:row>
     <x:row r="714">
       <x:c r="A714" s="34"/>
@@ -13820,6 +14538,7 @@
       <x:c r="N714" s="46"/>
       <x:c r="O714" s="34"/>
       <x:c r="P714" s="32"/>
+      <x:c r="Q714"/>
     </x:row>
     <x:row r="715">
       <x:c r="A715" s="34"/>
@@ -13838,6 +14557,7 @@
       <x:c r="N715" s="46"/>
       <x:c r="O715" s="34"/>
       <x:c r="P715" s="32"/>
+      <x:c r="Q715"/>
     </x:row>
     <x:row r="716">
       <x:c r="A716" s="34"/>
@@ -13856,6 +14576,7 @@
       <x:c r="N716" s="46"/>
       <x:c r="O716" s="34"/>
       <x:c r="P716" s="32"/>
+      <x:c r="Q716"/>
     </x:row>
     <x:row r="717">
       <x:c r="A717" s="34"/>
@@ -13874,6 +14595,7 @@
       <x:c r="N717" s="46"/>
       <x:c r="O717" s="34"/>
       <x:c r="P717" s="32"/>
+      <x:c r="Q717"/>
     </x:row>
     <x:row r="718">
       <x:c r="A718" s="34"/>
@@ -13892,6 +14614,7 @@
       <x:c r="N718" s="46"/>
       <x:c r="O718" s="34"/>
       <x:c r="P718" s="32"/>
+      <x:c r="Q718"/>
     </x:row>
     <x:row r="719">
       <x:c r="A719" s="34"/>
@@ -13910,6 +14633,7 @@
       <x:c r="N719" s="46"/>
       <x:c r="O719" s="34"/>
       <x:c r="P719" s="32"/>
+      <x:c r="Q719"/>
     </x:row>
     <x:row r="720">
       <x:c r="A720" s="34"/>
@@ -13928,6 +14652,7 @@
       <x:c r="N720" s="46"/>
       <x:c r="O720" s="34"/>
       <x:c r="P720" s="32"/>
+      <x:c r="Q720"/>
     </x:row>
     <x:row r="721">
       <x:c r="A721" s="34"/>
@@ -13946,6 +14671,7 @@
       <x:c r="N721" s="46"/>
       <x:c r="O721" s="34"/>
       <x:c r="P721" s="32"/>
+      <x:c r="Q721"/>
     </x:row>
     <x:row r="722">
       <x:c r="A722" s="34"/>
@@ -13964,6 +14690,7 @@
       <x:c r="N722" s="46"/>
       <x:c r="O722" s="34"/>
       <x:c r="P722" s="32"/>
+      <x:c r="Q722"/>
     </x:row>
     <x:row r="723">
       <x:c r="A723" s="34"/>
@@ -13982,6 +14709,7 @@
       <x:c r="N723" s="46"/>
       <x:c r="O723" s="34"/>
       <x:c r="P723" s="32"/>
+      <x:c r="Q723"/>
     </x:row>
     <x:row r="724">
       <x:c r="A724" s="34"/>
@@ -14000,6 +14728,7 @@
       <x:c r="N724" s="46"/>
       <x:c r="O724" s="34"/>
       <x:c r="P724" s="32"/>
+      <x:c r="Q724"/>
     </x:row>
     <x:row r="725">
       <x:c r="A725" s="34"/>
@@ -14018,6 +14747,7 @@
       <x:c r="N725" s="46"/>
       <x:c r="O725" s="34"/>
       <x:c r="P725" s="32"/>
+      <x:c r="Q725"/>
     </x:row>
     <x:row r="726">
       <x:c r="A726" s="34"/>
@@ -14036,6 +14766,7 @@
       <x:c r="N726" s="46"/>
       <x:c r="O726" s="34"/>
       <x:c r="P726" s="32"/>
+      <x:c r="Q726"/>
     </x:row>
     <x:row r="727">
       <x:c r="A727" s="34"/>
@@ -14054,6 +14785,7 @@
       <x:c r="N727" s="46"/>
       <x:c r="O727" s="34"/>
       <x:c r="P727" s="32"/>
+      <x:c r="Q727"/>
     </x:row>
     <x:row r="728">
       <x:c r="A728" s="34"/>
@@ -14072,6 +14804,7 @@
       <x:c r="N728" s="46"/>
       <x:c r="O728" s="34"/>
       <x:c r="P728" s="32"/>
+      <x:c r="Q728"/>
     </x:row>
     <x:row r="729">
       <x:c r="A729" s="34"/>
@@ -14090,6 +14823,7 @@
       <x:c r="N729" s="46"/>
       <x:c r="O729" s="34"/>
       <x:c r="P729" s="32"/>
+      <x:c r="Q729"/>
     </x:row>
     <x:row r="730">
       <x:c r="A730" s="34"/>
@@ -14108,6 +14842,7 @@
       <x:c r="N730" s="46"/>
       <x:c r="O730" s="34"/>
       <x:c r="P730" s="32"/>
+      <x:c r="Q730"/>
     </x:row>
     <x:row r="731">
       <x:c r="A731" s="34"/>
@@ -14126,6 +14861,7 @@
       <x:c r="N731" s="46"/>
       <x:c r="O731" s="34"/>
       <x:c r="P731" s="32"/>
+      <x:c r="Q731"/>
     </x:row>
     <x:row r="732">
       <x:c r="A732" s="34"/>
@@ -14144,6 +14880,7 @@
       <x:c r="N732" s="46"/>
       <x:c r="O732" s="34"/>
       <x:c r="P732" s="32"/>
+      <x:c r="Q732"/>
     </x:row>
     <x:row r="733">
       <x:c r="A733" s="34"/>
@@ -14162,6 +14899,7 @@
       <x:c r="N733" s="46"/>
       <x:c r="O733" s="34"/>
       <x:c r="P733" s="32"/>
+      <x:c r="Q733"/>
     </x:row>
     <x:row r="734">
       <x:c r="A734" s="34"/>
@@ -14180,6 +14918,7 @@
       <x:c r="N734" s="46"/>
       <x:c r="O734" s="34"/>
       <x:c r="P734" s="32"/>
+      <x:c r="Q734"/>
     </x:row>
     <x:row r="735">
       <x:c r="A735" s="34"/>
@@ -14198,6 +14937,7 @@
       <x:c r="N735" s="46"/>
       <x:c r="O735" s="34"/>
       <x:c r="P735" s="32"/>
+      <x:c r="Q735"/>
     </x:row>
     <x:row r="736">
       <x:c r="A736" s="34"/>
@@ -14216,6 +14956,7 @@
       <x:c r="N736" s="46"/>
       <x:c r="O736" s="34"/>
       <x:c r="P736" s="32"/>
+      <x:c r="Q736"/>
     </x:row>
     <x:row r="737">
       <x:c r="A737" s="34"/>
@@ -14234,6 +14975,7 @@
       <x:c r="N737" s="46"/>
       <x:c r="O737" s="34"/>
       <x:c r="P737" s="32"/>
+      <x:c r="Q737"/>
     </x:row>
     <x:row r="738">
       <x:c r="A738" s="34"/>
@@ -14252,6 +14994,7 @@
       <x:c r="N738" s="46"/>
       <x:c r="O738" s="34"/>
       <x:c r="P738" s="32"/>
+      <x:c r="Q738"/>
     </x:row>
     <x:row r="739">
       <x:c r="A739" s="34"/>
@@ -14270,6 +15013,7 @@
       <x:c r="N739" s="46"/>
       <x:c r="O739" s="34"/>
       <x:c r="P739" s="32"/>
+      <x:c r="Q739"/>
     </x:row>
     <x:row r="740">
       <x:c r="A740" s="34"/>
@@ -14288,6 +15032,7 @@
       <x:c r="N740" s="46"/>
       <x:c r="O740" s="34"/>
       <x:c r="P740" s="32"/>
+      <x:c r="Q740"/>
     </x:row>
     <x:row r="741">
       <x:c r="A741" s="34"/>
@@ -14306,6 +15051,7 @@
       <x:c r="N741" s="46"/>
       <x:c r="O741" s="34"/>
       <x:c r="P741" s="32"/>
+      <x:c r="Q741"/>
     </x:row>
     <x:row r="742">
       <x:c r="A742" s="34"/>
@@ -14324,6 +15070,7 @@
       <x:c r="N742" s="46"/>
       <x:c r="O742" s="34"/>
       <x:c r="P742" s="32"/>
+      <x:c r="Q742"/>
     </x:row>
     <x:row r="743">
       <x:c r="A743" s="34"/>
@@ -14342,6 +15089,7 @@
       <x:c r="N743" s="46"/>
       <x:c r="O743" s="34"/>
       <x:c r="P743" s="32"/>
+      <x:c r="Q743"/>
     </x:row>
     <x:row r="744">
       <x:c r="A744" s="34"/>
@@ -14360,6 +15108,7 @@
       <x:c r="N744" s="46"/>
       <x:c r="O744" s="34"/>
       <x:c r="P744" s="32"/>
+      <x:c r="Q744"/>
     </x:row>
     <x:row r="745">
       <x:c r="A745" s="34"/>
@@ -14378,6 +15127,7 @@
       <x:c r="N745" s="46"/>
       <x:c r="O745" s="34"/>
       <x:c r="P745" s="32"/>
+      <x:c r="Q745"/>
     </x:row>
     <x:row r="746">
       <x:c r="A746" s="34"/>
@@ -14396,6 +15146,7 @@
       <x:c r="N746" s="46"/>
       <x:c r="O746" s="34"/>
       <x:c r="P746" s="32"/>
+      <x:c r="Q746"/>
     </x:row>
     <x:row r="747">
       <x:c r="A747" s="34"/>
@@ -14414,6 +15165,7 @@
       <x:c r="N747" s="46"/>
       <x:c r="O747" s="34"/>
       <x:c r="P747" s="32"/>
+      <x:c r="Q747"/>
     </x:row>
     <x:row r="748">
       <x:c r="A748" s="34"/>
@@ -14432,6 +15184,7 @@
       <x:c r="N748" s="46"/>
       <x:c r="O748" s="34"/>
       <x:c r="P748" s="32"/>
+      <x:c r="Q748"/>
     </x:row>
     <x:row r="749">
       <x:c r="A749" s="34"/>
@@ -14450,6 +15203,7 @@
       <x:c r="N749" s="46"/>
       <x:c r="O749" s="34"/>
       <x:c r="P749" s="32"/>
+      <x:c r="Q749"/>
     </x:row>
     <x:row r="750">
       <x:c r="A750" s="34"/>
@@ -14468,6 +15222,7 @@
       <x:c r="N750" s="46"/>
       <x:c r="O750" s="34"/>
       <x:c r="P750" s="32"/>
+      <x:c r="Q750"/>
     </x:row>
     <x:row r="751">
       <x:c r="A751" s="34"/>
@@ -14486,6 +15241,7 @@
       <x:c r="N751" s="46"/>
       <x:c r="O751" s="34"/>
       <x:c r="P751" s="32"/>
+      <x:c r="Q751"/>
     </x:row>
     <x:row r="752">
       <x:c r="A752" s="34"/>
@@ -14504,6 +15260,7 @@
       <x:c r="N752" s="46"/>
       <x:c r="O752" s="34"/>
       <x:c r="P752" s="32"/>
+      <x:c r="Q752"/>
     </x:row>
     <x:row r="753">
       <x:c r="A753" s="34"/>
@@ -14522,6 +15279,7 @@
       <x:c r="N753" s="46"/>
       <x:c r="O753" s="34"/>
       <x:c r="P753" s="32"/>
+      <x:c r="Q753"/>
     </x:row>
     <x:row r="754">
       <x:c r="A754" s="34"/>
@@ -14540,6 +15298,7 @@
       <x:c r="N754" s="46"/>
       <x:c r="O754" s="34"/>
       <x:c r="P754" s="32"/>
+      <x:c r="Q754"/>
     </x:row>
     <x:row r="755">
       <x:c r="A755" s="34"/>
@@ -14558,6 +15317,7 @@
       <x:c r="N755" s="46"/>
       <x:c r="O755" s="34"/>
       <x:c r="P755" s="32"/>
+      <x:c r="Q755"/>
     </x:row>
     <x:row r="756">
       <x:c r="A756" s="34"/>
@@ -14576,6 +15336,7 @@
       <x:c r="N756" s="46"/>
       <x:c r="O756" s="34"/>
       <x:c r="P756" s="32"/>
+      <x:c r="Q756"/>
     </x:row>
     <x:row r="757">
       <x:c r="A757" s="34"/>
@@ -14594,6 +15355,7 @@
       <x:c r="N757" s="46"/>
       <x:c r="O757" s="34"/>
       <x:c r="P757" s="32"/>
+      <x:c r="Q757"/>
     </x:row>
     <x:row r="758">
       <x:c r="A758" s="34"/>
@@ -14612,6 +15374,7 @@
       <x:c r="N758" s="46"/>
       <x:c r="O758" s="34"/>
       <x:c r="P758" s="32"/>
+      <x:c r="Q758"/>
     </x:row>
     <x:row r="759">
       <x:c r="A759" s="34"/>
@@ -14630,6 +15393,7 @@
       <x:c r="N759" s="46"/>
       <x:c r="O759" s="34"/>
       <x:c r="P759" s="32"/>
+      <x:c r="Q759"/>
     </x:row>
     <x:row r="760">
       <x:c r="A760" s="34"/>
@@ -14648,6 +15412,7 @@
       <x:c r="N760" s="46"/>
       <x:c r="O760" s="34"/>
       <x:c r="P760" s="32"/>
+      <x:c r="Q760"/>
     </x:row>
     <x:row r="761">
       <x:c r="A761" s="34"/>
@@ -14666,6 +15431,7 @@
       <x:c r="N761" s="46"/>
       <x:c r="O761" s="34"/>
       <x:c r="P761" s="32"/>
+      <x:c r="Q761"/>
     </x:row>
     <x:row r="762">
       <x:c r="A762" s="34"/>
@@ -14684,6 +15450,7 @@
       <x:c r="N762" s="46"/>
       <x:c r="O762" s="34"/>
       <x:c r="P762" s="32"/>
+      <x:c r="Q762"/>
     </x:row>
     <x:row r="763">
       <x:c r="A763" s="34"/>
@@ -14702,6 +15469,7 @@
       <x:c r="N763" s="46"/>
       <x:c r="O763" s="34"/>
       <x:c r="P763" s="32"/>
+      <x:c r="Q763"/>
     </x:row>
     <x:row r="764">
       <x:c r="A764" s="34"/>
@@ -14720,6 +15488,7 @@
       <x:c r="N764" s="46"/>
       <x:c r="O764" s="34"/>
       <x:c r="P764" s="32"/>
+      <x:c r="Q764"/>
     </x:row>
     <x:row r="765">
       <x:c r="A765" s="34"/>
@@ -14738,6 +15507,7 @@
       <x:c r="N765" s="46"/>
       <x:c r="O765" s="34"/>
       <x:c r="P765" s="32"/>
+      <x:c r="Q765"/>
     </x:row>
     <x:row r="766">
       <x:c r="A766" s="34"/>
@@ -14756,6 +15526,7 @@
       <x:c r="N766" s="46"/>
       <x:c r="O766" s="34"/>
       <x:c r="P766" s="32"/>
+      <x:c r="Q766"/>
     </x:row>
     <x:row r="767">
       <x:c r="A767" s="34"/>
@@ -14774,6 +15545,7 @@
       <x:c r="N767" s="46"/>
       <x:c r="O767" s="34"/>
       <x:c r="P767" s="32"/>
+      <x:c r="Q767"/>
     </x:row>
     <x:row r="768">
       <x:c r="A768" s="34"/>
@@ -14792,6 +15564,7 @@
       <x:c r="N768" s="46"/>
       <x:c r="O768" s="34"/>
       <x:c r="P768" s="32"/>
+      <x:c r="Q768"/>
     </x:row>
     <x:row r="769">
       <x:c r="A769" s="34"/>
@@ -14810,6 +15583,7 @@
       <x:c r="N769" s="46"/>
       <x:c r="O769" s="34"/>
       <x:c r="P769" s="32"/>
+      <x:c r="Q769"/>
     </x:row>
     <x:row r="770">
       <x:c r="A770" s="34"/>
@@ -14828,6 +15602,7 @@
       <x:c r="N770" s="46"/>
       <x:c r="O770" s="34"/>
       <x:c r="P770" s="32"/>
+      <x:c r="Q770"/>
     </x:row>
     <x:row r="771">
       <x:c r="A771" s="34"/>
@@ -14846,6 +15621,7 @@
       <x:c r="N771" s="46"/>
       <x:c r="O771" s="34"/>
       <x:c r="P771" s="32"/>
+      <x:c r="Q771"/>
     </x:row>
     <x:row r="772">
       <x:c r="A772" s="34"/>
@@ -14864,6 +15640,7 @@
       <x:c r="N772" s="46"/>
       <x:c r="O772" s="34"/>
       <x:c r="P772" s="32"/>
+      <x:c r="Q772"/>
     </x:row>
     <x:row r="773">
       <x:c r="A773" s="34"/>
@@ -14882,6 +15659,7 @@
       <x:c r="N773" s="46"/>
       <x:c r="O773" s="34"/>
       <x:c r="P773" s="32"/>
+      <x:c r="Q773"/>
     </x:row>
     <x:row r="774">
       <x:c r="A774" s="34"/>
@@ -14900,6 +15678,7 @@
       <x:c r="N774" s="46"/>
       <x:c r="O774" s="34"/>
       <x:c r="P774" s="32"/>
+      <x:c r="Q774"/>
     </x:row>
     <x:row r="775">
       <x:c r="A775" s="34"/>
@@ -14918,6 +15697,7 @@
       <x:c r="N775" s="46"/>
       <x:c r="O775" s="34"/>
       <x:c r="P775" s="32"/>
+      <x:c r="Q775"/>
     </x:row>
     <x:row r="776">
       <x:c r="A776" s="34"/>
@@ -14936,6 +15716,7 @@
       <x:c r="N776" s="46"/>
       <x:c r="O776" s="34"/>
       <x:c r="P776" s="32"/>
+      <x:c r="Q776"/>
     </x:row>
     <x:row r="777">
       <x:c r="A777" s="34"/>
@@ -14954,6 +15735,7 @@
       <x:c r="N777" s="46"/>
       <x:c r="O777" s="34"/>
       <x:c r="P777" s="32"/>
+      <x:c r="Q777"/>
     </x:row>
     <x:row r="778">
       <x:c r="A778" s="34"/>
@@ -14972,6 +15754,7 @@
       <x:c r="N778" s="46"/>
       <x:c r="O778" s="34"/>
       <x:c r="P778" s="32"/>
+      <x:c r="Q778"/>
     </x:row>
     <x:row r="779">
       <x:c r="A779" s="34"/>
@@ -14990,6 +15773,7 @@
       <x:c r="N779" s="46"/>
       <x:c r="O779" s="34"/>
       <x:c r="P779" s="32"/>
+      <x:c r="Q779"/>
     </x:row>
     <x:row r="780">
       <x:c r="A780" s="34"/>
@@ -15008,6 +15792,7 @@
       <x:c r="N780" s="46"/>
       <x:c r="O780" s="34"/>
       <x:c r="P780" s="32"/>
+      <x:c r="Q780"/>
     </x:row>
     <x:row r="781">
       <x:c r="A781" s="34"/>
@@ -15026,6 +15811,7 @@
       <x:c r="N781" s="46"/>
       <x:c r="O781" s="34"/>
       <x:c r="P781" s="32"/>
+      <x:c r="Q781"/>
     </x:row>
     <x:row r="782">
       <x:c r="A782" s="34"/>
@@ -15044,6 +15830,7 @@
       <x:c r="N782" s="46"/>
       <x:c r="O782" s="34"/>
       <x:c r="P782" s="32"/>
+      <x:c r="Q782"/>
     </x:row>
     <x:row r="783">
       <x:c r="A783" s="34"/>
@@ -15062,6 +15849,7 @@
       <x:c r="N783" s="46"/>
       <x:c r="O783" s="34"/>
       <x:c r="P783" s="32"/>
+      <x:c r="Q783"/>
     </x:row>
     <x:row r="784">
       <x:c r="A784" s="34"/>
@@ -15080,6 +15868,7 @@
       <x:c r="N784" s="46"/>
       <x:c r="O784" s="34"/>
       <x:c r="P784" s="32"/>
+      <x:c r="Q784"/>
     </x:row>
     <x:row r="785">
       <x:c r="A785" s="34"/>
@@ -15098,6 +15887,7 @@
       <x:c r="N785" s="46"/>
       <x:c r="O785" s="34"/>
       <x:c r="P785" s="32"/>
+      <x:c r="Q785"/>
     </x:row>
     <x:row r="786">
       <x:c r="A786" s="34"/>
@@ -15116,6 +15906,7 @@
       <x:c r="N786" s="46"/>
       <x:c r="O786" s="34"/>
       <x:c r="P786" s="32"/>
+      <x:c r="Q786"/>
     </x:row>
     <x:row r="787">
       <x:c r="A787" s="34"/>
@@ -15134,6 +15925,7 @@
       <x:c r="N787" s="46"/>
       <x:c r="O787" s="34"/>
       <x:c r="P787" s="32"/>
+      <x:c r="Q787"/>
     </x:row>
     <x:row r="788">
       <x:c r="A788" s="34"/>
@@ -15152,6 +15944,7 @@
       <x:c r="N788" s="46"/>
       <x:c r="O788" s="34"/>
       <x:c r="P788" s="32"/>
+      <x:c r="Q788"/>
     </x:row>
     <x:row r="789">
       <x:c r="A789" s="34"/>
@@ -15170,6 +15963,7 @@
       <x:c r="N789" s="46"/>
       <x:c r="O789" s="34"/>
       <x:c r="P789" s="32"/>
+      <x:c r="Q789"/>
     </x:row>
     <x:row r="790">
       <x:c r="A790" s="34"/>
@@ -15188,6 +15982,7 @@
       <x:c r="N790" s="46"/>
       <x:c r="O790" s="34"/>
       <x:c r="P790" s="32"/>
+      <x:c r="Q790"/>
     </x:row>
     <x:row r="791">
       <x:c r="A791" s="34"/>
@@ -15206,6 +16001,7 @@
       <x:c r="N791" s="46"/>
       <x:c r="O791" s="34"/>
       <x:c r="P791" s="32"/>
+      <x:c r="Q791"/>
     </x:row>
     <x:row r="792">
       <x:c r="A792" s="34"/>
@@ -15224,6 +16020,7 @@
       <x:c r="N792" s="46"/>
       <x:c r="O792" s="34"/>
       <x:c r="P792" s="32"/>
+      <x:c r="Q792"/>
     </x:row>
     <x:row r="793">
       <x:c r="A793" s="34"/>
@@ -15242,6 +16039,7 @@
       <x:c r="N793" s="46"/>
       <x:c r="O793" s="34"/>
       <x:c r="P793" s="32"/>
+      <x:c r="Q793"/>
     </x:row>
     <x:row r="794">
       <x:c r="A794" s="34"/>
@@ -15260,6 +16058,7 @@
       <x:c r="N794" s="46"/>
       <x:c r="O794" s="34"/>
       <x:c r="P794" s="32"/>
+      <x:c r="Q794"/>
     </x:row>
     <x:row r="795">
       <x:c r="A795" s="34"/>
@@ -15278,6 +16077,7 @@
       <x:c r="N795" s="46"/>
       <x:c r="O795" s="34"/>
       <x:c r="P795" s="32"/>
+      <x:c r="Q795"/>
     </x:row>
     <x:row r="796">
       <x:c r="A796" s="34"/>
@@ -15296,6 +16096,7 @@
       <x:c r="N796" s="46"/>
       <x:c r="O796" s="34"/>
       <x:c r="P796" s="32"/>
+      <x:c r="Q796"/>
     </x:row>
     <x:row r="797">
       <x:c r="A797" s="34"/>
@@ -15314,6 +16115,7 @@
       <x:c r="N797" s="46"/>
       <x:c r="O797" s="34"/>
       <x:c r="P797" s="32"/>
+      <x:c r="Q797"/>
     </x:row>
     <x:row r="798">
       <x:c r="A798" s="34"/>
@@ -15332,6 +16134,7 @@
       <x:c r="N798" s="46"/>
       <x:c r="O798" s="34"/>
       <x:c r="P798" s="32"/>
+      <x:c r="Q798"/>
     </x:row>
     <x:row r="799">
       <x:c r="A799" s="34"/>
@@ -15350,6 +16153,7 @@
       <x:c r="N799" s="46"/>
       <x:c r="O799" s="34"/>
       <x:c r="P799" s="32"/>
+      <x:c r="Q799"/>
     </x:row>
     <x:row r="800">
       <x:c r="A800" s="34"/>
@@ -15368,6 +16172,7 @@
       <x:c r="N800" s="46"/>
       <x:c r="O800" s="34"/>
       <x:c r="P800" s="32"/>
+      <x:c r="Q800"/>
     </x:row>
     <x:row r="801">
       <x:c r="A801" s="34"/>
@@ -15386,6 +16191,7 @@
       <x:c r="N801" s="46"/>
       <x:c r="O801" s="34"/>
       <x:c r="P801" s="32"/>
+      <x:c r="Q801"/>
     </x:row>
     <x:row r="802">
       <x:c r="A802" s="34"/>
@@ -15404,6 +16210,7 @@
       <x:c r="N802" s="46"/>
       <x:c r="O802" s="34"/>
       <x:c r="P802" s="32"/>
+      <x:c r="Q802"/>
     </x:row>
     <x:row r="803">
       <x:c r="A803" s="34"/>
@@ -15422,6 +16229,7 @@
       <x:c r="N803" s="46"/>
       <x:c r="O803" s="34"/>
       <x:c r="P803" s="32"/>
+      <x:c r="Q803"/>
     </x:row>
     <x:row r="804">
       <x:c r="A804" s="34"/>
@@ -15440,6 +16248,7 @@
       <x:c r="N804" s="46"/>
       <x:c r="O804" s="34"/>
       <x:c r="P804" s="32"/>
+      <x:c r="Q804"/>
     </x:row>
     <x:row r="805">
       <x:c r="A805" s="34"/>
@@ -15458,6 +16267,7 @@
       <x:c r="N805" s="46"/>
       <x:c r="O805" s="34"/>
       <x:c r="P805" s="32"/>
+      <x:c r="Q805"/>
     </x:row>
     <x:row r="806">
       <x:c r="A806" s="34"/>
@@ -15476,6 +16286,7 @@
       <x:c r="N806" s="46"/>
       <x:c r="O806" s="34"/>
       <x:c r="P806" s="32"/>
+      <x:c r="Q806"/>
     </x:row>
     <x:row r="807">
       <x:c r="A807" s="34"/>
@@ -15494,6 +16305,7 @@
       <x:c r="N807" s="46"/>
       <x:c r="O807" s="34"/>
       <x:c r="P807" s="32"/>
+      <x:c r="Q807"/>
     </x:row>
     <x:row r="808">
       <x:c r="A808" s="34"/>
@@ -15512,6 +16324,7 @@
       <x:c r="N808" s="46"/>
       <x:c r="O808" s="34"/>
       <x:c r="P808" s="32"/>
+      <x:c r="Q808"/>
     </x:row>
     <x:row r="809">
       <x:c r="A809" s="34"/>
@@ -15530,6 +16343,7 @@
       <x:c r="N809" s="46"/>
       <x:c r="O809" s="34"/>
       <x:c r="P809" s="32"/>
+      <x:c r="Q809"/>
     </x:row>
     <x:row r="810">
       <x:c r="A810" s="34"/>
@@ -15548,6 +16362,7 @@
       <x:c r="N810" s="46"/>
       <x:c r="O810" s="34"/>
       <x:c r="P810" s="32"/>
+      <x:c r="Q810"/>
     </x:row>
     <x:row r="811">
       <x:c r="A811" s="34"/>
@@ -15566,6 +16381,7 @@
       <x:c r="N811" s="46"/>
       <x:c r="O811" s="34"/>
       <x:c r="P811" s="32"/>
+      <x:c r="Q811"/>
     </x:row>
     <x:row r="812">
       <x:c r="A812" s="34"/>
@@ -15584,6 +16400,7 @@
       <x:c r="N812" s="46"/>
       <x:c r="O812" s="34"/>
       <x:c r="P812" s="32"/>
+      <x:c r="Q812"/>
     </x:row>
     <x:row r="813">
       <x:c r="A813" s="34"/>
@@ -15602,6 +16419,7 @@
       <x:c r="N813" s="46"/>
       <x:c r="O813" s="34"/>
       <x:c r="P813" s="32"/>
+      <x:c r="Q813"/>
     </x:row>
     <x:row r="814">
       <x:c r="A814" s="34"/>
@@ -15620,6 +16438,7 @@
       <x:c r="N814" s="46"/>
       <x:c r="O814" s="34"/>
       <x:c r="P814" s="32"/>
+      <x:c r="Q814"/>
     </x:row>
     <x:row r="815">
       <x:c r="A815" s="34"/>
@@ -15638,6 +16457,7 @@
       <x:c r="N815" s="46"/>
       <x:c r="O815" s="34"/>
       <x:c r="P815" s="32"/>
+      <x:c r="Q815"/>
     </x:row>
     <x:row r="816">
       <x:c r="A816" s="34"/>
@@ -15656,6 +16476,7 @@
       <x:c r="N816" s="46"/>
       <x:c r="O816" s="34"/>
       <x:c r="P816" s="32"/>
+      <x:c r="Q816"/>
     </x:row>
     <x:row r="817">
       <x:c r="A817" s="34"/>
@@ -15674,6 +16495,7 @@
       <x:c r="N817" s="46"/>
       <x:c r="O817" s="34"/>
       <x:c r="P817" s="32"/>
+      <x:c r="Q817"/>
     </x:row>
     <x:row r="818">
       <x:c r="A818" s="34"/>
@@ -15692,6 +16514,7 @@
       <x:c r="N818" s="46"/>
       <x:c r="O818" s="34"/>
       <x:c r="P818" s="32"/>
+      <x:c r="Q818"/>
     </x:row>
     <x:row r="819">
       <x:c r="A819" s="34"/>
@@ -15710,6 +16533,7 @@
       <x:c r="N819" s="46"/>
       <x:c r="O819" s="34"/>
       <x:c r="P819" s="32"/>
+      <x:c r="Q819"/>
     </x:row>
     <x:row r="820">
       <x:c r="A820" s="34"/>
@@ -15728,6 +16552,7 @@
       <x:c r="N820" s="46"/>
       <x:c r="O820" s="34"/>
       <x:c r="P820" s="32"/>
+      <x:c r="Q820"/>
     </x:row>
     <x:row r="821">
       <x:c r="A821" s="34"/>
@@ -15746,6 +16571,7 @@
       <x:c r="N821" s="46"/>
       <x:c r="O821" s="34"/>
       <x:c r="P821" s="32"/>
+      <x:c r="Q821"/>
     </x:row>
     <x:row r="822">
       <x:c r="A822" s="34"/>
@@ -15764,6 +16590,7 @@
       <x:c r="N822" s="46"/>
       <x:c r="O822" s="34"/>
       <x:c r="P822" s="32"/>
+      <x:c r="Q822"/>
     </x:row>
     <x:row r="823">
       <x:c r="A823" s="34"/>
@@ -15782,6 +16609,7 @@
       <x:c r="N823" s="46"/>
       <x:c r="O823" s="34"/>
       <x:c r="P823" s="32"/>
+      <x:c r="Q823"/>
     </x:row>
     <x:row r="824">
       <x:c r="A824" s="34"/>
@@ -15800,6 +16628,7 @@
       <x:c r="N824" s="46"/>
       <x:c r="O824" s="34"/>
       <x:c r="P824" s="32"/>
+      <x:c r="Q824"/>
     </x:row>
     <x:row r="825">
       <x:c r="A825" s="34"/>
@@ -15818,6 +16647,7 @@
       <x:c r="N825" s="46"/>
       <x:c r="O825" s="34"/>
       <x:c r="P825" s="32"/>
+      <x:c r="Q825"/>
     </x:row>
     <x:row r="826">
       <x:c r="A826" s="34"/>
@@ -15836,6 +16666,7 @@
       <x:c r="N826" s="46"/>
       <x:c r="O826" s="34"/>
       <x:c r="P826" s="32"/>
+      <x:c r="Q826"/>
     </x:row>
     <x:row r="827">
       <x:c r="A827" s="34"/>
@@ -15854,6 +16685,7 @@
       <x:c r="N827" s="46"/>
       <x:c r="O827" s="34"/>
       <x:c r="P827" s="32"/>
+      <x:c r="Q827"/>
     </x:row>
     <x:row r="828">
       <x:c r="A828" s="34"/>
@@ -15872,6 +16704,7 @@
       <x:c r="N828" s="46"/>
       <x:c r="O828" s="34"/>
       <x:c r="P828" s="32"/>
+      <x:c r="Q828"/>
     </x:row>
     <x:row r="829">
       <x:c r="A829" s="34"/>
@@ -15890,6 +16723,7 @@
       <x:c r="N829" s="46"/>
       <x:c r="O829" s="34"/>
       <x:c r="P829" s="32"/>
+      <x:c r="Q829"/>
     </x:row>
     <x:row r="830">
       <x:c r="A830" s="34"/>
@@ -15908,6 +16742,7 @@
       <x:c r="N830" s="46"/>
       <x:c r="O830" s="34"/>
       <x:c r="P830" s="32"/>
+      <x:c r="Q830"/>
     </x:row>
     <x:row r="831">
       <x:c r="A831" s="34"/>
@@ -15926,6 +16761,7 @@
       <x:c r="N831" s="46"/>
       <x:c r="O831" s="34"/>
       <x:c r="P831" s="32"/>
+      <x:c r="Q831"/>
     </x:row>
     <x:row r="832">
       <x:c r="A832" s="34"/>
@@ -15944,6 +16780,7 @@
       <x:c r="N832" s="46"/>
       <x:c r="O832" s="34"/>
       <x:c r="P832" s="32"/>
+      <x:c r="Q832"/>
     </x:row>
     <x:row r="833">
       <x:c r="A833" s="34"/>
@@ -15962,6 +16799,7 @@
       <x:c r="N833" s="46"/>
       <x:c r="O833" s="34"/>
       <x:c r="P833" s="32"/>
+      <x:c r="Q833"/>
     </x:row>
     <x:row r="834">
       <x:c r="A834" s="34"/>
@@ -15980,6 +16818,7 @@
       <x:c r="N834" s="46"/>
       <x:c r="O834" s="34"/>
       <x:c r="P834" s="32"/>
+      <x:c r="Q834"/>
     </x:row>
     <x:row r="835">
       <x:c r="A835" s="34"/>
@@ -15998,6 +16837,7 @@
       <x:c r="N835" s="46"/>
       <x:c r="O835" s="34"/>
       <x:c r="P835" s="32"/>
+      <x:c r="Q835"/>
     </x:row>
     <x:row r="836">
       <x:c r="A836" s="34"/>
@@ -16016,6 +16856,7 @@
       <x:c r="N836" s="46"/>
       <x:c r="O836" s="34"/>
       <x:c r="P836" s="32"/>
+      <x:c r="Q836"/>
     </x:row>
     <x:row r="837">
       <x:c r="A837" s="34"/>
@@ -16034,6 +16875,7 @@
       <x:c r="N837" s="46"/>
       <x:c r="O837" s="34"/>
       <x:c r="P837" s="32"/>
+      <x:c r="Q837"/>
     </x:row>
     <x:row r="838">
       <x:c r="A838" s="34"/>
@@ -16052,6 +16894,7 @@
       <x:c r="N838" s="46"/>
       <x:c r="O838" s="34"/>
       <x:c r="P838" s="32"/>
+      <x:c r="Q838"/>
     </x:row>
     <x:row r="839">
       <x:c r="A839" s="34"/>
@@ -16070,6 +16913,7 @@
       <x:c r="N839" s="46"/>
       <x:c r="O839" s="34"/>
       <x:c r="P839" s="32"/>
+      <x:c r="Q839"/>
     </x:row>
     <x:row r="840">
       <x:c r="A840" s="34"/>
@@ -16088,6 +16932,7 @@
       <x:c r="N840" s="46"/>
       <x:c r="O840" s="34"/>
       <x:c r="P840" s="32"/>
+      <x:c r="Q840"/>
     </x:row>
     <x:row r="841">
       <x:c r="A841" s="34"/>
@@ -16106,6 +16951,7 @@
       <x:c r="N841" s="46"/>
       <x:c r="O841" s="34"/>
       <x:c r="P841" s="32"/>
+      <x:c r="Q841"/>
     </x:row>
     <x:row r="842">
       <x:c r="A842" s="34"/>
@@ -16124,6 +16970,7 @@
       <x:c r="N842" s="46"/>
       <x:c r="O842" s="34"/>
       <x:c r="P842" s="32"/>
+      <x:c r="Q842"/>
     </x:row>
     <x:row r="843">
       <x:c r="A843" s="34"/>
@@ -16142,6 +16989,7 @@
       <x:c r="N843" s="46"/>
       <x:c r="O843" s="34"/>
       <x:c r="P843" s="32"/>
+      <x:c r="Q843"/>
     </x:row>
     <x:row r="844">
       <x:c r="A844" s="34"/>
@@ -16160,6 +17008,7 @@
       <x:c r="N844" s="46"/>
       <x:c r="O844" s="34"/>
       <x:c r="P844" s="32"/>
+      <x:c r="Q844"/>
     </x:row>
     <x:row r="845">
       <x:c r="A845" s="34"/>
@@ -16178,6 +17027,7 @@
       <x:c r="N845" s="46"/>
       <x:c r="O845" s="34"/>
       <x:c r="P845" s="32"/>
+      <x:c r="Q845"/>
     </x:row>
     <x:row r="846">
       <x:c r="A846" s="34"/>
@@ -16196,6 +17046,7 @@
       <x:c r="N846" s="46"/>
       <x:c r="O846" s="34"/>
       <x:c r="P846" s="32"/>
+      <x:c r="Q846"/>
     </x:row>
     <x:row r="847">
       <x:c r="A847" s="34"/>
@@ -16214,6 +17065,7 @@
       <x:c r="N847" s="46"/>
       <x:c r="O847" s="34"/>
       <x:c r="P847" s="32"/>
+      <x:c r="Q847"/>
     </x:row>
     <x:row r="848">
       <x:c r="A848" s="34"/>
@@ -16232,6 +17084,7 @@
       <x:c r="N848" s="46"/>
       <x:c r="O848" s="34"/>
       <x:c r="P848" s="32"/>
+      <x:c r="Q848"/>
     </x:row>
     <x:row r="849">
       <x:c r="A849" s="34"/>
@@ -16250,6 +17103,7 @@
       <x:c r="N849" s="46"/>
       <x:c r="O849" s="34"/>
       <x:c r="P849" s="32"/>
+      <x:c r="Q849"/>
     </x:row>
     <x:row r="850">
       <x:c r="A850" s="34"/>
@@ -16268,6 +17122,7 @@
       <x:c r="N850" s="46"/>
       <x:c r="O850" s="34"/>
       <x:c r="P850" s="32"/>
+      <x:c r="Q850"/>
     </x:row>
     <x:row r="851">
       <x:c r="A851" s="34"/>
@@ -16286,6 +17141,7 @@
       <x:c r="N851" s="46"/>
       <x:c r="O851" s="34"/>
       <x:c r="P851" s="32"/>
+      <x:c r="Q851"/>
     </x:row>
     <x:row r="852">
       <x:c r="A852" s="34"/>
@@ -16304,6 +17160,7 @@
       <x:c r="N852" s="46"/>
       <x:c r="O852" s="34"/>
       <x:c r="P852" s="32"/>
+      <x:c r="Q852"/>
     </x:row>
     <x:row r="853">
       <x:c r="A853" s="34"/>
@@ -16322,6 +17179,7 @@
       <x:c r="N853" s="46"/>
       <x:c r="O853" s="34"/>
       <x:c r="P853" s="32"/>
+      <x:c r="Q853"/>
     </x:row>
     <x:row r="854">
       <x:c r="A854" s="34"/>
@@ -16340,6 +17198,7 @@
       <x:c r="N854" s="46"/>
       <x:c r="O854" s="34"/>
       <x:c r="P854" s="32"/>
+      <x:c r="Q854"/>
     </x:row>
     <x:row r="855">
       <x:c r="A855" s="34"/>
@@ -16358,6 +17217,7 @@
       <x:c r="N855" s="46"/>
       <x:c r="O855" s="34"/>
       <x:c r="P855" s="32"/>
+      <x:c r="Q855"/>
     </x:row>
     <x:row r="856">
       <x:c r="A856" s="34"/>
@@ -16376,6 +17236,7 @@
       <x:c r="N856" s="46"/>
       <x:c r="O856" s="34"/>
       <x:c r="P856" s="32"/>
+      <x:c r="Q856"/>
     </x:row>
     <x:row r="857">
       <x:c r="A857" s="34"/>
@@ -16394,6 +17255,7 @@
       <x:c r="N857" s="46"/>
       <x:c r="O857" s="34"/>
       <x:c r="P857" s="32"/>
+      <x:c r="Q857"/>
     </x:row>
     <x:row r="858">
       <x:c r="A858" s="34"/>
@@ -16412,6 +17274,7 @@
       <x:c r="N858" s="46"/>
       <x:c r="O858" s="34"/>
       <x:c r="P858" s="32"/>
+      <x:c r="Q858"/>
     </x:row>
     <x:row r="859">
       <x:c r="A859" s="34"/>
@@ -16430,6 +17293,7 @@
       <x:c r="N859" s="46"/>
       <x:c r="O859" s="34"/>
       <x:c r="P859" s="32"/>
+      <x:c r="Q859"/>
     </x:row>
     <x:row r="860">
       <x:c r="A860" s="34"/>
@@ -16448,6 +17312,7 @@
       <x:c r="N860" s="46"/>
       <x:c r="O860" s="34"/>
       <x:c r="P860" s="32"/>
+      <x:c r="Q860"/>
     </x:row>
     <x:row r="861">
       <x:c r="A861" s="34"/>
@@ -16466,6 +17331,7 @@
       <x:c r="N861" s="46"/>
       <x:c r="O861" s="34"/>
       <x:c r="P861" s="32"/>
+      <x:c r="Q861"/>
     </x:row>
     <x:row r="862">
       <x:c r="A862" s="34"/>
@@ -16484,6 +17350,7 @@
       <x:c r="N862" s="46"/>
       <x:c r="O862" s="34"/>
       <x:c r="P862" s="32"/>
+      <x:c r="Q862"/>
     </x:row>
     <x:row r="863">
       <x:c r="A863" s="34"/>
@@ -16502,6 +17369,7 @@
       <x:c r="N863" s="46"/>
       <x:c r="O863" s="34"/>
       <x:c r="P863" s="32"/>
+      <x:c r="Q863"/>
     </x:row>
     <x:row r="864">
       <x:c r="A864" s="34"/>
@@ -16520,6 +17388,7 @@
       <x:c r="N864" s="46"/>
       <x:c r="O864" s="34"/>
       <x:c r="P864" s="32"/>
+      <x:c r="Q864"/>
     </x:row>
     <x:row r="865">
       <x:c r="A865" s="34"/>
@@ -16538,6 +17407,7 @@
       <x:c r="N865" s="46"/>
       <x:c r="O865" s="34"/>
       <x:c r="P865" s="32"/>
+      <x:c r="Q865"/>
     </x:row>
     <x:row r="866">
       <x:c r="A866" s="34"/>
@@ -16556,6 +17426,7 @@
       <x:c r="N866" s="46"/>
       <x:c r="O866" s="34"/>
       <x:c r="P866" s="32"/>
+      <x:c r="Q866"/>
     </x:row>
     <x:row r="867">
       <x:c r="A867" s="34"/>
@@ -16574,6 +17445,7 @@
       <x:c r="N867" s="46"/>
       <x:c r="O867" s="34"/>
       <x:c r="P867" s="32"/>
+      <x:c r="Q867"/>
     </x:row>
     <x:row r="868">
       <x:c r="A868" s="34"/>
@@ -16592,6 +17464,7 @@
       <x:c r="N868" s="46"/>
       <x:c r="O868" s="34"/>
       <x:c r="P868" s="32"/>
+      <x:c r="Q868"/>
     </x:row>
     <x:row r="869">
       <x:c r="A869" s="34"/>
@@ -16610,6 +17483,7 @@
       <x:c r="N869" s="46"/>
       <x:c r="O869" s="34"/>
       <x:c r="P869" s="32"/>
+      <x:c r="Q869"/>
     </x:row>
     <x:row r="870">
       <x:c r="A870" s="34"/>
@@ -16628,6 +17502,7 @@
       <x:c r="N870" s="46"/>
       <x:c r="O870" s="34"/>
       <x:c r="P870" s="32"/>
+      <x:c r="Q870"/>
     </x:row>
     <x:row r="871">
       <x:c r="A871" s="34"/>
@@ -16646,6 +17521,7 @@
       <x:c r="N871" s="46"/>
       <x:c r="O871" s="34"/>
       <x:c r="P871" s="32"/>
+      <x:c r="Q871"/>
     </x:row>
     <x:row r="872">
       <x:c r="A872" s="34"/>
@@ -16664,6 +17540,7 @@
       <x:c r="N872" s="46"/>
       <x:c r="O872" s="34"/>
       <x:c r="P872" s="32"/>
+      <x:c r="Q872"/>
     </x:row>
     <x:row r="873">
       <x:c r="A873" s="34"/>
@@ -16682,6 +17559,7 @@
       <x:c r="N873" s="46"/>
       <x:c r="O873" s="34"/>
       <x:c r="P873" s="32"/>
+      <x:c r="Q873"/>
     </x:row>
     <x:row r="874">
       <x:c r="A874" s="34"/>
@@ -16700,6 +17578,7 @@
       <x:c r="N874" s="46"/>
       <x:c r="O874" s="34"/>
       <x:c r="P874" s="32"/>
+      <x:c r="Q874"/>
     </x:row>
     <x:row r="875">
       <x:c r="A875" s="34"/>
@@ -16718,6 +17597,7 @@
       <x:c r="N875" s="46"/>
       <x:c r="O875" s="34"/>
       <x:c r="P875" s="32"/>
+      <x:c r="Q875"/>
     </x:row>
     <x:row r="876">
       <x:c r="A876" s="34"/>
@@ -16736,6 +17616,7 @@
       <x:c r="N876" s="46"/>
       <x:c r="O876" s="34"/>
       <x:c r="P876" s="32"/>
+      <x:c r="Q876"/>
     </x:row>
     <x:row r="877">
       <x:c r="A877" s="34"/>
@@ -16754,6 +17635,7 @@
       <x:c r="N877" s="46"/>
       <x:c r="O877" s="34"/>
       <x:c r="P877" s="32"/>
+      <x:c r="Q877"/>
     </x:row>
     <x:row r="878">
       <x:c r="A878" s="34"/>
@@ -16772,6 +17654,7 @@
       <x:c r="N878" s="46"/>
       <x:c r="O878" s="34"/>
       <x:c r="P878" s="32"/>
+      <x:c r="Q878"/>
     </x:row>
     <x:row r="879">
       <x:c r="A879" s="34"/>
@@ -16790,6 +17673,7 @@
       <x:c r="N879" s="46"/>
       <x:c r="O879" s="34"/>
       <x:c r="P879" s="32"/>
+      <x:c r="Q879"/>
     </x:row>
     <x:row r="880">
       <x:c r="A880" s="34"/>
@@ -16808,6 +17692,7 @@
       <x:c r="N880" s="46"/>
       <x:c r="O880" s="34"/>
       <x:c r="P880" s="32"/>
+      <x:c r="Q880"/>
     </x:row>
     <x:row r="881">
       <x:c r="A881" s="34"/>
@@ -16826,6 +17711,7 @@
       <x:c r="N881" s="46"/>
       <x:c r="O881" s="34"/>
       <x:c r="P881" s="32"/>
+      <x:c r="Q881"/>
     </x:row>
     <x:row r="882">
       <x:c r="A882" s="34"/>
@@ -16844,6 +17730,7 @@
       <x:c r="N882" s="46"/>
       <x:c r="O882" s="34"/>
       <x:c r="P882" s="32"/>
+      <x:c r="Q882"/>
     </x:row>
     <x:row r="883">
       <x:c r="A883" s="34"/>
@@ -16862,6 +17749,7 @@
       <x:c r="N883" s="46"/>
       <x:c r="O883" s="34"/>
       <x:c r="P883" s="32"/>
+      <x:c r="Q883"/>
     </x:row>
     <x:row r="884">
       <x:c r="A884" s="34"/>
@@ -16880,6 +17768,7 @@
       <x:c r="N884" s="46"/>
       <x:c r="O884" s="34"/>
       <x:c r="P884" s="32"/>
+      <x:c r="Q884"/>
     </x:row>
     <x:row r="885">
       <x:c r="A885" s="34"/>
@@ -16898,6 +17787,7 @@
       <x:c r="N885" s="46"/>
       <x:c r="O885" s="34"/>
       <x:c r="P885" s="32"/>
+      <x:c r="Q885"/>
     </x:row>
     <x:row r="886">
       <x:c r="A886" s="34"/>
@@ -16916,6 +17806,7 @@
       <x:c r="N886" s="46"/>
       <x:c r="O886" s="34"/>
       <x:c r="P886" s="32"/>
+      <x:c r="Q886"/>
     </x:row>
     <x:row r="887">
       <x:c r="A887" s="34"/>
@@ -16934,6 +17825,7 @@
       <x:c r="N887" s="46"/>
       <x:c r="O887" s="34"/>
       <x:c r="P887" s="32"/>
+      <x:c r="Q887"/>
     </x:row>
     <x:row r="888">
       <x:c r="A888" s="34"/>
@@ -16952,6 +17844,7 @@
       <x:c r="N888" s="46"/>
       <x:c r="O888" s="34"/>
       <x:c r="P888" s="32"/>
+      <x:c r="Q888"/>
     </x:row>
     <x:row r="889">
       <x:c r="A889" s="34"/>
@@ -16970,6 +17863,7 @@
       <x:c r="N889" s="46"/>
       <x:c r="O889" s="34"/>
       <x:c r="P889" s="32"/>
+      <x:c r="Q889"/>
     </x:row>
     <x:row r="890">
       <x:c r="A890" s="34"/>
@@ -16988,6 +17882,7 @@
       <x:c r="N890" s="46"/>
       <x:c r="O890" s="34"/>
       <x:c r="P890" s="32"/>
+      <x:c r="Q890"/>
     </x:row>
     <x:row r="891">
       <x:c r="A891" s="34"/>
@@ -17006,6 +17901,7 @@
       <x:c r="N891" s="46"/>
       <x:c r="O891" s="34"/>
       <x:c r="P891" s="32"/>
+      <x:c r="Q891"/>
     </x:row>
     <x:row r="892">
       <x:c r="A892" s="34"/>
@@ -17024,6 +17920,7 @@
       <x:c r="N892" s="46"/>
       <x:c r="O892" s="34"/>
       <x:c r="P892" s="32"/>
+      <x:c r="Q892"/>
     </x:row>
     <x:row r="893">
       <x:c r="A893" s="34"/>
@@ -17042,6 +17939,7 @@
       <x:c r="N893" s="46"/>
       <x:c r="O893" s="34"/>
       <x:c r="P893" s="32"/>
+      <x:c r="Q893"/>
     </x:row>
     <x:row r="894">
       <x:c r="A894" s="34"/>
@@ -17060,6 +17958,7 @@
       <x:c r="N894" s="46"/>
       <x:c r="O894" s="34"/>
       <x:c r="P894" s="32"/>
+      <x:c r="Q894"/>
     </x:row>
     <x:row r="895">
       <x:c r="A895" s="34"/>
@@ -17078,6 +17977,7 @@
       <x:c r="N895" s="46"/>
       <x:c r="O895" s="34"/>
       <x:c r="P895" s="32"/>
+      <x:c r="Q895"/>
     </x:row>
     <x:row r="896">
       <x:c r="A896" s="34"/>
@@ -17096,6 +17996,7 @@
       <x:c r="N896" s="46"/>
       <x:c r="O896" s="34"/>
       <x:c r="P896" s="32"/>
+      <x:c r="Q896"/>
     </x:row>
     <x:row r="897">
       <x:c r="A897" s="34"/>
@@ -17114,6 +18015,7 @@
       <x:c r="N897" s="46"/>
       <x:c r="O897" s="34"/>
       <x:c r="P897" s="32"/>
+      <x:c r="Q897"/>
     </x:row>
     <x:row r="898">
       <x:c r="A898" s="34"/>
@@ -17132,6 +18034,7 @@
       <x:c r="N898" s="46"/>
       <x:c r="O898" s="34"/>
       <x:c r="P898" s="32"/>
+      <x:c r="Q898"/>
     </x:row>
     <x:row r="899">
       <x:c r="A899" s="34"/>
@@ -17150,6 +18053,7 @@
       <x:c r="N899" s="46"/>
       <x:c r="O899" s="34"/>
       <x:c r="P899" s="32"/>
+      <x:c r="Q899"/>
     </x:row>
     <x:row r="900">
       <x:c r="A900" s="34"/>
@@ -17168,6 +18072,7 @@
       <x:c r="N900" s="46"/>
       <x:c r="O900" s="34"/>
       <x:c r="P900" s="32"/>
+      <x:c r="Q900"/>
     </x:row>
     <x:row r="901">
       <x:c r="A901" s="34"/>
@@ -17186,6 +18091,7 @@
       <x:c r="N901" s="46"/>
       <x:c r="O901" s="34"/>
       <x:c r="P901" s="32"/>
+      <x:c r="Q901"/>
     </x:row>
     <x:row r="902">
       <x:c r="A902" s="34"/>
@@ -17204,6 +18110,7 @@
       <x:c r="N902" s="46"/>
       <x:c r="O902" s="34"/>
       <x:c r="P902" s="32"/>
+      <x:c r="Q902"/>
     </x:row>
     <x:row r="903">
       <x:c r="A903" s="34"/>
@@ -17222,6 +18129,7 @@
       <x:c r="N903" s="46"/>
       <x:c r="O903" s="34"/>
       <x:c r="P903" s="32"/>
+      <x:c r="Q903"/>
     </x:row>
     <x:row r="904">
       <x:c r="A904" s="34"/>
@@ -17240,6 +18148,7 @@
       <x:c r="N904" s="46"/>
       <x:c r="O904" s="34"/>
       <x:c r="P904" s="32"/>
+      <x:c r="Q904"/>
     </x:row>
     <x:row r="905">
       <x:c r="A905" s="34"/>
@@ -17258,6 +18167,7 @@
       <x:c r="N905" s="46"/>
       <x:c r="O905" s="34"/>
       <x:c r="P905" s="32"/>
+      <x:c r="Q905"/>
     </x:row>
     <x:row r="906">
       <x:c r="A906" s="34"/>
@@ -17276,6 +18186,7 @@
       <x:c r="N906" s="46"/>
       <x:c r="O906" s="34"/>
       <x:c r="P906" s="32"/>
+      <x:c r="Q906"/>
     </x:row>
     <x:row r="907">
       <x:c r="A907" s="34"/>
@@ -17294,6 +18205,7 @@
       <x:c r="N907" s="46"/>
       <x:c r="O907" s="34"/>
       <x:c r="P907" s="32"/>
+      <x:c r="Q907"/>
     </x:row>
     <x:row r="908">
       <x:c r="A908" s="34"/>
@@ -17312,6 +18224,7 @@
       <x:c r="N908" s="46"/>
       <x:c r="O908" s="34"/>
       <x:c r="P908" s="32"/>
+      <x:c r="Q908"/>
     </x:row>
     <x:row r="909">
       <x:c r="A909" s="34"/>
@@ -17330,6 +18243,7 @@
       <x:c r="N909" s="46"/>
       <x:c r="O909" s="34"/>
       <x:c r="P909" s="32"/>
+      <x:c r="Q909"/>
     </x:row>
     <x:row r="910">
       <x:c r="A910" s="34"/>
@@ -17348,6 +18262,7 @@
       <x:c r="N910" s="46"/>
       <x:c r="O910" s="34"/>
       <x:c r="P910" s="32"/>
+      <x:c r="Q910"/>
     </x:row>
     <x:row r="911">
       <x:c r="A911" s="34"/>
@@ -17366,6 +18281,7 @@
       <x:c r="N911" s="46"/>
       <x:c r="O911" s="34"/>
       <x:c r="P911" s="32"/>
+      <x:c r="Q911"/>
     </x:row>
     <x:row r="912">
       <x:c r="A912" s="34"/>
@@ -17384,6 +18300,7 @@
       <x:c r="N912" s="46"/>
       <x:c r="O912" s="34"/>
       <x:c r="P912" s="32"/>
+      <x:c r="Q912"/>
     </x:row>
     <x:row r="913">
       <x:c r="A913" s="34"/>
@@ -17402,6 +18319,7 @@
       <x:c r="N913" s="46"/>
       <x:c r="O913" s="34"/>
       <x:c r="P913" s="32"/>
+      <x:c r="Q913"/>
     </x:row>
     <x:row r="914">
       <x:c r="A914" s="34"/>
@@ -17420,6 +18338,7 @@
       <x:c r="N914" s="46"/>
       <x:c r="O914" s="34"/>
       <x:c r="P914" s="32"/>
+      <x:c r="Q914"/>
     </x:row>
     <x:row r="915">
       <x:c r="A915" s="34"/>
@@ -17438,6 +18357,7 @@
       <x:c r="N915" s="46"/>
       <x:c r="O915" s="34"/>
       <x:c r="P915" s="32"/>
+      <x:c r="Q915"/>
     </x:row>
     <x:row r="916">
       <x:c r="A916" s="34"/>
@@ -17456,6 +18376,7 @@
       <x:c r="N916" s="46"/>
       <x:c r="O916" s="34"/>
       <x:c r="P916" s="32"/>
+      <x:c r="Q916"/>
     </x:row>
     <x:row r="917">
       <x:c r="A917" s="34"/>
@@ -17474,6 +18395,7 @@
       <x:c r="N917" s="46"/>
       <x:c r="O917" s="34"/>
       <x:c r="P917" s="32"/>
+      <x:c r="Q917"/>
     </x:row>
     <x:row r="918">
       <x:c r="A918" s="34"/>
@@ -17492,6 +18414,7 @@
       <x:c r="N918" s="46"/>
       <x:c r="O918" s="34"/>
       <x:c r="P918" s="32"/>
+      <x:c r="Q918"/>
     </x:row>
     <x:row r="919">
       <x:c r="A919" s="34"/>
@@ -17510,6 +18433,7 @@
       <x:c r="N919" s="46"/>
       <x:c r="O919" s="34"/>
       <x:c r="P919" s="32"/>
+      <x:c r="Q919"/>
     </x:row>
     <x:row r="920">
       <x:c r="A920" s="34"/>
@@ -17528,6 +18452,7 @@
       <x:c r="N920" s="46"/>
       <x:c r="O920" s="34"/>
       <x:c r="P920" s="32"/>
+      <x:c r="Q920"/>
     </x:row>
     <x:row r="921">
       <x:c r="A921" s="34"/>
@@ -17546,6 +18471,7 @@
       <x:c r="N921" s="46"/>
       <x:c r="O921" s="34"/>
       <x:c r="P921" s="32"/>
+      <x:c r="Q921"/>
     </x:row>
     <x:row r="922">
       <x:c r="A922" s="34"/>
@@ -17564,6 +18490,7 @@
       <x:c r="N922" s="46"/>
       <x:c r="O922" s="34"/>
       <x:c r="P922" s="32"/>
+      <x:c r="Q922"/>
     </x:row>
     <x:row r="923">
       <x:c r="A923" s="34"/>
@@ -17582,6 +18509,7 @@
       <x:c r="N923" s="46"/>
       <x:c r="O923" s="34"/>
       <x:c r="P923" s="32"/>
+      <x:c r="Q923"/>
     </x:row>
     <x:row r="924">
       <x:c r="A924" s="34"/>
@@ -17600,6 +18528,7 @@
       <x:c r="N924" s="46"/>
       <x:c r="O924" s="34"/>
       <x:c r="P924" s="32"/>
+      <x:c r="Q924"/>
     </x:row>
     <x:row r="925">
       <x:c r="A925" s="34"/>
@@ -17618,6 +18547,7 @@
       <x:c r="N925" s="46"/>
       <x:c r="O925" s="34"/>
       <x:c r="P925" s="32"/>
+      <x:c r="Q925"/>
     </x:row>
     <x:row r="926">
       <x:c r="A926" s="34"/>
@@ -17636,6 +18566,7 @@
       <x:c r="N926" s="46"/>
       <x:c r="O926" s="34"/>
       <x:c r="P926" s="32"/>
+      <x:c r="Q926"/>
     </x:row>
     <x:row r="927">
       <x:c r="A927" s="34"/>
@@ -17654,6 +18585,7 @@
       <x:c r="N927" s="46"/>
       <x:c r="O927" s="34"/>
       <x:c r="P927" s="32"/>
+      <x:c r="Q927"/>
     </x:row>
     <x:row r="928">
       <x:c r="A928" s="34"/>
@@ -17672,6 +18604,7 @@
       <x:c r="N928" s="46"/>
       <x:c r="O928" s="34"/>
       <x:c r="P928" s="32"/>
+      <x:c r="Q928"/>
     </x:row>
     <x:row r="929">
       <x:c r="A929" s="34"/>
@@ -17690,6 +18623,7 @@
       <x:c r="N929" s="46"/>
       <x:c r="O929" s="34"/>
       <x:c r="P929" s="32"/>
+      <x:c r="Q929"/>
     </x:row>
     <x:row r="930">
       <x:c r="A930" s="34"/>
@@ -17708,6 +18642,7 @@
       <x:c r="N930" s="46"/>
       <x:c r="O930" s="34"/>
       <x:c r="P930" s="32"/>
+      <x:c r="Q930"/>
     </x:row>
     <x:row r="931">
       <x:c r="A931" s="34"/>
@@ -17726,6 +18661,7 @@
       <x:c r="N931" s="46"/>
       <x:c r="O931" s="34"/>
       <x:c r="P931" s="32"/>
+      <x:c r="Q931"/>
     </x:row>
     <x:row r="932">
       <x:c r="A932" s="34"/>
@@ -17744,6 +18680,7 @@
       <x:c r="N932" s="46"/>
       <x:c r="O932" s="34"/>
       <x:c r="P932" s="32"/>
+      <x:c r="Q932"/>
     </x:row>
     <x:row r="933">
       <x:c r="A933" s="34"/>
@@ -17762,6 +18699,7 @@
       <x:c r="N933" s="46"/>
       <x:c r="O933" s="34"/>
       <x:c r="P933" s="32"/>
+      <x:c r="Q933"/>
     </x:row>
     <x:row r="934">
       <x:c r="A934" s="34"/>
@@ -17780,6 +18718,7 @@
       <x:c r="N934" s="46"/>
       <x:c r="O934" s="34"/>
       <x:c r="P934" s="32"/>
+      <x:c r="Q934"/>
     </x:row>
     <x:row r="935">
       <x:c r="A935" s="34"/>
@@ -17798,6 +18737,7 @@
       <x:c r="N935" s="46"/>
       <x:c r="O935" s="34"/>
       <x:c r="P935" s="32"/>
+      <x:c r="Q935"/>
     </x:row>
     <x:row r="936">
       <x:c r="A936" s="34"/>
@@ -17816,6 +18756,7 @@
       <x:c r="N936" s="46"/>
       <x:c r="O936" s="34"/>
       <x:c r="P936" s="32"/>
+      <x:c r="Q936"/>
     </x:row>
     <x:row r="937">
       <x:c r="A937" s="34"/>
@@ -17834,6 +18775,7 @@
       <x:c r="N937" s="46"/>
       <x:c r="O937" s="34"/>
       <x:c r="P937" s="32"/>
+      <x:c r="Q937"/>
     </x:row>
     <x:row r="938">
       <x:c r="A938" s="34"/>
@@ -17852,6 +18794,7 @@
       <x:c r="N938" s="46"/>
       <x:c r="O938" s="34"/>
       <x:c r="P938" s="32"/>
+      <x:c r="Q938"/>
     </x:row>
     <x:row r="939">
       <x:c r="A939" s="34"/>
@@ -17870,6 +18813,7 @@
       <x:c r="N939" s="46"/>
       <x:c r="O939" s="34"/>
       <x:c r="P939" s="32"/>
+      <x:c r="Q939"/>
     </x:row>
     <x:row r="940">
       <x:c r="A940" s="34"/>
@@ -17888,6 +18832,7 @@
       <x:c r="N940" s="46"/>
       <x:c r="O940" s="34"/>
       <x:c r="P940" s="32"/>
+      <x:c r="Q940"/>
     </x:row>
     <x:row r="941">
       <x:c r="A941" s="34"/>
@@ -17906,6 +18851,7 @@
       <x:c r="N941" s="46"/>
       <x:c r="O941" s="34"/>
       <x:c r="P941" s="32"/>
+      <x:c r="Q941"/>
     </x:row>
     <x:row r="942">
       <x:c r="A942" s="34"/>
@@ -17924,6 +18870,7 @@
       <x:c r="N942" s="46"/>
       <x:c r="O942" s="34"/>
       <x:c r="P942" s="32"/>
+      <x:c r="Q942"/>
     </x:row>
     <x:row r="943">
       <x:c r="A943" s="34"/>
@@ -17942,6 +18889,7 @@
       <x:c r="N943" s="46"/>
       <x:c r="O943" s="34"/>
       <x:c r="P943" s="32"/>
+      <x:c r="Q943"/>
     </x:row>
     <x:row r="944">
       <x:c r="A944" s="34"/>
@@ -17960,6 +18908,7 @@
       <x:c r="N944" s="46"/>
       <x:c r="O944" s="34"/>
       <x:c r="P944" s="32"/>
+      <x:c r="Q944"/>
     </x:row>
     <x:row r="945">
       <x:c r="A945" s="34"/>
@@ -17978,6 +18927,7 @@
       <x:c r="N945" s="46"/>
       <x:c r="O945" s="34"/>
       <x:c r="P945" s="32"/>
+      <x:c r="Q945"/>
     </x:row>
     <x:row r="946">
       <x:c r="A946" s="34"/>
@@ -17996,6 +18946,7 @@
       <x:c r="N946" s="46"/>
       <x:c r="O946" s="34"/>
       <x:c r="P946" s="32"/>
+      <x:c r="Q946"/>
     </x:row>
     <x:row r="947">
       <x:c r="A947" s="34"/>
@@ -18014,6 +18965,7 @@
       <x:c r="N947" s="46"/>
       <x:c r="O947" s="34"/>
       <x:c r="P947" s="32"/>
+      <x:c r="Q947"/>
     </x:row>
     <x:row r="948">
       <x:c r="A948" s="34"/>
@@ -18032,6 +18984,7 @@
       <x:c r="N948" s="46"/>
       <x:c r="O948" s="34"/>
       <x:c r="P948" s="32"/>
+      <x:c r="Q948"/>
     </x:row>
     <x:row r="949">
       <x:c r="A949" s="34"/>
@@ -18050,6 +19003,7 @@
       <x:c r="N949" s="46"/>
       <x:c r="O949" s="34"/>
       <x:c r="P949" s="32"/>
+      <x:c r="Q949"/>
     </x:row>
     <x:row r="950">
       <x:c r="A950" s="34"/>
@@ -18068,6 +19022,7 @@
       <x:c r="N950" s="46"/>
       <x:c r="O950" s="34"/>
       <x:c r="P950" s="32"/>
+      <x:c r="Q950"/>
     </x:row>
     <x:row r="951">
       <x:c r="A951" s="34"/>
@@ -18086,6 +19041,7 @@
       <x:c r="N951" s="46"/>
       <x:c r="O951" s="34"/>
       <x:c r="P951" s="32"/>
+      <x:c r="Q951"/>
     </x:row>
     <x:row r="952">
       <x:c r="A952" s="34"/>
@@ -18104,6 +19060,7 @@
       <x:c r="N952" s="46"/>
       <x:c r="O952" s="34"/>
       <x:c r="P952" s="32"/>
+      <x:c r="Q952"/>
     </x:row>
     <x:row r="953">
       <x:c r="A953" s="34"/>
@@ -18122,6 +19079,7 @@
       <x:c r="N953" s="46"/>
       <x:c r="O953" s="34"/>
       <x:c r="P953" s="32"/>
+      <x:c r="Q953"/>
     </x:row>
     <x:row r="954">
       <x:c r="A954" s="34"/>
@@ -18140,6 +19098,7 @@
       <x:c r="N954" s="46"/>
       <x:c r="O954" s="34"/>
       <x:c r="P954" s="32"/>
+      <x:c r="Q954"/>
     </x:row>
     <x:row r="955">
       <x:c r="A955" s="34"/>
@@ -18158,6 +19117,7 @@
       <x:c r="N955" s="46"/>
       <x:c r="O955" s="34"/>
       <x:c r="P955" s="32"/>
+      <x:c r="Q955"/>
     </x:row>
     <x:row r="956">
       <x:c r="A956" s="34"/>
@@ -18176,6 +19136,7 @@
       <x:c r="N956" s="46"/>
       <x:c r="O956" s="34"/>
       <x:c r="P956" s="32"/>
+      <x:c r="Q956"/>
     </x:row>
     <x:row r="957">
       <x:c r="A957" s="34"/>
@@ -18194,6 +19155,7 @@
       <x:c r="N957" s="46"/>
       <x:c r="O957" s="34"/>
       <x:c r="P957" s="32"/>
+      <x:c r="Q957"/>
     </x:row>
     <x:row r="958">
       <x:c r="A958" s="34"/>
@@ -18212,6 +19174,7 @@
       <x:c r="N958" s="46"/>
       <x:c r="O958" s="34"/>
       <x:c r="P958" s="32"/>
+      <x:c r="Q958"/>
     </x:row>
     <x:row r="959">
       <x:c r="A959" s="34"/>
@@ -18230,6 +19193,7 @@
       <x:c r="N959" s="46"/>
       <x:c r="O959" s="34"/>
       <x:c r="P959" s="32"/>
+      <x:c r="Q959"/>
     </x:row>
     <x:row r="960">
       <x:c r="A960" s="34"/>
@@ -18248,6 +19212,7 @@
       <x:c r="N960" s="46"/>
       <x:c r="O960" s="34"/>
       <x:c r="P960" s="32"/>
+      <x:c r="Q960"/>
     </x:row>
     <x:row r="961">
       <x:c r="A961" s="34"/>
@@ -18266,6 +19231,7 @@
       <x:c r="N961" s="46"/>
       <x:c r="O961" s="34"/>
       <x:c r="P961" s="32"/>
+      <x:c r="Q961"/>
     </x:row>
     <x:row r="962">
       <x:c r="A962" s="34"/>
@@ -18284,6 +19250,7 @@
       <x:c r="N962" s="46"/>
       <x:c r="O962" s="34"/>
       <x:c r="P962" s="32"/>
+      <x:c r="Q962"/>
     </x:row>
     <x:row r="963">
       <x:c r="A963" s="34"/>
@@ -18302,6 +19269,7 @@
       <x:c r="N963" s="46"/>
       <x:c r="O963" s="34"/>
       <x:c r="P963" s="32"/>
+      <x:c r="Q963"/>
     </x:row>
     <x:row r="964">
       <x:c r="A964" s="34"/>
@@ -18320,6 +19288,7 @@
       <x:c r="N964" s="46"/>
       <x:c r="O964" s="34"/>
       <x:c r="P964" s="32"/>
+      <x:c r="Q964"/>
     </x:row>
     <x:row r="965">
       <x:c r="A965" s="34"/>
@@ -18338,6 +19307,7 @@
       <x:c r="N965" s="46"/>
       <x:c r="O965" s="34"/>
       <x:c r="P965" s="32"/>
+      <x:c r="Q965"/>
     </x:row>
     <x:row r="966">
       <x:c r="A966" s="34"/>
@@ -18356,6 +19326,7 @@
       <x:c r="N966" s="46"/>
       <x:c r="O966" s="34"/>
       <x:c r="P966" s="32"/>
+      <x:c r="Q966"/>
     </x:row>
     <x:row r="967">
       <x:c r="A967" s="34"/>
@@ -18374,6 +19345,7 @@
       <x:c r="N967" s="46"/>
       <x:c r="O967" s="34"/>
       <x:c r="P967" s="32"/>
+      <x:c r="Q967"/>
     </x:row>
     <x:row r="968">
       <x:c r="A968" s="34"/>
@@ -18392,6 +19364,7 @@
       <x:c r="N968" s="46"/>
       <x:c r="O968" s="34"/>
       <x:c r="P968" s="32"/>
+      <x:c r="Q968"/>
     </x:row>
     <x:row r="969">
       <x:c r="A969" s="34"/>
@@ -18410,6 +19383,7 @@
       <x:c r="N969" s="46"/>
       <x:c r="O969" s="34"/>
       <x:c r="P969" s="32"/>
+      <x:c r="Q969"/>
     </x:row>
     <x:row r="970">
       <x:c r="A970" s="34"/>
@@ -18428,6 +19402,7 @@
       <x:c r="N970" s="46"/>
       <x:c r="O970" s="34"/>
       <x:c r="P970" s="32"/>
+      <x:c r="Q970"/>
     </x:row>
     <x:row r="971">
       <x:c r="A971" s="34"/>
@@ -18446,6 +19421,7 @@
       <x:c r="N971" s="46"/>
       <x:c r="O971" s="34"/>
       <x:c r="P971" s="32"/>
+      <x:c r="Q971"/>
     </x:row>
     <x:row r="972">
       <x:c r="A972" s="34"/>
@@ -18464,6 +19440,7 @@
       <x:c r="N972" s="46"/>
       <x:c r="O972" s="34"/>
       <x:c r="P972" s="32"/>
+      <x:c r="Q972"/>
     </x:row>
     <x:row r="973">
       <x:c r="A973" s="34"/>
@@ -18482,6 +19459,7 @@
       <x:c r="N973" s="46"/>
       <x:c r="O973" s="34"/>
       <x:c r="P973" s="32"/>
+      <x:c r="Q973"/>
     </x:row>
     <x:row r="974">
       <x:c r="A974" s="34"/>
@@ -18500,6 +19478,7 @@
       <x:c r="N974" s="46"/>
       <x:c r="O974" s="34"/>
       <x:c r="P974" s="32"/>
+      <x:c r="Q974"/>
     </x:row>
     <x:row r="975">
       <x:c r="A975" s="34"/>
@@ -18518,6 +19497,7 @@
       <x:c r="N975" s="46"/>
       <x:c r="O975" s="34"/>
       <x:c r="P975" s="32"/>
+      <x:c r="Q975"/>
     </x:row>
     <x:row r="976">
       <x:c r="A976" s="34"/>
@@ -18536,6 +19516,7 @@
       <x:c r="N976" s="46"/>
       <x:c r="O976" s="34"/>
       <x:c r="P976" s="32"/>
+      <x:c r="Q976"/>
     </x:row>
     <x:row r="977">
       <x:c r="A977" s="34"/>
@@ -18554,6 +19535,7 @@
       <x:c r="N977" s="46"/>
       <x:c r="O977" s="34"/>
       <x:c r="P977" s="32"/>
+      <x:c r="Q977"/>
     </x:row>
     <x:row r="978">
       <x:c r="A978" s="34"/>
@@ -18572,6 +19554,7 @@
       <x:c r="N978" s="46"/>
       <x:c r="O978" s="34"/>
       <x:c r="P978" s="32"/>
+      <x:c r="Q978"/>
     </x:row>
     <x:row r="979">
       <x:c r="A979" s="34"/>
@@ -18590,6 +19573,7 @@
       <x:c r="N979" s="46"/>
       <x:c r="O979" s="34"/>
       <x:c r="P979" s="32"/>
+      <x:c r="Q979"/>
     </x:row>
     <x:row r="980">
       <x:c r="A980" s="34"/>
@@ -18608,6 +19592,7 @@
       <x:c r="N980" s="46"/>
       <x:c r="O980" s="34"/>
       <x:c r="P980" s="32"/>
+      <x:c r="Q980"/>
     </x:row>
     <x:row r="981">
       <x:c r="A981" s="34"/>
@@ -18626,6 +19611,7 @@
       <x:c r="N981" s="46"/>
       <x:c r="O981" s="34"/>
       <x:c r="P981" s="32"/>
+      <x:c r="Q981"/>
     </x:row>
     <x:row r="982">
       <x:c r="A982" s="34"/>
@@ -18644,6 +19630,7 @@
       <x:c r="N982" s="46"/>
       <x:c r="O982" s="34"/>
       <x:c r="P982" s="32"/>
+      <x:c r="Q982"/>
     </x:row>
     <x:row r="983">
       <x:c r="A983" s="34"/>
@@ -18662,6 +19649,7 @@
       <x:c r="N983" s="46"/>
       <x:c r="O983" s="34"/>
       <x:c r="P983" s="32"/>
+      <x:c r="Q983"/>
     </x:row>
     <x:row r="984">
       <x:c r="A984" s="34"/>
@@ -18680,6 +19668,7 @@
       <x:c r="N984" s="46"/>
       <x:c r="O984" s="34"/>
       <x:c r="P984" s="32"/>
+      <x:c r="Q984"/>
     </x:row>
     <x:row r="985">
       <x:c r="A985" s="34"/>
@@ -18698,6 +19687,7 @@
       <x:c r="N985" s="46"/>
       <x:c r="O985" s="34"/>
       <x:c r="P985" s="32"/>
+      <x:c r="Q985"/>
     </x:row>
     <x:row r="986">
       <x:c r="A986" s="34"/>
@@ -18716,6 +19706,7 @@
       <x:c r="N986" s="46"/>
       <x:c r="O986" s="34"/>
       <x:c r="P986" s="32"/>
+      <x:c r="Q986"/>
     </x:row>
     <x:row r="987">
       <x:c r="A987" s="34"/>
@@ -18734,6 +19725,7 @@
       <x:c r="N987" s="46"/>
       <x:c r="O987" s="34"/>
       <x:c r="P987" s="32"/>
+      <x:c r="Q987"/>
     </x:row>
     <x:row r="988">
       <x:c r="A988" s="34"/>
@@ -18752,6 +19744,7 @@
       <x:c r="N988" s="46"/>
       <x:c r="O988" s="34"/>
       <x:c r="P988" s="32"/>
+      <x:c r="Q988"/>
     </x:row>
     <x:row r="989">
       <x:c r="A989" s="34"/>
@@ -18770,6 +19763,7 @@
       <x:c r="N989" s="46"/>
       <x:c r="O989" s="34"/>
       <x:c r="P989" s="32"/>
+      <x:c r="Q989"/>
     </x:row>
     <x:row r="990">
       <x:c r="A990" s="34"/>
@@ -18788,6 +19782,7 @@
       <x:c r="N990" s="46"/>
       <x:c r="O990" s="34"/>
       <x:c r="P990" s="32"/>
+      <x:c r="Q990"/>
     </x:row>
     <x:row r="991">
       <x:c r="A991" s="34"/>
@@ -18806,6 +19801,7 @@
       <x:c r="N991" s="46"/>
       <x:c r="O991" s="34"/>
       <x:c r="P991" s="32"/>
+      <x:c r="Q991"/>
     </x:row>
     <x:row r="992">
       <x:c r="A992" s="34"/>
@@ -18824,6 +19820,7 @@
       <x:c r="N992" s="46"/>
       <x:c r="O992" s="34"/>
       <x:c r="P992" s="32"/>
+      <x:c r="Q992"/>
     </x:row>
     <x:row r="993">
       <x:c r="A993" s="34"/>
@@ -18842,6 +19839,7 @@
       <x:c r="N993" s="46"/>
       <x:c r="O993" s="34"/>
       <x:c r="P993" s="32"/>
+      <x:c r="Q993"/>
     </x:row>
     <x:row r="994">
       <x:c r="A994" s="34"/>
@@ -18860,6 +19858,7 @@
       <x:c r="N994" s="46"/>
       <x:c r="O994" s="34"/>
       <x:c r="P994" s="32"/>
+      <x:c r="Q994"/>
     </x:row>
     <x:row r="995">
       <x:c r="A995" s="34"/>
@@ -18878,6 +19877,7 @@
       <x:c r="N995" s="46"/>
       <x:c r="O995" s="34"/>
       <x:c r="P995" s="32"/>
+      <x:c r="Q995"/>
     </x:row>
     <x:row r="996">
       <x:c r="A996" s="34"/>
@@ -18896,6 +19896,7 @@
       <x:c r="N996" s="46"/>
       <x:c r="O996" s="34"/>
       <x:c r="P996" s="32"/>
+      <x:c r="Q996"/>
     </x:row>
     <x:row r="997">
       <x:c r="A997" s="34"/>
@@ -18914,6 +19915,7 @@
       <x:c r="N997" s="46"/>
       <x:c r="O997" s="34"/>
       <x:c r="P997" s="32"/>
+      <x:c r="Q997"/>
     </x:row>
     <x:row r="998">
       <x:c r="A998" s="34"/>
@@ -18932,6 +19934,7 @@
       <x:c r="N998" s="46"/>
       <x:c r="O998" s="34"/>
       <x:c r="P998" s="32"/>
+      <x:c r="Q998"/>
     </x:row>
     <x:row r="999">
       <x:c r="A999" s="34"/>
@@ -18950,6 +19953,7 @@
       <x:c r="N999" s="46"/>
       <x:c r="O999" s="34"/>
       <x:c r="P999" s="32"/>
+      <x:c r="Q999"/>
     </x:row>
     <x:row r="1000">
       <x:c r="A1000" s="35"/>
@@ -18968,9 +19972,14 @@
       <x:c r="N1000" s="47"/>
       <x:c r="O1000" s="35"/>
       <x:c r="P1000" s="32"/>
+      <x:c r="Q1000"/>
     </x:row>
     <x:row r="1001">
       <x:c r="P1001" s="32"/>
+      <x:c r="Q1001"/>
+    </x:row>
+    <x:row r="1002">
+      <x:c r="Q1002"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A2:A1000">
@@ -19013,7 +20022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc4527cd30e64f22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752fa246f9af43e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
